--- a/INDmoney-All-Sectors-Under-20-Review.xlsx
+++ b/INDmoney-All-Sectors-Under-20-Review.xlsx
@@ -5,13 +5,14 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Stocks under 20Rs" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Focus Sectors" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="987">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1974" uniqueCount="1000">
   <si>
     <t>Sector</t>
   </si>
@@ -2972,13 +2973,52 @@
   </si>
   <si>
     <t>https://www.indmoney.com/stocks/centrum-capital-ltd-share-price</t>
+  </si>
+  <si>
+    <t>Focus Group</t>
+  </si>
+  <si>
+    <t>Metal Type</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Metals</t>
+  </si>
+  <si>
+    <t>Steel / Other</t>
+  </si>
+  <si>
+    <t>Watchlist - Infrastructure</t>
+  </si>
+  <si>
+    <t>Brass</t>
+  </si>
+  <si>
+    <t>FMCG</t>
+  </si>
+  <si>
+    <t>Steel / Ferro-alloys</t>
+  </si>
+  <si>
+    <t>Copper</t>
+  </si>
+  <si>
+    <t>Aluminium</t>
+  </si>
+  <si>
+    <t>Watchlist - Defence</t>
+  </si>
+  <si>
+    <t>Metal types follow INDmoney company descriptions. No company explicitly focused on zinc and no Railway-category stock appeared below ₹20 in the 47 source sectors. Additional watchlist groups are not investment recommendations.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -2993,6 +3033,10 @@
     <font>
       <u/>
       <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF666666"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3020,7 +3064,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3028,6 +3072,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17687,4 +17734,4280 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O115"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="38" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="11" width="12" customWidth="1"/>
+    <col min="12" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="58" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>989</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="F2" s="4">
+        <v>25.95</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3">
+        <v>2.42</v>
+      </c>
+      <c r="J2" s="3">
+        <v>3.81</v>
+      </c>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>989</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.27</v>
+      </c>
+      <c r="F3" s="4">
+        <v>22.93</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3">
+        <v>1.76</v>
+      </c>
+      <c r="J3" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>989</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.37</v>
+      </c>
+      <c r="F4" s="4">
+        <v>36.55</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>990</v>
+      </c>
+      <c r="B5" t="s">
+        <v>991</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.37</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>990</v>
+      </c>
+      <c r="B6" t="s">
+        <v>991</v>
+      </c>
+      <c r="C6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.82</v>
+      </c>
+      <c r="F6" s="4">
+        <v>24.29</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3">
+        <v>6.08</v>
+      </c>
+      <c r="J6" s="3">
+        <v>4.64</v>
+      </c>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>992</v>
+      </c>
+      <c r="B7" t="s">
+        <v>989</v>
+      </c>
+      <c r="C7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.85</v>
+      </c>
+      <c r="F7" s="4">
+        <v>95.38</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3">
+        <v>3.49</v>
+      </c>
+      <c r="J7" s="3">
+        <v>2.41</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>990</v>
+      </c>
+      <c r="B8" t="s">
+        <v>993</v>
+      </c>
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="F8" s="4">
+        <v>25.36</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3">
+        <v>4.34</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1.27</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>992</v>
+      </c>
+      <c r="B9" t="s">
+        <v>989</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="F9" s="4">
+        <v>74.73</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3">
+        <v>5.03</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1.96</v>
+      </c>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" t="s">
+        <v>989</v>
+      </c>
+      <c r="C10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1.74</v>
+      </c>
+      <c r="F10" s="4">
+        <v>9.51</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>992</v>
+      </c>
+      <c r="B11" t="s">
+        <v>989</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1.87</v>
+      </c>
+      <c r="F11" s="4">
+        <v>61.52</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>990</v>
+      </c>
+      <c r="B12" t="s">
+        <v>991</v>
+      </c>
+      <c r="C12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2.06</v>
+      </c>
+      <c r="F12" s="4">
+        <v>29.07</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>992</v>
+      </c>
+      <c r="B13" t="s">
+        <v>989</v>
+      </c>
+      <c r="C13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2.13</v>
+      </c>
+      <c r="F13" s="4">
+        <v>92.69</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>994</v>
+      </c>
+      <c r="B14" t="s">
+        <v>989</v>
+      </c>
+      <c r="C14" t="s">
+        <v>146</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2.26</v>
+      </c>
+      <c r="F14" s="4">
+        <v>383.27</v>
+      </c>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3">
+        <v>6.28</v>
+      </c>
+      <c r="J14" s="3">
+        <v>3.12</v>
+      </c>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B15" t="s">
+        <v>989</v>
+      </c>
+      <c r="C15" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2.34</v>
+      </c>
+      <c r="F15" s="4">
+        <v>18.18</v>
+      </c>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>992</v>
+      </c>
+      <c r="B16" t="s">
+        <v>989</v>
+      </c>
+      <c r="C16" t="s">
+        <v>158</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2.51</v>
+      </c>
+      <c r="F16" s="4">
+        <v>396.38</v>
+      </c>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>992</v>
+      </c>
+      <c r="B17" t="s">
+        <v>989</v>
+      </c>
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2.62</v>
+      </c>
+      <c r="F17" s="4">
+        <v>92.28</v>
+      </c>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3">
+        <v>-1.52</v>
+      </c>
+      <c r="J17" s="3">
+        <v>-9.2</v>
+      </c>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>990</v>
+      </c>
+      <c r="B18" t="s">
+        <v>991</v>
+      </c>
+      <c r="C18" t="s">
+        <v>190</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E18" s="3">
+        <v>3.03</v>
+      </c>
+      <c r="F18" s="4">
+        <v>119.67</v>
+      </c>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>990</v>
+      </c>
+      <c r="B19" t="s">
+        <v>991</v>
+      </c>
+      <c r="C19" t="s">
+        <v>190</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E19" s="3">
+        <v>3.03</v>
+      </c>
+      <c r="F19" s="4">
+        <v>300.69</v>
+      </c>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3">
+        <v>4.23</v>
+      </c>
+      <c r="J19" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>990</v>
+      </c>
+      <c r="B20" t="s">
+        <v>995</v>
+      </c>
+      <c r="C20" t="s">
+        <v>190</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E20" s="3">
+        <v>3.07</v>
+      </c>
+      <c r="F20" s="4">
+        <v>59.25</v>
+      </c>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>994</v>
+      </c>
+      <c r="B21" t="s">
+        <v>989</v>
+      </c>
+      <c r="C21" t="s">
+        <v>146</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3.08</v>
+      </c>
+      <c r="F21" s="4">
+        <v>330.83</v>
+      </c>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3">
+        <v>3.71</v>
+      </c>
+      <c r="J21" s="3">
+        <v>2.36</v>
+      </c>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>990</v>
+      </c>
+      <c r="B22" t="s">
+        <v>996</v>
+      </c>
+      <c r="C22" t="s">
+        <v>199</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E22" s="3">
+        <v>3.08</v>
+      </c>
+      <c r="F22" s="4">
+        <v>85.16</v>
+      </c>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3">
+        <v>4.85</v>
+      </c>
+      <c r="J22" s="3">
+        <v>-0.21</v>
+      </c>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>994</v>
+      </c>
+      <c r="B23" t="s">
+        <v>989</v>
+      </c>
+      <c r="C23" t="s">
+        <v>146</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3.44</v>
+      </c>
+      <c r="F23" s="4">
+        <v>424.04</v>
+      </c>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3">
+        <v>8.46</v>
+      </c>
+      <c r="J23" s="3">
+        <v>4.07</v>
+      </c>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>992</v>
+      </c>
+      <c r="B24" t="s">
+        <v>989</v>
+      </c>
+      <c r="C24" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E24" s="3">
+        <v>3.56</v>
+      </c>
+      <c r="F24" s="4">
+        <v>66.29</v>
+      </c>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>990</v>
+      </c>
+      <c r="B25" t="s">
+        <v>991</v>
+      </c>
+      <c r="C25" t="s">
+        <v>190</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E25" s="3">
+        <v>3.56</v>
+      </c>
+      <c r="F25" s="4">
+        <v>62.3</v>
+      </c>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3">
+        <v>1.01</v>
+      </c>
+      <c r="J25" s="3">
+        <v>0.72</v>
+      </c>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>990</v>
+      </c>
+      <c r="B26" t="s">
+        <v>997</v>
+      </c>
+      <c r="C26" t="s">
+        <v>220</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E26" s="3">
+        <v>3.7</v>
+      </c>
+      <c r="F26" s="4">
+        <v>46</v>
+      </c>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3">
+        <v>10.2</v>
+      </c>
+      <c r="J26" s="3">
+        <v>8.89</v>
+      </c>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>990</v>
+      </c>
+      <c r="B27" t="s">
+        <v>991</v>
+      </c>
+      <c r="C27" t="s">
+        <v>190</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E27" s="3">
+        <v>4.02</v>
+      </c>
+      <c r="F27" s="4">
+        <v>43.8</v>
+      </c>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3">
+        <v>3.56</v>
+      </c>
+      <c r="J27" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>990</v>
+      </c>
+      <c r="B28" t="s">
+        <v>991</v>
+      </c>
+      <c r="C28" t="s">
+        <v>190</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E28" s="3">
+        <v>4.1</v>
+      </c>
+      <c r="F28" s="4">
+        <v>134.89</v>
+      </c>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>990</v>
+      </c>
+      <c r="B29" t="s">
+        <v>991</v>
+      </c>
+      <c r="C29" t="s">
+        <v>190</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E29" s="3">
+        <v>4.13</v>
+      </c>
+      <c r="F29" s="4">
+        <v>721.9</v>
+      </c>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3">
+        <v>10.05</v>
+      </c>
+      <c r="J29" s="3">
+        <v>5.83</v>
+      </c>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>990</v>
+      </c>
+      <c r="B30" t="s">
+        <v>991</v>
+      </c>
+      <c r="C30" t="s">
+        <v>190</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E30" s="3">
+        <v>4.24</v>
+      </c>
+      <c r="F30" s="4">
+        <v>105.98</v>
+      </c>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3">
+        <v>0</v>
+      </c>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>990</v>
+      </c>
+      <c r="B31" t="s">
+        <v>991</v>
+      </c>
+      <c r="C31" t="s">
+        <v>190</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E31" s="3">
+        <v>4.47</v>
+      </c>
+      <c r="F31" s="4">
+        <v>731.31</v>
+      </c>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3">
+        <v>6.13</v>
+      </c>
+      <c r="J31" s="3">
+        <v>3.98</v>
+      </c>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>104</v>
+      </c>
+      <c r="B32" t="s">
+        <v>989</v>
+      </c>
+      <c r="C32" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E32" s="3">
+        <v>4.67</v>
+      </c>
+      <c r="F32" s="4">
+        <v>4.77</v>
+      </c>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3">
+        <v>2.9</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0.81</v>
+      </c>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>990</v>
+      </c>
+      <c r="B33" t="s">
+        <v>991</v>
+      </c>
+      <c r="C33" t="s">
+        <v>190</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E33" s="3">
+        <v>4.91</v>
+      </c>
+      <c r="F33" s="4">
+        <v>130.74</v>
+      </c>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3">
+        <v>8.85</v>
+      </c>
+      <c r="J33" s="3">
+        <v>7.72</v>
+      </c>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>990</v>
+      </c>
+      <c r="B34" t="s">
+        <v>991</v>
+      </c>
+      <c r="C34" t="s">
+        <v>190</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E34" s="3">
+        <v>5</v>
+      </c>
+      <c r="F34" s="4">
+        <v>106.09</v>
+      </c>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3">
+        <v>-7.38</v>
+      </c>
+      <c r="J34" s="3">
+        <v>-5.54</v>
+      </c>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>992</v>
+      </c>
+      <c r="B35" t="s">
+        <v>989</v>
+      </c>
+      <c r="C35" t="s">
+        <v>158</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E35" s="3">
+        <v>5.08</v>
+      </c>
+      <c r="F35" s="4">
+        <v>972.83</v>
+      </c>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3">
+        <v>1.97</v>
+      </c>
+      <c r="J35" s="3">
+        <v>0.55</v>
+      </c>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>990</v>
+      </c>
+      <c r="B36" t="s">
+        <v>991</v>
+      </c>
+      <c r="C36" t="s">
+        <v>190</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E36" s="3">
+        <v>5.1</v>
+      </c>
+      <c r="F36" s="4">
+        <v>72.56</v>
+      </c>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3">
+        <v>0.74</v>
+      </c>
+      <c r="J36" s="3">
+        <v>0.57</v>
+      </c>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>24</v>
+      </c>
+      <c r="B37" t="s">
+        <v>989</v>
+      </c>
+      <c r="C37" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E37" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="F37" s="4">
+        <v>28.06</v>
+      </c>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3">
+        <v>0</v>
+      </c>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>24</v>
+      </c>
+      <c r="B38" t="s">
+        <v>989</v>
+      </c>
+      <c r="C38" t="s">
+        <v>24</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E38" s="3">
+        <v>5.71</v>
+      </c>
+      <c r="F38" s="4">
+        <v>47.34</v>
+      </c>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3">
+        <v>0</v>
+      </c>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39" t="s">
+        <v>989</v>
+      </c>
+      <c r="C39" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E39" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="F39" s="4">
+        <v>142.64</v>
+      </c>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3">
+        <v>1.21</v>
+      </c>
+      <c r="J39" s="3">
+        <v>0.96</v>
+      </c>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" t="s">
+        <v>989</v>
+      </c>
+      <c r="C40" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="E40" s="3">
+        <v>6.19</v>
+      </c>
+      <c r="F40" s="4">
+        <v>38.22</v>
+      </c>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3">
+        <v>0</v>
+      </c>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>990</v>
+      </c>
+      <c r="B41" t="s">
+        <v>991</v>
+      </c>
+      <c r="C41" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E41" s="3">
+        <v>6.3</v>
+      </c>
+      <c r="F41" s="4">
+        <v>3.71</v>
+      </c>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>990</v>
+      </c>
+      <c r="B42" t="s">
+        <v>997</v>
+      </c>
+      <c r="C42" t="s">
+        <v>72</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E42" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="F42" s="4">
+        <v>12.04</v>
+      </c>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3">
+        <v>2.52</v>
+      </c>
+      <c r="J42" s="3">
+        <v>1.11</v>
+      </c>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>992</v>
+      </c>
+      <c r="B43" t="s">
+        <v>989</v>
+      </c>
+      <c r="C43" t="s">
+        <v>51</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E43" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="F43" s="4">
+        <v>302.78</v>
+      </c>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3">
+        <v>20.35</v>
+      </c>
+      <c r="J43" s="3">
+        <v>20.26</v>
+      </c>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>990</v>
+      </c>
+      <c r="B44" t="s">
+        <v>991</v>
+      </c>
+      <c r="C44" t="s">
+        <v>190</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E44" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="F44" s="4">
+        <v>57.16</v>
+      </c>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3">
+        <v>0</v>
+      </c>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>992</v>
+      </c>
+      <c r="B45" t="s">
+        <v>989</v>
+      </c>
+      <c r="C45" t="s">
+        <v>51</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E45" s="3">
+        <v>6.57</v>
+      </c>
+      <c r="F45" s="4">
+        <v>258.79</v>
+      </c>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3">
+        <v>18.26</v>
+      </c>
+      <c r="J45" s="3">
+        <v>13.88</v>
+      </c>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>404</v>
+      </c>
+      <c r="B46" t="s">
+        <v>989</v>
+      </c>
+      <c r="C46" t="s">
+        <v>404</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="E46" s="3">
+        <v>6.74</v>
+      </c>
+      <c r="F46" s="4">
+        <v>3619.45</v>
+      </c>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3">
+        <v>4.21</v>
+      </c>
+      <c r="J46" s="3">
+        <v>0.61</v>
+      </c>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>404</v>
+      </c>
+      <c r="B47" t="s">
+        <v>989</v>
+      </c>
+      <c r="C47" t="s">
+        <v>404</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E47" s="3">
+        <v>6.8</v>
+      </c>
+      <c r="F47" s="4">
+        <v>662.18</v>
+      </c>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3">
+        <v>2.49</v>
+      </c>
+      <c r="J47" s="3">
+        <v>0.44</v>
+      </c>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3"/>
+      <c r="O47" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>992</v>
+      </c>
+      <c r="B48" t="s">
+        <v>989</v>
+      </c>
+      <c r="C48" t="s">
+        <v>51</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E48" s="3">
+        <v>6.8</v>
+      </c>
+      <c r="F48" s="4">
+        <v>116.67</v>
+      </c>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3">
+        <v>2.45</v>
+      </c>
+      <c r="J48" s="3">
+        <v>-23.09</v>
+      </c>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>104</v>
+      </c>
+      <c r="B49" t="s">
+        <v>989</v>
+      </c>
+      <c r="C49" t="s">
+        <v>104</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="E49" s="3">
+        <v>6.89</v>
+      </c>
+      <c r="F49" s="4">
+        <v>5.95</v>
+      </c>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3">
+        <v>2.74</v>
+      </c>
+      <c r="J49" s="3">
+        <v>3.08</v>
+      </c>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
+      <c r="O49" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>992</v>
+      </c>
+      <c r="B50" t="s">
+        <v>989</v>
+      </c>
+      <c r="C50" t="s">
+        <v>51</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E50" s="3">
+        <v>7.31</v>
+      </c>
+      <c r="F50" s="4">
+        <v>197.06</v>
+      </c>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3">
+        <v>14.57</v>
+      </c>
+      <c r="J50" s="3">
+        <v>11.56</v>
+      </c>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>994</v>
+      </c>
+      <c r="B51" t="s">
+        <v>989</v>
+      </c>
+      <c r="C51" t="s">
+        <v>473</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E51" s="3">
+        <v>7.79</v>
+      </c>
+      <c r="F51" s="4">
+        <v>1245.23</v>
+      </c>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3">
+        <v>20.91</v>
+      </c>
+      <c r="J51" s="3">
+        <v>38.89</v>
+      </c>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
+      <c r="O51" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>992</v>
+      </c>
+      <c r="B52" t="s">
+        <v>989</v>
+      </c>
+      <c r="C52" t="s">
+        <v>51</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E52" s="3">
+        <v>7.79</v>
+      </c>
+      <c r="F52" s="4">
+        <v>120.75</v>
+      </c>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+      <c r="I52" s="3">
+        <v>20.91</v>
+      </c>
+      <c r="J52" s="3">
+        <v>23.35</v>
+      </c>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+      <c r="O52" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>990</v>
+      </c>
+      <c r="B53" t="s">
+        <v>991</v>
+      </c>
+      <c r="C53" t="s">
+        <v>46</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="E53" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="F53" s="4">
+        <v>4.33</v>
+      </c>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3">
+        <v>0</v>
+      </c>
+      <c r="J53" s="3">
+        <v>0</v>
+      </c>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3"/>
+      <c r="O53" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>24</v>
+      </c>
+      <c r="B54" t="s">
+        <v>989</v>
+      </c>
+      <c r="C54" t="s">
+        <v>24</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="E54" s="3">
+        <v>8.18</v>
+      </c>
+      <c r="F54" s="4">
+        <v>35.32</v>
+      </c>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3">
+        <v>0</v>
+      </c>
+      <c r="K54" s="3"/>
+      <c r="L54" s="3"/>
+      <c r="M54" s="3"/>
+      <c r="N54" s="3"/>
+      <c r="O54" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>24</v>
+      </c>
+      <c r="B55" t="s">
+        <v>989</v>
+      </c>
+      <c r="C55" t="s">
+        <v>24</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="E55" s="3">
+        <v>8.38</v>
+      </c>
+      <c r="F55" s="4">
+        <v>109.33</v>
+      </c>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3">
+        <v>4.92</v>
+      </c>
+      <c r="J55" s="3">
+        <v>1.52</v>
+      </c>
+      <c r="K55" s="3"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>404</v>
+      </c>
+      <c r="B56" t="s">
+        <v>989</v>
+      </c>
+      <c r="C56" t="s">
+        <v>404</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="E56" s="3">
+        <v>8.44</v>
+      </c>
+      <c r="F56" s="4">
+        <v>135.89</v>
+      </c>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3">
+        <v>1.44</v>
+      </c>
+      <c r="J56" s="3">
+        <v>0.09</v>
+      </c>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>990</v>
+      </c>
+      <c r="B57" t="s">
+        <v>991</v>
+      </c>
+      <c r="C57" t="s">
+        <v>46</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E57" s="3">
+        <v>8.6</v>
+      </c>
+      <c r="F57" s="4">
+        <v>4.26</v>
+      </c>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>404</v>
+      </c>
+      <c r="B58" t="s">
+        <v>989</v>
+      </c>
+      <c r="C58" t="s">
+        <v>404</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="E58" s="3">
+        <v>8.77</v>
+      </c>
+      <c r="F58" s="4">
+        <v>1028.75</v>
+      </c>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3"/>
+      <c r="L58" s="3"/>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3"/>
+      <c r="O58" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>990</v>
+      </c>
+      <c r="B59" t="s">
+        <v>991</v>
+      </c>
+      <c r="C59" t="s">
+        <v>190</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="E59" s="3">
+        <v>8.87</v>
+      </c>
+      <c r="F59" s="4">
+        <v>38.81</v>
+      </c>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="3">
+        <v>15.01</v>
+      </c>
+      <c r="J59" s="3">
+        <v>13.21</v>
+      </c>
+      <c r="K59" s="3"/>
+      <c r="L59" s="3"/>
+      <c r="M59" s="3"/>
+      <c r="N59" s="3"/>
+      <c r="O59" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>990</v>
+      </c>
+      <c r="B60" t="s">
+        <v>996</v>
+      </c>
+      <c r="C60" t="s">
+        <v>220</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E60" s="3">
+        <v>9.04</v>
+      </c>
+      <c r="F60" s="4">
+        <v>178.44</v>
+      </c>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="3">
+        <v>20.19</v>
+      </c>
+      <c r="J60" s="3">
+        <v>20.78</v>
+      </c>
+      <c r="K60" s="3"/>
+      <c r="L60" s="3"/>
+      <c r="M60" s="3"/>
+      <c r="N60" s="3"/>
+      <c r="O60" s="2" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>104</v>
+      </c>
+      <c r="B61" t="s">
+        <v>989</v>
+      </c>
+      <c r="C61" t="s">
+        <v>104</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E61" s="3">
+        <v>9.67</v>
+      </c>
+      <c r="F61" s="4">
+        <v>10.15</v>
+      </c>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="3">
+        <v>0.19</v>
+      </c>
+      <c r="J61" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3"/>
+      <c r="O61" s="2" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>24</v>
+      </c>
+      <c r="B62" t="s">
+        <v>989</v>
+      </c>
+      <c r="C62" t="s">
+        <v>24</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="E62" s="3">
+        <v>9.8</v>
+      </c>
+      <c r="F62" s="4">
+        <v>238.09</v>
+      </c>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3">
+        <v>9.52</v>
+      </c>
+      <c r="J62" s="3">
+        <v>8.01</v>
+      </c>
+      <c r="K62" s="3"/>
+      <c r="L62" s="3"/>
+      <c r="M62" s="3"/>
+      <c r="N62" s="3"/>
+      <c r="O62" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>990</v>
+      </c>
+      <c r="B63" t="s">
+        <v>991</v>
+      </c>
+      <c r="C63" t="s">
+        <v>46</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E63" s="3">
+        <v>9.95</v>
+      </c>
+      <c r="F63" s="4">
+        <v>5.25</v>
+      </c>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3">
+        <v>8.6</v>
+      </c>
+      <c r="J63" s="3">
+        <v>9.78</v>
+      </c>
+      <c r="K63" s="3"/>
+      <c r="L63" s="3"/>
+      <c r="M63" s="3"/>
+      <c r="N63" s="3"/>
+      <c r="O63" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>24</v>
+      </c>
+      <c r="B64" t="s">
+        <v>989</v>
+      </c>
+      <c r="C64" t="s">
+        <v>24</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="E64" s="3">
+        <v>10</v>
+      </c>
+      <c r="F64" s="4">
+        <v>33</v>
+      </c>
+      <c r="G64" s="3"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3">
+        <v>15.77</v>
+      </c>
+      <c r="J64" s="3">
+        <v>11.09</v>
+      </c>
+      <c r="K64" s="3"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
+      <c r="N64" s="3"/>
+      <c r="O64" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>990</v>
+      </c>
+      <c r="B65" t="s">
+        <v>991</v>
+      </c>
+      <c r="C65" t="s">
+        <v>190</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="E65" s="3">
+        <v>10</v>
+      </c>
+      <c r="F65" s="4">
+        <v>131.14</v>
+      </c>
+      <c r="G65" s="3"/>
+      <c r="H65" s="3"/>
+      <c r="I65" s="3">
+        <v>14.38</v>
+      </c>
+      <c r="J65" s="3">
+        <v>10.51</v>
+      </c>
+      <c r="K65" s="3"/>
+      <c r="L65" s="3"/>
+      <c r="M65" s="3"/>
+      <c r="N65" s="3"/>
+      <c r="O65" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>104</v>
+      </c>
+      <c r="B66" t="s">
+        <v>989</v>
+      </c>
+      <c r="C66" t="s">
+        <v>104</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="E66" s="3">
+        <v>10.12</v>
+      </c>
+      <c r="F66" s="4">
+        <v>7.08</v>
+      </c>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="3">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3">
+        <v>0</v>
+      </c>
+      <c r="K66" s="3"/>
+      <c r="L66" s="3"/>
+      <c r="M66" s="3"/>
+      <c r="N66" s="3"/>
+      <c r="O66" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>24</v>
+      </c>
+      <c r="B67" t="s">
+        <v>989</v>
+      </c>
+      <c r="C67" t="s">
+        <v>24</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="E67" s="3">
+        <v>10.23</v>
+      </c>
+      <c r="F67" s="4">
+        <v>198.73</v>
+      </c>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="J67" s="3">
+        <v>-31.28</v>
+      </c>
+      <c r="K67" s="3"/>
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>992</v>
+      </c>
+      <c r="B68" t="s">
+        <v>989</v>
+      </c>
+      <c r="C68" t="s">
+        <v>51</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="E68" s="3">
+        <v>11.22</v>
+      </c>
+      <c r="F68" s="4">
+        <v>105.19</v>
+      </c>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="3">
+        <v>6.88</v>
+      </c>
+      <c r="J68" s="3">
+        <v>4.21</v>
+      </c>
+      <c r="K68" s="3"/>
+      <c r="L68" s="3"/>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3"/>
+      <c r="O68" s="2" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>990</v>
+      </c>
+      <c r="B69" t="s">
+        <v>991</v>
+      </c>
+      <c r="C69" t="s">
+        <v>190</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="E69" s="3">
+        <v>11.22</v>
+      </c>
+      <c r="F69" s="4">
+        <v>1431.13</v>
+      </c>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3">
+        <v>8.8</v>
+      </c>
+      <c r="J69" s="3">
+        <v>2.65</v>
+      </c>
+      <c r="K69" s="3"/>
+      <c r="L69" s="3"/>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3"/>
+      <c r="O69" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>104</v>
+      </c>
+      <c r="B70" t="s">
+        <v>989</v>
+      </c>
+      <c r="C70" t="s">
+        <v>104</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="E70" s="3">
+        <v>11.7</v>
+      </c>
+      <c r="F70" s="4">
+        <v>28.96</v>
+      </c>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="3">
+        <v>3.08</v>
+      </c>
+      <c r="J70" s="3">
+        <v>2.11</v>
+      </c>
+      <c r="K70" s="3"/>
+      <c r="L70" s="3"/>
+      <c r="M70" s="3"/>
+      <c r="N70" s="3"/>
+      <c r="O70" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>990</v>
+      </c>
+      <c r="B71" t="s">
+        <v>991</v>
+      </c>
+      <c r="C71" t="s">
+        <v>46</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="E71" s="3">
+        <v>11.93</v>
+      </c>
+      <c r="F71" s="4">
+        <v>14.6</v>
+      </c>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3"/>
+      <c r="I71" s="3">
+        <v>-9.63</v>
+      </c>
+      <c r="J71" s="3">
+        <v>-14</v>
+      </c>
+      <c r="K71" s="3"/>
+      <c r="L71" s="3"/>
+      <c r="M71" s="3"/>
+      <c r="N71" s="3"/>
+      <c r="O71" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>104</v>
+      </c>
+      <c r="B72" t="s">
+        <v>989</v>
+      </c>
+      <c r="C72" t="s">
+        <v>104</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="E72" s="3">
+        <v>12.15</v>
+      </c>
+      <c r="F72" s="4">
+        <v>12.76</v>
+      </c>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="3">
+        <v>0</v>
+      </c>
+      <c r="J72" s="3">
+        <v>0</v>
+      </c>
+      <c r="K72" s="3"/>
+      <c r="L72" s="3"/>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3"/>
+      <c r="O72" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>998</v>
+      </c>
+      <c r="B73" t="s">
+        <v>989</v>
+      </c>
+      <c r="C73" t="s">
+        <v>669</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="E73" s="3">
+        <v>12.19</v>
+      </c>
+      <c r="F73" s="4">
+        <v>1.87</v>
+      </c>
+      <c r="G73" s="3"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="3">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3">
+        <v>0</v>
+      </c>
+      <c r="K73" s="3"/>
+      <c r="L73" s="3"/>
+      <c r="M73" s="3"/>
+      <c r="N73" s="3"/>
+      <c r="O73" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>990</v>
+      </c>
+      <c r="B74" t="s">
+        <v>991</v>
+      </c>
+      <c r="C74" t="s">
+        <v>190</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="E74" s="3">
+        <v>12.29</v>
+      </c>
+      <c r="F74" s="4">
+        <v>110.05</v>
+      </c>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="3">
+        <v>4.92</v>
+      </c>
+      <c r="J74" s="3">
+        <v>9.93</v>
+      </c>
+      <c r="K74" s="3"/>
+      <c r="L74" s="3"/>
+      <c r="M74" s="3"/>
+      <c r="N74" s="3"/>
+      <c r="O74" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>992</v>
+      </c>
+      <c r="B75" t="s">
+        <v>989</v>
+      </c>
+      <c r="C75" t="s">
+        <v>158</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="E75" s="3">
+        <v>12.56</v>
+      </c>
+      <c r="F75" s="4">
+        <v>802.32</v>
+      </c>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="3">
+        <v>17.09</v>
+      </c>
+      <c r="J75" s="3">
+        <v>16.8</v>
+      </c>
+      <c r="K75" s="3"/>
+      <c r="L75" s="3"/>
+      <c r="M75" s="3"/>
+      <c r="N75" s="3"/>
+      <c r="O75" s="2" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>104</v>
+      </c>
+      <c r="B76" t="s">
+        <v>989</v>
+      </c>
+      <c r="C76" t="s">
+        <v>104</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="E76" s="3">
+        <v>12.65</v>
+      </c>
+      <c r="F76" s="4">
+        <v>187.14</v>
+      </c>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="3">
+        <v>0.88</v>
+      </c>
+      <c r="J76" s="3">
+        <v>0.76</v>
+      </c>
+      <c r="K76" s="3"/>
+      <c r="L76" s="3"/>
+      <c r="M76" s="3"/>
+      <c r="N76" s="3"/>
+      <c r="O76" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>104</v>
+      </c>
+      <c r="B77" t="s">
+        <v>989</v>
+      </c>
+      <c r="C77" t="s">
+        <v>104</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="E77" s="3">
+        <v>12.7</v>
+      </c>
+      <c r="F77" s="4">
+        <v>25.47</v>
+      </c>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="3">
+        <v>7.07</v>
+      </c>
+      <c r="J77" s="3">
+        <v>5.29</v>
+      </c>
+      <c r="K77" s="3"/>
+      <c r="L77" s="3"/>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3"/>
+      <c r="O77" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>990</v>
+      </c>
+      <c r="B78" t="s">
+        <v>991</v>
+      </c>
+      <c r="C78" t="s">
+        <v>190</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="E78" s="3">
+        <v>12.75</v>
+      </c>
+      <c r="F78" s="4">
+        <v>46.08</v>
+      </c>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="3">
+        <v>-2.48</v>
+      </c>
+      <c r="J78" s="3">
+        <v>14.45</v>
+      </c>
+      <c r="K78" s="3"/>
+      <c r="L78" s="3"/>
+      <c r="M78" s="3"/>
+      <c r="N78" s="3"/>
+      <c r="O78" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>992</v>
+      </c>
+      <c r="B79" t="s">
+        <v>989</v>
+      </c>
+      <c r="C79" t="s">
+        <v>51</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="E79" s="3">
+        <v>12.78</v>
+      </c>
+      <c r="F79" s="4">
+        <v>158.34</v>
+      </c>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="J79" s="3">
+        <v>7.95</v>
+      </c>
+      <c r="K79" s="3"/>
+      <c r="L79" s="3"/>
+      <c r="M79" s="3"/>
+      <c r="N79" s="3"/>
+      <c r="O79" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>104</v>
+      </c>
+      <c r="B80" t="s">
+        <v>989</v>
+      </c>
+      <c r="C80" t="s">
+        <v>104</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="E80" s="3">
+        <v>12.9</v>
+      </c>
+      <c r="F80" s="4">
+        <v>17.93</v>
+      </c>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="3">
+        <v>5.97</v>
+      </c>
+      <c r="J80" s="3">
+        <v>2.58</v>
+      </c>
+      <c r="K80" s="3"/>
+      <c r="L80" s="3"/>
+      <c r="M80" s="3"/>
+      <c r="N80" s="3"/>
+      <c r="O80" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>992</v>
+      </c>
+      <c r="B81" t="s">
+        <v>989</v>
+      </c>
+      <c r="C81" t="s">
+        <v>158</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="E81" s="3">
+        <v>13.45</v>
+      </c>
+      <c r="F81" s="4">
+        <v>600.89</v>
+      </c>
+      <c r="G81" s="3"/>
+      <c r="H81" s="3"/>
+      <c r="I81" s="3">
+        <v>4.03</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-2.55</v>
+      </c>
+      <c r="K81" s="3"/>
+      <c r="L81" s="3"/>
+      <c r="M81" s="3"/>
+      <c r="N81" s="3"/>
+      <c r="O81" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>990</v>
+      </c>
+      <c r="B82" t="s">
+        <v>991</v>
+      </c>
+      <c r="C82" t="s">
+        <v>46</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="E82" s="3">
+        <v>13.86</v>
+      </c>
+      <c r="F82" s="4">
+        <v>16.56</v>
+      </c>
+      <c r="G82" s="3"/>
+      <c r="H82" s="3"/>
+      <c r="I82" s="3">
+        <v>1.81</v>
+      </c>
+      <c r="J82" s="3">
+        <v>4.24</v>
+      </c>
+      <c r="K82" s="3"/>
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+      <c r="O82" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>404</v>
+      </c>
+      <c r="B83" t="s">
+        <v>989</v>
+      </c>
+      <c r="C83" t="s">
+        <v>404</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="E83" s="3">
+        <v>13.91</v>
+      </c>
+      <c r="F83" s="4">
+        <v>19.37</v>
+      </c>
+      <c r="G83" s="3"/>
+      <c r="H83" s="3"/>
+      <c r="I83" s="3">
+        <v>0.07</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0.34</v>
+      </c>
+      <c r="K83" s="3"/>
+      <c r="L83" s="3"/>
+      <c r="M83" s="3"/>
+      <c r="N83" s="3"/>
+      <c r="O83" s="2" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>990</v>
+      </c>
+      <c r="B84" t="s">
+        <v>991</v>
+      </c>
+      <c r="C84" t="s">
+        <v>46</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="E84" s="3">
+        <v>14.12</v>
+      </c>
+      <c r="F84" s="4">
+        <v>19.46</v>
+      </c>
+      <c r="G84" s="3"/>
+      <c r="H84" s="3"/>
+      <c r="I84" s="3">
+        <v>8.38</v>
+      </c>
+      <c r="J84" s="3">
+        <v>8.41</v>
+      </c>
+      <c r="K84" s="3"/>
+      <c r="L84" s="3"/>
+      <c r="M84" s="3"/>
+      <c r="N84" s="3"/>
+      <c r="O84" s="2" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>992</v>
+      </c>
+      <c r="B85" t="s">
+        <v>989</v>
+      </c>
+      <c r="C85" t="s">
+        <v>51</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="E85" s="3">
+        <v>14.38</v>
+      </c>
+      <c r="F85" s="4">
+        <v>255.28</v>
+      </c>
+      <c r="G85" s="3"/>
+      <c r="H85" s="3"/>
+      <c r="I85" s="3">
+        <v>0</v>
+      </c>
+      <c r="J85" s="3">
+        <v>0</v>
+      </c>
+      <c r="K85" s="3"/>
+      <c r="L85" s="3"/>
+      <c r="M85" s="3"/>
+      <c r="N85" s="3"/>
+      <c r="O85" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>990</v>
+      </c>
+      <c r="B86" t="s">
+        <v>991</v>
+      </c>
+      <c r="C86" t="s">
+        <v>46</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="E86" s="3">
+        <v>14.43</v>
+      </c>
+      <c r="F86" s="4">
+        <v>6.86</v>
+      </c>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3"/>
+      <c r="I86" s="3">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3">
+        <v>0</v>
+      </c>
+      <c r="K86" s="3"/>
+      <c r="L86" s="3"/>
+      <c r="M86" s="3"/>
+      <c r="N86" s="3"/>
+      <c r="O86" s="2" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>404</v>
+      </c>
+      <c r="B87" t="s">
+        <v>989</v>
+      </c>
+      <c r="C87" t="s">
+        <v>404</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="E87" s="3">
+        <v>14.52</v>
+      </c>
+      <c r="F87" s="4">
+        <v>68.97</v>
+      </c>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+      <c r="I87" s="3">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3">
+        <v>0</v>
+      </c>
+      <c r="K87" s="3"/>
+      <c r="L87" s="3"/>
+      <c r="M87" s="3"/>
+      <c r="N87" s="3"/>
+      <c r="O87" s="2" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B88" t="s">
+        <v>989</v>
+      </c>
+      <c r="C88" t="s">
+        <v>24</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="E88" s="3">
+        <v>14.76</v>
+      </c>
+      <c r="F88" s="4">
+        <v>21</v>
+      </c>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3"/>
+      <c r="I88" s="3">
+        <v>2.28</v>
+      </c>
+      <c r="J88" s="3">
+        <v>2.07</v>
+      </c>
+      <c r="K88" s="3"/>
+      <c r="L88" s="3"/>
+      <c r="M88" s="3"/>
+      <c r="N88" s="3"/>
+      <c r="O88" s="2" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>404</v>
+      </c>
+      <c r="B89" t="s">
+        <v>989</v>
+      </c>
+      <c r="C89" t="s">
+        <v>404</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="E89" s="3">
+        <v>14.8</v>
+      </c>
+      <c r="F89" s="4">
+        <v>10143.12</v>
+      </c>
+      <c r="G89" s="3"/>
+      <c r="H89" s="3"/>
+      <c r="I89" s="3">
+        <v>6.35</v>
+      </c>
+      <c r="J89" s="3">
+        <v>3.21</v>
+      </c>
+      <c r="K89" s="3"/>
+      <c r="L89" s="3"/>
+      <c r="M89" s="3"/>
+      <c r="N89" s="3"/>
+      <c r="O89" s="2" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>104</v>
+      </c>
+      <c r="B90" t="s">
+        <v>989</v>
+      </c>
+      <c r="C90" t="s">
+        <v>104</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="E90" s="3">
+        <v>15</v>
+      </c>
+      <c r="F90" s="4">
+        <v>9.11</v>
+      </c>
+      <c r="G90" s="3"/>
+      <c r="H90" s="3"/>
+      <c r="I90" s="3">
+        <v>2.52</v>
+      </c>
+      <c r="J90" s="3">
+        <v>0.96</v>
+      </c>
+      <c r="K90" s="3"/>
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+      <c r="O90" s="2" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>992</v>
+      </c>
+      <c r="B91" t="s">
+        <v>989</v>
+      </c>
+      <c r="C91" t="s">
+        <v>51</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="E91" s="3">
+        <v>15.56</v>
+      </c>
+      <c r="F91" s="4">
+        <v>163.33</v>
+      </c>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3"/>
+      <c r="L91" s="3"/>
+      <c r="M91" s="3"/>
+      <c r="N91" s="3"/>
+      <c r="O91" s="2" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>990</v>
+      </c>
+      <c r="B92" t="s">
+        <v>991</v>
+      </c>
+      <c r="C92" t="s">
+        <v>46</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="E92" s="3">
+        <v>15.7</v>
+      </c>
+      <c r="F92" s="4">
+        <v>8.48</v>
+      </c>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
+      <c r="I92" s="3">
+        <v>-0.6</v>
+      </c>
+      <c r="J92" s="3">
+        <v>-2.51</v>
+      </c>
+      <c r="K92" s="3"/>
+      <c r="L92" s="3"/>
+      <c r="M92" s="3"/>
+      <c r="N92" s="3"/>
+      <c r="O92" s="2" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>990</v>
+      </c>
+      <c r="B93" t="s">
+        <v>991</v>
+      </c>
+      <c r="C93" t="s">
+        <v>46</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="E93" s="3">
+        <v>15.75</v>
+      </c>
+      <c r="F93" s="4">
+        <v>25.72</v>
+      </c>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3"/>
+      <c r="I93" s="3">
+        <v>5.9</v>
+      </c>
+      <c r="J93" s="3">
+        <v>2.7</v>
+      </c>
+      <c r="K93" s="3"/>
+      <c r="L93" s="3"/>
+      <c r="M93" s="3"/>
+      <c r="N93" s="3"/>
+      <c r="O93" s="2" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>404</v>
+      </c>
+      <c r="B94" t="s">
+        <v>989</v>
+      </c>
+      <c r="C94" t="s">
+        <v>404</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="E94" s="3">
+        <v>15.98</v>
+      </c>
+      <c r="F94" s="4">
+        <v>216.94</v>
+      </c>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3"/>
+      <c r="I94" s="3">
+        <v>1.18</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="K94" s="3"/>
+      <c r="L94" s="3"/>
+      <c r="M94" s="3"/>
+      <c r="N94" s="3"/>
+      <c r="O94" s="2" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>992</v>
+      </c>
+      <c r="B95" t="s">
+        <v>989</v>
+      </c>
+      <c r="C95" t="s">
+        <v>51</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="E95" s="3">
+        <v>16.03</v>
+      </c>
+      <c r="F95" s="4">
+        <v>134.57</v>
+      </c>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
+      <c r="I95" s="3">
+        <v>0.36</v>
+      </c>
+      <c r="J95" s="3">
+        <v>0.44</v>
+      </c>
+      <c r="K95" s="3"/>
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+      <c r="O95" s="2" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>990</v>
+      </c>
+      <c r="B96" t="s">
+        <v>993</v>
+      </c>
+      <c r="C96" t="s">
+        <v>72</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="E96" s="3">
+        <v>16.18</v>
+      </c>
+      <c r="F96" s="4">
+        <v>16.11</v>
+      </c>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+      <c r="I96" s="3">
+        <v>6.92</v>
+      </c>
+      <c r="J96" s="3">
+        <v>4.35</v>
+      </c>
+      <c r="K96" s="3"/>
+      <c r="L96" s="3"/>
+      <c r="M96" s="3"/>
+      <c r="N96" s="3"/>
+      <c r="O96" s="2" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>404</v>
+      </c>
+      <c r="B97" t="s">
+        <v>989</v>
+      </c>
+      <c r="C97" t="s">
+        <v>404</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="E97" s="3">
+        <v>16.19</v>
+      </c>
+      <c r="F97" s="4">
+        <v>160.2</v>
+      </c>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3"/>
+      <c r="I97" s="3">
+        <v>0</v>
+      </c>
+      <c r="J97" s="3">
+        <v>0</v>
+      </c>
+      <c r="K97" s="3"/>
+      <c r="L97" s="3"/>
+      <c r="M97" s="3"/>
+      <c r="N97" s="3"/>
+      <c r="O97" s="2" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>990</v>
+      </c>
+      <c r="B98" t="s">
+        <v>991</v>
+      </c>
+      <c r="C98" t="s">
+        <v>190</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="E98" s="3">
+        <v>16.64</v>
+      </c>
+      <c r="F98" s="4">
+        <v>1326</v>
+      </c>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="3">
+        <v>11.05</v>
+      </c>
+      <c r="J98" s="3">
+        <v>10.23</v>
+      </c>
+      <c r="K98" s="3"/>
+      <c r="L98" s="3"/>
+      <c r="M98" s="3"/>
+      <c r="N98" s="3"/>
+      <c r="O98" s="2" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>104</v>
+      </c>
+      <c r="B99" t="s">
+        <v>989</v>
+      </c>
+      <c r="C99" t="s">
+        <v>104</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="E99" s="3">
+        <v>17</v>
+      </c>
+      <c r="F99" s="4">
+        <v>25.79</v>
+      </c>
+      <c r="G99" s="3"/>
+      <c r="H99" s="3"/>
+      <c r="I99" s="3">
+        <v>15.92</v>
+      </c>
+      <c r="J99" s="3">
+        <v>12.91</v>
+      </c>
+      <c r="K99" s="3"/>
+      <c r="L99" s="3"/>
+      <c r="M99" s="3"/>
+      <c r="N99" s="3"/>
+      <c r="O99" s="2" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>992</v>
+      </c>
+      <c r="B100" t="s">
+        <v>989</v>
+      </c>
+      <c r="C100" t="s">
+        <v>158</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="E100" s="3">
+        <v>17</v>
+      </c>
+      <c r="F100" s="4">
+        <v>20532.6</v>
+      </c>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3"/>
+      <c r="I100" s="3">
+        <v>7.27</v>
+      </c>
+      <c r="J100" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="K100" s="3"/>
+      <c r="L100" s="3"/>
+      <c r="M100" s="3"/>
+      <c r="N100" s="3"/>
+      <c r="O100" s="2" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>24</v>
+      </c>
+      <c r="B101" t="s">
+        <v>989</v>
+      </c>
+      <c r="C101" t="s">
+        <v>24</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="E101" s="3">
+        <v>17.13</v>
+      </c>
+      <c r="F101" s="4">
+        <v>38.01</v>
+      </c>
+      <c r="G101" s="3"/>
+      <c r="H101" s="3"/>
+      <c r="I101" s="3">
+        <v>9.37</v>
+      </c>
+      <c r="J101" s="3">
+        <v>6.05</v>
+      </c>
+      <c r="K101" s="3"/>
+      <c r="L101" s="3"/>
+      <c r="M101" s="3"/>
+      <c r="N101" s="3"/>
+      <c r="O101" s="2" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>104</v>
+      </c>
+      <c r="B102" t="s">
+        <v>989</v>
+      </c>
+      <c r="C102" t="s">
+        <v>104</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="E102" s="3">
+        <v>17.25</v>
+      </c>
+      <c r="F102" s="4">
+        <v>23.45</v>
+      </c>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3"/>
+      <c r="I102" s="3">
+        <v>5.16</v>
+      </c>
+      <c r="J102" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
+      <c r="O102" s="2" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>992</v>
+      </c>
+      <c r="B103" t="s">
+        <v>989</v>
+      </c>
+      <c r="C103" t="s">
+        <v>51</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="E103" s="3">
+        <v>17.7</v>
+      </c>
+      <c r="F103" s="4">
+        <v>67.45</v>
+      </c>
+      <c r="G103" s="3"/>
+      <c r="H103" s="3"/>
+      <c r="I103" s="3">
+        <v>8.2</v>
+      </c>
+      <c r="J103" s="3">
+        <v>6.75</v>
+      </c>
+      <c r="K103" s="3"/>
+      <c r="L103" s="3"/>
+      <c r="M103" s="3"/>
+      <c r="N103" s="3"/>
+      <c r="O103" s="2" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>992</v>
+      </c>
+      <c r="B104" t="s">
+        <v>989</v>
+      </c>
+      <c r="C104" t="s">
+        <v>158</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="E104" s="3">
+        <v>17.94</v>
+      </c>
+      <c r="F104" s="4">
+        <v>485.51</v>
+      </c>
+      <c r="G104" s="3"/>
+      <c r="H104" s="3"/>
+      <c r="I104" s="3">
+        <v>6.06</v>
+      </c>
+      <c r="J104" s="3">
+        <v>4.4</v>
+      </c>
+      <c r="K104" s="3"/>
+      <c r="L104" s="3"/>
+      <c r="M104" s="3"/>
+      <c r="N104" s="3"/>
+      <c r="O104" s="2" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>990</v>
+      </c>
+      <c r="B105" t="s">
+        <v>997</v>
+      </c>
+      <c r="C105" t="s">
+        <v>220</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="E105" s="3">
+        <v>18.18</v>
+      </c>
+      <c r="F105" s="4">
+        <v>199.98</v>
+      </c>
+      <c r="G105" s="3"/>
+      <c r="H105" s="3"/>
+      <c r="I105" s="3">
+        <v>18.06</v>
+      </c>
+      <c r="J105" s="3">
+        <v>13.23</v>
+      </c>
+      <c r="K105" s="3"/>
+      <c r="L105" s="3"/>
+      <c r="M105" s="3"/>
+      <c r="N105" s="3"/>
+      <c r="O105" s="2" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>990</v>
+      </c>
+      <c r="B106" t="s">
+        <v>991</v>
+      </c>
+      <c r="C106" t="s">
+        <v>190</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="E106" s="3">
+        <v>18.23</v>
+      </c>
+      <c r="F106" s="4">
+        <v>182.93</v>
+      </c>
+      <c r="G106" s="3"/>
+      <c r="H106" s="3"/>
+      <c r="I106" s="3">
+        <v>12.82</v>
+      </c>
+      <c r="J106" s="3">
+        <v>10.23</v>
+      </c>
+      <c r="K106" s="3"/>
+      <c r="L106" s="3"/>
+      <c r="M106" s="3"/>
+      <c r="N106" s="3"/>
+      <c r="O106" s="2" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>998</v>
+      </c>
+      <c r="B107" t="s">
+        <v>989</v>
+      </c>
+      <c r="C107" t="s">
+        <v>939</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="E107" s="3">
+        <v>18.3</v>
+      </c>
+      <c r="F107" s="4">
+        <v>44.79</v>
+      </c>
+      <c r="G107" s="3"/>
+      <c r="H107" s="3"/>
+      <c r="I107" s="3">
+        <v>5.08</v>
+      </c>
+      <c r="J107" s="3">
+        <v>1.51</v>
+      </c>
+      <c r="K107" s="3"/>
+      <c r="L107" s="3"/>
+      <c r="M107" s="3"/>
+      <c r="N107" s="3"/>
+      <c r="O107" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>992</v>
+      </c>
+      <c r="B108" t="s">
+        <v>989</v>
+      </c>
+      <c r="C108" t="s">
+        <v>51</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="E108" s="3">
+        <v>18.39</v>
+      </c>
+      <c r="F108" s="4">
+        <v>101.8</v>
+      </c>
+      <c r="G108" s="3"/>
+      <c r="H108" s="3"/>
+      <c r="I108" s="3">
+        <v>3.15</v>
+      </c>
+      <c r="J108" s="3">
+        <v>0.98</v>
+      </c>
+      <c r="K108" s="3"/>
+      <c r="L108" s="3"/>
+      <c r="M108" s="3"/>
+      <c r="N108" s="3"/>
+      <c r="O108" s="2" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>990</v>
+      </c>
+      <c r="B109" t="s">
+        <v>991</v>
+      </c>
+      <c r="C109" t="s">
+        <v>46</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="E109" s="3">
+        <v>18.5</v>
+      </c>
+      <c r="F109" s="4">
+        <v>24.12</v>
+      </c>
+      <c r="G109" s="3"/>
+      <c r="H109" s="3"/>
+      <c r="I109" s="3">
+        <v>3.51</v>
+      </c>
+      <c r="J109" s="3">
+        <v>2.23</v>
+      </c>
+      <c r="K109" s="3"/>
+      <c r="L109" s="3"/>
+      <c r="M109" s="3"/>
+      <c r="N109" s="3"/>
+      <c r="O109" s="2" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>24</v>
+      </c>
+      <c r="B110" t="s">
+        <v>989</v>
+      </c>
+      <c r="C110" t="s">
+        <v>24</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="E110" s="3">
+        <v>18.71</v>
+      </c>
+      <c r="F110" s="4">
+        <v>44.36</v>
+      </c>
+      <c r="G110" s="3"/>
+      <c r="H110" s="3"/>
+      <c r="I110" s="3">
+        <v>20.08</v>
+      </c>
+      <c r="J110" s="3">
+        <v>17.63</v>
+      </c>
+      <c r="K110" s="3"/>
+      <c r="L110" s="3"/>
+      <c r="M110" s="3"/>
+      <c r="N110" s="3"/>
+      <c r="O110" s="2" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>998</v>
+      </c>
+      <c r="B111" t="s">
+        <v>989</v>
+      </c>
+      <c r="C111" t="s">
+        <v>939</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="E111" s="3">
+        <v>19</v>
+      </c>
+      <c r="F111" s="4">
+        <v>10.95</v>
+      </c>
+      <c r="G111" s="3"/>
+      <c r="H111" s="3"/>
+      <c r="I111" s="3">
+        <v>0.89</v>
+      </c>
+      <c r="J111" s="3">
+        <v>0.84</v>
+      </c>
+      <c r="K111" s="3"/>
+      <c r="L111" s="3"/>
+      <c r="M111" s="3"/>
+      <c r="N111" s="3"/>
+      <c r="O111" s="2" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>990</v>
+      </c>
+      <c r="B112" t="s">
+        <v>991</v>
+      </c>
+      <c r="C112" t="s">
+        <v>190</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="E112" s="3">
+        <v>19</v>
+      </c>
+      <c r="F112" s="4">
+        <v>44.14</v>
+      </c>
+      <c r="G112" s="3"/>
+      <c r="H112" s="3"/>
+      <c r="I112" s="3">
+        <v>0</v>
+      </c>
+      <c r="J112" s="3">
+        <v>0</v>
+      </c>
+      <c r="K112" s="3"/>
+      <c r="L112" s="3"/>
+      <c r="M112" s="3"/>
+      <c r="N112" s="3"/>
+      <c r="O112" s="2" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>994</v>
+      </c>
+      <c r="B113" t="s">
+        <v>989</v>
+      </c>
+      <c r="C113" t="s">
+        <v>968</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="E113" s="3">
+        <v>19.19</v>
+      </c>
+      <c r="F113" s="4">
+        <v>4587.69</v>
+      </c>
+      <c r="G113" s="3"/>
+      <c r="H113" s="3"/>
+      <c r="I113" s="3">
+        <v>2.15</v>
+      </c>
+      <c r="J113" s="3">
+        <v>4.64</v>
+      </c>
+      <c r="K113" s="3"/>
+      <c r="L113" s="3"/>
+      <c r="M113" s="3"/>
+      <c r="N113" s="3"/>
+      <c r="O113" s="2" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>404</v>
+      </c>
+      <c r="B114" t="s">
+        <v>989</v>
+      </c>
+      <c r="C114" t="s">
+        <v>404</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="E114" s="3">
+        <v>19.41</v>
+      </c>
+      <c r="F114" s="4">
+        <v>8027.53</v>
+      </c>
+      <c r="G114" s="3"/>
+      <c r="H114" s="3"/>
+      <c r="I114" s="3">
+        <v>0.46</v>
+      </c>
+      <c r="J114" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="K114" s="3"/>
+      <c r="L114" s="3"/>
+      <c r="M114" s="3"/>
+      <c r="N114" s="3"/>
+      <c r="O114" s="2" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="115" ht="32" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A115" s="5" t="s">
+        <v>999</v>
+      </c>
+      <c r="B115" s="5"/>
+      <c r="C115" s="5"/>
+      <c r="D115" s="5"/>
+      <c r="E115" s="5"/>
+      <c r="F115" s="5"/>
+      <c r="G115" s="5"/>
+      <c r="H115" s="5"/>
+      <c r="I115" s="5"/>
+      <c r="J115" s="5"/>
+      <c r="K115" s="5"/>
+      <c r="L115" s="5"/>
+      <c r="M115" s="5"/>
+      <c r="N115" s="5"/>
+      <c r="O115" s="5"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A115:O115"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" tooltip="https://www.indmoney.com/stocks/welcure-drugs-and-pharmaceuticals-ltd-share-price"/>
+    <hyperlink ref="O2" r:id="rId2" tooltip="https://www.indmoney.com/stocks/welcure-drugs-and-pharmaceuticals-ltd-share-price"/>
+    <hyperlink ref="D3" r:id="rId3" tooltip="https://www.indmoney.com/stocks/remedium-lifecare-ltd-share-price"/>
+    <hyperlink ref="O3" r:id="rId4" tooltip="https://www.indmoney.com/stocks/remedium-lifecare-ltd-share-price"/>
+    <hyperlink ref="D4" r:id="rId5" tooltip="https://www.indmoney.com/stocks/rajnish-wellness-ltd-share-price"/>
+    <hyperlink ref="O4" r:id="rId6" tooltip="https://www.indmoney.com/stocks/rajnish-wellness-ltd-share-price"/>
+    <hyperlink ref="D5" r:id="rId7" tooltip="https://www.indmoney.com/stocks/western-ministil-ltd-share-price"/>
+    <hyperlink ref="O5" r:id="rId8" tooltip="https://www.indmoney.com/stocks/western-ministil-ltd-share-price"/>
+    <hyperlink ref="D6" r:id="rId9" tooltip="https://www.indmoney.com/stocks/unison-metals-ltd-share-price"/>
+    <hyperlink ref="O6" r:id="rId10" tooltip="https://www.indmoney.com/stocks/unison-metals-ltd-share-price"/>
+    <hyperlink ref="D7" r:id="rId11" tooltip="https://www.indmoney.com/stocks/navkar-urbanstructure-ltd-share-price"/>
+    <hyperlink ref="O7" r:id="rId12" tooltip="https://www.indmoney.com/stocks/navkar-urbanstructure-ltd-share-price"/>
+    <hyperlink ref="D8" r:id="rId13" tooltip="https://www.indmoney.com/stocks/sprayking-ltd-share-price"/>
+    <hyperlink ref="O8" r:id="rId14" tooltip="https://www.indmoney.com/stocks/sprayking-ltd-share-price"/>
+    <hyperlink ref="D9" r:id="rId15" tooltip="https://www.indmoney.com/stocks/ducon-infratechnologies-ltd-share-price"/>
+    <hyperlink ref="O9" r:id="rId16" tooltip="https://www.indmoney.com/stocks/ducon-infratechnologies-ltd-share-price"/>
+    <hyperlink ref="D10" r:id="rId17" tooltip="https://www.indmoney.com/stocks/family-care-hospitals-ltd-share-price"/>
+    <hyperlink ref="O10" r:id="rId18" tooltip="https://www.indmoney.com/stocks/family-care-hospitals-ltd-share-price"/>
+    <hyperlink ref="D11" r:id="rId19" tooltip="https://www.indmoney.com/stocks/ilandfs-transportation-networks-ltd-share-price"/>
+    <hyperlink ref="O11" r:id="rId20" tooltip="https://www.indmoney.com/stocks/ilandfs-transportation-networks-ltd-share-price"/>
+    <hyperlink ref="D12" r:id="rId21" tooltip="https://www.indmoney.com/stocks/ankit-metal-and-power-ltd-share-price"/>
+    <hyperlink ref="O12" r:id="rId22" tooltip="https://www.indmoney.com/stocks/ankit-metal-and-power-ltd-share-price"/>
+    <hyperlink ref="D13" r:id="rId23" tooltip="https://www.indmoney.com/stocks/parsvnath-developers-ltd-share-price"/>
+    <hyperlink ref="O13" r:id="rId24" tooltip="https://www.indmoney.com/stocks/parsvnath-developers-ltd-share-price"/>
+    <hyperlink ref="D14" r:id="rId25" tooltip="https://www.indmoney.com/stocks/davangere-sugar-company-ltd-share-price"/>
+    <hyperlink ref="O14" r:id="rId26" tooltip="https://www.indmoney.com/stocks/davangere-sugar-company-ltd-share-price"/>
+    <hyperlink ref="D15" r:id="rId27" tooltip="https://www.indmoney.com/stocks/transgene-biotek-ltd-share-price"/>
+    <hyperlink ref="O15" r:id="rId28" tooltip="https://www.indmoney.com/stocks/transgene-biotek-ltd-share-price"/>
+    <hyperlink ref="D16" r:id="rId29" tooltip="https://www.indmoney.com/stocks/gvk-power-and-infrastructure-ltd-share-price"/>
+    <hyperlink ref="O16" r:id="rId30" tooltip="https://www.indmoney.com/stocks/gvk-power-and-infrastructure-ltd-share-price"/>
+    <hyperlink ref="D17" r:id="rId31" tooltip="https://www.indmoney.com/stocks/sadbhav-infrastructure-projects-ltd-share-price"/>
+    <hyperlink ref="O17" r:id="rId32" tooltip="https://www.indmoney.com/stocks/sadbhav-infrastructure-projects-ltd-share-price"/>
+    <hyperlink ref="D18" r:id="rId33" tooltip="https://www.indmoney.com/stocks/alliance-integrated-metaliks-ltd-share-price"/>
+    <hyperlink ref="O18" r:id="rId34" tooltip="https://www.indmoney.com/stocks/alliance-integrated-metaliks-ltd-share-price"/>
+    <hyperlink ref="D19" r:id="rId35" tooltip="https://www.indmoney.com/stocks/shah-metacorp-ltd-share-price"/>
+    <hyperlink ref="O19" r:id="rId36" tooltip="https://www.indmoney.com/stocks/shah-metacorp-ltd-share-price"/>
+    <hyperlink ref="D20" r:id="rId37" tooltip="https://www.indmoney.com/stocks/facor-alloys-ltd-share-price"/>
+    <hyperlink ref="O20" r:id="rId38" tooltip="https://www.indmoney.com/stocks/facor-alloys-ltd-share-price"/>
+    <hyperlink ref="D21" r:id="rId39" tooltip="https://www.indmoney.com/stocks/mishtann-foods-ltd-share-price"/>
+    <hyperlink ref="O21" r:id="rId40" tooltip="https://www.indmoney.com/stocks/mishtann-foods-ltd-share-price"/>
+    <hyperlink ref="D22" r:id="rId41" tooltip="https://www.indmoney.com/stocks/rajnandini-metal-ltd-share-price"/>
+    <hyperlink ref="O22" r:id="rId42" tooltip="https://www.indmoney.com/stocks/rajnandini-metal-ltd-share-price"/>
+    <hyperlink ref="D23" r:id="rId43" tooltip="https://www.indmoney.com/stocks/sarveshwar-foods-ltd-share-price"/>
+    <hyperlink ref="O23" r:id="rId44" tooltip="https://www.indmoney.com/stocks/sarveshwar-foods-ltd-share-price"/>
+    <hyperlink ref="D24" r:id="rId45" tooltip="https://www.indmoney.com/stocks/noida-toll-bridge-company-ltd-share-price"/>
+    <hyperlink ref="O24" r:id="rId46" tooltip="https://www.indmoney.com/stocks/noida-toll-bridge-company-ltd-share-price"/>
+    <hyperlink ref="D25" r:id="rId47" tooltip="https://www.indmoney.com/stocks/prakash-steelage-ltd-share-price"/>
+    <hyperlink ref="O25" r:id="rId48" tooltip="https://www.indmoney.com/stocks/prakash-steelage-ltd-share-price"/>
+    <hyperlink ref="D26" r:id="rId49" tooltip="https://www.indmoney.com/stocks/sacheta-metals-ltd-share-price"/>
+    <hyperlink ref="O26" r:id="rId50" tooltip="https://www.indmoney.com/stocks/sacheta-metals-ltd-share-price"/>
+    <hyperlink ref="D27" r:id="rId51" tooltip="https://www.indmoney.com/stocks/dhatre-udyog-ltd-share-price"/>
+    <hyperlink ref="O27" r:id="rId52" tooltip="https://www.indmoney.com/stocks/dhatre-udyog-ltd-share-price"/>
+    <hyperlink ref="D28" r:id="rId53" tooltip="https://www.indmoney.com/stocks/kamdhenu-ventures-ltd-share-price"/>
+    <hyperlink ref="O28" r:id="rId54" tooltip="https://www.indmoney.com/stocks/kamdhenu-ventures-ltd-share-price"/>
+    <hyperlink ref="D29" r:id="rId55" tooltip="https://www.indmoney.com/stocks/salasar-techno-engineering-ltd-share-price"/>
+    <hyperlink ref="O29" r:id="rId56" tooltip="https://www.indmoney.com/stocks/salasar-techno-engineering-ltd-share-price"/>
+    <hyperlink ref="D30" r:id="rId57" tooltip="https://www.indmoney.com/stocks/supreme-engineering-ltd-share-price"/>
+    <hyperlink ref="O30" r:id="rId58" tooltip="https://www.indmoney.com/stocks/supreme-engineering-ltd-share-price"/>
+    <hyperlink ref="D31" r:id="rId59" tooltip="https://www.indmoney.com/stocks/rama-steel-tubes-ltd-share-price"/>
+    <hyperlink ref="O31" r:id="rId60" tooltip="https://www.indmoney.com/stocks/rama-steel-tubes-ltd-share-price"/>
+    <hyperlink ref="D32" r:id="rId61" tooltip="https://www.indmoney.com/stocks/gian-lifecare-ltd-share-price"/>
+    <hyperlink ref="O32" r:id="rId62" tooltip="https://www.indmoney.com/stocks/gian-lifecare-ltd-share-price"/>
+    <hyperlink ref="D33" r:id="rId63" tooltip="https://www.indmoney.com/stocks/kritika-wires-ltd-share-price"/>
+    <hyperlink ref="O33" r:id="rId64" tooltip="https://www.indmoney.com/stocks/kritika-wires-ltd-share-price"/>
+    <hyperlink ref="D34" r:id="rId65" tooltip="https://www.indmoney.com/stocks/shyam-century-ferrous-ltd-share-price"/>
+    <hyperlink ref="O34" r:id="rId66" tooltip="https://www.indmoney.com/stocks/shyam-century-ferrous-ltd-share-price"/>
+    <hyperlink ref="D35" r:id="rId67" tooltip="https://www.indmoney.com/stocks/sepc-ltd-share-price"/>
+    <hyperlink ref="O35" r:id="rId68" tooltip="https://www.indmoney.com/stocks/sepc-ltd-share-price"/>
+    <hyperlink ref="D36" r:id="rId69" tooltip="https://www.indmoney.com/stocks/zenith-steel-pipes-and-industries-ltd-share-price"/>
+    <hyperlink ref="O36" r:id="rId70" tooltip="https://www.indmoney.com/stocks/zenith-steel-pipes-and-industries-ltd-share-price"/>
+    <hyperlink ref="D37" r:id="rId71" tooltip="https://www.indmoney.com/stocks/lasa-supergenerics-ltd-share-price"/>
+    <hyperlink ref="O37" r:id="rId72" tooltip="https://www.indmoney.com/stocks/lasa-supergenerics-ltd-share-price"/>
+    <hyperlink ref="D38" r:id="rId73" tooltip="https://www.indmoney.com/stocks/vivimed-labs-ltd-share-price"/>
+    <hyperlink ref="O38" r:id="rId74" tooltip="https://www.indmoney.com/stocks/vivimed-labs-ltd-share-price"/>
+    <hyperlink ref="D39" r:id="rId75" tooltip="https://www.indmoney.com/stocks/achyut-healthcare-ltd-share-price"/>
+    <hyperlink ref="O39" r:id="rId76" tooltip="https://www.indmoney.com/stocks/achyut-healthcare-ltd-share-price"/>
+    <hyperlink ref="D40" r:id="rId77" tooltip="https://www.indmoney.com/stocks/vista-pharmaceuticals-ltd-share-price"/>
+    <hyperlink ref="O40" r:id="rId78" tooltip="https://www.indmoney.com/stocks/vista-pharmaceuticals-ltd-share-price"/>
+    <hyperlink ref="D41" r:id="rId79" tooltip="https://www.indmoney.com/stocks/heera-ispat-ltd-share-price"/>
+    <hyperlink ref="O41" r:id="rId80" tooltip="https://www.indmoney.com/stocks/heera-ispat-ltd-share-price"/>
+    <hyperlink ref="D42" r:id="rId81" tooltip="https://www.indmoney.com/stocks/bothra-metals-and-alloys-ltd-share-price"/>
+    <hyperlink ref="O42" r:id="rId82" tooltip="https://www.indmoney.com/stocks/bothra-metals-and-alloys-ltd-share-price"/>
+    <hyperlink ref="D43" r:id="rId83" tooltip="https://www.indmoney.com/stocks/deepak-builders-and-engineers-india-ltd-share-price"/>
+    <hyperlink ref="O43" r:id="rId84" tooltip="https://www.indmoney.com/stocks/deepak-builders-and-engineers-india-ltd-share-price"/>
+    <hyperlink ref="D44" r:id="rId85" tooltip="https://www.indmoney.com/stocks/impex-ferro-tech-ltd-share-price"/>
+    <hyperlink ref="O44" r:id="rId86" tooltip="https://www.indmoney.com/stocks/impex-ferro-tech-ltd-share-price"/>
+    <hyperlink ref="D45" r:id="rId87" tooltip="https://www.indmoney.com/stocks/nila-infrastructures-ltd-share-price"/>
+    <hyperlink ref="O45" r:id="rId88" tooltip="https://www.indmoney.com/stocks/nila-infrastructures-ltd-share-price"/>
+    <hyperlink ref="D46" r:id="rId89" tooltip="https://www.indmoney.com/stocks/rattanindia-power-ltd-share-price"/>
+    <hyperlink ref="O46" r:id="rId90" tooltip="https://www.indmoney.com/stocks/rattanindia-power-ltd-share-price"/>
+    <hyperlink ref="D47" r:id="rId91" tooltip="https://www.indmoney.com/stocks/india-power-corporation-ltd-share-price"/>
+    <hyperlink ref="O47" r:id="rId92" tooltip="https://www.indmoney.com/stocks/india-power-corporation-ltd-share-price"/>
+    <hyperlink ref="D48" r:id="rId93" tooltip="https://www.indmoney.com/stocks/sadbhav-engineering-ltd-share-price"/>
+    <hyperlink ref="O48" r:id="rId94" tooltip="https://www.indmoney.com/stocks/sadbhav-engineering-ltd-share-price"/>
+    <hyperlink ref="D49" r:id="rId95" tooltip="https://www.indmoney.com/stocks/dr-lalchandani-labs-ltd-share-price"/>
+    <hyperlink ref="O49" r:id="rId96" tooltip="https://www.indmoney.com/stocks/dr-lalchandani-labs-ltd-share-price"/>
+    <hyperlink ref="D50" r:id="rId97" tooltip="https://www.indmoney.com/stocks/madhav-infra-projects-ltd-share-price"/>
+    <hyperlink ref="O50" r:id="rId98" tooltip="https://www.indmoney.com/stocks/madhav-infra-projects-ltd-share-price"/>
+    <hyperlink ref="D51" r:id="rId99" tooltip="https://www.indmoney.com/stocks/elitecon-international-ltd-share-price"/>
+    <hyperlink ref="O51" r:id="rId100" tooltip="https://www.indmoney.com/stocks/elitecon-international-ltd-share-price"/>
+    <hyperlink ref="D52" r:id="rId101" tooltip="https://www.indmoney.com/stocks/twamev-construction-and-infrastructure-ltd-share-price"/>
+    <hyperlink ref="O52" r:id="rId102" tooltip="https://www.indmoney.com/stocks/twamev-construction-and-infrastructure-ltd-share-price"/>
+    <hyperlink ref="D53" r:id="rId103" tooltip="https://www.indmoney.com/stocks/aditya-ispat-ltd-share-price"/>
+    <hyperlink ref="O53" r:id="rId104" tooltip="https://www.indmoney.com/stocks/aditya-ispat-ltd-share-price"/>
+    <hyperlink ref="D54" r:id="rId105" tooltip="https://www.indmoney.com/stocks/bharat-immunological-and-biological-corporation-ltd-share-price"/>
+    <hyperlink ref="O54" r:id="rId106" tooltip="https://www.indmoney.com/stocks/bharat-immunological-and-biological-corporation-ltd-share-price"/>
+    <hyperlink ref="D55" r:id="rId107" tooltip="https://www.indmoney.com/stocks/vaishali-pharma-ltd-share-price"/>
+    <hyperlink ref="O55" r:id="rId108" tooltip="https://www.indmoney.com/stocks/vaishali-pharma-ltd-share-price"/>
+    <hyperlink ref="D56" r:id="rId109" tooltip="https://www.indmoney.com/stocks/indowind-energy-ltd-share-price"/>
+    <hyperlink ref="O56" r:id="rId110" tooltip="https://www.indmoney.com/stocks/indowind-energy-ltd-share-price"/>
+    <hyperlink ref="D57" r:id="rId111" tooltip="https://www.indmoney.com/stocks/vallabh-steels-ltd-share-price"/>
+    <hyperlink ref="O57" r:id="rId112" tooltip="https://www.indmoney.com/stocks/vallabh-steels-ltd-share-price"/>
+    <hyperlink ref="D58" r:id="rId113" tooltip="https://www.indmoney.com/stocks/orient-green-power-company-ltd-share-price"/>
+    <hyperlink ref="O58" r:id="rId114" tooltip="https://www.indmoney.com/stocks/orient-green-power-company-ltd-share-price"/>
+    <hyperlink ref="D59" r:id="rId115" tooltip="https://www.indmoney.com/stocks/rajasthan-tube-manufacturing-co-ltd-share-price"/>
+    <hyperlink ref="O59" r:id="rId116" tooltip="https://www.indmoney.com/stocks/rajasthan-tube-manufacturing-co-ltd-share-price"/>
+    <hyperlink ref="D60" r:id="rId117" tooltip="https://www.indmoney.com/stocks/baroda-extrusion-ltd-share-price"/>
+    <hyperlink ref="O60" r:id="rId118" tooltip="https://www.indmoney.com/stocks/baroda-extrusion-ltd-share-price"/>
+    <hyperlink ref="D61" r:id="rId119" tooltip="https://www.indmoney.com/stocks/looks-health-services-ltd-share-price"/>
+    <hyperlink ref="O61" r:id="rId120" tooltip="https://www.indmoney.com/stocks/looks-health-services-ltd-share-price"/>
+    <hyperlink ref="D62" r:id="rId121" tooltip="https://www.indmoney.com/stocks/gennex-laboratories-ltd-share-price"/>
+    <hyperlink ref="O62" r:id="rId122" tooltip="https://www.indmoney.com/stocks/gennex-laboratories-ltd-share-price"/>
+    <hyperlink ref="D63" r:id="rId123" tooltip="https://www.indmoney.com/stocks/mahalaxmi-seamless-ltd-share-price"/>
+    <hyperlink ref="O63" r:id="rId124" tooltip="https://www.indmoney.com/stocks/mahalaxmi-seamless-ltd-share-price"/>
+    <hyperlink ref="D64" r:id="rId125" tooltip="https://www.indmoney.com/stocks/jfl-life-sciences-ltd-share-price"/>
+    <hyperlink ref="O64" r:id="rId126" tooltip="https://www.indmoney.com/stocks/jfl-life-sciences-ltd-share-price"/>
+    <hyperlink ref="D65" r:id="rId127" tooltip="https://www.indmoney.com/stocks/la-tim-metal-and-industries-ltd-share-price"/>
+    <hyperlink ref="O65" r:id="rId128" tooltip="https://www.indmoney.com/stocks/la-tim-metal-and-industries-ltd-share-price"/>
+    <hyperlink ref="D66" r:id="rId129" tooltip="https://www.indmoney.com/stocks/boston-commerce-limited-share-price"/>
+    <hyperlink ref="O66" r:id="rId130" tooltip="https://www.indmoney.com/stocks/boston-commerce-limited-share-price"/>
+    <hyperlink ref="D67" r:id="rId131" tooltip="https://www.indmoney.com/stocks/nectar-lifescience-ltd-share-price"/>
+    <hyperlink ref="O67" r:id="rId132" tooltip="https://www.indmoney.com/stocks/nectar-lifescience-ltd-share-price"/>
+    <hyperlink ref="D68" r:id="rId133" tooltip="https://www.indmoney.com/stocks/maruti-infrastructure-ltd-share-price"/>
+    <hyperlink ref="O68" r:id="rId134" tooltip="https://www.indmoney.com/stocks/maruti-infrastructure-ltd-share-price"/>
+    <hyperlink ref="D69" r:id="rId135" tooltip="https://www.indmoney.com/stocks/steel-exchange-india-ltd-share-price"/>
+    <hyperlink ref="O69" r:id="rId136" tooltip="https://www.indmoney.com/stocks/steel-exchange-india-ltd-share-price"/>
+    <hyperlink ref="D70" r:id="rId137" tooltip="https://www.indmoney.com/stocks/deccan-health-care-ltd-share-price"/>
+    <hyperlink ref="O70" r:id="rId138" tooltip="https://www.indmoney.com/stocks/deccan-health-care-ltd-share-price"/>
+    <hyperlink ref="D71" r:id="rId139" tooltip="https://www.indmoney.com/stocks/earthstahl-and-alloys-ltd-share-price"/>
+    <hyperlink ref="O71" r:id="rId140" tooltip="https://www.indmoney.com/stocks/earthstahl-and-alloys-ltd-share-price"/>
+    <hyperlink ref="D72" r:id="rId141" tooltip="https://www.indmoney.com/stocks/global-longlife-hospital-and-research-ltd-share-price"/>
+    <hyperlink ref="O72" r:id="rId142" tooltip="https://www.indmoney.com/stocks/global-longlife-hospital-and-research-ltd-share-price"/>
+    <hyperlink ref="D73" r:id="rId143" tooltip="https://www.indmoney.com/stocks/global-defence-industries-limited-share-price"/>
+    <hyperlink ref="O73" r:id="rId144" tooltip="https://www.indmoney.com/stocks/global-defence-industries-limited-share-price"/>
+    <hyperlink ref="D74" r:id="rId145" tooltip="https://www.indmoney.com/stocks/bihar-sponge-iron-ltd-share-price"/>
+    <hyperlink ref="O74" r:id="rId146" tooltip="https://www.indmoney.com/stocks/bihar-sponge-iron-ltd-share-price"/>
+    <hyperlink ref="D75" r:id="rId147" tooltip="https://www.indmoney.com/stocks/a-b-infrabuild-ltd-share-price"/>
+    <hyperlink ref="O75" r:id="rId148" tooltip="https://www.indmoney.com/stocks/a-b-infrabuild-ltd-share-price"/>
+    <hyperlink ref="D76" r:id="rId149" tooltip="https://www.indmoney.com/stocks/take-ltd-share-price"/>
+    <hyperlink ref="O76" r:id="rId150" tooltip="https://www.indmoney.com/stocks/take-ltd-share-price"/>
+    <hyperlink ref="D77" r:id="rId151" tooltip="https://www.indmoney.com/stocks/tejnaksh-healthcare-ltd-share-price"/>
+    <hyperlink ref="O77" r:id="rId152" tooltip="https://www.indmoney.com/stocks/tejnaksh-healthcare-ltd-share-price"/>
+    <hyperlink ref="D78" r:id="rId153" tooltip="https://www.indmoney.com/stocks/nova-iron-and-steel-ltd-share-price"/>
+    <hyperlink ref="O78" r:id="rId154" tooltip="https://www.indmoney.com/stocks/nova-iron-and-steel-ltd-share-price"/>
+    <hyperlink ref="D79" r:id="rId155" tooltip="https://www.indmoney.com/stocks/atal-realtech-ltd-share-price"/>
+    <hyperlink ref="O79" r:id="rId156" tooltip="https://www.indmoney.com/stocks/atal-realtech-ltd-share-price"/>
+    <hyperlink ref="D80" r:id="rId157" tooltip="https://www.indmoney.com/stocks/nidan-laboratories-and-healthcare-ltd-share-price"/>
+    <hyperlink ref="O80" r:id="rId158" tooltip="https://www.indmoney.com/stocks/nidan-laboratories-and-healthcare-ltd-share-price"/>
+    <hyperlink ref="D81" r:id="rId159" tooltip="https://www.indmoney.com/stocks/consolidated-construction-consortium-ltd-share-price"/>
+    <hyperlink ref="O81" r:id="rId160" tooltip="https://www.indmoney.com/stocks/consolidated-construction-consortium-ltd-share-price"/>
+    <hyperlink ref="D82" r:id="rId161" tooltip="https://www.indmoney.com/stocks/mukat-pipes-ltd-share-price"/>
+    <hyperlink ref="O82" r:id="rId162" tooltip="https://www.indmoney.com/stocks/mukat-pipes-ltd-share-price"/>
+    <hyperlink ref="D83" r:id="rId163" tooltip="https://www.indmoney.com/stocks/ind-renewable-energy-ltd-share-price"/>
+    <hyperlink ref="O83" r:id="rId164" tooltip="https://www.indmoney.com/stocks/ind-renewable-energy-ltd-share-price"/>
+    <hyperlink ref="D84" r:id="rId165" tooltip="https://www.indmoney.com/stocks/modern-steels-ltd-share-price"/>
+    <hyperlink ref="O84" r:id="rId166" tooltip="https://www.indmoney.com/stocks/modern-steels-ltd-share-price"/>
+    <hyperlink ref="D85" r:id="rId167" tooltip="https://www.indmoney.com/stocks/a2z-infra-engineering-ltd-share-price"/>
+    <hyperlink ref="O85" r:id="rId168" tooltip="https://www.indmoney.com/stocks/a2z-infra-engineering-ltd-share-price"/>
+    <hyperlink ref="D86" r:id="rId169" tooltip="https://www.indmoney.com/stocks/arcee-industries-ltd-share-price"/>
+    <hyperlink ref="O86" r:id="rId170" tooltip="https://www.indmoney.com/stocks/arcee-industries-ltd-share-price"/>
+    <hyperlink ref="D87" r:id="rId171" tooltip="https://www.indmoney.com/stocks/energy-development-company-ltd-share-price"/>
+    <hyperlink ref="O87" r:id="rId172" tooltip="https://www.indmoney.com/stocks/energy-development-company-ltd-share-price"/>
+    <hyperlink ref="D88" r:id="rId173" tooltip="https://www.indmoney.com/stocks/venmax-drugs-and-pharmaceuticals-ltd-share-price"/>
+    <hyperlink ref="O88" r:id="rId174" tooltip="https://www.indmoney.com/stocks/venmax-drugs-and-pharmaceuticals-ltd-share-price"/>
+    <hyperlink ref="D89" r:id="rId175" tooltip="https://www.indmoney.com/stocks/jaiprakash-power-ventures-ltd-share-price"/>
+    <hyperlink ref="O89" r:id="rId176" tooltip="https://www.indmoney.com/stocks/jaiprakash-power-ventures-ltd-share-price"/>
+    <hyperlink ref="D90" r:id="rId177" tooltip="https://www.indmoney.com/stocks/broach-lifecare-hospital-ltd-share-price"/>
+    <hyperlink ref="O90" r:id="rId178" tooltip="https://www.indmoney.com/stocks/broach-lifecare-hospital-ltd-share-price"/>
+    <hyperlink ref="D91" r:id="rId179" tooltip="https://www.indmoney.com/stocks/modulex-construction-technologies-ltd-share-price"/>
+    <hyperlink ref="O91" r:id="rId180" tooltip="https://www.indmoney.com/stocks/modulex-construction-technologies-ltd-share-price"/>
+    <hyperlink ref="D92" r:id="rId181" tooltip="https://www.indmoney.com/stocks/eastcoast-steel-ltd-share-price"/>
+    <hyperlink ref="O92" r:id="rId182" tooltip="https://www.indmoney.com/stocks/eastcoast-steel-ltd-share-price"/>
+    <hyperlink ref="D93" r:id="rId183" tooltip="https://www.indmoney.com/stocks/rathi-bars-ltd-share-price"/>
+    <hyperlink ref="O93" r:id="rId184" tooltip="https://www.indmoney.com/stocks/rathi-bars-ltd-share-price"/>
+    <hyperlink ref="D94" r:id="rId185" tooltip="https://www.indmoney.com/stocks/surana-telecom-and-power-ltd-share-price"/>
+    <hyperlink ref="O94" r:id="rId186" tooltip="https://www.indmoney.com/stocks/surana-telecom-and-power-ltd-share-price"/>
+    <hyperlink ref="D95" r:id="rId187" tooltip="https://www.indmoney.com/stocks/bharat-road-network-ltd-share-price"/>
+    <hyperlink ref="O95" r:id="rId188" tooltip="https://www.indmoney.com/stocks/bharat-road-network-ltd-share-price"/>
+    <hyperlink ref="D96" r:id="rId189" tooltip="https://www.indmoney.com/stocks/poojawestern-metaliks-ltd-share-price"/>
+    <hyperlink ref="O96" r:id="rId190" tooltip="https://www.indmoney.com/stocks/poojawestern-metaliks-ltd-share-price"/>
+    <hyperlink ref="D97" r:id="rId191" tooltip="https://www.indmoney.com/stocks/globus-power-generation-ltd-share-price"/>
+    <hyperlink ref="O97" r:id="rId192" tooltip="https://www.indmoney.com/stocks/globus-power-generation-ltd-share-price"/>
+    <hyperlink ref="D98" r:id="rId193" tooltip="https://www.indmoney.com/stocks/rhetan-tmt-ltd-share-price"/>
+    <hyperlink ref="O98" r:id="rId194" tooltip="https://www.indmoney.com/stocks/rhetan-tmt-ltd-share-price"/>
+    <hyperlink ref="D99" r:id="rId195" tooltip="https://www.indmoney.com/stocks/galaxy-medicare-ltd-share-price"/>
+    <hyperlink ref="O99" r:id="rId196" tooltip="https://www.indmoney.com/stocks/galaxy-medicare-ltd-share-price"/>
+    <hyperlink ref="D100" r:id="rId197" tooltip="https://www.indmoney.com/stocks/irb-infrastructure-developers-ltd-share-price"/>
+    <hyperlink ref="O100" r:id="rId198" tooltip="https://www.indmoney.com/stocks/irb-infrastructure-developers-ltd-share-price"/>
+    <hyperlink ref="D101" r:id="rId199" tooltip="https://www.indmoney.com/stocks/vivo-bio-tech-ltd-share-price"/>
+    <hyperlink ref="O101" r:id="rId200" tooltip="https://www.indmoney.com/stocks/vivo-bio-tech-ltd-share-price"/>
+    <hyperlink ref="D102" r:id="rId201" tooltip="https://www.indmoney.com/stocks/adeshwar-meditex-ltd-share-price"/>
+    <hyperlink ref="O102" r:id="rId202" tooltip="https://www.indmoney.com/stocks/adeshwar-meditex-ltd-share-price"/>
+    <hyperlink ref="D103" r:id="rId203" tooltip="https://www.indmoney.com/stocks/kandr-rail-engineering-ltd-share-price"/>
+    <hyperlink ref="O103" r:id="rId204" tooltip="https://www.indmoney.com/stocks/kandr-rail-engineering-ltd-share-price"/>
+    <hyperlink ref="D104" r:id="rId205" tooltip="https://www.indmoney.com/stocks/hazoor-multi-projects-ltd-share-price"/>
+    <hyperlink ref="O104" r:id="rId206" tooltip="https://www.indmoney.com/stocks/hazoor-multi-projects-ltd-share-price"/>
+    <hyperlink ref="D105" r:id="rId207" tooltip="https://www.indmoney.com/stocks/century-extrusions-ltd-share-price"/>
+    <hyperlink ref="O105" r:id="rId208" tooltip="https://www.indmoney.com/stocks/century-extrusions-ltd-share-price"/>
+    <hyperlink ref="D106" r:id="rId209" tooltip="https://www.indmoney.com/stocks/rudra-global-infra-products-ltd-share-price"/>
+    <hyperlink ref="O106" r:id="rId210" tooltip="https://www.indmoney.com/stocks/rudra-global-infra-products-ltd-share-price"/>
+    <hyperlink ref="D107" r:id="rId211" tooltip="https://www.indmoney.com/stocks/vms-industries-ltd-share-price"/>
+    <hyperlink ref="O107" r:id="rId212" tooltip="https://www.indmoney.com/stocks/vms-industries-ltd-share-price"/>
+    <hyperlink ref="D108" r:id="rId213" tooltip="https://www.indmoney.com/stocks/udayshivakumar-infra-ltd-share-price"/>
+    <hyperlink ref="O108" r:id="rId214" tooltip="https://www.indmoney.com/stocks/udayshivakumar-infra-ltd-share-price"/>
+    <hyperlink ref="D109" r:id="rId215" tooltip="https://www.indmoney.com/stocks/kalana-ispat-ltd-share-price"/>
+    <hyperlink ref="O109" r:id="rId216" tooltip="https://www.indmoney.com/stocks/kalana-ispat-ltd-share-price"/>
+    <hyperlink ref="D110" r:id="rId217" tooltip="https://www.indmoney.com/stocks/kabra-drugs-ltd-share-price"/>
+    <hyperlink ref="O110" r:id="rId218" tooltip="https://www.indmoney.com/stocks/kabra-drugs-ltd-share-price"/>
+    <hyperlink ref="D111" r:id="rId219" tooltip="https://www.indmoney.com/stocks/garware-marine-industries-ltd-share-price"/>
+    <hyperlink ref="O111" r:id="rId220" tooltip="https://www.indmoney.com/stocks/garware-marine-industries-ltd-share-price"/>
+    <hyperlink ref="D112" r:id="rId221" tooltip="https://www.indmoney.com/stocks/swastik-pipe-ltd-share-price"/>
+    <hyperlink ref="O112" r:id="rId222" tooltip="https://www.indmoney.com/stocks/swastik-pipe-ltd-share-price"/>
+    <hyperlink ref="D113" r:id="rId223" tooltip="https://www.indmoney.com/stocks/bajaj-hindusthan-sugar-ltd-share-price"/>
+    <hyperlink ref="O113" r:id="rId224" tooltip="https://www.indmoney.com/stocks/bajaj-hindusthan-sugar-ltd-share-price"/>
+    <hyperlink ref="D114" r:id="rId225" tooltip="https://www.indmoney.com/stocks/reliance-power-ltd-share-price"/>
+    <hyperlink ref="O114" r:id="rId226" tooltip="https://www.indmoney.com/stocks/reliance-power-ltd-share-price"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/INDmoney-All-Sectors-Under-20-Review.xlsx
+++ b/INDmoney-All-Sectors-Under-20-Review.xlsx
@@ -1,12 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D6BCE08-1330-4E08-9704-41142DEE060F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Stocks under 20Rs" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Focus Sectors" state="visible" r:id="rId5"/>
+    <sheet name="Stocks under 20Rs" sheetId="1" r:id="rId1"/>
+    <sheet name="Focus Sectors" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Focus Sectors'!$A$1:$O$115</definedName>
+  </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
@@ -3017,26 +3024,32 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-    </font>
-    <font>
       <u/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <i/>
+      <sz val="11"/>
       <color rgb="FF666666"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3413,9 +3426,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M461"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="38" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
@@ -3426,7 +3439,7 @@
     <col min="13" max="13" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="1" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3467,7 +3480,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -3496,7 +3509,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -3525,7 +3538,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -3554,7 +3567,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -3570,7 +3583,7 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="H5" s="3">
         <v>0.9</v>
@@ -3583,7 +3596,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -3612,7 +3625,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -3641,7 +3654,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -3670,7 +3683,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -3699,7 +3712,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -3710,7 +3723,7 @@
         <v>0.37</v>
       </c>
       <c r="D10" s="4">
-        <v>36.55</v>
+        <v>36.549999999999997</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -3728,7 +3741,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -3757,7 +3770,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -3786,7 +3799,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -3815,7 +3828,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>43</v>
       </c>
@@ -3823,10 +3836,10 @@
         <v>44</v>
       </c>
       <c r="C14" s="3">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="D14" s="4">
-        <v>4.44</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -3844,7 +3857,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>46</v>
       </c>
@@ -3873,7 +3886,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -3892,7 +3905,7 @@
         <v>6.08</v>
       </c>
       <c r="H16" s="3">
-        <v>4.64</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
@@ -3902,7 +3915,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>51</v>
       </c>
@@ -3931,7 +3944,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>54</v>
       </c>
@@ -3960,7 +3973,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -3989,7 +4002,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -4018,7 +4031,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -4047,7 +4060,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>63</v>
       </c>
@@ -4076,7 +4089,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -4084,7 +4097,7 @@
         <v>66</v>
       </c>
       <c r="C23" s="3">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D23" s="4">
         <v>7.79</v>
@@ -4105,7 +4118,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -4113,7 +4126,7 @@
         <v>68</v>
       </c>
       <c r="C24" s="3">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="D24" s="4">
         <v>63.6</v>
@@ -4121,7 +4134,7 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3">
-        <v>4.56</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="H24" s="3">
         <v>1.19</v>
@@ -4134,7 +4147,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -4142,7 +4155,7 @@
         <v>70</v>
       </c>
       <c r="C25" s="3">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="D25" s="4">
         <v>4.05</v>
@@ -4163,7 +4176,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>72</v>
       </c>
@@ -4192,7 +4205,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -4221,7 +4234,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>51</v>
       </c>
@@ -4250,7 +4263,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -4279,7 +4292,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -4308,7 +4321,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>83</v>
       </c>
@@ -4337,7 +4350,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>13</v>
       </c>
@@ -4348,12 +4361,12 @@
         <v>1.37</v>
       </c>
       <c r="D32" s="4">
-        <v>74.1</v>
+        <v>74.099999999999994</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3">
-        <v>4.31</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="H32" s="3">
         <v>4.96</v>
@@ -4366,7 +4379,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>88</v>
       </c>
@@ -4395,7 +4408,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>21</v>
       </c>
@@ -4424,7 +4437,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>13</v>
       </c>
@@ -4443,7 +4456,7 @@
         <v>7.11</v>
       </c>
       <c r="H35" s="3">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
@@ -4453,7 +4466,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -4482,7 +4495,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -4511,7 +4524,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>99</v>
       </c>
@@ -4540,7 +4553,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>21</v>
       </c>
@@ -4569,7 +4582,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>104</v>
       </c>
@@ -4598,7 +4611,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>107</v>
       </c>
@@ -4627,7 +4640,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>13</v>
       </c>
@@ -4656,7 +4669,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>51</v>
       </c>
@@ -4685,7 +4698,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>114</v>
       </c>
@@ -4714,7 +4727,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>40</v>
       </c>
@@ -4733,7 +4746,7 @@
         <v>8.26</v>
       </c>
       <c r="H45" s="3">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
@@ -4743,7 +4756,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>21</v>
       </c>
@@ -4772,7 +4785,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>21</v>
       </c>
@@ -4801,7 +4814,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -4812,7 +4825,7 @@
         <v>2.02</v>
       </c>
       <c r="D48" s="4">
-        <v>67.51</v>
+        <v>67.510000000000005</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
@@ -4830,7 +4843,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>46</v>
       </c>
@@ -4859,7 +4872,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>13</v>
       </c>
@@ -4878,7 +4891,7 @@
         <v>0.64</v>
       </c>
       <c r="H50" s="3">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
@@ -4888,7 +4901,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>129</v>
       </c>
@@ -4917,7 +4930,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -4946,7 +4959,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>40</v>
       </c>
@@ -4975,7 +4988,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>51</v>
       </c>
@@ -5004,7 +5017,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -5033,7 +5046,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>21</v>
       </c>
@@ -5062,7 +5075,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>13</v>
       </c>
@@ -5091,7 +5104,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>21</v>
       </c>
@@ -5099,10 +5112,10 @@
         <v>144</v>
       </c>
       <c r="C58" s="3">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D58" s="4">
-        <v>4.39</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
@@ -5120,7 +5133,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>146</v>
       </c>
@@ -5128,7 +5141,7 @@
         <v>147</v>
       </c>
       <c r="C59" s="3">
-        <v>2.26</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="D59" s="4">
         <v>383.27</v>
@@ -5149,7 +5162,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>35</v>
       </c>
@@ -5178,7 +5191,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>104</v>
       </c>
@@ -5207,7 +5220,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>21</v>
       </c>
@@ -5236,7 +5249,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>155</v>
       </c>
@@ -5244,7 +5257,7 @@
         <v>156</v>
       </c>
       <c r="C63" s="3">
-        <v>2.47</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="D63" s="4">
         <v>748.95</v>
@@ -5265,7 +5278,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>158</v>
       </c>
@@ -5273,7 +5286,7 @@
         <v>159</v>
       </c>
       <c r="C64" s="3">
-        <v>2.51</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="D64" s="4">
         <v>396.38</v>
@@ -5294,7 +5307,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>13</v>
       </c>
@@ -5323,7 +5336,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -5352,7 +5365,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>21</v>
       </c>
@@ -5360,10 +5373,10 @@
         <v>165</v>
       </c>
       <c r="C67" s="3">
-        <v>2.55</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="D67" s="4">
-        <v>9.88</v>
+        <v>9.8800000000000008</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
@@ -5381,7 +5394,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>129</v>
       </c>
@@ -5410,7 +5423,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>51</v>
       </c>
@@ -5429,7 +5442,7 @@
         <v>-1.52</v>
       </c>
       <c r="H69" s="3">
-        <v>-9.2</v>
+        <v>-9.1999999999999993</v>
       </c>
       <c r="I69" s="3"/>
       <c r="J69" s="3"/>
@@ -5439,7 +5452,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>21</v>
       </c>
@@ -5468,7 +5481,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>63</v>
       </c>
@@ -5497,7 +5510,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -5526,7 +5539,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>63</v>
       </c>
@@ -5537,7 +5550,7 @@
         <v>2.9</v>
       </c>
       <c r="D73" s="4">
-        <v>4.73</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
@@ -5555,7 +5568,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>21</v>
       </c>
@@ -5584,7 +5597,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>21</v>
       </c>
@@ -5613,7 +5626,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>183</v>
       </c>
@@ -5642,7 +5655,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>21</v>
       </c>
@@ -5661,7 +5674,7 @@
         <v>3.28</v>
       </c>
       <c r="H77" s="3">
-        <v>2.47</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="I77" s="3"/>
       <c r="J77" s="3"/>
@@ -5671,7 +5684,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>40</v>
       </c>
@@ -5700,7 +5713,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>190</v>
       </c>
@@ -5729,7 +5742,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>190</v>
       </c>
@@ -5745,7 +5758,7 @@
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="3">
-        <v>4.23</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="H80" s="3">
         <v>3.43</v>
@@ -5758,7 +5771,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>190</v>
       </c>
@@ -5787,7 +5800,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>146</v>
       </c>
@@ -5816,7 +5829,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>199</v>
       </c>
@@ -5832,7 +5845,7 @@
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3">
-        <v>4.85</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="H83" s="3">
         <v>-0.21</v>
@@ -5845,7 +5858,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>107</v>
       </c>
@@ -5874,7 +5887,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>35</v>
       </c>
@@ -5903,7 +5916,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>146</v>
       </c>
@@ -5919,7 +5932,7 @@
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3">
-        <v>8.46</v>
+        <v>8.4600000000000009</v>
       </c>
       <c r="H86" s="3">
         <v>4.07</v>
@@ -5932,7 +5945,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>13</v>
       </c>
@@ -5961,7 +5974,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>51</v>
       </c>
@@ -5972,7 +5985,7 @@
         <v>3.56</v>
       </c>
       <c r="D88" s="4">
-        <v>66.29</v>
+        <v>66.290000000000006</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
@@ -5990,7 +6003,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>190</v>
       </c>
@@ -6019,7 +6032,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>114</v>
       </c>
@@ -6030,7 +6043,7 @@
         <v>3.6</v>
       </c>
       <c r="D90" s="4">
-        <v>4.86</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
@@ -6048,7 +6061,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>21</v>
       </c>
@@ -6077,7 +6090,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>63</v>
       </c>
@@ -6106,7 +6119,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>220</v>
       </c>
@@ -6122,7 +6135,7 @@
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3">
-        <v>10.2</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="H93" s="3">
         <v>8.89</v>
@@ -6135,7 +6148,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>21</v>
       </c>
@@ -6154,7 +6167,7 @@
         <v>2.38</v>
       </c>
       <c r="H94" s="3">
-        <v>2.51</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="I94" s="3"/>
       <c r="J94" s="3"/>
@@ -6164,7 +6177,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>225</v>
       </c>
@@ -6193,7 +6206,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>129</v>
       </c>
@@ -6222,7 +6235,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>21</v>
       </c>
@@ -6251,7 +6264,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>232</v>
       </c>
@@ -6280,7 +6293,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>235</v>
       </c>
@@ -6309,7 +6322,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>63</v>
       </c>
@@ -6338,7 +6351,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>107</v>
       </c>
@@ -6367,7 +6380,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>190</v>
       </c>
@@ -6375,7 +6388,7 @@
         <v>242</v>
       </c>
       <c r="C102" s="3">
-        <v>4.02</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="D102" s="4">
         <v>43.8</v>
@@ -6396,7 +6409,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>40</v>
       </c>
@@ -6412,7 +6425,7 @@
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3">
-        <v>16.19</v>
+        <v>16.190000000000001</v>
       </c>
       <c r="H103" s="3">
         <v>12.57</v>
@@ -6425,7 +6438,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>13</v>
       </c>
@@ -6454,7 +6467,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>21</v>
       </c>
@@ -6470,7 +6483,7 @@
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3">
-        <v>2.28</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="H105" s="3">
         <v>1.25</v>
@@ -6483,7 +6496,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>13</v>
       </c>
@@ -6512,7 +6525,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>190</v>
       </c>
@@ -6520,10 +6533,10 @@
         <v>252</v>
       </c>
       <c r="C107" s="3">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="D107" s="4">
-        <v>134.89</v>
+        <v>134.88999999999999</v>
       </c>
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
@@ -6541,7 +6554,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>13</v>
       </c>
@@ -6549,7 +6562,7 @@
         <v>254</v>
       </c>
       <c r="C108" s="3">
-        <v>4.11</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="D108" s="4">
         <v>0</v>
@@ -6570,7 +6583,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>35</v>
       </c>
@@ -6599,7 +6612,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>190</v>
       </c>
@@ -6615,7 +6628,7 @@
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
       <c r="G110" s="3">
-        <v>10.05</v>
+        <v>10.050000000000001</v>
       </c>
       <c r="H110" s="3">
         <v>5.83</v>
@@ -6628,7 +6641,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>260</v>
       </c>
@@ -6657,7 +6670,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>190</v>
       </c>
@@ -6686,7 +6699,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>40</v>
       </c>
@@ -6715,7 +6728,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>40</v>
       </c>
@@ -6723,7 +6736,7 @@
         <v>267</v>
       </c>
       <c r="C114" s="3">
-        <v>4.35</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="D114" s="4">
         <v>144.66</v>
@@ -6744,7 +6757,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>43</v>
       </c>
@@ -6752,7 +6765,7 @@
         <v>269</v>
       </c>
       <c r="C115" s="3">
-        <v>4.39</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="D115" s="4">
         <v>4.47</v>
@@ -6773,7 +6786,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>40</v>
       </c>
@@ -6781,7 +6794,7 @@
         <v>271</v>
       </c>
       <c r="C116" s="3">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="D116" s="4">
         <v>12.97</v>
@@ -6802,7 +6815,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>190</v>
       </c>
@@ -6831,7 +6844,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>83</v>
       </c>
@@ -6860,7 +6873,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>277</v>
       </c>
@@ -6889,7 +6902,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>104</v>
       </c>
@@ -6900,7 +6913,7 @@
         <v>4.67</v>
       </c>
       <c r="D120" s="4">
-        <v>4.77</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
@@ -6918,7 +6931,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>107</v>
       </c>
@@ -6947,7 +6960,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>190</v>
       </c>
@@ -6976,7 +6989,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>13</v>
       </c>
@@ -6992,7 +7005,7 @@
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
       <c r="G123" s="3">
-        <v>9.21</v>
+        <v>9.2100000000000009</v>
       </c>
       <c r="H123" s="3">
         <v>7.9</v>
@@ -7005,7 +7018,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>13</v>
       </c>
@@ -7034,7 +7047,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>190</v>
       </c>
@@ -7063,7 +7076,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>158</v>
       </c>
@@ -7082,7 +7095,7 @@
         <v>1.97</v>
       </c>
       <c r="H126" s="3">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="I126" s="3"/>
       <c r="J126" s="3"/>
@@ -7092,7 +7105,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>190</v>
       </c>
@@ -7100,7 +7113,7 @@
         <v>294</v>
       </c>
       <c r="C127" s="3">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="D127" s="4">
         <v>72.56</v>
@@ -7111,7 +7124,7 @@
         <v>0.74</v>
       </c>
       <c r="H127" s="3">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="I127" s="3"/>
       <c r="J127" s="3"/>
@@ -7121,7 +7134,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>88</v>
       </c>
@@ -7132,12 +7145,12 @@
         <v>5.12</v>
       </c>
       <c r="D128" s="4">
-        <v>554.81</v>
+        <v>554.80999999999995</v>
       </c>
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
       <c r="G128" s="3">
-        <v>9.37</v>
+        <v>9.3699999999999992</v>
       </c>
       <c r="H128" s="3">
         <v>7.18</v>
@@ -7150,7 +7163,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>298</v>
       </c>
@@ -7161,7 +7174,7 @@
         <v>5.17</v>
       </c>
       <c r="D129" s="4">
-        <v>69.76</v>
+        <v>69.760000000000005</v>
       </c>
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
@@ -7179,7 +7192,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>225</v>
       </c>
@@ -7208,7 +7221,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>129</v>
       </c>
@@ -7237,7 +7250,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>129</v>
       </c>
@@ -7256,7 +7269,7 @@
         <v>12.27</v>
       </c>
       <c r="H132" s="3">
-        <v>9.55</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="I132" s="3"/>
       <c r="J132" s="3"/>
@@ -7266,7 +7279,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>232</v>
       </c>
@@ -7277,7 +7290,7 @@
         <v>5.31</v>
       </c>
       <c r="D133" s="4">
-        <v>159.73</v>
+        <v>159.72999999999999</v>
       </c>
       <c r="E133" s="3"/>
       <c r="F133" s="3"/>
@@ -7295,7 +7308,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>63</v>
       </c>
@@ -7324,7 +7337,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>13</v>
       </c>
@@ -7353,7 +7366,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>13</v>
       </c>
@@ -7382,7 +7395,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>21</v>
       </c>
@@ -7411,7 +7424,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>21</v>
       </c>
@@ -7440,7 +7453,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>24</v>
       </c>
@@ -7469,7 +7482,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>13</v>
       </c>
@@ -7485,7 +7498,7 @@
       <c r="E140" s="3"/>
       <c r="F140" s="3"/>
       <c r="G140" s="3">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H140" s="3">
         <v>0.04</v>
@@ -7498,7 +7511,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -7509,7 +7522,7 @@
         <v>5.65</v>
       </c>
       <c r="D141" s="4">
-        <v>76.46</v>
+        <v>76.459999999999994</v>
       </c>
       <c r="E141" s="3"/>
       <c r="F141" s="3"/>
@@ -7527,7 +7540,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>13</v>
       </c>
@@ -7556,7 +7569,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>63</v>
       </c>
@@ -7575,7 +7588,7 @@
         <v>1.28</v>
       </c>
       <c r="H143" s="3">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I143" s="3"/>
       <c r="J143" s="3"/>
@@ -7585,7 +7598,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>329</v>
       </c>
@@ -7614,7 +7627,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -7643,7 +7656,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>24</v>
       </c>
@@ -7672,7 +7685,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>88</v>
       </c>
@@ -7701,7 +7714,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>24</v>
       </c>
@@ -7712,7 +7725,7 @@
         <v>5.8</v>
       </c>
       <c r="D148" s="4">
-        <v>142.64</v>
+        <v>142.63999999999999</v>
       </c>
       <c r="E148" s="3"/>
       <c r="F148" s="3"/>
@@ -7730,7 +7743,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>21</v>
       </c>
@@ -7759,7 +7772,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>88</v>
       </c>
@@ -7788,7 +7801,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>40</v>
       </c>
@@ -7799,7 +7812,7 @@
         <v>5.92</v>
       </c>
       <c r="D151" s="4">
-        <v>18.1</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
@@ -7817,7 +7830,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>346</v>
       </c>
@@ -7846,7 +7859,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>349</v>
       </c>
@@ -7875,7 +7888,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>21</v>
       </c>
@@ -7904,7 +7917,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>354</v>
       </c>
@@ -7933,7 +7946,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>21</v>
       </c>
@@ -7962,7 +7975,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>24</v>
       </c>
@@ -7991,7 +8004,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>13</v>
       </c>
@@ -8007,7 +8020,7 @@
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
       <c r="G158" s="3">
-        <v>4.48</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="H158" s="3">
         <v>3.38</v>
@@ -8020,7 +8033,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>99</v>
       </c>
@@ -8049,7 +8062,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>46</v>
       </c>
@@ -8078,7 +8091,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>367</v>
       </c>
@@ -8107,7 +8120,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>83</v>
       </c>
@@ -8136,7 +8149,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>13</v>
       </c>
@@ -8155,7 +8168,7 @@
         <v>4.17</v>
       </c>
       <c r="H163" s="3">
-        <v>2.32</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="I163" s="3"/>
       <c r="J163" s="3"/>
@@ -8165,7 +8178,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>13</v>
       </c>
@@ -8194,7 +8207,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>232</v>
       </c>
@@ -8210,7 +8223,7 @@
       <c r="E165" s="3"/>
       <c r="F165" s="3"/>
       <c r="G165" s="3">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H165" s="3">
         <v>1.79</v>
@@ -8223,7 +8236,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>107</v>
       </c>
@@ -8252,7 +8265,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>72</v>
       </c>
@@ -8271,7 +8284,7 @@
         <v>2.52</v>
       </c>
       <c r="H167" s="3">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="I167" s="3"/>
       <c r="J167" s="3"/>
@@ -8281,7 +8294,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>51</v>
       </c>
@@ -8292,15 +8305,15 @@
         <v>6.5</v>
       </c>
       <c r="D168" s="4">
-        <v>302.78</v>
+        <v>302.77999999999997</v>
       </c>
       <c r="E168" s="3"/>
       <c r="F168" s="3"/>
       <c r="G168" s="3">
-        <v>20.35</v>
+        <v>20.350000000000001</v>
       </c>
       <c r="H168" s="3">
-        <v>20.26</v>
+        <v>20.260000000000002</v>
       </c>
       <c r="I168" s="3"/>
       <c r="J168" s="3"/>
@@ -8310,7 +8323,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>190</v>
       </c>
@@ -8339,7 +8352,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>13</v>
       </c>
@@ -8368,7 +8381,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>298</v>
       </c>
@@ -8384,7 +8397,7 @@
       <c r="E171" s="3"/>
       <c r="F171" s="3"/>
       <c r="G171" s="3">
-        <v>2.03</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="H171" s="3">
         <v>2.13</v>
@@ -8397,7 +8410,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>51</v>
       </c>
@@ -8408,12 +8421,12 @@
         <v>6.57</v>
       </c>
       <c r="D172" s="4">
-        <v>258.79</v>
+        <v>258.79000000000002</v>
       </c>
       <c r="E172" s="3"/>
       <c r="F172" s="3"/>
       <c r="G172" s="3">
-        <v>18.26</v>
+        <v>18.260000000000002</v>
       </c>
       <c r="H172" s="3">
         <v>13.88</v>
@@ -8426,7 +8439,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>88</v>
       </c>
@@ -8442,7 +8455,7 @@
       <c r="E173" s="3"/>
       <c r="F173" s="3"/>
       <c r="G173" s="3">
-        <v>16.15</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="H173" s="3">
         <v>14.37</v>
@@ -8455,7 +8468,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>277</v>
       </c>
@@ -8484,7 +8497,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>40</v>
       </c>
@@ -8513,7 +8526,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>13</v>
       </c>
@@ -8532,7 +8545,7 @@
         <v>-3.55</v>
       </c>
       <c r="H176" s="3">
-        <v>-4.11</v>
+        <v>-4.1100000000000003</v>
       </c>
       <c r="I176" s="3"/>
       <c r="J176" s="3"/>
@@ -8542,7 +8555,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>107</v>
       </c>
@@ -8571,7 +8584,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>225</v>
       </c>
@@ -8600,7 +8613,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>404</v>
       </c>
@@ -8629,7 +8642,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>404</v>
       </c>
@@ -8645,7 +8658,7 @@
       <c r="E180" s="3"/>
       <c r="F180" s="3"/>
       <c r="G180" s="3">
-        <v>2.49</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="H180" s="3">
         <v>0.44</v>
@@ -8658,7 +8671,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>232</v>
       </c>
@@ -8687,7 +8700,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>51</v>
       </c>
@@ -8703,7 +8716,7 @@
       <c r="E182" s="3"/>
       <c r="F182" s="3"/>
       <c r="G182" s="3">
-        <v>2.45</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="H182" s="3">
         <v>-23.09</v>
@@ -8716,7 +8729,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>54</v>
       </c>
@@ -8745,7 +8758,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>13</v>
       </c>
@@ -8774,7 +8787,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>21</v>
       </c>
@@ -8803,7 +8816,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>104</v>
       </c>
@@ -8832,7 +8845,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>225</v>
       </c>
@@ -8861,7 +8874,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>83</v>
       </c>
@@ -8890,7 +8903,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>13</v>
       </c>
@@ -8909,7 +8922,7 @@
         <v>3.23</v>
       </c>
       <c r="H189" s="3">
-        <v>2.07</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="I189" s="3"/>
       <c r="J189" s="3"/>
@@ -8919,7 +8932,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>18</v>
       </c>
@@ -8948,7 +8961,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>43</v>
       </c>
@@ -8977,7 +8990,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>21</v>
       </c>
@@ -9006,7 +9019,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>13</v>
       </c>
@@ -9035,7 +9048,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>107</v>
       </c>
@@ -9064,7 +9077,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>21</v>
       </c>
@@ -9093,7 +9106,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>83</v>
       </c>
@@ -9122,7 +9135,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>13</v>
       </c>
@@ -9133,7 +9146,7 @@
         <v>7.3</v>
       </c>
       <c r="D197" s="4">
-        <v>9.21</v>
+        <v>9.2100000000000009</v>
       </c>
       <c r="E197" s="3"/>
       <c r="F197" s="3"/>
@@ -9151,7 +9164,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>51</v>
       </c>
@@ -9180,7 +9193,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>298</v>
       </c>
@@ -9209,7 +9222,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>225</v>
       </c>
@@ -9238,7 +9251,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>54</v>
       </c>
@@ -9267,7 +9280,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>451</v>
       </c>
@@ -9296,7 +9309,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>107</v>
       </c>
@@ -9325,7 +9338,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>13</v>
       </c>
@@ -9354,7 +9367,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>349</v>
       </c>
@@ -9383,7 +9396,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>13</v>
       </c>
@@ -9412,7 +9425,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>18</v>
       </c>
@@ -9441,7 +9454,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>464</v>
       </c>
@@ -9470,7 +9483,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>88</v>
       </c>
@@ -9499,7 +9512,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>107</v>
       </c>
@@ -9528,7 +9541,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>88</v>
       </c>
@@ -9539,7 +9552,7 @@
         <v>7.75</v>
       </c>
       <c r="D211" s="4">
-        <v>141.55</v>
+        <v>141.55000000000001</v>
       </c>
       <c r="E211" s="3"/>
       <c r="F211" s="3"/>
@@ -9557,7 +9570,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>473</v>
       </c>
@@ -9586,7 +9599,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>51</v>
       </c>
@@ -9615,7 +9628,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>18</v>
       </c>
@@ -9644,7 +9657,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>21</v>
       </c>
@@ -9673,7 +9686,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>451</v>
       </c>
@@ -9702,7 +9715,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>43</v>
       </c>
@@ -9731,7 +9744,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>486</v>
       </c>
@@ -9760,7 +9773,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>35</v>
       </c>
@@ -9768,7 +9781,7 @@
         <v>489</v>
       </c>
       <c r="C219" s="3">
-        <v>8.03</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="D219" s="4">
         <v>102.09</v>
@@ -9789,7 +9802,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>232</v>
       </c>
@@ -9797,7 +9810,7 @@
         <v>491</v>
       </c>
       <c r="C220" s="3">
-        <v>8.04</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="D220" s="4">
         <v>12.82</v>
@@ -9818,7 +9831,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>354</v>
       </c>
@@ -9847,7 +9860,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>13</v>
       </c>
@@ -9876,7 +9889,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>46</v>
       </c>
@@ -9905,7 +9918,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>13</v>
       </c>
@@ -9934,7 +9947,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>54</v>
       </c>
@@ -9963,7 +9976,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>13</v>
       </c>
@@ -9971,7 +9984,7 @@
         <v>503</v>
       </c>
       <c r="C226" s="3">
-        <v>8.13</v>
+        <v>8.1300000000000008</v>
       </c>
       <c r="D226" s="4">
         <v>21.66</v>
@@ -9992,7 +10005,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>24</v>
       </c>
@@ -10021,7 +10034,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>507</v>
       </c>
@@ -10050,7 +10063,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>24</v>
       </c>
@@ -10058,7 +10071,7 @@
         <v>510</v>
       </c>
       <c r="C229" s="3">
-        <v>8.38</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="D229" s="4">
         <v>109.33</v>
@@ -10079,7 +10092,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>404</v>
       </c>
@@ -10090,7 +10103,7 @@
         <v>8.44</v>
       </c>
       <c r="D230" s="4">
-        <v>135.89</v>
+        <v>135.88999999999999</v>
       </c>
       <c r="E230" s="3"/>
       <c r="F230" s="3"/>
@@ -10108,7 +10121,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>18</v>
       </c>
@@ -10116,7 +10129,7 @@
         <v>514</v>
       </c>
       <c r="C231" s="3">
-        <v>8.45</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="D231" s="4">
         <v>145.96</v>
@@ -10124,7 +10137,7 @@
       <c r="E231" s="3"/>
       <c r="F231" s="3"/>
       <c r="G231" s="3">
-        <v>10.22</v>
+        <v>10.220000000000001</v>
       </c>
       <c r="H231" s="3">
         <v>5.66</v>
@@ -10137,7 +10150,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>40</v>
       </c>
@@ -10166,7 +10179,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>518</v>
       </c>
@@ -10174,7 +10187,7 @@
         <v>519</v>
       </c>
       <c r="C233" s="3">
-        <v>8.53</v>
+        <v>8.5299999999999994</v>
       </c>
       <c r="D233" s="4">
         <v>15.1</v>
@@ -10195,7 +10208,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>46</v>
       </c>
@@ -10224,7 +10237,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>232</v>
       </c>
@@ -10253,7 +10266,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>63</v>
       </c>
@@ -10282,7 +10295,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>404</v>
       </c>
@@ -10311,7 +10324,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>21</v>
       </c>
@@ -10319,7 +10332,7 @@
         <v>529</v>
       </c>
       <c r="C238" s="3">
-        <v>8.8</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="D238" s="4">
         <v>45.66</v>
@@ -10340,7 +10353,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>35</v>
       </c>
@@ -10369,7 +10382,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>190</v>
       </c>
@@ -10377,7 +10390,7 @@
         <v>533</v>
       </c>
       <c r="C240" s="3">
-        <v>8.87</v>
+        <v>8.8699999999999992</v>
       </c>
       <c r="D240" s="4">
         <v>38.81</v>
@@ -10398,7 +10411,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>43</v>
       </c>
@@ -10409,7 +10422,7 @@
         <v>8.9</v>
       </c>
       <c r="D241" s="4">
-        <v>1062.36</v>
+        <v>1062.3599999999999</v>
       </c>
       <c r="E241" s="3"/>
       <c r="F241" s="3"/>
@@ -10427,7 +10440,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>35</v>
       </c>
@@ -10456,7 +10469,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>40</v>
       </c>
@@ -10485,7 +10498,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>107</v>
       </c>
@@ -10514,7 +10527,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>18</v>
       </c>
@@ -10522,7 +10535,7 @@
         <v>543</v>
       </c>
       <c r="C245" s="3">
-        <v>9.03</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="D245" s="4">
         <v>243.74</v>
@@ -10543,7 +10556,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>220</v>
       </c>
@@ -10551,7 +10564,7 @@
         <v>545</v>
       </c>
       <c r="C246" s="3">
-        <v>9.04</v>
+        <v>9.0399999999999991</v>
       </c>
       <c r="D246" s="4">
         <v>178.44</v>
@@ -10559,7 +10572,7 @@
       <c r="E246" s="3"/>
       <c r="F246" s="3"/>
       <c r="G246" s="3">
-        <v>20.19</v>
+        <v>20.190000000000001</v>
       </c>
       <c r="H246" s="3">
         <v>20.78</v>
@@ -10572,7 +10585,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>63</v>
       </c>
@@ -10601,7 +10614,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>21</v>
       </c>
@@ -10630,7 +10643,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>40</v>
       </c>
@@ -10641,7 +10654,7 @@
         <v>9.19</v>
       </c>
       <c r="D249" s="4">
-        <v>81.1</v>
+        <v>81.099999999999994</v>
       </c>
       <c r="E249" s="3"/>
       <c r="F249" s="3"/>
@@ -10649,7 +10662,7 @@
         <v>11.36</v>
       </c>
       <c r="H249" s="3">
-        <v>8.21</v>
+        <v>8.2100000000000009</v>
       </c>
       <c r="I249" s="3"/>
       <c r="J249" s="3"/>
@@ -10659,7 +10672,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>63</v>
       </c>
@@ -10667,10 +10680,10 @@
         <v>553</v>
       </c>
       <c r="C250" s="3">
-        <v>9.2</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D250" s="4">
-        <v>4.65</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="E250" s="3"/>
       <c r="F250" s="3"/>
@@ -10688,7 +10701,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>555</v>
       </c>
@@ -10696,7 +10709,7 @@
         <v>556</v>
       </c>
       <c r="C251" s="3">
-        <v>9.3</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="D251" s="4">
         <v>1419.27</v>
@@ -10717,7 +10730,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>54</v>
       </c>
@@ -10746,7 +10759,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>13</v>
       </c>
@@ -10775,7 +10788,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>83</v>
       </c>
@@ -10794,7 +10807,7 @@
         <v>1.99</v>
       </c>
       <c r="H254" s="3">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="I254" s="3"/>
       <c r="J254" s="3"/>
@@ -10804,7 +10817,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>21</v>
       </c>
@@ -10812,7 +10825,7 @@
         <v>564</v>
       </c>
       <c r="C255" s="3">
-        <v>9.45</v>
+        <v>9.4499999999999993</v>
       </c>
       <c r="D255" s="4">
         <v>12.86</v>
@@ -10833,7 +10846,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>107</v>
       </c>
@@ -10862,7 +10875,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>88</v>
       </c>
@@ -10891,7 +10904,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>129</v>
       </c>
@@ -10920,7 +10933,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>40</v>
       </c>
@@ -10949,7 +10962,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>104</v>
       </c>
@@ -10978,7 +10991,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>464</v>
       </c>
@@ -10986,7 +10999,7 @@
         <v>576</v>
       </c>
       <c r="C261" s="3">
-        <v>9.79</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="D261" s="4">
         <v>34.1</v>
@@ -11007,7 +11020,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>24</v>
       </c>
@@ -11015,7 +11028,7 @@
         <v>578</v>
       </c>
       <c r="C262" s="3">
-        <v>9.8</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="D262" s="4">
         <v>238.09</v>
@@ -11036,7 +11049,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>21</v>
       </c>
@@ -11044,10 +11057,10 @@
         <v>580</v>
       </c>
       <c r="C263" s="3">
-        <v>9.8</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="D263" s="4">
-        <v>17.67</v>
+        <v>17.670000000000002</v>
       </c>
       <c r="E263" s="3"/>
       <c r="F263" s="3"/>
@@ -11065,7 +11078,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>46</v>
       </c>
@@ -11073,7 +11086,7 @@
         <v>582</v>
       </c>
       <c r="C264" s="3">
-        <v>9.95</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="D264" s="4">
         <v>5.25</v>
@@ -11084,7 +11097,7 @@
         <v>8.6</v>
       </c>
       <c r="H264" s="3">
-        <v>9.78</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="I264" s="3"/>
       <c r="J264" s="3"/>
@@ -11094,7 +11107,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>24</v>
       </c>
@@ -11123,7 +11136,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>190</v>
       </c>
@@ -11134,7 +11147,7 @@
         <v>10</v>
       </c>
       <c r="D266" s="4">
-        <v>131.14</v>
+        <v>131.13999999999999</v>
       </c>
       <c r="E266" s="3"/>
       <c r="F266" s="3"/>
@@ -11152,7 +11165,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>35</v>
       </c>
@@ -11160,7 +11173,7 @@
         <v>588</v>
       </c>
       <c r="C267" s="3">
-        <v>10.12</v>
+        <v>10.119999999999999</v>
       </c>
       <c r="D267" s="4">
         <v>1515.75</v>
@@ -11181,7 +11194,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>104</v>
       </c>
@@ -11189,7 +11202,7 @@
         <v>590</v>
       </c>
       <c r="C268" s="3">
-        <v>10.12</v>
+        <v>10.119999999999999</v>
       </c>
       <c r="D268" s="4">
         <v>7.08</v>
@@ -11210,7 +11223,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>24</v>
       </c>
@@ -11239,7 +11252,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>21</v>
       </c>
@@ -11268,7 +11281,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>18</v>
       </c>
@@ -11297,7 +11310,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>83</v>
       </c>
@@ -11326,7 +11339,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>63</v>
       </c>
@@ -11355,7 +11368,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>13</v>
       </c>
@@ -11384,7 +11397,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>451</v>
       </c>
@@ -11413,7 +11426,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>464</v>
       </c>
@@ -11442,7 +11455,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>349</v>
       </c>
@@ -11471,7 +11484,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>13</v>
       </c>
@@ -11500,7 +11513,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>83</v>
       </c>
@@ -11516,7 +11529,7 @@
       <c r="E279" s="3"/>
       <c r="F279" s="3"/>
       <c r="G279" s="3">
-        <v>17.51</v>
+        <v>17.510000000000002</v>
       </c>
       <c r="H279" s="3">
         <v>20.54</v>
@@ -11529,7 +11542,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>21</v>
       </c>
@@ -11558,7 +11571,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>54</v>
       </c>
@@ -11587,7 +11600,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>13</v>
       </c>
@@ -11616,7 +11629,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>83</v>
       </c>
@@ -11627,7 +11640,7 @@
         <v>10.98</v>
       </c>
       <c r="D283" s="4">
-        <v>80.21</v>
+        <v>80.209999999999994</v>
       </c>
       <c r="E283" s="3"/>
       <c r="F283" s="3"/>
@@ -11645,7 +11658,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>99</v>
       </c>
@@ -11674,7 +11687,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>107</v>
       </c>
@@ -11690,7 +11703,7 @@
       <c r="E285" s="3"/>
       <c r="F285" s="3"/>
       <c r="G285" s="3">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="H285" s="3">
         <v>1.82</v>
@@ -11703,7 +11716,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>35</v>
       </c>
@@ -11732,7 +11745,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>35</v>
       </c>
@@ -11761,7 +11774,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>83</v>
       </c>
@@ -11790,7 +11803,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>51</v>
       </c>
@@ -11819,7 +11832,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>235</v>
       </c>
@@ -11835,7 +11848,7 @@
       <c r="E290" s="3"/>
       <c r="F290" s="3"/>
       <c r="G290" s="3">
-        <v>32.12</v>
+        <v>32.119999999999997</v>
       </c>
       <c r="H290" s="3">
         <v>16.82</v>
@@ -11848,7 +11861,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>190</v>
       </c>
@@ -11864,7 +11877,7 @@
       <c r="E291" s="3"/>
       <c r="F291" s="3"/>
       <c r="G291" s="3">
-        <v>8.8</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="H291" s="3">
         <v>2.65</v>
@@ -11877,7 +11890,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>13</v>
       </c>
@@ -11906,7 +11919,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>13</v>
       </c>
@@ -11935,7 +11948,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>21</v>
       </c>
@@ -11964,7 +11977,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>21</v>
       </c>
@@ -11993,7 +12006,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>13</v>
       </c>
@@ -12004,7 +12017,7 @@
         <v>11.52</v>
       </c>
       <c r="D296" s="4">
-        <v>4.77</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="E296" s="3"/>
       <c r="F296" s="3"/>
@@ -12022,7 +12035,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>648</v>
       </c>
@@ -12051,7 +12064,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>43</v>
       </c>
@@ -12080,7 +12093,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>35</v>
       </c>
@@ -12091,7 +12104,7 @@
         <v>11.6</v>
       </c>
       <c r="D299" s="4">
-        <v>16.81</v>
+        <v>16.809999999999999</v>
       </c>
       <c r="E299" s="3"/>
       <c r="F299" s="3"/>
@@ -12109,7 +12122,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>451</v>
       </c>
@@ -12125,7 +12138,7 @@
       <c r="E300" s="3"/>
       <c r="F300" s="3"/>
       <c r="G300" s="3">
-        <v>2.49</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="H300" s="3">
         <v>0.02</v>
@@ -12138,7 +12151,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>104</v>
       </c>
@@ -12167,7 +12180,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>46</v>
       </c>
@@ -12183,7 +12196,7 @@
       <c r="E302" s="3"/>
       <c r="F302" s="3"/>
       <c r="G302" s="3">
-        <v>-9.63</v>
+        <v>-9.6300000000000008</v>
       </c>
       <c r="H302" s="3">
         <v>-14</v>
@@ -12196,7 +12209,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>298</v>
       </c>
@@ -12225,7 +12238,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>107</v>
       </c>
@@ -12254,7 +12267,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>13</v>
       </c>
@@ -12283,7 +12296,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>104</v>
       </c>
@@ -12312,7 +12325,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>669</v>
       </c>
@@ -12341,7 +12354,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>43</v>
       </c>
@@ -12370,7 +12383,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>190</v>
       </c>
@@ -12399,7 +12412,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>88</v>
       </c>
@@ -12428,7 +12441,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>40</v>
       </c>
@@ -12457,7 +12470,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>13</v>
       </c>
@@ -12486,7 +12499,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>260</v>
       </c>
@@ -12497,7 +12510,7 @@
         <v>12.45</v>
       </c>
       <c r="D313" s="4">
-        <v>75.49</v>
+        <v>75.489999999999995</v>
       </c>
       <c r="E313" s="3"/>
       <c r="F313" s="3"/>
@@ -12515,7 +12528,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>158</v>
       </c>
@@ -12544,7 +12557,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>54</v>
       </c>
@@ -12555,12 +12568,12 @@
         <v>12.64</v>
       </c>
       <c r="D315" s="4">
-        <v>136945.6</v>
+        <v>136945.60000000001</v>
       </c>
       <c r="E315" s="3"/>
       <c r="F315" s="3"/>
       <c r="G315" s="3">
-        <v>-1.1</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="H315" s="3">
         <v>-38.85</v>
@@ -12573,7 +12586,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>104</v>
       </c>
@@ -12602,7 +12615,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>225</v>
       </c>
@@ -12631,7 +12644,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>104</v>
       </c>
@@ -12660,7 +12673,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>190</v>
       </c>
@@ -12689,7 +12702,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>51</v>
       </c>
@@ -12718,7 +12731,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>486</v>
       </c>
@@ -12734,10 +12747,10 @@
       <c r="E321" s="3"/>
       <c r="F321" s="3"/>
       <c r="G321" s="3">
-        <v>9.55</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="H321" s="3">
-        <v>9.95</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="I321" s="3"/>
       <c r="J321" s="3"/>
@@ -12747,7 +12760,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>232</v>
       </c>
@@ -12776,7 +12789,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>104</v>
       </c>
@@ -12805,7 +12818,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>107</v>
       </c>
@@ -12834,7 +12847,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>706</v>
       </c>
@@ -12863,7 +12876,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>83</v>
       </c>
@@ -12879,7 +12892,7 @@
       <c r="E326" s="3"/>
       <c r="F326" s="3"/>
       <c r="G326" s="3">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="H326" s="3">
         <v>0.09</v>
@@ -12892,7 +12905,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>88</v>
       </c>
@@ -12921,7 +12934,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>107</v>
       </c>
@@ -12937,7 +12950,7 @@
       <c r="E328" s="3"/>
       <c r="F328" s="3"/>
       <c r="G328" s="3">
-        <v>4.89</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="H328" s="3">
         <v>4.16</v>
@@ -12950,7 +12963,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>277</v>
       </c>
@@ -12979,7 +12992,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>40</v>
       </c>
@@ -13008,7 +13021,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>225</v>
       </c>
@@ -13037,7 +13050,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>13</v>
       </c>
@@ -13066,7 +13079,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>35</v>
       </c>
@@ -13095,7 +13108,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>88</v>
       </c>
@@ -13124,7 +13137,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>727</v>
       </c>
@@ -13153,7 +13166,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>99</v>
       </c>
@@ -13182,7 +13195,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>732</v>
       </c>
@@ -13211,7 +13224,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>114</v>
       </c>
@@ -13240,7 +13253,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>158</v>
       </c>
@@ -13259,7 +13272,7 @@
         <v>4.03</v>
       </c>
       <c r="H339" s="3">
-        <v>-2.55</v>
+        <v>-2.5499999999999998</v>
       </c>
       <c r="I339" s="3"/>
       <c r="J339" s="3"/>
@@ -13269,7 +13282,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>225</v>
       </c>
@@ -13288,7 +13301,7 @@
         <v>6.13</v>
       </c>
       <c r="H340" s="3">
-        <v>4.02</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="I340" s="3"/>
       <c r="J340" s="3"/>
@@ -13298,7 +13311,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>232</v>
       </c>
@@ -13309,7 +13322,7 @@
         <v>13.5</v>
       </c>
       <c r="D341" s="4">
-        <v>32.52</v>
+        <v>32.520000000000003</v>
       </c>
       <c r="E341" s="3"/>
       <c r="F341" s="3"/>
@@ -13327,7 +13340,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>21</v>
       </c>
@@ -13356,7 +13369,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>13</v>
       </c>
@@ -13367,7 +13380,7 @@
         <v>13.63</v>
       </c>
       <c r="D343" s="4">
-        <v>78.29</v>
+        <v>78.290000000000006</v>
       </c>
       <c r="E343" s="3"/>
       <c r="F343" s="3"/>
@@ -13385,7 +13398,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>40</v>
       </c>
@@ -13414,7 +13427,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>54</v>
       </c>
@@ -13443,7 +13456,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>13</v>
       </c>
@@ -13454,7 +13467,7 @@
         <v>13.8</v>
       </c>
       <c r="D346" s="4">
-        <v>16.56</v>
+        <v>16.559999999999999</v>
       </c>
       <c r="E346" s="3"/>
       <c r="F346" s="3"/>
@@ -13472,7 +13485,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>18</v>
       </c>
@@ -13488,7 +13501,7 @@
       <c r="E347" s="3"/>
       <c r="F347" s="3"/>
       <c r="G347" s="3">
-        <v>157.33</v>
+        <v>157.33000000000001</v>
       </c>
       <c r="H347" s="3">
         <v>151.44</v>
@@ -13501,7 +13514,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>46</v>
       </c>
@@ -13512,7 +13525,7 @@
         <v>13.86</v>
       </c>
       <c r="D348" s="4">
-        <v>16.56</v>
+        <v>16.559999999999999</v>
       </c>
       <c r="E348" s="3"/>
       <c r="F348" s="3"/>
@@ -13530,7 +13543,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>404</v>
       </c>
@@ -13546,7 +13559,7 @@
       <c r="E349" s="3"/>
       <c r="F349" s="3"/>
       <c r="G349" s="3">
-        <v>0.07</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="H349" s="3">
         <v>0.34</v>
@@ -13559,7 +13572,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>46</v>
       </c>
@@ -13575,7 +13588,7 @@
       <c r="E350" s="3"/>
       <c r="F350" s="3"/>
       <c r="G350" s="3">
-        <v>8.38</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="H350" s="3">
         <v>8.41</v>
@@ -13588,7 +13601,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>107</v>
       </c>
@@ -13617,7 +13630,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>13</v>
       </c>
@@ -13628,7 +13641,7 @@
         <v>14.25</v>
       </c>
       <c r="D352" s="4">
-        <v>16.67</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="E352" s="3"/>
       <c r="F352" s="3"/>
@@ -13646,7 +13659,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>43</v>
       </c>
@@ -13657,12 +13670,12 @@
         <v>14.25</v>
       </c>
       <c r="D353" s="4">
-        <v>9.88</v>
+        <v>9.8800000000000008</v>
       </c>
       <c r="E353" s="3"/>
       <c r="F353" s="3"/>
       <c r="G353" s="3">
-        <v>9.29</v>
+        <v>9.2899999999999991</v>
       </c>
       <c r="H353" s="3">
         <v>4.53</v>
@@ -13675,7 +13688,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>51</v>
       </c>
@@ -13704,7 +13717,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>46</v>
       </c>
@@ -13733,7 +13746,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>83</v>
       </c>
@@ -13762,7 +13775,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>83</v>
       </c>
@@ -13791,7 +13804,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>35</v>
       </c>
@@ -13820,7 +13833,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>404</v>
       </c>
@@ -13849,7 +13862,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>43</v>
       </c>
@@ -13878,7 +13891,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>232</v>
       </c>
@@ -13907,7 +13920,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>235</v>
       </c>
@@ -13936,7 +13949,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>99</v>
       </c>
@@ -13965,7 +13978,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>24</v>
       </c>
@@ -13981,10 +13994,10 @@
       <c r="E364" s="3"/>
       <c r="F364" s="3"/>
       <c r="G364" s="3">
-        <v>2.28</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="H364" s="3">
-        <v>2.07</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="I364" s="3"/>
       <c r="J364" s="3"/>
@@ -13994,7 +14007,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>13</v>
       </c>
@@ -14023,7 +14036,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>88</v>
       </c>
@@ -14052,7 +14065,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>404</v>
       </c>
@@ -14063,7 +14076,7 @@
         <v>14.8</v>
       </c>
       <c r="D367" s="4">
-        <v>10143.12</v>
+        <v>10143.120000000001</v>
       </c>
       <c r="E367" s="3"/>
       <c r="F367" s="3"/>
@@ -14081,7 +14094,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>232</v>
       </c>
@@ -14110,7 +14123,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>104</v>
       </c>
@@ -14139,7 +14152,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>13</v>
       </c>
@@ -14155,7 +14168,7 @@
       <c r="E370" s="3"/>
       <c r="F370" s="3"/>
       <c r="G370" s="3">
-        <v>-0.58</v>
+        <v>-0.57999999999999996</v>
       </c>
       <c r="H370" s="3">
         <v>-0.69</v>
@@ -14168,7 +14181,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>13</v>
       </c>
@@ -14197,7 +14210,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>83</v>
       </c>
@@ -14226,7 +14239,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>13</v>
       </c>
@@ -14255,7 +14268,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>35</v>
       </c>
@@ -14284,7 +14297,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>88</v>
       </c>
@@ -14295,7 +14308,7 @@
         <v>15.25</v>
       </c>
       <c r="D375" s="4">
-        <v>132.92</v>
+        <v>132.91999999999999</v>
       </c>
       <c r="E375" s="3"/>
       <c r="F375" s="3"/>
@@ -14313,7 +14326,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>88</v>
       </c>
@@ -14342,7 +14355,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>43</v>
       </c>
@@ -14361,7 +14374,7 @@
         <v>12.97</v>
       </c>
       <c r="H377" s="3">
-        <v>9.71</v>
+        <v>9.7100000000000009</v>
       </c>
       <c r="I377" s="3"/>
       <c r="J377" s="3"/>
@@ -14371,7 +14384,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>232</v>
       </c>
@@ -14400,7 +14413,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>21</v>
       </c>
@@ -14429,7 +14442,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>21</v>
       </c>
@@ -14458,7 +14471,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>21</v>
       </c>
@@ -14469,7 +14482,7 @@
         <v>15.55</v>
       </c>
       <c r="D381" s="4">
-        <v>19.42</v>
+        <v>19.420000000000002</v>
       </c>
       <c r="E381" s="3"/>
       <c r="F381" s="3"/>
@@ -14487,7 +14500,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>21</v>
       </c>
@@ -14516,7 +14529,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>51</v>
       </c>
@@ -14527,7 +14540,7 @@
         <v>15.56</v>
       </c>
       <c r="D383" s="4">
-        <v>163.33</v>
+        <v>163.33000000000001</v>
       </c>
       <c r="E383" s="3"/>
       <c r="F383" s="3"/>
@@ -14545,7 +14558,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>88</v>
       </c>
@@ -14574,7 +14587,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>46</v>
       </c>
@@ -14593,7 +14606,7 @@
         <v>-0.6</v>
       </c>
       <c r="H385" s="3">
-        <v>-2.51</v>
+        <v>-2.5099999999999998</v>
       </c>
       <c r="I385" s="3"/>
       <c r="J385" s="3"/>
@@ -14603,7 +14616,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>107</v>
       </c>
@@ -14622,7 +14635,7 @@
         <v>19.7</v>
       </c>
       <c r="H386" s="3">
-        <v>17.42</v>
+        <v>17.420000000000002</v>
       </c>
       <c r="I386" s="3"/>
       <c r="J386" s="3"/>
@@ -14632,7 +14645,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>46</v>
       </c>
@@ -14661,7 +14674,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>18</v>
       </c>
@@ -14690,7 +14703,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>837</v>
       </c>
@@ -14719,7 +14732,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>404</v>
       </c>
@@ -14748,7 +14761,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>51</v>
       </c>
@@ -14777,7 +14790,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>129</v>
       </c>
@@ -14785,7 +14798,7 @@
         <v>844</v>
       </c>
       <c r="C392" s="3">
-        <v>16.1</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="D392" s="4">
         <v>9.43</v>
@@ -14806,7 +14819,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>232</v>
       </c>
@@ -14822,7 +14835,7 @@
       <c r="E393" s="3"/>
       <c r="F393" s="3"/>
       <c r="G393" s="3">
-        <v>8.63</v>
+        <v>8.6300000000000008</v>
       </c>
       <c r="H393" s="3">
         <v>4.74</v>
@@ -14835,7 +14848,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>129</v>
       </c>
@@ -14843,10 +14856,10 @@
         <v>848</v>
       </c>
       <c r="C394" s="3">
-        <v>16.17</v>
+        <v>16.170000000000002</v>
       </c>
       <c r="D394" s="4">
-        <v>17.6</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="E394" s="3"/>
       <c r="F394" s="3"/>
@@ -14854,7 +14867,7 @@
         <v>-0.06</v>
       </c>
       <c r="H394" s="3">
-        <v>-1.15</v>
+        <v>-1.1499999999999999</v>
       </c>
       <c r="I394" s="3"/>
       <c r="J394" s="3"/>
@@ -14864,7 +14877,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>72</v>
       </c>
@@ -14883,7 +14896,7 @@
         <v>6.92</v>
       </c>
       <c r="H395" s="3">
-        <v>4.35</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="I395" s="3"/>
       <c r="J395" s="3"/>
@@ -14893,7 +14906,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>404</v>
       </c>
@@ -14901,10 +14914,10 @@
         <v>852</v>
       </c>
       <c r="C396" s="3">
-        <v>16.19</v>
+        <v>16.190000000000001</v>
       </c>
       <c r="D396" s="4">
-        <v>160.2</v>
+        <v>160.19999999999999</v>
       </c>
       <c r="E396" s="3"/>
       <c r="F396" s="3"/>
@@ -14922,7 +14935,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>298</v>
       </c>
@@ -14951,7 +14964,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>464</v>
       </c>
@@ -14980,7 +14993,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>43</v>
       </c>
@@ -15009,7 +15022,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>190</v>
       </c>
@@ -15038,7 +15051,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>35</v>
       </c>
@@ -15046,7 +15059,7 @@
         <v>862</v>
       </c>
       <c r="C401" s="3">
-        <v>16.81</v>
+        <v>16.809999999999999</v>
       </c>
       <c r="D401" s="4">
         <v>19.45</v>
@@ -15067,7 +15080,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>21</v>
       </c>
@@ -15096,7 +15109,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>104</v>
       </c>
@@ -15125,7 +15138,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>158</v>
       </c>
@@ -15136,7 +15149,7 @@
         <v>17</v>
       </c>
       <c r="D404" s="4">
-        <v>20532.6</v>
+        <v>20532.599999999999</v>
       </c>
       <c r="E404" s="3"/>
       <c r="F404" s="3"/>
@@ -15154,7 +15167,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>99</v>
       </c>
@@ -15183,7 +15196,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="406" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>129</v>
       </c>
@@ -15212,7 +15225,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>232</v>
       </c>
@@ -15241,7 +15254,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>107</v>
       </c>
@@ -15270,7 +15283,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>24</v>
       </c>
@@ -15286,7 +15299,7 @@
       <c r="E409" s="3"/>
       <c r="F409" s="3"/>
       <c r="G409" s="3">
-        <v>9.37</v>
+        <v>9.3699999999999992</v>
       </c>
       <c r="H409" s="3">
         <v>6.05</v>
@@ -15299,7 +15312,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>13</v>
       </c>
@@ -15315,10 +15328,10 @@
       <c r="E410" s="3"/>
       <c r="F410" s="3"/>
       <c r="G410" s="3">
-        <v>-2.22</v>
+        <v>-2.2200000000000002</v>
       </c>
       <c r="H410" s="3">
-        <v>-2.51</v>
+        <v>-2.5099999999999998</v>
       </c>
       <c r="I410" s="3"/>
       <c r="J410" s="3"/>
@@ -15328,7 +15341,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>35</v>
       </c>
@@ -15344,7 +15357,7 @@
       <c r="E411" s="3"/>
       <c r="F411" s="3"/>
       <c r="G411" s="3">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H411" s="3">
         <v>-0.24</v>
@@ -15357,7 +15370,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>260</v>
       </c>
@@ -15365,7 +15378,7 @@
         <v>884</v>
       </c>
       <c r="C412" s="3">
-        <v>17.24</v>
+        <v>17.239999999999998</v>
       </c>
       <c r="D412" s="4">
         <v>41.38</v>
@@ -15386,7 +15399,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>104</v>
       </c>
@@ -15415,7 +15428,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>40</v>
       </c>
@@ -15444,7 +15457,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>99</v>
       </c>
@@ -15473,7 +15486,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>183</v>
       </c>
@@ -15502,7 +15515,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>18</v>
       </c>
@@ -15518,7 +15531,7 @@
       <c r="E417" s="3"/>
       <c r="F417" s="3"/>
       <c r="G417" s="3">
-        <v>9.97</v>
+        <v>9.9700000000000006</v>
       </c>
       <c r="H417" s="3">
         <v>5.79</v>
@@ -15531,7 +15544,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>896</v>
       </c>
@@ -15560,7 +15573,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>225</v>
       </c>
@@ -15568,7 +15581,7 @@
         <v>899</v>
       </c>
       <c r="C419" s="3">
-        <v>17.58</v>
+        <v>17.579999999999998</v>
       </c>
       <c r="D419" s="4">
         <v>208.94</v>
@@ -15589,7 +15602,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>107</v>
       </c>
@@ -15597,7 +15610,7 @@
         <v>901</v>
       </c>
       <c r="C420" s="3">
-        <v>17.6</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="D420" s="4">
         <v>15.41</v>
@@ -15618,7 +15631,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>51</v>
       </c>
@@ -15634,7 +15647,7 @@
       <c r="E421" s="3"/>
       <c r="F421" s="3"/>
       <c r="G421" s="3">
-        <v>8.2</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="H421" s="3">
         <v>6.75</v>
@@ -15647,7 +15660,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>464</v>
       </c>
@@ -15658,7 +15671,7 @@
         <v>17.7</v>
       </c>
       <c r="D422" s="4">
-        <v>16.85</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="E422" s="3"/>
       <c r="F422" s="3"/>
@@ -15676,7 +15689,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>88</v>
       </c>
@@ -15684,7 +15697,7 @@
         <v>907</v>
       </c>
       <c r="C423" s="3">
-        <v>17.76</v>
+        <v>17.760000000000002</v>
       </c>
       <c r="D423" s="4">
         <v>140.38</v>
@@ -15705,7 +15718,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="424" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>83</v>
       </c>
@@ -15734,7 +15747,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="425" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>107</v>
       </c>
@@ -15745,7 +15758,7 @@
         <v>17.8</v>
       </c>
       <c r="D425" s="4">
-        <v>36.09</v>
+        <v>36.090000000000003</v>
       </c>
       <c r="E425" s="3"/>
       <c r="F425" s="3"/>
@@ -15763,7 +15776,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="426" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>486</v>
       </c>
@@ -15792,7 +15805,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>232</v>
       </c>
@@ -15800,7 +15813,7 @@
         <v>915</v>
       </c>
       <c r="C427" s="3">
-        <v>17.9</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="D427" s="4">
         <v>77.94</v>
@@ -15821,7 +15834,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="428" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>83</v>
       </c>
@@ -15829,10 +15842,10 @@
         <v>917</v>
       </c>
       <c r="C428" s="3">
-        <v>17.9</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="D428" s="4">
-        <v>16.31</v>
+        <v>16.309999999999999</v>
       </c>
       <c r="E428" s="3"/>
       <c r="F428" s="3"/>
@@ -15850,7 +15863,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="429" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>158</v>
       </c>
@@ -15858,7 +15871,7 @@
         <v>919</v>
       </c>
       <c r="C429" s="3">
-        <v>17.94</v>
+        <v>17.940000000000001</v>
       </c>
       <c r="D429" s="4">
         <v>485.51</v>
@@ -15869,7 +15882,7 @@
         <v>6.06</v>
       </c>
       <c r="H429" s="3">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I429" s="3"/>
       <c r="J429" s="3"/>
@@ -15879,7 +15892,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="430" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>21</v>
       </c>
@@ -15908,7 +15921,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="431" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>21</v>
       </c>
@@ -15937,7 +15950,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="432" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>21</v>
       </c>
@@ -15966,7 +15979,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="433" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>232</v>
       </c>
@@ -15995,7 +16008,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="434" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>220</v>
       </c>
@@ -16011,7 +16024,7 @@
       <c r="E434" s="3"/>
       <c r="F434" s="3"/>
       <c r="G434" s="3">
-        <v>18.06</v>
+        <v>18.059999999999999</v>
       </c>
       <c r="H434" s="3">
         <v>13.23</v>
@@ -16024,7 +16037,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="435" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>129</v>
       </c>
@@ -16053,7 +16066,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="436" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>190</v>
       </c>
@@ -16082,7 +16095,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="437" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>13</v>
       </c>
@@ -16101,7 +16114,7 @@
         <v>3.07</v>
       </c>
       <c r="H437" s="3">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="I437" s="3"/>
       <c r="J437" s="3"/>
@@ -16111,7 +16124,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="438" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>107</v>
       </c>
@@ -16122,7 +16135,7 @@
         <v>18.27</v>
       </c>
       <c r="D438" s="4">
-        <v>34.13</v>
+        <v>34.130000000000003</v>
       </c>
       <c r="E438" s="3"/>
       <c r="F438" s="3"/>
@@ -16140,7 +16153,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="439" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>939</v>
       </c>
@@ -16169,7 +16182,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="440" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>107</v>
       </c>
@@ -16177,7 +16190,7 @@
         <v>942</v>
       </c>
       <c r="C440" s="3">
-        <v>18.31</v>
+        <v>18.309999999999999</v>
       </c>
       <c r="D440" s="4">
         <v>77.94</v>
@@ -16185,7 +16198,7 @@
       <c r="E440" s="3"/>
       <c r="F440" s="3"/>
       <c r="G440" s="3">
-        <v>9.03</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="H440" s="3">
         <v>10.07</v>
@@ -16198,7 +16211,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="441" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>51</v>
       </c>
@@ -16227,7 +16240,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="442" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>43</v>
       </c>
@@ -16235,7 +16248,7 @@
         <v>946</v>
       </c>
       <c r="C442" s="3">
-        <v>18.4</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="D442" s="4">
         <v>43.06</v>
@@ -16256,7 +16269,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="443" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>232</v>
       </c>
@@ -16264,7 +16277,7 @@
         <v>948</v>
       </c>
       <c r="C443" s="3">
-        <v>18.4</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="D443" s="4">
         <v>21.05</v>
@@ -16285,7 +16298,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="444" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>35</v>
       </c>
@@ -16314,7 +16327,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="445" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>21</v>
       </c>
@@ -16343,7 +16356,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="446" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>46</v>
       </c>
@@ -16372,7 +16385,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="447" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>464</v>
       </c>
@@ -16401,7 +16414,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="448" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>107</v>
       </c>
@@ -16430,7 +16443,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="449" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>24</v>
       </c>
@@ -16446,7 +16459,7 @@
       <c r="E449" s="3"/>
       <c r="F449" s="3"/>
       <c r="G449" s="3">
-        <v>20.08</v>
+        <v>20.079999999999998</v>
       </c>
       <c r="H449" s="3">
         <v>17.63</v>
@@ -16459,7 +16472,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="450" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>40</v>
       </c>
@@ -16467,7 +16480,7 @@
         <v>962</v>
       </c>
       <c r="C450" s="3">
-        <v>18.76</v>
+        <v>18.760000000000002</v>
       </c>
       <c r="D450" s="4">
         <v>89.02</v>
@@ -16488,7 +16501,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="451" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>939</v>
       </c>
@@ -16517,7 +16530,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="452" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>190</v>
       </c>
@@ -16546,7 +16559,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="453" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>968</v>
       </c>
@@ -16554,10 +16567,10 @@
         <v>969</v>
       </c>
       <c r="C453" s="3">
-        <v>19.19</v>
+        <v>19.190000000000001</v>
       </c>
       <c r="D453" s="4">
-        <v>4587.69</v>
+        <v>4587.6899999999996</v>
       </c>
       <c r="E453" s="3"/>
       <c r="F453" s="3"/>
@@ -16565,7 +16578,7 @@
         <v>2.15</v>
       </c>
       <c r="H453" s="3">
-        <v>4.64</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="I453" s="3"/>
       <c r="J453" s="3"/>
@@ -16575,7 +16588,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="454" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>18</v>
       </c>
@@ -16594,7 +16607,7 @@
         <v>7.98</v>
       </c>
       <c r="H454" s="3">
-        <v>5.02</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="I454" s="3"/>
       <c r="J454" s="3"/>
@@ -16604,7 +16617,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="455" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>88</v>
       </c>
@@ -16615,7 +16628,7 @@
         <v>19.34</v>
       </c>
       <c r="D455" s="4">
-        <v>1090.16</v>
+        <v>1090.1600000000001</v>
       </c>
       <c r="E455" s="3"/>
       <c r="F455" s="3"/>
@@ -16633,7 +16646,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="456" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>404</v>
       </c>
@@ -16662,7 +16675,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="457" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>35</v>
       </c>
@@ -16681,7 +16694,7 @@
         <v>13.31</v>
       </c>
       <c r="H457" s="3">
-        <v>9.79</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="I457" s="3"/>
       <c r="J457" s="3"/>
@@ -16691,7 +16704,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="458" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>107</v>
       </c>
@@ -16699,10 +16712,10 @@
         <v>979</v>
       </c>
       <c r="C458" s="3">
-        <v>19.6</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="D458" s="4">
-        <v>145.52</v>
+        <v>145.52000000000001</v>
       </c>
       <c r="E458" s="3"/>
       <c r="F458" s="3"/>
@@ -16720,7 +16733,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="459" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>107</v>
       </c>
@@ -16731,7 +16744,7 @@
         <v>19.8</v>
       </c>
       <c r="D459" s="4">
-        <v>38.55</v>
+        <v>38.549999999999997</v>
       </c>
       <c r="E459" s="3"/>
       <c r="F459" s="3"/>
@@ -16749,7 +16762,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="460" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>88</v>
       </c>
@@ -16778,7 +16791,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="461" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>329</v>
       </c>
@@ -16786,7 +16799,7 @@
         <v>985</v>
       </c>
       <c r="C461" s="3">
-        <v>19.9</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="D461" s="4">
         <v>968.79</v>
@@ -16794,7 +16807,7 @@
       <c r="E461" s="3"/>
       <c r="F461" s="3"/>
       <c r="G461" s="3">
-        <v>4.31</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="H461" s="3">
         <v>-25.92</v>
@@ -16808,938 +16821,938 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1"/>
+  <autoFilter ref="A1:M1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" tooltip="https://www.indmoney.com/stocks/bengal-steel-industries-ltd-share-price"/>
-    <hyperlink ref="M2" r:id="rId2" tooltip="https://www.indmoney.com/stocks/bengal-steel-industries-ltd-share-price"/>
-    <hyperlink ref="B3" r:id="rId3" tooltip="https://www.indmoney.com/stocks/dharan-infra-epc-ltd-share-price"/>
-    <hyperlink ref="M3" r:id="rId4" tooltip="https://www.indmoney.com/stocks/dharan-infra-epc-ltd-share-price"/>
-    <hyperlink ref="B4" r:id="rId5" tooltip="https://www.indmoney.com/stocks/filatex-fashions-ltd-share-price"/>
-    <hyperlink ref="M4" r:id="rId6" tooltip="https://www.indmoney.com/stocks/filatex-fashions-ltd-share-price"/>
-    <hyperlink ref="B5" r:id="rId7" tooltip="https://www.indmoney.com/stocks/thinkink-picturez-ltd-share-price"/>
-    <hyperlink ref="M5" r:id="rId8" tooltip="https://www.indmoney.com/stocks/thinkink-picturez-ltd-share-price"/>
-    <hyperlink ref="B6" r:id="rId9" tooltip="https://www.indmoney.com/stocks/welcure-drugs-and-pharmaceuticals-ltd-share-price"/>
-    <hyperlink ref="M6" r:id="rId10" tooltip="https://www.indmoney.com/stocks/welcure-drugs-and-pharmaceuticals-ltd-share-price"/>
-    <hyperlink ref="B7" r:id="rId11" tooltip="https://www.indmoney.com/stocks/shalimar-productions-ltd-share-price"/>
-    <hyperlink ref="M7" r:id="rId12" tooltip="https://www.indmoney.com/stocks/shalimar-productions-ltd-share-price"/>
-    <hyperlink ref="B8" r:id="rId13" tooltip="https://www.indmoney.com/stocks/remedium-lifecare-ltd-share-price"/>
-    <hyperlink ref="M8" r:id="rId14" tooltip="https://www.indmoney.com/stocks/remedium-lifecare-ltd-share-price"/>
-    <hyperlink ref="B9" r:id="rId15" tooltip="https://www.indmoney.com/stocks/siti-networks-ltd-share-price"/>
-    <hyperlink ref="M9" r:id="rId16" tooltip="https://www.indmoney.com/stocks/siti-networks-ltd-share-price"/>
-    <hyperlink ref="B10" r:id="rId17" tooltip="https://www.indmoney.com/stocks/rajnish-wellness-ltd-share-price"/>
-    <hyperlink ref="M10" r:id="rId18" tooltip="https://www.indmoney.com/stocks/rajnish-wellness-ltd-share-price"/>
-    <hyperlink ref="B11" r:id="rId19" tooltip="https://www.indmoney.com/stocks/mfl-india-ltd-share-price"/>
-    <hyperlink ref="M11" r:id="rId20" tooltip="https://www.indmoney.com/stocks/mfl-india-ltd-share-price"/>
-    <hyperlink ref="B12" r:id="rId21" tooltip="https://www.indmoney.com/stocks/laddu-gopal-online-services-ltd-share-price"/>
-    <hyperlink ref="M12" r:id="rId22" tooltip="https://www.indmoney.com/stocks/laddu-gopal-online-services-ltd-share-price"/>
-    <hyperlink ref="B13" r:id="rId23" tooltip="https://www.indmoney.com/stocks/veerkrupa-jewellers-ltd-share-price"/>
-    <hyperlink ref="M13" r:id="rId24" tooltip="https://www.indmoney.com/stocks/veerkrupa-jewellers-ltd-share-price"/>
-    <hyperlink ref="B14" r:id="rId25" tooltip="https://www.indmoney.com/stocks/sgn-telecoms-ltd-share-price"/>
-    <hyperlink ref="M14" r:id="rId26" tooltip="https://www.indmoney.com/stocks/sgn-telecoms-ltd-share-price"/>
-    <hyperlink ref="B15" r:id="rId27" tooltip="https://www.indmoney.com/stocks/western-ministil-ltd-share-price"/>
-    <hyperlink ref="M15" r:id="rId28" tooltip="https://www.indmoney.com/stocks/western-ministil-ltd-share-price"/>
-    <hyperlink ref="B16" r:id="rId29" tooltip="https://www.indmoney.com/stocks/unison-metals-ltd-share-price"/>
-    <hyperlink ref="M16" r:id="rId30" tooltip="https://www.indmoney.com/stocks/unison-metals-ltd-share-price"/>
-    <hyperlink ref="B17" r:id="rId31" tooltip="https://www.indmoney.com/stocks/navkar-urbanstructure-ltd-share-price"/>
-    <hyperlink ref="M17" r:id="rId32" tooltip="https://www.indmoney.com/stocks/navkar-urbanstructure-ltd-share-price"/>
-    <hyperlink ref="B18" r:id="rId33" tooltip="https://www.indmoney.com/stocks/reliance-communications-ltd-share-price"/>
-    <hyperlink ref="M18" r:id="rId34" tooltip="https://www.indmoney.com/stocks/reliance-communications-ltd-share-price"/>
-    <hyperlink ref="B19" r:id="rId35" tooltip="https://www.indmoney.com/stocks/starbeam-ventures-ltd-share-price"/>
-    <hyperlink ref="M19" r:id="rId36" tooltip="https://www.indmoney.com/stocks/starbeam-ventures-ltd-share-price"/>
-    <hyperlink ref="B20" r:id="rId37" tooltip="https://www.indmoney.com/stocks/croissance-ltd-share-price"/>
-    <hyperlink ref="M20" r:id="rId38" tooltip="https://www.indmoney.com/stocks/croissance-ltd-share-price"/>
-    <hyperlink ref="B21" r:id="rId39" tooltip="https://www.indmoney.com/stocks/gtl-infrastructure-ltd-share-price"/>
-    <hyperlink ref="M21" r:id="rId40" tooltip="https://www.indmoney.com/stocks/gtl-infrastructure-ltd-share-price"/>
-    <hyperlink ref="B22" r:id="rId41" tooltip="https://www.indmoney.com/stocks/sundaram-multi-pap-ltd-share-price"/>
-    <hyperlink ref="M22" r:id="rId42" tooltip="https://www.indmoney.com/stocks/sundaram-multi-pap-ltd-share-price"/>
-    <hyperlink ref="B23" r:id="rId43" tooltip="https://www.indmoney.com/stocks/vision-cinemas-ltd-share-price"/>
-    <hyperlink ref="M23" r:id="rId44" tooltip="https://www.indmoney.com/stocks/vision-cinemas-ltd-share-price"/>
-    <hyperlink ref="B24" r:id="rId45" tooltip="https://www.indmoney.com/stocks/garment-mantra-lifestyle-ltd-share-price"/>
-    <hyperlink ref="M24" r:id="rId46" tooltip="https://www.indmoney.com/stocks/garment-mantra-lifestyle-ltd-share-price"/>
-    <hyperlink ref="B25" r:id="rId47" tooltip="https://www.indmoney.com/stocks/52-weeks-entertainment-ltd-share-price"/>
-    <hyperlink ref="M25" r:id="rId48" tooltip="https://www.indmoney.com/stocks/52-weeks-entertainment-ltd-share-price"/>
-    <hyperlink ref="B26" r:id="rId49" tooltip="https://www.indmoney.com/stocks/sprayking-ltd-share-price"/>
-    <hyperlink ref="M26" r:id="rId50" tooltip="https://www.indmoney.com/stocks/sprayking-ltd-share-price"/>
-    <hyperlink ref="B27" r:id="rId51" tooltip="https://www.indmoney.com/stocks/gala-global-products-ltd-share-price"/>
-    <hyperlink ref="M27" r:id="rId52" tooltip="https://www.indmoney.com/stocks/gala-global-products-ltd-share-price"/>
-    <hyperlink ref="B28" r:id="rId53" tooltip="https://www.indmoney.com/stocks/ducon-infratechnologies-ltd-share-price"/>
-    <hyperlink ref="M28" r:id="rId54" tooltip="https://www.indmoney.com/stocks/ducon-infratechnologies-ltd-share-price"/>
-    <hyperlink ref="B29" r:id="rId55" tooltip="https://www.indmoney.com/stocks/kanani-industries-ltd-share-price"/>
-    <hyperlink ref="M29" r:id="rId56" tooltip="https://www.indmoney.com/stocks/kanani-industries-ltd-share-price"/>
-    <hyperlink ref="B30" r:id="rId57" tooltip="https://www.indmoney.com/stocks/r-o-jewels-ltd-share-price"/>
-    <hyperlink ref="M30" r:id="rId58" tooltip="https://www.indmoney.com/stocks/r-o-jewels-ltd-share-price"/>
-    <hyperlink ref="B31" r:id="rId59" tooltip="https://www.indmoney.com/stocks/sri-havisha-hospitality-and-infrastructure-ltd-share-price"/>
-    <hyperlink ref="M31" r:id="rId60" tooltip="https://www.indmoney.com/stocks/sri-havisha-hospitality-and-infrastructure-ltd-share-price"/>
-    <hyperlink ref="B32" r:id="rId61" tooltip="https://www.indmoney.com/stocks/radhe-developers-india-ltd-share-price"/>
-    <hyperlink ref="M32" r:id="rId62" tooltip="https://www.indmoney.com/stocks/radhe-developers-india-ltd-share-price"/>
-    <hyperlink ref="B33" r:id="rId63" tooltip="https://www.indmoney.com/stocks/fcs-software-solutions-ltd-share-price"/>
-    <hyperlink ref="M33" r:id="rId64" tooltip="https://www.indmoney.com/stocks/fcs-software-solutions-ltd-share-price"/>
-    <hyperlink ref="B34" r:id="rId65" tooltip="https://www.indmoney.com/stocks/filmcity-media-ltd-share-price"/>
-    <hyperlink ref="M34" r:id="rId66" tooltip="https://www.indmoney.com/stocks/filmcity-media-ltd-share-price"/>
-    <hyperlink ref="B35" r:id="rId67" tooltip="https://www.indmoney.com/stocks/zodiac-ventures-ltd-share-price"/>
-    <hyperlink ref="M35" r:id="rId68" tooltip="https://www.indmoney.com/stocks/zodiac-ventures-ltd-share-price"/>
-    <hyperlink ref="B36" r:id="rId69" tooltip="https://www.indmoney.com/stocks/deep-health-ai-india-ltd-share-price"/>
-    <hyperlink ref="M36" r:id="rId70" tooltip="https://www.indmoney.com/stocks/deep-health-ai-india-ltd-share-price"/>
-    <hyperlink ref="B37" r:id="rId71" tooltip="https://www.indmoney.com/stocks/jalan-transolutions-india-ltd-share-price"/>
-    <hyperlink ref="M37" r:id="rId72" tooltip="https://www.indmoney.com/stocks/jalan-transolutions-india-ltd-share-price"/>
-    <hyperlink ref="B38" r:id="rId73" tooltip="https://www.indmoney.com/stocks/nagarjuna-fertilizers-and-chemicals-ltd-share-price"/>
-    <hyperlink ref="M38" r:id="rId74" tooltip="https://www.indmoney.com/stocks/nagarjuna-fertilizers-and-chemicals-ltd-share-price"/>
-    <hyperlink ref="B39" r:id="rId75" tooltip="https://www.indmoney.com/stocks/ortel-communications-ltd-share-price"/>
-    <hyperlink ref="M39" r:id="rId76" tooltip="https://www.indmoney.com/stocks/ortel-communications-ltd-share-price"/>
-    <hyperlink ref="B40" r:id="rId77" tooltip="https://www.indmoney.com/stocks/family-care-hospitals-ltd-share-price"/>
-    <hyperlink ref="M40" r:id="rId78" tooltip="https://www.indmoney.com/stocks/family-care-hospitals-ltd-share-price"/>
-    <hyperlink ref="B41" r:id="rId79" tooltip="https://www.indmoney.com/stocks/shivamshree-businesses-ltd-share-price"/>
-    <hyperlink ref="M41" r:id="rId80" tooltip="https://www.indmoney.com/stocks/shivamshree-businesses-ltd-share-price"/>
-    <hyperlink ref="B42" r:id="rId81" tooltip="https://www.indmoney.com/stocks/newtime-infrastructure-ltd-share-price"/>
-    <hyperlink ref="M42" r:id="rId82" tooltip="https://www.indmoney.com/stocks/newtime-infrastructure-ltd-share-price"/>
-    <hyperlink ref="B43" r:id="rId83" tooltip="https://www.indmoney.com/stocks/ilandfs-transportation-networks-ltd-share-price"/>
-    <hyperlink ref="M43" r:id="rId84" tooltip="https://www.indmoney.com/stocks/ilandfs-transportation-networks-ltd-share-price"/>
-    <hyperlink ref="B44" r:id="rId85" tooltip="https://www.indmoney.com/stocks/amin-tannery-ltd-share-price"/>
-    <hyperlink ref="M44" r:id="rId86" tooltip="https://www.indmoney.com/stocks/amin-tannery-ltd-share-price"/>
-    <hyperlink ref="B45" r:id="rId87" tooltip="https://www.indmoney.com/stocks/kenvi-jewels-ltd-share-price"/>
-    <hyperlink ref="M45" r:id="rId88" tooltip="https://www.indmoney.com/stocks/kenvi-jewels-ltd-share-price"/>
-    <hyperlink ref="B46" r:id="rId89" tooltip="https://www.indmoney.com/stocks/crystal-business-system-ltd-share-price"/>
-    <hyperlink ref="M46" r:id="rId90" tooltip="https://www.indmoney.com/stocks/crystal-business-system-ltd-share-price"/>
-    <hyperlink ref="B47" r:id="rId91" tooltip="https://www.indmoney.com/stocks/landmarc-leisure-corporation-ltd-share-price"/>
-    <hyperlink ref="M47" r:id="rId92" tooltip="https://www.indmoney.com/stocks/landmarc-leisure-corporation-ltd-share-price"/>
-    <hyperlink ref="B48" r:id="rId93" tooltip="https://www.indmoney.com/stocks/paras-petrofils-ltd-share-price"/>
-    <hyperlink ref="M48" r:id="rId94" tooltip="https://www.indmoney.com/stocks/paras-petrofils-ltd-share-price"/>
-    <hyperlink ref="B49" r:id="rId95" tooltip="https://www.indmoney.com/stocks/ankit-metal-and-power-ltd-share-price"/>
-    <hyperlink ref="M49" r:id="rId96" tooltip="https://www.indmoney.com/stocks/ankit-metal-and-power-ltd-share-price"/>
-    <hyperlink ref="B50" r:id="rId97" tooltip="https://www.indmoney.com/stocks/tatia-global-venture-ltd-share-price"/>
-    <hyperlink ref="M50" r:id="rId98" tooltip="https://www.indmoney.com/stocks/tatia-global-venture-ltd-share-price"/>
-    <hyperlink ref="B51" r:id="rId99" tooltip="https://www.indmoney.com/stocks/diligent-industries-ltd-share-price"/>
-    <hyperlink ref="M51" r:id="rId100" tooltip="https://www.indmoney.com/stocks/diligent-industries-ltd-share-price"/>
-    <hyperlink ref="B52" r:id="rId101" tooltip="https://www.indmoney.com/stocks/globe-enterprises-india-ltd-share-price"/>
-    <hyperlink ref="M52" r:id="rId102" tooltip="https://www.indmoney.com/stocks/globe-enterprises-india-ltd-share-price"/>
-    <hyperlink ref="B53" r:id="rId103" tooltip="https://www.indmoney.com/stocks/darshan-orna-ltd-share-price"/>
-    <hyperlink ref="M53" r:id="rId104" tooltip="https://www.indmoney.com/stocks/darshan-orna-ltd-share-price"/>
-    <hyperlink ref="B54" r:id="rId105" tooltip="https://www.indmoney.com/stocks/parsvnath-developers-ltd-share-price"/>
-    <hyperlink ref="M54" r:id="rId106" tooltip="https://www.indmoney.com/stocks/parsvnath-developers-ltd-share-price"/>
-    <hyperlink ref="B55" r:id="rId107" tooltip="https://www.indmoney.com/stocks/tuni-textile-mills-ltd-share-price"/>
-    <hyperlink ref="M55" r:id="rId108" tooltip="https://www.indmoney.com/stocks/tuni-textile-mills-ltd-share-price"/>
-    <hyperlink ref="B56" r:id="rId109" tooltip="https://www.indmoney.com/stocks/dish-tv-india-ltd-share-price"/>
-    <hyperlink ref="M56" r:id="rId110" tooltip="https://www.indmoney.com/stocks/dish-tv-india-ltd-share-price"/>
-    <hyperlink ref="B57" r:id="rId111" tooltip="https://www.indmoney.com/stocks/pvv-infra-ltd-share-price"/>
-    <hyperlink ref="M57" r:id="rId112" tooltip="https://www.indmoney.com/stocks/pvv-infra-ltd-share-price"/>
-    <hyperlink ref="B58" r:id="rId113" tooltip="https://www.indmoney.com/stocks/vision-corporation-ltd-share-price"/>
-    <hyperlink ref="M58" r:id="rId114" tooltip="https://www.indmoney.com/stocks/vision-corporation-ltd-share-price"/>
-    <hyperlink ref="B59" r:id="rId115" tooltip="https://www.indmoney.com/stocks/davangere-sugar-company-ltd-share-price"/>
-    <hyperlink ref="M59" r:id="rId116" tooltip="https://www.indmoney.com/stocks/davangere-sugar-company-ltd-share-price"/>
-    <hyperlink ref="B60" r:id="rId117" tooltip="https://www.indmoney.com/stocks/east-west-freight-carriers-ltd-share-price"/>
-    <hyperlink ref="M60" r:id="rId118" tooltip="https://www.indmoney.com/stocks/east-west-freight-carriers-ltd-share-price"/>
-    <hyperlink ref="B61" r:id="rId119" tooltip="https://www.indmoney.com/stocks/transgene-biotek-ltd-share-price"/>
-    <hyperlink ref="M61" r:id="rId120" tooltip="https://www.indmoney.com/stocks/transgene-biotek-ltd-share-price"/>
-    <hyperlink ref="B62" r:id="rId121" tooltip="https://www.indmoney.com/stocks/diligent-media-corporation-ltd-share-price"/>
-    <hyperlink ref="M62" r:id="rId122" tooltip="https://www.indmoney.com/stocks/diligent-media-corporation-ltd-share-price"/>
-    <hyperlink ref="B63" r:id="rId123" tooltip="https://www.indmoney.com/stocks/sadhana-nitro-chem-ltd-share-price"/>
-    <hyperlink ref="M63" r:id="rId124" tooltip="https://www.indmoney.com/stocks/sadhana-nitro-chem-ltd-share-price"/>
-    <hyperlink ref="B64" r:id="rId125" tooltip="https://www.indmoney.com/stocks/gvk-power-and-infrastructure-ltd-share-price"/>
-    <hyperlink ref="M64" r:id="rId126" tooltip="https://www.indmoney.com/stocks/gvk-power-and-infrastructure-ltd-share-price"/>
-    <hyperlink ref="B65" r:id="rId127" tooltip="https://www.indmoney.com/stocks/aci-infocom-ltd-share-price"/>
-    <hyperlink ref="M65" r:id="rId128" tooltip="https://www.indmoney.com/stocks/aci-infocom-ltd-share-price"/>
-    <hyperlink ref="B66" r:id="rId129" tooltip="https://www.indmoney.com/stocks/nandan-denim-ltd-share-price"/>
-    <hyperlink ref="M66" r:id="rId130" tooltip="https://www.indmoney.com/stocks/nandan-denim-ltd-share-price"/>
-    <hyperlink ref="B67" r:id="rId131" tooltip="https://www.indmoney.com/stocks/tv-vision-ltd-share-price"/>
-    <hyperlink ref="M67" r:id="rId132" tooltip="https://www.indmoney.com/stocks/tv-vision-ltd-share-price"/>
-    <hyperlink ref="B68" r:id="rId133" tooltip="https://www.indmoney.com/stocks/coromandel-agro-products-and-oils-ltd-share-price"/>
-    <hyperlink ref="M68" r:id="rId134" tooltip="https://www.indmoney.com/stocks/coromandel-agro-products-and-oils-ltd-share-price"/>
-    <hyperlink ref="B69" r:id="rId135" tooltip="https://www.indmoney.com/stocks/sadbhav-infrastructure-projects-ltd-share-price"/>
-    <hyperlink ref="M69" r:id="rId136" tooltip="https://www.indmoney.com/stocks/sadbhav-infrastructure-projects-ltd-share-price"/>
-    <hyperlink ref="B70" r:id="rId137" tooltip="https://www.indmoney.com/stocks/picturepost-studios-ltd-share-price"/>
-    <hyperlink ref="M70" r:id="rId138" tooltip="https://www.indmoney.com/stocks/picturepost-studios-ltd-share-price"/>
-    <hyperlink ref="B71" r:id="rId139" tooltip="https://www.indmoney.com/stocks/astron-paper-and-board-mill-ltd-share-price"/>
-    <hyperlink ref="M71" r:id="rId140" tooltip="https://www.indmoney.com/stocks/astron-paper-and-board-mill-ltd-share-price"/>
-    <hyperlink ref="B72" r:id="rId141" tooltip="https://www.indmoney.com/stocks/bhandari-hosiery-exports-ltd-share-price"/>
-    <hyperlink ref="M72" r:id="rId142" tooltip="https://www.indmoney.com/stocks/bhandari-hosiery-exports-ltd-share-price"/>
-    <hyperlink ref="B73" r:id="rId143" tooltip="https://www.indmoney.com/stocks/olympic-cards-ltd-share-price"/>
-    <hyperlink ref="M73" r:id="rId144" tooltip="https://www.indmoney.com/stocks/olympic-cards-ltd-share-price"/>
-    <hyperlink ref="B74" r:id="rId145" tooltip="https://www.indmoney.com/stocks/sea-tv-network-ltd-share-price"/>
-    <hyperlink ref="M74" r:id="rId146" tooltip="https://www.indmoney.com/stocks/sea-tv-network-ltd-share-price"/>
-    <hyperlink ref="B75" r:id="rId147" tooltip="https://www.indmoney.com/stocks/radaan-mediaworks-i-ltd-share-price"/>
-    <hyperlink ref="M75" r:id="rId148" tooltip="https://www.indmoney.com/stocks/radaan-mediaworks-i-ltd-share-price"/>
-    <hyperlink ref="B76" r:id="rId149" tooltip="https://www.indmoney.com/stocks/vaishno-cement-co-ltd-share-price"/>
-    <hyperlink ref="M76" r:id="rId150" tooltip="https://www.indmoney.com/stocks/vaishno-cement-co-ltd-share-price"/>
-    <hyperlink ref="B77" r:id="rId151" tooltip="https://www.indmoney.com/stocks/khyati-multimedia-entertainment-ltd-share-price"/>
-    <hyperlink ref="M77" r:id="rId152" tooltip="https://www.indmoney.com/stocks/khyati-multimedia-entertainment-ltd-share-price"/>
-    <hyperlink ref="B78" r:id="rId153" tooltip="https://www.indmoney.com/stocks/gautam-gems-ltd-share-price"/>
-    <hyperlink ref="M78" r:id="rId154" tooltip="https://www.indmoney.com/stocks/gautam-gems-ltd-share-price"/>
-    <hyperlink ref="B79" r:id="rId155" tooltip="https://www.indmoney.com/stocks/alliance-integrated-metaliks-ltd-share-price"/>
-    <hyperlink ref="M79" r:id="rId156" tooltip="https://www.indmoney.com/stocks/alliance-integrated-metaliks-ltd-share-price"/>
-    <hyperlink ref="B80" r:id="rId157" tooltip="https://www.indmoney.com/stocks/shah-metacorp-ltd-share-price"/>
-    <hyperlink ref="M80" r:id="rId158" tooltip="https://www.indmoney.com/stocks/shah-metacorp-ltd-share-price"/>
-    <hyperlink ref="B81" r:id="rId159" tooltip="https://www.indmoney.com/stocks/facor-alloys-ltd-share-price"/>
-    <hyperlink ref="M81" r:id="rId160" tooltip="https://www.indmoney.com/stocks/facor-alloys-ltd-share-price"/>
-    <hyperlink ref="B82" r:id="rId161" tooltip="https://www.indmoney.com/stocks/mishtann-foods-ltd-share-price"/>
-    <hyperlink ref="M82" r:id="rId162" tooltip="https://www.indmoney.com/stocks/mishtann-foods-ltd-share-price"/>
-    <hyperlink ref="B83" r:id="rId163" tooltip="https://www.indmoney.com/stocks/rajnandini-metal-ltd-share-price"/>
-    <hyperlink ref="M83" r:id="rId164" tooltip="https://www.indmoney.com/stocks/rajnandini-metal-ltd-share-price"/>
-    <hyperlink ref="B84" r:id="rId165" tooltip="https://www.indmoney.com/stocks/ok-play-india-ltd-share-price"/>
-    <hyperlink ref="M84" r:id="rId166" tooltip="https://www.indmoney.com/stocks/ok-play-india-ltd-share-price"/>
-    <hyperlink ref="B85" r:id="rId167" tooltip="https://www.indmoney.com/stocks/shipwaves-online-ltd-share-price"/>
-    <hyperlink ref="M85" r:id="rId168" tooltip="https://www.indmoney.com/stocks/shipwaves-online-ltd-share-price"/>
-    <hyperlink ref="B86" r:id="rId169" tooltip="https://www.indmoney.com/stocks/sarveshwar-foods-ltd-share-price"/>
-    <hyperlink ref="M86" r:id="rId170" tooltip="https://www.indmoney.com/stocks/sarveshwar-foods-ltd-share-price"/>
-    <hyperlink ref="B87" r:id="rId171" tooltip="https://www.indmoney.com/stocks/kcd-industries-india-ltd-share-price"/>
-    <hyperlink ref="M87" r:id="rId172" tooltip="https://www.indmoney.com/stocks/kcd-industries-india-ltd-share-price"/>
-    <hyperlink ref="B88" r:id="rId173" tooltip="https://www.indmoney.com/stocks/noida-toll-bridge-company-ltd-share-price"/>
-    <hyperlink ref="M88" r:id="rId174" tooltip="https://www.indmoney.com/stocks/noida-toll-bridge-company-ltd-share-price"/>
-    <hyperlink ref="B89" r:id="rId175" tooltip="https://www.indmoney.com/stocks/prakash-steelage-ltd-share-price"/>
-    <hyperlink ref="M89" r:id="rId176" tooltip="https://www.indmoney.com/stocks/prakash-steelage-ltd-share-price"/>
-    <hyperlink ref="B90" r:id="rId177" tooltip="https://www.indmoney.com/stocks/nb-footwear-ltd-share-price"/>
-    <hyperlink ref="M90" r:id="rId178" tooltip="https://www.indmoney.com/stocks/nb-footwear-ltd-share-price"/>
-    <hyperlink ref="B91" r:id="rId179" tooltip="https://www.indmoney.com/stocks/next-mediaworks-ltd-share-price"/>
-    <hyperlink ref="M91" r:id="rId180" tooltip="https://www.indmoney.com/stocks/next-mediaworks-ltd-share-price"/>
-    <hyperlink ref="B92" r:id="rId181" tooltip="https://www.indmoney.com/stocks/agio-paper-and-industries-ltd-share-price"/>
-    <hyperlink ref="M92" r:id="rId182" tooltip="https://www.indmoney.com/stocks/agio-paper-and-industries-ltd-share-price"/>
-    <hyperlink ref="B93" r:id="rId183" tooltip="https://www.indmoney.com/stocks/sacheta-metals-ltd-share-price"/>
-    <hyperlink ref="M93" r:id="rId184" tooltip="https://www.indmoney.com/stocks/sacheta-metals-ltd-share-price"/>
-    <hyperlink ref="B94" r:id="rId185" tooltip="https://www.indmoney.com/stocks/perfect-octave-media-projects-ltd-share-price"/>
-    <hyperlink ref="M94" r:id="rId186" tooltip="https://www.indmoney.com/stocks/perfect-octave-media-projects-ltd-share-price"/>
-    <hyperlink ref="B95" r:id="rId187" tooltip="https://www.indmoney.com/stocks/shree-hanuman-sugar-and-industries-ltd-share-price"/>
-    <hyperlink ref="M95" r:id="rId188" tooltip="https://www.indmoney.com/stocks/shree-hanuman-sugar-and-industries-ltd-share-price"/>
-    <hyperlink ref="B96" r:id="rId189" tooltip="https://www.indmoney.com/stocks/m-k-proteins-ltd-share-price"/>
-    <hyperlink ref="M96" r:id="rId190" tooltip="https://www.indmoney.com/stocks/m-k-proteins-ltd-share-price"/>
-    <hyperlink ref="B97" r:id="rId191" tooltip="https://www.indmoney.com/stocks/padmalaya-telefilms-ltd-share-price"/>
-    <hyperlink ref="M97" r:id="rId192" tooltip="https://www.indmoney.com/stocks/padmalaya-telefilms-ltd-share-price"/>
-    <hyperlink ref="B98" r:id="rId193" tooltip="https://www.indmoney.com/stocks/spectra-industries-ltd-share-price"/>
-    <hyperlink ref="M98" r:id="rId194" tooltip="https://www.indmoney.com/stocks/spectra-industries-ltd-share-price"/>
-    <hyperlink ref="B99" r:id="rId195" tooltip="https://www.indmoney.com/stocks/unitech-ltd-share-price"/>
-    <hyperlink ref="M99" r:id="rId196" tooltip="https://www.indmoney.com/stocks/unitech-ltd-share-price"/>
-    <hyperlink ref="B100" r:id="rId197" tooltip="https://www.indmoney.com/stocks/kshitij-polyline-ltd-share-price"/>
-    <hyperlink ref="M100" r:id="rId198" tooltip="https://www.indmoney.com/stocks/kshitij-polyline-ltd-share-price"/>
-    <hyperlink ref="B101" r:id="rId199" tooltip="https://www.indmoney.com/stocks/arunjyoti-bio-ventures-ltd-share-price"/>
-    <hyperlink ref="M101" r:id="rId200" tooltip="https://www.indmoney.com/stocks/arunjyoti-bio-ventures-ltd-share-price"/>
-    <hyperlink ref="B102" r:id="rId201" tooltip="https://www.indmoney.com/stocks/dhatre-udyog-ltd-share-price"/>
-    <hyperlink ref="M102" r:id="rId202" tooltip="https://www.indmoney.com/stocks/dhatre-udyog-ltd-share-price"/>
-    <hyperlink ref="B103" r:id="rId203" tooltip="https://www.indmoney.com/stocks/mini-diamonds-india-ltd-share-price"/>
-    <hyperlink ref="M103" r:id="rId204" tooltip="https://www.indmoney.com/stocks/mini-diamonds-india-ltd-share-price"/>
-    <hyperlink ref="B104" r:id="rId205" tooltip="https://www.indmoney.com/stocks/orient-tradelink-ltd-share-price"/>
-    <hyperlink ref="M104" r:id="rId206" tooltip="https://www.indmoney.com/stocks/orient-tradelink-ltd-share-price"/>
-    <hyperlink ref="B105" r:id="rId207" tooltip="https://www.indmoney.com/stocks/b-a-g-films-and-media-ltd-share-price"/>
-    <hyperlink ref="M105" r:id="rId208" tooltip="https://www.indmoney.com/stocks/b-a-g-films-and-media-ltd-share-price"/>
-    <hyperlink ref="B106" r:id="rId209" tooltip="https://www.indmoney.com/stocks/ansal-properties-and-infrastructure-ltd-share-price"/>
-    <hyperlink ref="M106" r:id="rId210" tooltip="https://www.indmoney.com/stocks/ansal-properties-and-infrastructure-ltd-share-price"/>
-    <hyperlink ref="B107" r:id="rId211" tooltip="https://www.indmoney.com/stocks/kamdhenu-ventures-ltd-share-price"/>
-    <hyperlink ref="M107" r:id="rId212" tooltip="https://www.indmoney.com/stocks/kamdhenu-ventures-ltd-share-price"/>
-    <hyperlink ref="B108" r:id="rId213" tooltip="https://www.indmoney.com/stocks/ridhi-synthetics-ltd-share-price"/>
-    <hyperlink ref="M108" r:id="rId214" tooltip="https://www.indmoney.com/stocks/ridhi-synthetics-ltd-share-price"/>
-    <hyperlink ref="B109" r:id="rId215" tooltip="https://www.indmoney.com/stocks/accuracy-shipping-ltd-share-price"/>
-    <hyperlink ref="M109" r:id="rId216" tooltip="https://www.indmoney.com/stocks/accuracy-shipping-ltd-share-price"/>
-    <hyperlink ref="B110" r:id="rId217" tooltip="https://www.indmoney.com/stocks/salasar-techno-engineering-ltd-share-price"/>
-    <hyperlink ref="M110" r:id="rId218" tooltip="https://www.indmoney.com/stocks/salasar-techno-engineering-ltd-share-price"/>
-    <hyperlink ref="B111" r:id="rId219" tooltip="https://www.indmoney.com/stocks/tahmar-enterprises-ltd-share-price"/>
-    <hyperlink ref="M111" r:id="rId220" tooltip="https://www.indmoney.com/stocks/tahmar-enterprises-ltd-share-price"/>
-    <hyperlink ref="B112" r:id="rId221" tooltip="https://www.indmoney.com/stocks/supreme-engineering-ltd-share-price"/>
-    <hyperlink ref="M112" r:id="rId222" tooltip="https://www.indmoney.com/stocks/supreme-engineering-ltd-share-price"/>
-    <hyperlink ref="B113" r:id="rId223" tooltip="https://www.indmoney.com/stocks/minal-industries-ltd-share-price"/>
-    <hyperlink ref="M113" r:id="rId224" tooltip="https://www.indmoney.com/stocks/minal-industries-ltd-share-price"/>
-    <hyperlink ref="B114" r:id="rId225" tooltip="https://www.indmoney.com/stocks/ashapuri-gold-ornament-ltd-share-price"/>
-    <hyperlink ref="M114" r:id="rId226" tooltip="https://www.indmoney.com/stocks/ashapuri-gold-ornament-ltd-share-price"/>
-    <hyperlink ref="B115" r:id="rId227" tooltip="https://www.indmoney.com/stocks/sparc-electrex-ltd-share-price"/>
-    <hyperlink ref="M115" r:id="rId228" tooltip="https://www.indmoney.com/stocks/sparc-electrex-ltd-share-price"/>
-    <hyperlink ref="B116" r:id="rId229" tooltip="https://www.indmoney.com/stocks/aurus-gem-corporation-ltd-share-price"/>
-    <hyperlink ref="M116" r:id="rId230" tooltip="https://www.indmoney.com/stocks/aurus-gem-corporation-ltd-share-price"/>
-    <hyperlink ref="B117" r:id="rId231" tooltip="https://www.indmoney.com/stocks/rama-steel-tubes-ltd-share-price"/>
-    <hyperlink ref="M117" r:id="rId232" tooltip="https://www.indmoney.com/stocks/rama-steel-tubes-ltd-share-price"/>
-    <hyperlink ref="B118" r:id="rId233" tooltip="https://www.indmoney.com/stocks/silver-pearl-hospitality-and-luxury-spaces-ltd-share-price"/>
-    <hyperlink ref="M118" r:id="rId234" tooltip="https://www.indmoney.com/stocks/silver-pearl-hospitality-and-luxury-spaces-ltd-share-price"/>
-    <hyperlink ref="B119" r:id="rId235" tooltip="https://www.indmoney.com/stocks/usha-martin-education-and-solutions-ltd-share-price"/>
-    <hyperlink ref="M119" r:id="rId236" tooltip="https://www.indmoney.com/stocks/usha-martin-education-and-solutions-ltd-share-price"/>
-    <hyperlink ref="B120" r:id="rId237" tooltip="https://www.indmoney.com/stocks/gian-lifecare-ltd-share-price"/>
-    <hyperlink ref="M120" r:id="rId238" tooltip="https://www.indmoney.com/stocks/gian-lifecare-ltd-share-price"/>
-    <hyperlink ref="B121" r:id="rId239" tooltip="https://www.indmoney.com/stocks/rollatainers-ltd-share-price"/>
-    <hyperlink ref="M121" r:id="rId240" tooltip="https://www.indmoney.com/stocks/rollatainers-ltd-share-price"/>
-    <hyperlink ref="B122" r:id="rId241" tooltip="https://www.indmoney.com/stocks/kritika-wires-ltd-share-price"/>
-    <hyperlink ref="M122" r:id="rId242" tooltip="https://www.indmoney.com/stocks/kritika-wires-ltd-share-price"/>
-    <hyperlink ref="B123" r:id="rId243" tooltip="https://www.indmoney.com/stocks/ansal-housing-ltd-share-price"/>
-    <hyperlink ref="M123" r:id="rId244" tooltip="https://www.indmoney.com/stocks/ansal-housing-ltd-share-price"/>
-    <hyperlink ref="B124" r:id="rId245" tooltip="https://www.indmoney.com/stocks/cemantic-infra-tech-ltd-share-price"/>
-    <hyperlink ref="M124" r:id="rId246" tooltip="https://www.indmoney.com/stocks/cemantic-infra-tech-ltd-share-price"/>
-    <hyperlink ref="B125" r:id="rId247" tooltip="https://www.indmoney.com/stocks/shyam-century-ferrous-ltd-share-price"/>
-    <hyperlink ref="M125" r:id="rId248" tooltip="https://www.indmoney.com/stocks/shyam-century-ferrous-ltd-share-price"/>
-    <hyperlink ref="B126" r:id="rId249" tooltip="https://www.indmoney.com/stocks/sepc-ltd-share-price"/>
-    <hyperlink ref="M126" r:id="rId250" tooltip="https://www.indmoney.com/stocks/sepc-ltd-share-price"/>
-    <hyperlink ref="B127" r:id="rId251" tooltip="https://www.indmoney.com/stocks/zenith-steel-pipes-and-industries-ltd-share-price"/>
-    <hyperlink ref="M127" r:id="rId252" tooltip="https://www.indmoney.com/stocks/zenith-steel-pipes-and-industries-ltd-share-price"/>
-    <hyperlink ref="B128" r:id="rId253" tooltip="https://www.indmoney.com/stocks/vakrangee-ltd-share-price"/>
-    <hyperlink ref="M128" r:id="rId254" tooltip="https://www.indmoney.com/stocks/vakrangee-ltd-share-price"/>
-    <hyperlink ref="B129" r:id="rId255" tooltip="https://www.indmoney.com/stocks/iel-ltd-share-price"/>
-    <hyperlink ref="M129" r:id="rId256" tooltip="https://www.indmoney.com/stocks/iel-ltd-share-price"/>
-    <hyperlink ref="B130" r:id="rId257" tooltip="https://www.indmoney.com/stocks/vishwaraj-sugar-industries-ltd-share-price"/>
-    <hyperlink ref="M130" r:id="rId258" tooltip="https://www.indmoney.com/stocks/vishwaraj-sugar-industries-ltd-share-price"/>
-    <hyperlink ref="B131" r:id="rId259" tooltip="https://www.indmoney.com/stocks/signature-green-corporation-ltd-share-price"/>
-    <hyperlink ref="M131" r:id="rId260" tooltip="https://www.indmoney.com/stocks/signature-green-corporation-ltd-share-price"/>
-    <hyperlink ref="B132" r:id="rId261" tooltip="https://www.indmoney.com/stocks/regent-enterprises-ltd-share-price"/>
-    <hyperlink ref="M132" r:id="rId262" tooltip="https://www.indmoney.com/stocks/regent-enterprises-ltd-share-price"/>
-    <hyperlink ref="B133" r:id="rId263" tooltip="https://www.indmoney.com/stocks/wardwizard-innovations-and-mobility-ltd-share-price"/>
-    <hyperlink ref="M133" r:id="rId264" tooltip="https://www.indmoney.com/stocks/wardwizard-innovations-and-mobility-ltd-share-price"/>
-    <hyperlink ref="B134" r:id="rId265" tooltip="https://www.indmoney.com/stocks/infomedia-press-ltd-share-price"/>
-    <hyperlink ref="M134" r:id="rId266" tooltip="https://www.indmoney.com/stocks/infomedia-press-ltd-share-price"/>
-    <hyperlink ref="B135" r:id="rId267" tooltip="https://www.indmoney.com/stocks/last-mile-enterprises-ltd-share-price"/>
-    <hyperlink ref="M135" r:id="rId268" tooltip="https://www.indmoney.com/stocks/last-mile-enterprises-ltd-share-price"/>
-    <hyperlink ref="B136" r:id="rId269" tooltip="https://www.indmoney.com/stocks/patidar-buildcon-ltd-share-price"/>
-    <hyperlink ref="M136" r:id="rId270" tooltip="https://www.indmoney.com/stocks/patidar-buildcon-ltd-share-price"/>
-    <hyperlink ref="B137" r:id="rId271" tooltip="https://www.indmoney.com/stocks/universal-arts-ltd-share-price"/>
-    <hyperlink ref="M137" r:id="rId272" tooltip="https://www.indmoney.com/stocks/universal-arts-ltd-share-price"/>
-    <hyperlink ref="B138" r:id="rId273" tooltip="https://www.indmoney.com/stocks/sambhaav-media-ltd-share-price"/>
-    <hyperlink ref="M138" r:id="rId274" tooltip="https://www.indmoney.com/stocks/sambhaav-media-ltd-share-price"/>
-    <hyperlink ref="B139" r:id="rId275" tooltip="https://www.indmoney.com/stocks/lasa-supergenerics-ltd-share-price"/>
-    <hyperlink ref="M139" r:id="rId276" tooltip="https://www.indmoney.com/stocks/lasa-supergenerics-ltd-share-price"/>
-    <hyperlink ref="B140" r:id="rId277" tooltip="https://www.indmoney.com/stocks/parle-industries-ltd-share-price"/>
-    <hyperlink ref="M140" r:id="rId278" tooltip="https://www.indmoney.com/stocks/parle-industries-ltd-share-price"/>
-    <hyperlink ref="B141" r:id="rId279" tooltip="https://www.indmoney.com/stocks/indian-acrylics-ltd-share-price"/>
-    <hyperlink ref="M141" r:id="rId280" tooltip="https://www.indmoney.com/stocks/indian-acrylics-ltd-share-price"/>
-    <hyperlink ref="B142" r:id="rId281" tooltip="https://www.indmoney.com/stocks/vsd-confin-ltd-share-price"/>
-    <hyperlink ref="M142" r:id="rId282" tooltip="https://www.indmoney.com/stocks/vsd-confin-ltd-share-price"/>
-    <hyperlink ref="B143" r:id="rId283" tooltip="https://www.indmoney.com/stocks/kaiser-corporation-ltd-share-price"/>
-    <hyperlink ref="M143" r:id="rId284" tooltip="https://www.indmoney.com/stocks/kaiser-corporation-ltd-share-price"/>
-    <hyperlink ref="B144" r:id="rId285" tooltip="https://www.indmoney.com/stocks/dhenu-buildcon-infra-ltd-share-price"/>
-    <hyperlink ref="M144" r:id="rId286" tooltip="https://www.indmoney.com/stocks/dhenu-buildcon-infra-ltd-share-price"/>
-    <hyperlink ref="B145" r:id="rId287" tooltip="https://www.indmoney.com/stocks/vardhman-polytex-ltd-share-price"/>
-    <hyperlink ref="M145" r:id="rId288" tooltip="https://www.indmoney.com/stocks/vardhman-polytex-ltd-share-price"/>
-    <hyperlink ref="B146" r:id="rId289" tooltip="https://www.indmoney.com/stocks/vivimed-labs-ltd-share-price"/>
-    <hyperlink ref="M146" r:id="rId290" tooltip="https://www.indmoney.com/stocks/vivimed-labs-ltd-share-price"/>
-    <hyperlink ref="B147" r:id="rId291" tooltip="https://www.indmoney.com/stocks/easy-trip-planners-ltd-share-price"/>
-    <hyperlink ref="M147" r:id="rId292" tooltip="https://www.indmoney.com/stocks/easy-trip-planners-ltd-share-price"/>
-    <hyperlink ref="B148" r:id="rId293" tooltip="https://www.indmoney.com/stocks/achyut-healthcare-ltd-share-price"/>
-    <hyperlink ref="M148" r:id="rId294" tooltip="https://www.indmoney.com/stocks/achyut-healthcare-ltd-share-price"/>
-    <hyperlink ref="B149" r:id="rId295" tooltip="https://www.indmoney.com/stocks/music-broadcast-ltd-share-price"/>
-    <hyperlink ref="M149" r:id="rId296" tooltip="https://www.indmoney.com/stocks/music-broadcast-ltd-share-price"/>
-    <hyperlink ref="B150" r:id="rId297" tooltip="https://www.indmoney.com/stocks/avio-smart-market-stack-limited-share-price"/>
-    <hyperlink ref="M150" r:id="rId298" tooltip="https://www.indmoney.com/stocks/avio-smart-market-stack-limited-share-price"/>
-    <hyperlink ref="B151" r:id="rId299" tooltip="https://www.indmoney.com/stocks/u-h-zaveri-ltd-share-price"/>
-    <hyperlink ref="M151" r:id="rId300" tooltip="https://www.indmoney.com/stocks/u-h-zaveri-ltd-share-price"/>
-    <hyperlink ref="B152" r:id="rId301" tooltip="https://www.indmoney.com/stocks/indong-tea-company-ltd-share-price"/>
-    <hyperlink ref="M152" r:id="rId302" tooltip="https://www.indmoney.com/stocks/indong-tea-company-ltd-share-price"/>
-    <hyperlink ref="B153" r:id="rId303" tooltip="https://www.indmoney.com/stocks/exxaro-tiles-ltd-share-price"/>
-    <hyperlink ref="M153" r:id="rId304" tooltip="https://www.indmoney.com/stocks/exxaro-tiles-ltd-share-price"/>
-    <hyperlink ref="B154" r:id="rId305" tooltip="https://www.indmoney.com/stocks/purple-agrotech-industries-ltd-share-price"/>
-    <hyperlink ref="M154" r:id="rId306" tooltip="https://www.indmoney.com/stocks/purple-agrotech-industries-ltd-share-price"/>
-    <hyperlink ref="B155" r:id="rId307" tooltip="https://www.indmoney.com/stocks/aki-india-ltd-share-price"/>
-    <hyperlink ref="M155" r:id="rId308" tooltip="https://www.indmoney.com/stocks/aki-india-ltd-share-price"/>
-    <hyperlink ref="B156" r:id="rId309" tooltip="https://www.indmoney.com/stocks/creative-eye-ltd-share-price"/>
-    <hyperlink ref="M156" r:id="rId310" tooltip="https://www.indmoney.com/stocks/creative-eye-ltd-share-price"/>
-    <hyperlink ref="B157" r:id="rId311" tooltip="https://www.indmoney.com/stocks/vista-pharmaceuticals-ltd-share-price"/>
-    <hyperlink ref="M157" r:id="rId312" tooltip="https://www.indmoney.com/stocks/vista-pharmaceuticals-ltd-share-price"/>
-    <hyperlink ref="B158" r:id="rId313" tooltip="https://www.indmoney.com/stocks/landmark-property-development-company-ltd-share-price"/>
-    <hyperlink ref="M158" r:id="rId314" tooltip="https://www.indmoney.com/stocks/landmark-property-development-company-ltd-share-price"/>
-    <hyperlink ref="B159" r:id="rId315" tooltip="https://www.indmoney.com/stocks/sikko-industries-ltd-share-price"/>
-    <hyperlink ref="M159" r:id="rId316" tooltip="https://www.indmoney.com/stocks/sikko-industries-ltd-share-price"/>
-    <hyperlink ref="B160" r:id="rId317" tooltip="https://www.indmoney.com/stocks/heera-ispat-ltd-share-price"/>
-    <hyperlink ref="M160" r:id="rId318" tooltip="https://www.indmoney.com/stocks/heera-ispat-ltd-share-price"/>
-    <hyperlink ref="B161" r:id="rId319" tooltip="https://www.indmoney.com/stocks/zee-learn-ltd-share-price"/>
-    <hyperlink ref="M161" r:id="rId320" tooltip="https://www.indmoney.com/stocks/zee-learn-ltd-share-price"/>
-    <hyperlink ref="B162" r:id="rId321" tooltip="https://www.indmoney.com/stocks/hlv-ltd-share-price"/>
-    <hyperlink ref="M162" r:id="rId322" tooltip="https://www.indmoney.com/stocks/hlv-ltd-share-price"/>
-    <hyperlink ref="B163" r:id="rId323" tooltip="https://www.indmoney.com/stocks/country-condos-ltd-share-price"/>
-    <hyperlink ref="M163" r:id="rId324" tooltip="https://www.indmoney.com/stocks/country-condos-ltd-share-price"/>
-    <hyperlink ref="B164" r:id="rId325" tooltip="https://www.indmoney.com/stocks/ladam-affordable-housing-ltd-share-price"/>
-    <hyperlink ref="M164" r:id="rId326" tooltip="https://www.indmoney.com/stocks/ladam-affordable-housing-ltd-share-price"/>
-    <hyperlink ref="B165" r:id="rId327" tooltip="https://www.indmoney.com/stocks/tirupati-innovar-limited-share-price"/>
-    <hyperlink ref="M165" r:id="rId328" tooltip="https://www.indmoney.com/stocks/tirupati-innovar-limited-share-price"/>
-    <hyperlink ref="B166" r:id="rId329" tooltip="https://www.indmoney.com/stocks/tijaria-polypipes-ltd-share-price"/>
-    <hyperlink ref="M166" r:id="rId330" tooltip="https://www.indmoney.com/stocks/tijaria-polypipes-ltd-share-price"/>
-    <hyperlink ref="B167" r:id="rId331" tooltip="https://www.indmoney.com/stocks/bothra-metals-and-alloys-ltd-share-price"/>
-    <hyperlink ref="M167" r:id="rId332" tooltip="https://www.indmoney.com/stocks/bothra-metals-and-alloys-ltd-share-price"/>
-    <hyperlink ref="B168" r:id="rId333" tooltip="https://www.indmoney.com/stocks/deepak-builders-and-engineers-india-ltd-share-price"/>
-    <hyperlink ref="M168" r:id="rId334" tooltip="https://www.indmoney.com/stocks/deepak-builders-and-engineers-india-ltd-share-price"/>
-    <hyperlink ref="B169" r:id="rId335" tooltip="https://www.indmoney.com/stocks/impex-ferro-tech-ltd-share-price"/>
-    <hyperlink ref="M169" r:id="rId336" tooltip="https://www.indmoney.com/stocks/impex-ferro-tech-ltd-share-price"/>
-    <hyperlink ref="B170" r:id="rId337" tooltip="https://www.indmoney.com/stocks/terraform-realstate-ltd-share-price"/>
-    <hyperlink ref="M170" r:id="rId338" tooltip="https://www.indmoney.com/stocks/terraform-realstate-ltd-share-price"/>
-    <hyperlink ref="B171" r:id="rId339" tooltip="https://www.indmoney.com/stocks/kkalpana-industries-india-ltd-share-price"/>
-    <hyperlink ref="M171" r:id="rId340" tooltip="https://www.indmoney.com/stocks/kkalpana-industries-india-ltd-share-price"/>
-    <hyperlink ref="B172" r:id="rId341" tooltip="https://www.indmoney.com/stocks/nila-infrastructures-ltd-share-price"/>
-    <hyperlink ref="M172" r:id="rId342" tooltip="https://www.indmoney.com/stocks/nila-infrastructures-ltd-share-price"/>
-    <hyperlink ref="B173" r:id="rId343" tooltip="https://www.indmoney.com/stocks/mos-utility-ltd-share-price"/>
-    <hyperlink ref="M173" r:id="rId344" tooltip="https://www.indmoney.com/stocks/mos-utility-ltd-share-price"/>
-    <hyperlink ref="B174" r:id="rId345" tooltip="https://www.indmoney.com/stocks/bits-ltd-share-price"/>
-    <hyperlink ref="M174" r:id="rId346" tooltip="https://www.indmoney.com/stocks/bits-ltd-share-price"/>
-    <hyperlink ref="B175" r:id="rId347" tooltip="https://www.indmoney.com/stocks/orosil-smiths-india-ltd-share-price"/>
-    <hyperlink ref="M175" r:id="rId348" tooltip="https://www.indmoney.com/stocks/orosil-smiths-india-ltd-share-price"/>
-    <hyperlink ref="B176" r:id="rId349" tooltip="https://www.indmoney.com/stocks/kmf-builders-and-developers-ltd-share-price"/>
-    <hyperlink ref="M176" r:id="rId350" tooltip="https://www.indmoney.com/stocks/kmf-builders-and-developers-ltd-share-price"/>
-    <hyperlink ref="B177" r:id="rId351" tooltip="https://www.indmoney.com/stocks/avro-india-ltd-share-price"/>
-    <hyperlink ref="M177" r:id="rId352" tooltip="https://www.indmoney.com/stocks/avro-india-ltd-share-price"/>
-    <hyperlink ref="B178" r:id="rId353" tooltip="https://www.indmoney.com/stocks/simbhaoli-sugars-ltd-share-price"/>
-    <hyperlink ref="M178" r:id="rId354" tooltip="https://www.indmoney.com/stocks/simbhaoli-sugars-ltd-share-price"/>
-    <hyperlink ref="B179" r:id="rId355" tooltip="https://www.indmoney.com/stocks/rattanindia-power-ltd-share-price"/>
-    <hyperlink ref="M179" r:id="rId356" tooltip="https://www.indmoney.com/stocks/rattanindia-power-ltd-share-price"/>
-    <hyperlink ref="B180" r:id="rId357" tooltip="https://www.indmoney.com/stocks/india-power-corporation-ltd-share-price"/>
-    <hyperlink ref="M180" r:id="rId358" tooltip="https://www.indmoney.com/stocks/india-power-corporation-ltd-share-price"/>
-    <hyperlink ref="B181" r:id="rId359" tooltip="https://www.indmoney.com/stocks/precision-metaliks-ltd-share-price"/>
-    <hyperlink ref="M181" r:id="rId360" tooltip="https://www.indmoney.com/stocks/precision-metaliks-ltd-share-price"/>
-    <hyperlink ref="B182" r:id="rId361" tooltip="https://www.indmoney.com/stocks/sadbhav-engineering-ltd-share-price"/>
-    <hyperlink ref="M182" r:id="rId362" tooltip="https://www.indmoney.com/stocks/sadbhav-engineering-ltd-share-price"/>
-    <hyperlink ref="B183" r:id="rId363" tooltip="https://www.indmoney.com/stocks/gtl-ltd-share-price"/>
-    <hyperlink ref="M183" r:id="rId364" tooltip="https://www.indmoney.com/stocks/gtl-ltd-share-price"/>
-    <hyperlink ref="B184" r:id="rId365" tooltip="https://www.indmoney.com/stocks/vas-infrastructure-ltd-share-price"/>
-    <hyperlink ref="M184" r:id="rId366" tooltip="https://www.indmoney.com/stocks/vas-infrastructure-ltd-share-price"/>
-    <hyperlink ref="B185" r:id="rId367" tooltip="https://www.indmoney.com/stocks/bgil-films-and-technologies-ltd-share-price"/>
-    <hyperlink ref="M185" r:id="rId368" tooltip="https://www.indmoney.com/stocks/bgil-films-and-technologies-ltd-share-price"/>
-    <hyperlink ref="B186" r:id="rId369" tooltip="https://www.indmoney.com/stocks/dr-lalchandani-labs-ltd-share-price"/>
-    <hyperlink ref="M186" r:id="rId370" tooltip="https://www.indmoney.com/stocks/dr-lalchandani-labs-ltd-share-price"/>
-    <hyperlink ref="B187" r:id="rId371" tooltip="https://www.indmoney.com/stocks/parvati-sweetners-and-power-ltd-share-price"/>
-    <hyperlink ref="M187" r:id="rId372" tooltip="https://www.indmoney.com/stocks/parvati-sweetners-and-power-ltd-share-price"/>
-    <hyperlink ref="B188" r:id="rId373" tooltip="https://www.indmoney.com/stocks/velan-hotels-ltd-share-price"/>
-    <hyperlink ref="M188" r:id="rId374" tooltip="https://www.indmoney.com/stocks/velan-hotels-ltd-share-price"/>
-    <hyperlink ref="B189" r:id="rId375" tooltip="https://www.indmoney.com/stocks/trescon-ltd-share-price"/>
-    <hyperlink ref="M189" r:id="rId376" tooltip="https://www.indmoney.com/stocks/trescon-ltd-share-price"/>
-    <hyperlink ref="B190" r:id="rId377" tooltip="https://www.indmoney.com/stocks/alok-industries-ltd-share-price"/>
-    <hyperlink ref="M190" r:id="rId378" tooltip="https://www.indmoney.com/stocks/alok-industries-ltd-share-price"/>
-    <hyperlink ref="B191" r:id="rId379" tooltip="https://www.indmoney.com/stocks/aksh-optifibre-ltd-share-price"/>
-    <hyperlink ref="M191" r:id="rId380" tooltip="https://www.indmoney.com/stocks/aksh-optifibre-ltd-share-price"/>
-    <hyperlink ref="B192" r:id="rId381" tooltip="https://www.indmoney.com/stocks/bodhi-tree-multimedia-ltd-share-price"/>
-    <hyperlink ref="M192" r:id="rId382" tooltip="https://www.indmoney.com/stocks/bodhi-tree-multimedia-ltd-share-price"/>
-    <hyperlink ref="B193" r:id="rId383" tooltip="https://www.indmoney.com/stocks/manor-estates-and-industries-ltd-share-price"/>
-    <hyperlink ref="M193" r:id="rId384" tooltip="https://www.indmoney.com/stocks/manor-estates-and-industries-ltd-share-price"/>
-    <hyperlink ref="B194" r:id="rId385" tooltip="https://www.indmoney.com/stocks/mauria-udyog-ltd-share-price"/>
-    <hyperlink ref="M194" r:id="rId386" tooltip="https://www.indmoney.com/stocks/mauria-udyog-ltd-share-price"/>
-    <hyperlink ref="B195" r:id="rId387" tooltip="https://www.indmoney.com/stocks/zee-media-corporation-ltd-share-price"/>
-    <hyperlink ref="M195" r:id="rId388" tooltip="https://www.indmoney.com/stocks/zee-media-corporation-ltd-share-price"/>
-    <hyperlink ref="B196" r:id="rId389" tooltip="https://www.indmoney.com/stocks/aruna-hotels-ltd-share-price"/>
-    <hyperlink ref="M196" r:id="rId390" tooltip="https://www.indmoney.com/stocks/aruna-hotels-ltd-share-price"/>
-    <hyperlink ref="B197" r:id="rId391" tooltip="https://www.indmoney.com/stocks/triveni-glass-ltd-share-price"/>
-    <hyperlink ref="M197" r:id="rId392" tooltip="https://www.indmoney.com/stocks/triveni-glass-ltd-share-price"/>
-    <hyperlink ref="B198" r:id="rId393" tooltip="https://www.indmoney.com/stocks/madhav-infra-projects-ltd-share-price"/>
-    <hyperlink ref="M198" r:id="rId394" tooltip="https://www.indmoney.com/stocks/madhav-infra-projects-ltd-share-price"/>
-    <hyperlink ref="B199" r:id="rId395" tooltip="https://www.indmoney.com/stocks/shreyas-intermediates-ltd-share-price"/>
-    <hyperlink ref="M199" r:id="rId396" tooltip="https://www.indmoney.com/stocks/shreyas-intermediates-ltd-share-price"/>
-    <hyperlink ref="B200" r:id="rId397" tooltip="https://www.indmoney.com/stocks/gayatri-sugars-ltd-share-price"/>
-    <hyperlink ref="M200" r:id="rId398" tooltip="https://www.indmoney.com/stocks/gayatri-sugars-ltd-share-price"/>
-    <hyperlink ref="B201" r:id="rId399" tooltip="https://www.indmoney.com/stocks/city-online-services-ltd-share-price"/>
-    <hyperlink ref="M201" r:id="rId400" tooltip="https://www.indmoney.com/stocks/city-online-services-ltd-share-price"/>
-    <hyperlink ref="B202" r:id="rId401" tooltip="https://www.indmoney.com/stocks/dolphin-kitchen-utensils-and-appliances-limited-share-price"/>
-    <hyperlink ref="M202" r:id="rId402" tooltip="https://www.indmoney.com/stocks/dolphin-kitchen-utensils-and-appliances-limited-share-price"/>
-    <hyperlink ref="B203" r:id="rId403" tooltip="https://www.indmoney.com/stocks/pil-italica-lifestyle-ltd-share-price"/>
-    <hyperlink ref="M203" r:id="rId404" tooltip="https://www.indmoney.com/stocks/pil-italica-lifestyle-ltd-share-price"/>
-    <hyperlink ref="B204" r:id="rId405" tooltip="https://www.indmoney.com/stocks/tirupati-sarjan-ltd-share-price"/>
-    <hyperlink ref="M204" r:id="rId406" tooltip="https://www.indmoney.com/stocks/tirupati-sarjan-ltd-share-price"/>
-    <hyperlink ref="B205" r:id="rId407" tooltip="https://www.indmoney.com/stocks/restile-ceramics-ltd-share-price"/>
-    <hyperlink ref="M205" r:id="rId408" tooltip="https://www.indmoney.com/stocks/restile-ceramics-ltd-share-price"/>
-    <hyperlink ref="B206" r:id="rId409" tooltip="https://www.indmoney.com/stocks/terraform-magnum-ltd-share-price"/>
-    <hyperlink ref="M206" r:id="rId410" tooltip="https://www.indmoney.com/stocks/terraform-magnum-ltd-share-price"/>
-    <hyperlink ref="B207" r:id="rId411" tooltip="https://www.indmoney.com/stocks/axita-cotton-ltd-share-price"/>
-    <hyperlink ref="M207" r:id="rId412" tooltip="https://www.indmoney.com/stocks/axita-cotton-ltd-share-price"/>
-    <hyperlink ref="B208" r:id="rId413" tooltip="https://www.indmoney.com/stocks/shree-karthik-papers-ltd-share-price"/>
-    <hyperlink ref="M208" r:id="rId414" tooltip="https://www.indmoney.com/stocks/shree-karthik-papers-ltd-share-price"/>
-    <hyperlink ref="B209" r:id="rId415" tooltip="https://www.indmoney.com/stocks/alankit-ltd-share-price"/>
-    <hyperlink ref="M209" r:id="rId416" tooltip="https://www.indmoney.com/stocks/alankit-ltd-share-price"/>
-    <hyperlink ref="B210" r:id="rId417" tooltip="https://www.indmoney.com/stocks/captain-pipes-ltd-share-price"/>
-    <hyperlink ref="M210" r:id="rId418" tooltip="https://www.indmoney.com/stocks/captain-pipes-ltd-share-price"/>
-    <hyperlink ref="B211" r:id="rId419" tooltip="https://www.indmoney.com/stocks/gvp-infotech-ltd-share-price"/>
-    <hyperlink ref="M211" r:id="rId420" tooltip="https://www.indmoney.com/stocks/gvp-infotech-ltd-share-price"/>
-    <hyperlink ref="B212" r:id="rId421" tooltip="https://www.indmoney.com/stocks/elitecon-international-ltd-share-price"/>
-    <hyperlink ref="M212" r:id="rId422" tooltip="https://www.indmoney.com/stocks/elitecon-international-ltd-share-price"/>
-    <hyperlink ref="B213" r:id="rId423" tooltip="https://www.indmoney.com/stocks/twamev-construction-and-infrastructure-ltd-share-price"/>
-    <hyperlink ref="M213" r:id="rId424" tooltip="https://www.indmoney.com/stocks/twamev-construction-and-infrastructure-ltd-share-price"/>
-    <hyperlink ref="B214" r:id="rId425" tooltip="https://www.indmoney.com/stocks/t-t-ltd-share-price"/>
-    <hyperlink ref="M214" r:id="rId426" tooltip="https://www.indmoney.com/stocks/t-t-ltd-share-price"/>
-    <hyperlink ref="B215" r:id="rId427" tooltip="https://www.indmoney.com/stocks/picturehouse-media-ltd-share-price"/>
-    <hyperlink ref="M215" r:id="rId428" tooltip="https://www.indmoney.com/stocks/picturehouse-media-ltd-share-price"/>
-    <hyperlink ref="B216" r:id="rId429" tooltip="https://www.indmoney.com/stocks/magenta-lifecare-ltd-share-price"/>
-    <hyperlink ref="M216" r:id="rId430" tooltip="https://www.indmoney.com/stocks/magenta-lifecare-ltd-share-price"/>
-    <hyperlink ref="B217" r:id="rId431" tooltip="https://www.indmoney.com/stocks/ultracab-india-ltd-share-price"/>
-    <hyperlink ref="M217" r:id="rId432" tooltip="https://www.indmoney.com/stocks/ultracab-india-ltd-share-price"/>
-    <hyperlink ref="B218" r:id="rId433" tooltip="https://www.indmoney.com/stocks/starlineps-enterprises-ltd-share-price"/>
-    <hyperlink ref="M218" r:id="rId434" tooltip="https://www.indmoney.com/stocks/starlineps-enterprises-ltd-share-price"/>
-    <hyperlink ref="B219" r:id="rId435" tooltip="https://www.indmoney.com/stocks/chartered-logistics-ltd-share-price"/>
-    <hyperlink ref="M219" r:id="rId436" tooltip="https://www.indmoney.com/stocks/chartered-logistics-ltd-share-price"/>
-    <hyperlink ref="B220" r:id="rId437" tooltip="https://www.indmoney.com/stocks/sibar-auto-parts-ltd-share-price"/>
-    <hyperlink ref="M220" r:id="rId438" tooltip="https://www.indmoney.com/stocks/sibar-auto-parts-ltd-share-price"/>
-    <hyperlink ref="B221" r:id="rId439" tooltip="https://www.indmoney.com/stocks/super-tannery-ltd-share-price"/>
-    <hyperlink ref="M221" r:id="rId440" tooltip="https://www.indmoney.com/stocks/super-tannery-ltd-share-price"/>
-    <hyperlink ref="B222" r:id="rId441" tooltip="https://www.indmoney.com/stocks/hampton-sky-realty-ltd-share-price"/>
-    <hyperlink ref="M222" r:id="rId442" tooltip="https://www.indmoney.com/stocks/hampton-sky-realty-ltd-share-price"/>
-    <hyperlink ref="B223" r:id="rId443" tooltip="https://www.indmoney.com/stocks/aditya-ispat-ltd-share-price"/>
-    <hyperlink ref="M223" r:id="rId444" tooltip="https://www.indmoney.com/stocks/aditya-ispat-ltd-share-price"/>
-    <hyperlink ref="B224" r:id="rId445" tooltip="https://www.indmoney.com/stocks/square-four-projects-india-ltd-share-price"/>
-    <hyperlink ref="M224" r:id="rId446" tooltip="https://www.indmoney.com/stocks/square-four-projects-india-ltd-share-price"/>
-    <hyperlink ref="B225" r:id="rId447" tooltip="https://www.indmoney.com/stocks/telogica-ltd-share-price"/>
-    <hyperlink ref="M225" r:id="rId448" tooltip="https://www.indmoney.com/stocks/telogica-ltd-share-price"/>
-    <hyperlink ref="B226" r:id="rId449" tooltip="https://www.indmoney.com/stocks/prime-urban-development-india-ltd-share-price"/>
-    <hyperlink ref="M226" r:id="rId450" tooltip="https://www.indmoney.com/stocks/prime-urban-development-india-ltd-share-price"/>
-    <hyperlink ref="B227" r:id="rId451" tooltip="https://www.indmoney.com/stocks/bharat-immunological-and-biological-corporation-ltd-share-price"/>
-    <hyperlink ref="M227" r:id="rId452" tooltip="https://www.indmoney.com/stocks/bharat-immunological-and-biological-corporation-ltd-share-price"/>
-    <hyperlink ref="B228" r:id="rId453" tooltip="https://www.indmoney.com/stocks/aakash-exploration-services-ltd-share-price"/>
-    <hyperlink ref="M228" r:id="rId454" tooltip="https://www.indmoney.com/stocks/aakash-exploration-services-ltd-share-price"/>
-    <hyperlink ref="B229" r:id="rId455" tooltip="https://www.indmoney.com/stocks/vaishali-pharma-ltd-share-price"/>
-    <hyperlink ref="M229" r:id="rId456" tooltip="https://www.indmoney.com/stocks/vaishali-pharma-ltd-share-price"/>
-    <hyperlink ref="B230" r:id="rId457" tooltip="https://www.indmoney.com/stocks/indowind-energy-ltd-share-price"/>
-    <hyperlink ref="M230" r:id="rId458" tooltip="https://www.indmoney.com/stocks/indowind-energy-ltd-share-price"/>
-    <hyperlink ref="B231" r:id="rId459" tooltip="https://www.indmoney.com/stocks/lorenzini-apparels-ltd-share-price"/>
-    <hyperlink ref="M231" r:id="rId460" tooltip="https://www.indmoney.com/stocks/lorenzini-apparels-ltd-share-price"/>
-    <hyperlink ref="B232" r:id="rId461" tooltip="https://www.indmoney.com/stocks/equilateral-enterprises-ltd-share-price"/>
-    <hyperlink ref="M232" r:id="rId462" tooltip="https://www.indmoney.com/stocks/equilateral-enterprises-ltd-share-price"/>
-    <hyperlink ref="B233" r:id="rId463" tooltip="https://www.indmoney.com/stocks/benara-bearings-and-pistons-ltd-share-price"/>
-    <hyperlink ref="M233" r:id="rId464" tooltip="https://www.indmoney.com/stocks/benara-bearings-and-pistons-ltd-share-price"/>
-    <hyperlink ref="B234" r:id="rId465" tooltip="https://www.indmoney.com/stocks/vallabh-steels-ltd-share-price"/>
-    <hyperlink ref="M234" r:id="rId466" tooltip="https://www.indmoney.com/stocks/vallabh-steels-ltd-share-price"/>
-    <hyperlink ref="B235" r:id="rId467" tooltip="https://www.indmoney.com/stocks/urja-global-ltd-share-price"/>
-    <hyperlink ref="M235" r:id="rId468" tooltip="https://www.indmoney.com/stocks/urja-global-ltd-share-price"/>
-    <hyperlink ref="B236" r:id="rId469" tooltip="https://www.indmoney.com/stocks/chadha-papers-ltd-share-price"/>
-    <hyperlink ref="M236" r:id="rId470" tooltip="https://www.indmoney.com/stocks/chadha-papers-ltd-share-price"/>
-    <hyperlink ref="B237" r:id="rId471" tooltip="https://www.indmoney.com/stocks/orient-green-power-company-ltd-share-price"/>
-    <hyperlink ref="M237" r:id="rId472" tooltip="https://www.indmoney.com/stocks/orient-green-power-company-ltd-share-price"/>
-    <hyperlink ref="B238" r:id="rId473" tooltip="https://www.indmoney.com/stocks/studio-lsd-ltd-share-price"/>
-    <hyperlink ref="M238" r:id="rId474" tooltip="https://www.indmoney.com/stocks/studio-lsd-ltd-share-price"/>
-    <hyperlink ref="B239" r:id="rId475" tooltip="https://www.indmoney.com/stocks/allcargo-terminals-ltd-partly-paidup-share-price"/>
-    <hyperlink ref="M239" r:id="rId476" tooltip="https://www.indmoney.com/stocks/allcargo-terminals-ltd-partly-paidup-share-price"/>
-    <hyperlink ref="B240" r:id="rId477" tooltip="https://www.indmoney.com/stocks/rajasthan-tube-manufacturing-co-ltd-share-price"/>
-    <hyperlink ref="M240" r:id="rId478" tooltip="https://www.indmoney.com/stocks/rajasthan-tube-manufacturing-co-ltd-share-price"/>
-    <hyperlink ref="B241" r:id="rId479" tooltip="https://www.indmoney.com/stocks/jyoti-structures-ltd-share-price"/>
-    <hyperlink ref="M241" r:id="rId480" tooltip="https://www.indmoney.com/stocks/jyoti-structures-ltd-share-price"/>
-    <hyperlink ref="B242" r:id="rId481" tooltip="https://www.indmoney.com/stocks/shreeji-translogistics-ltd-share-price"/>
-    <hyperlink ref="M242" r:id="rId482" tooltip="https://www.indmoney.com/stocks/shreeji-translogistics-ltd-share-price"/>
-    <hyperlink ref="B243" r:id="rId483" tooltip="https://www.indmoney.com/stocks/shukra-jewellery-ltd-share-price"/>
-    <hyperlink ref="M243" r:id="rId484" tooltip="https://www.indmoney.com/stocks/shukra-jewellery-ltd-share-price"/>
-    <hyperlink ref="B244" r:id="rId485" tooltip="https://www.indmoney.com/stocks/yuvraaj-hygiene-products-ltd-share-price"/>
-    <hyperlink ref="M244" r:id="rId486" tooltip="https://www.indmoney.com/stocks/yuvraaj-hygiene-products-ltd-share-price"/>
-    <hyperlink ref="B245" r:id="rId487" tooltip="https://www.indmoney.com/stocks/randb-denims-ltd-share-price"/>
-    <hyperlink ref="M245" r:id="rId488" tooltip="https://www.indmoney.com/stocks/randb-denims-ltd-share-price"/>
-    <hyperlink ref="B246" r:id="rId489" tooltip="https://www.indmoney.com/stocks/baroda-extrusion-ltd-share-price"/>
-    <hyperlink ref="M246" r:id="rId490" tooltip="https://www.indmoney.com/stocks/baroda-extrusion-ltd-share-price"/>
-    <hyperlink ref="B247" r:id="rId491" tooltip="https://www.indmoney.com/stocks/shakti-press-ltd-share-price"/>
-    <hyperlink ref="M247" r:id="rId492" tooltip="https://www.indmoney.com/stocks/shakti-press-ltd-share-price"/>
-    <hyperlink ref="B248" r:id="rId493" tooltip="https://www.indmoney.com/stocks/sharpline-broadcast-ltd-share-price"/>
-    <hyperlink ref="M248" r:id="rId494" tooltip="https://www.indmoney.com/stocks/sharpline-broadcast-ltd-share-price"/>
-    <hyperlink ref="B249" r:id="rId495" tooltip="https://www.indmoney.com/stocks/moksh-ornaments-ltd-share-price"/>
-    <hyperlink ref="M249" r:id="rId496" tooltip="https://www.indmoney.com/stocks/moksh-ornaments-ltd-share-price"/>
-    <hyperlink ref="B250" r:id="rId497" tooltip="https://www.indmoney.com/stocks/coral-newsprints-ltd-share-price"/>
-    <hyperlink ref="M250" r:id="rId498" tooltip="https://www.indmoney.com/stocks/coral-newsprints-ltd-share-price"/>
-    <hyperlink ref="B251" r:id="rId499" tooltip="https://www.indmoney.com/stocks/spicejet-ltd-share-price"/>
-    <hyperlink ref="M251" r:id="rId500" tooltip="https://www.indmoney.com/stocks/spicejet-ltd-share-price"/>
-    <hyperlink ref="B252" r:id="rId501" tooltip="https://www.indmoney.com/stocks/hathway-cable-and-datacom-ltd-share-price"/>
-    <hyperlink ref="M252" r:id="rId502" tooltip="https://www.indmoney.com/stocks/hathway-cable-and-datacom-ltd-share-price"/>
-    <hyperlink ref="B253" r:id="rId503" tooltip="https://www.indmoney.com/stocks/skyline-millars-ltd-share-price"/>
-    <hyperlink ref="M253" r:id="rId504" tooltip="https://www.indmoney.com/stocks/skyline-millars-ltd-share-price"/>
-    <hyperlink ref="B254" r:id="rId505" tooltip="https://www.indmoney.com/stocks/tgb-banquets-and-hotels-ltd-share-price"/>
-    <hyperlink ref="M254" r:id="rId506" tooltip="https://www.indmoney.com/stocks/tgb-banquets-and-hotels-ltd-share-price"/>
-    <hyperlink ref="B255" r:id="rId507" tooltip="https://www.indmoney.com/stocks/inspire-films-ltd-share-price"/>
-    <hyperlink ref="M255" r:id="rId508" tooltip="https://www.indmoney.com/stocks/inspire-films-ltd-share-price"/>
-    <hyperlink ref="B256" r:id="rId509" tooltip="https://www.indmoney.com/stocks/sabar-flex-india-ltd-share-price"/>
-    <hyperlink ref="M256" r:id="rId510" tooltip="https://www.indmoney.com/stocks/sabar-flex-india-ltd-share-price"/>
-    <hyperlink ref="B257" r:id="rId511" tooltip="https://www.indmoney.com/stocks/brightcom-group-ltd-share-price"/>
-    <hyperlink ref="M257" r:id="rId512" tooltip="https://www.indmoney.com/stocks/brightcom-group-ltd-share-price"/>
-    <hyperlink ref="B258" r:id="rId513" tooltip="https://www.indmoney.com/stocks/ambo-agritec-ltd-share-price"/>
-    <hyperlink ref="M258" r:id="rId514" tooltip="https://www.indmoney.com/stocks/ambo-agritec-ltd-share-price"/>
-    <hyperlink ref="B259" r:id="rId515" tooltip="https://www.indmoney.com/stocks/viram-suvarn-ltd-share-price"/>
-    <hyperlink ref="M259" r:id="rId516" tooltip="https://www.indmoney.com/stocks/viram-suvarn-ltd-share-price"/>
-    <hyperlink ref="B260" r:id="rId517" tooltip="https://www.indmoney.com/stocks/looks-health-services-ltd-share-price"/>
-    <hyperlink ref="M260" r:id="rId518" tooltip="https://www.indmoney.com/stocks/looks-health-services-ltd-share-price"/>
-    <hyperlink ref="B261" r:id="rId519" tooltip="https://www.indmoney.com/stocks/kay-power-and-paper-ltd-share-price"/>
-    <hyperlink ref="M261" r:id="rId520" tooltip="https://www.indmoney.com/stocks/kay-power-and-paper-ltd-share-price"/>
-    <hyperlink ref="B262" r:id="rId521" tooltip="https://www.indmoney.com/stocks/gennex-laboratories-ltd-share-price"/>
-    <hyperlink ref="M262" r:id="rId522" tooltip="https://www.indmoney.com/stocks/gennex-laboratories-ltd-share-price"/>
-    <hyperlink ref="B263" r:id="rId523" tooltip="https://www.indmoney.com/stocks/raconteur-global-resources-ltd-share-price"/>
-    <hyperlink ref="M263" r:id="rId524" tooltip="https://www.indmoney.com/stocks/raconteur-global-resources-ltd-share-price"/>
-    <hyperlink ref="B264" r:id="rId525" tooltip="https://www.indmoney.com/stocks/mahalaxmi-seamless-ltd-share-price"/>
-    <hyperlink ref="M264" r:id="rId526" tooltip="https://www.indmoney.com/stocks/mahalaxmi-seamless-ltd-share-price"/>
-    <hyperlink ref="B265" r:id="rId527" tooltip="https://www.indmoney.com/stocks/jfl-life-sciences-ltd-share-price"/>
-    <hyperlink ref="M265" r:id="rId528" tooltip="https://www.indmoney.com/stocks/jfl-life-sciences-ltd-share-price"/>
-    <hyperlink ref="B266" r:id="rId529" tooltip="https://www.indmoney.com/stocks/la-tim-metal-and-industries-ltd-share-price"/>
-    <hyperlink ref="M266" r:id="rId530" tooltip="https://www.indmoney.com/stocks/la-tim-metal-and-industries-ltd-share-price"/>
-    <hyperlink ref="B267" r:id="rId531" tooltip="https://www.indmoney.com/stocks/allcargo-logistics-ltd-share-price"/>
-    <hyperlink ref="M267" r:id="rId532" tooltip="https://www.indmoney.com/stocks/allcargo-logistics-ltd-share-price"/>
-    <hyperlink ref="B268" r:id="rId533" tooltip="https://www.indmoney.com/stocks/boston-commerce-limited-share-price"/>
-    <hyperlink ref="M268" r:id="rId534" tooltip="https://www.indmoney.com/stocks/boston-commerce-limited-share-price"/>
-    <hyperlink ref="B269" r:id="rId535" tooltip="https://www.indmoney.com/stocks/nectar-lifescience-ltd-share-price"/>
-    <hyperlink ref="M269" r:id="rId536" tooltip="https://www.indmoney.com/stocks/nectar-lifescience-ltd-share-price"/>
-    <hyperlink ref="B270" r:id="rId537" tooltip="https://www.indmoney.com/stocks/colorchips-new-media-ltd-share-price"/>
-    <hyperlink ref="M270" r:id="rId538" tooltip="https://www.indmoney.com/stocks/colorchips-new-media-ltd-share-price"/>
-    <hyperlink ref="B271" r:id="rId539" tooltip="https://www.indmoney.com/stocks/sumeet-industries-ltd-share-price"/>
-    <hyperlink ref="M271" r:id="rId540" tooltip="https://www.indmoney.com/stocks/sumeet-industries-ltd-share-price"/>
-    <hyperlink ref="B272" r:id="rId541" tooltip="https://www.indmoney.com/stocks/gourmet-gateway-india-ltd-share-price"/>
-    <hyperlink ref="M272" r:id="rId542" tooltip="https://www.indmoney.com/stocks/gourmet-gateway-india-ltd-share-price"/>
-    <hyperlink ref="B273" r:id="rId543" tooltip="https://www.indmoney.com/stocks/gujarat-winding-systems-ltd-share-price"/>
-    <hyperlink ref="M273" r:id="rId544" tooltip="https://www.indmoney.com/stocks/gujarat-winding-systems-ltd-share-price"/>
-    <hyperlink ref="B274" r:id="rId545" tooltip="https://www.indmoney.com/stocks/max-heights-infrastructure-ltd-share-price"/>
-    <hyperlink ref="M274" r:id="rId546" tooltip="https://www.indmoney.com/stocks/max-heights-infrastructure-ltd-share-price"/>
-    <hyperlink ref="B275" r:id="rId547" tooltip="https://www.indmoney.com/stocks/shiva-granito-export-ltd-share-price"/>
-    <hyperlink ref="M275" r:id="rId548" tooltip="https://www.indmoney.com/stocks/shiva-granito-export-ltd-share-price"/>
-    <hyperlink ref="B276" r:id="rId549" tooltip="https://www.indmoney.com/stocks/genus-paper-and-boards-ltd-share-price"/>
-    <hyperlink ref="M276" r:id="rId550" tooltip="https://www.indmoney.com/stocks/genus-paper-and-boards-ltd-share-price"/>
-    <hyperlink ref="B277" r:id="rId551" tooltip="https://www.indmoney.com/stocks/lexus-granito-india-ltd-share-price"/>
-    <hyperlink ref="M277" r:id="rId552" tooltip="https://www.indmoney.com/stocks/lexus-granito-india-ltd-share-price"/>
-    <hyperlink ref="B278" r:id="rId553" tooltip="https://www.indmoney.com/stocks/vipul-ltd-share-price"/>
-    <hyperlink ref="M278" r:id="rId554" tooltip="https://www.indmoney.com/stocks/vipul-ltd-share-price"/>
-    <hyperlink ref="B279" r:id="rId555" tooltip="https://www.indmoney.com/stocks/goel-food-products-ltd-share-price"/>
-    <hyperlink ref="M279" r:id="rId556" tooltip="https://www.indmoney.com/stocks/goel-food-products-ltd-share-price"/>
-    <hyperlink ref="B280" r:id="rId557" tooltip="https://www.indmoney.com/stocks/raj-television-network-ltd-share-price"/>
-    <hyperlink ref="M280" r:id="rId558" tooltip="https://www.indmoney.com/stocks/raj-television-network-ltd-share-price"/>
-    <hyperlink ref="B281" r:id="rId559" tooltip="https://www.indmoney.com/stocks/uniinfo-telecom-services-ltd-share-price"/>
-    <hyperlink ref="M281" r:id="rId560" tooltip="https://www.indmoney.com/stocks/uniinfo-telecom-services-ltd-share-price"/>
-    <hyperlink ref="B282" r:id="rId561" tooltip="https://www.indmoney.com/stocks/raghunath-international-ltd-share-price"/>
-    <hyperlink ref="M282" r:id="rId562" tooltip="https://www.indmoney.com/stocks/raghunath-international-ltd-share-price"/>
-    <hyperlink ref="B283" r:id="rId563" tooltip="https://www.indmoney.com/stocks/eco-hotels-and-resorts-ltd-share-price"/>
-    <hyperlink ref="M283" r:id="rId564" tooltip="https://www.indmoney.com/stocks/eco-hotels-and-resorts-ltd-share-price"/>
-    <hyperlink ref="B284" r:id="rId565" tooltip="https://www.indmoney.com/stocks/basant-agro-tech-india-ltd-share-price"/>
-    <hyperlink ref="M284" r:id="rId566" tooltip="https://www.indmoney.com/stocks/basant-agro-tech-india-ltd-share-price"/>
-    <hyperlink ref="B285" r:id="rId567" tooltip="https://www.indmoney.com/stocks/chiraharit-ltd-share-price"/>
-    <hyperlink ref="M285" r:id="rId568" tooltip="https://www.indmoney.com/stocks/chiraharit-ltd-share-price"/>
-    <hyperlink ref="B286" r:id="rId569" tooltip="https://www.indmoney.com/stocks/gconnect-logitech-and-supply-chain-ltd-share-price"/>
-    <hyperlink ref="M286" r:id="rId570" tooltip="https://www.indmoney.com/stocks/gconnect-logitech-and-supply-chain-ltd-share-price"/>
-    <hyperlink ref="B287" r:id="rId571" tooltip="https://www.indmoney.com/stocks/lancer-containers-lines-ltd-share-price"/>
-    <hyperlink ref="M287" r:id="rId572" tooltip="https://www.indmoney.com/stocks/lancer-containers-lines-ltd-share-price"/>
-    <hyperlink ref="B288" r:id="rId573" tooltip="https://www.indmoney.com/stocks/h-s-india-ltd-share-price"/>
-    <hyperlink ref="M288" r:id="rId574" tooltip="https://www.indmoney.com/stocks/h-s-india-ltd-share-price"/>
-    <hyperlink ref="B289" r:id="rId575" tooltip="https://www.indmoney.com/stocks/maruti-infrastructure-ltd-share-price"/>
-    <hyperlink ref="M289" r:id="rId576" tooltip="https://www.indmoney.com/stocks/maruti-infrastructure-ltd-share-price"/>
-    <hyperlink ref="B290" r:id="rId577" tooltip="https://www.indmoney.com/stocks/nila-spaces-ltd-share-price"/>
-    <hyperlink ref="M290" r:id="rId578" tooltip="https://www.indmoney.com/stocks/nila-spaces-ltd-share-price"/>
-    <hyperlink ref="B291" r:id="rId579" tooltip="https://www.indmoney.com/stocks/steel-exchange-india-ltd-share-price"/>
-    <hyperlink ref="M291" r:id="rId580" tooltip="https://www.indmoney.com/stocks/steel-exchange-india-ltd-share-price"/>
-    <hyperlink ref="B292" r:id="rId581" tooltip="https://www.indmoney.com/stocks/suvidha-infraestate-corporation-ltd-share-price"/>
-    <hyperlink ref="M292" r:id="rId582" tooltip="https://www.indmoney.com/stocks/suvidha-infraestate-corporation-ltd-share-price"/>
-    <hyperlink ref="B293" r:id="rId583" tooltip="https://www.indmoney.com/stocks/crane-infrastructure-ltd-share-price"/>
-    <hyperlink ref="M293" r:id="rId584" tooltip="https://www.indmoney.com/stocks/crane-infrastructure-ltd-share-price"/>
-    <hyperlink ref="B294" r:id="rId585" tooltip="https://www.indmoney.com/stocks/hathway-bhawani-cabletel-and-datacom-ltd-share-price"/>
-    <hyperlink ref="M294" r:id="rId586" tooltip="https://www.indmoney.com/stocks/hathway-bhawani-cabletel-and-datacom-ltd-share-price"/>
-    <hyperlink ref="B295" r:id="rId587" tooltip="https://www.indmoney.com/stocks/v-r-films-and-studios-ltd-share-price"/>
-    <hyperlink ref="M295" r:id="rId588" tooltip="https://www.indmoney.com/stocks/v-r-films-and-studios-ltd-share-price"/>
-    <hyperlink ref="B296" r:id="rId589" tooltip="https://www.indmoney.com/stocks/shree-precoated-steels-ltd-share-price"/>
-    <hyperlink ref="M296" r:id="rId590" tooltip="https://www.indmoney.com/stocks/shree-precoated-steels-ltd-share-price"/>
-    <hyperlink ref="B297" r:id="rId591" tooltip="https://www.indmoney.com/stocks/chandrima-mercantiles-ltd-share-price"/>
-    <hyperlink ref="M297" r:id="rId592" tooltip="https://www.indmoney.com/stocks/chandrima-mercantiles-ltd-share-price"/>
-    <hyperlink ref="B298" r:id="rId593" tooltip="https://www.indmoney.com/stocks/tamil-nadu-telecommunications-ltd-share-price"/>
-    <hyperlink ref="M298" r:id="rId594" tooltip="https://www.indmoney.com/stocks/tamil-nadu-telecommunications-ltd-share-price"/>
-    <hyperlink ref="B299" r:id="rId595" tooltip="https://www.indmoney.com/stocks/shahi-shipping-ltd-share-price"/>
-    <hyperlink ref="M299" r:id="rId596" tooltip="https://www.indmoney.com/stocks/shahi-shipping-ltd-share-price"/>
-    <hyperlink ref="B300" r:id="rId597" tooltip="https://www.indmoney.com/stocks/inani-marbles-and-industries-ltd-share-price"/>
-    <hyperlink ref="M300" r:id="rId598" tooltip="https://www.indmoney.com/stocks/inani-marbles-and-industries-ltd-share-price"/>
-    <hyperlink ref="B301" r:id="rId599" tooltip="https://www.indmoney.com/stocks/deccan-health-care-ltd-share-price"/>
-    <hyperlink ref="M301" r:id="rId600" tooltip="https://www.indmoney.com/stocks/deccan-health-care-ltd-share-price"/>
-    <hyperlink ref="B302" r:id="rId601" tooltip="https://www.indmoney.com/stocks/earthstahl-and-alloys-ltd-share-price"/>
-    <hyperlink ref="M302" r:id="rId602" tooltip="https://www.indmoney.com/stocks/earthstahl-and-alloys-ltd-share-price"/>
-    <hyperlink ref="B303" r:id="rId603" tooltip="https://www.indmoney.com/stocks/kesar-petroproducts-ltd-share-price"/>
-    <hyperlink ref="M303" r:id="rId604" tooltip="https://www.indmoney.com/stocks/kesar-petroproducts-ltd-share-price"/>
-    <hyperlink ref="B304" r:id="rId605" tooltip="https://www.indmoney.com/stocks/spp-polymer-ltd-share-price"/>
-    <hyperlink ref="M304" r:id="rId606" tooltip="https://www.indmoney.com/stocks/spp-polymer-ltd-share-price"/>
-    <hyperlink ref="B305" r:id="rId607" tooltip="https://www.indmoney.com/stocks/tivoli-construction-ltd-share-price"/>
-    <hyperlink ref="M305" r:id="rId608" tooltip="https://www.indmoney.com/stocks/tivoli-construction-ltd-share-price"/>
-    <hyperlink ref="B306" r:id="rId609" tooltip="https://www.indmoney.com/stocks/global-longlife-hospital-and-research-ltd-share-price"/>
-    <hyperlink ref="M306" r:id="rId610" tooltip="https://www.indmoney.com/stocks/global-longlife-hospital-and-research-ltd-share-price"/>
-    <hyperlink ref="B307" r:id="rId611" tooltip="https://www.indmoney.com/stocks/global-defence-industries-limited-share-price"/>
-    <hyperlink ref="M307" r:id="rId612" tooltip="https://www.indmoney.com/stocks/global-defence-industries-limited-share-price"/>
-    <hyperlink ref="B308" r:id="rId613" tooltip="https://www.indmoney.com/stocks/tarapur-transformers-ltd-share-price"/>
-    <hyperlink ref="M308" r:id="rId614" tooltip="https://www.indmoney.com/stocks/tarapur-transformers-ltd-share-price"/>
-    <hyperlink ref="B309" r:id="rId615" tooltip="https://www.indmoney.com/stocks/bihar-sponge-iron-ltd-share-price"/>
-    <hyperlink ref="M309" r:id="rId616" tooltip="https://www.indmoney.com/stocks/bihar-sponge-iron-ltd-share-price"/>
-    <hyperlink ref="B310" r:id="rId617" tooltip="https://www.indmoney.com/stocks/kellton-tech-solutions-ltd-share-price"/>
-    <hyperlink ref="M310" r:id="rId618" tooltip="https://www.indmoney.com/stocks/kellton-tech-solutions-ltd-share-price"/>
-    <hyperlink ref="B311" r:id="rId619" tooltip="https://www.indmoney.com/stocks/sunraj-diamond-exports-ltd-share-price"/>
-    <hyperlink ref="M311" r:id="rId620" tooltip="https://www.indmoney.com/stocks/sunraj-diamond-exports-ltd-share-price"/>
-    <hyperlink ref="B312" r:id="rId621" tooltip="https://www.indmoney.com/stocks/diggi-multitrade-ltd-share-price"/>
-    <hyperlink ref="M312" r:id="rId622" tooltip="https://www.indmoney.com/stocks/diggi-multitrade-ltd-share-price"/>
-    <hyperlink ref="B313" r:id="rId623" tooltip="https://www.indmoney.com/stocks/kati-patang-lifestyle-ltd-share-price"/>
-    <hyperlink ref="M313" r:id="rId624" tooltip="https://www.indmoney.com/stocks/kati-patang-lifestyle-ltd-share-price"/>
-    <hyperlink ref="B314" r:id="rId625" tooltip="https://www.indmoney.com/stocks/a-b-infrabuild-ltd-share-price"/>
-    <hyperlink ref="M314" r:id="rId626" tooltip="https://www.indmoney.com/stocks/a-b-infrabuild-ltd-share-price"/>
-    <hyperlink ref="B315" r:id="rId627" tooltip="https://www.indmoney.com/stocks/vodafone-idea-ltd-share-price"/>
-    <hyperlink ref="M315" r:id="rId628" tooltip="https://www.indmoney.com/stocks/vodafone-idea-ltd-share-price"/>
-    <hyperlink ref="B316" r:id="rId629" tooltip="https://www.indmoney.com/stocks/take-ltd-share-price"/>
-    <hyperlink ref="M316" r:id="rId630" tooltip="https://www.indmoney.com/stocks/take-ltd-share-price"/>
-    <hyperlink ref="B317" r:id="rId631" tooltip="https://www.indmoney.com/stocks/kesar-enterprises-ltd-share-price"/>
-    <hyperlink ref="M317" r:id="rId632" tooltip="https://www.indmoney.com/stocks/kesar-enterprises-ltd-share-price"/>
-    <hyperlink ref="B318" r:id="rId633" tooltip="https://www.indmoney.com/stocks/tejnaksh-healthcare-ltd-share-price"/>
-    <hyperlink ref="M318" r:id="rId634" tooltip="https://www.indmoney.com/stocks/tejnaksh-healthcare-ltd-share-price"/>
-    <hyperlink ref="B319" r:id="rId635" tooltip="https://www.indmoney.com/stocks/nova-iron-and-steel-ltd-share-price"/>
-    <hyperlink ref="M319" r:id="rId636" tooltip="https://www.indmoney.com/stocks/nova-iron-and-steel-ltd-share-price"/>
-    <hyperlink ref="B320" r:id="rId637" tooltip="https://www.indmoney.com/stocks/atal-realtech-ltd-share-price"/>
-    <hyperlink ref="M320" r:id="rId638" tooltip="https://www.indmoney.com/stocks/atal-realtech-ltd-share-price"/>
-    <hyperlink ref="B321" r:id="rId639" tooltip="https://www.indmoney.com/stocks/pc-jeweller-ltd-share-price"/>
-    <hyperlink ref="M321" r:id="rId640" tooltip="https://www.indmoney.com/stocks/pc-jeweller-ltd-share-price"/>
-    <hyperlink ref="B322" r:id="rId641" tooltip="https://www.indmoney.com/stocks/goldstar-power-ltd-share-price"/>
-    <hyperlink ref="M322" r:id="rId642" tooltip="https://www.indmoney.com/stocks/goldstar-power-ltd-share-price"/>
-    <hyperlink ref="B323" r:id="rId643" tooltip="https://www.indmoney.com/stocks/nidan-laboratories-and-healthcare-ltd-share-price"/>
-    <hyperlink ref="M323" r:id="rId644" tooltip="https://www.indmoney.com/stocks/nidan-laboratories-and-healthcare-ltd-share-price"/>
-    <hyperlink ref="B324" r:id="rId645" tooltip="https://www.indmoney.com/stocks/royal-cushion-vinyl-products-ltd-share-price"/>
-    <hyperlink ref="M324" r:id="rId646" tooltip="https://www.indmoney.com/stocks/royal-cushion-vinyl-products-ltd-share-price"/>
-    <hyperlink ref="B325" r:id="rId647" tooltip="https://www.indmoney.com/stocks/shish-industries-ltd-share-price"/>
-    <hyperlink ref="M325" r:id="rId648" tooltip="https://www.indmoney.com/stocks/shish-industries-ltd-share-price"/>
-    <hyperlink ref="B326" r:id="rId649" tooltip="https://www.indmoney.com/stocks/country-club-hospitality-and-holidays-ltd-share-price"/>
-    <hyperlink ref="M326" r:id="rId650" tooltip="https://www.indmoney.com/stocks/country-club-hospitality-and-holidays-ltd-share-price"/>
-    <hyperlink ref="B327" r:id="rId651" tooltip="https://www.indmoney.com/stocks/drc-systems-india-ltd-share-price"/>
-    <hyperlink ref="M327" r:id="rId652" tooltip="https://www.indmoney.com/stocks/drc-systems-india-ltd-share-price"/>
-    <hyperlink ref="B328" r:id="rId653" tooltip="https://www.indmoney.com/stocks/3b-films-ltd-share-price"/>
-    <hyperlink ref="M328" r:id="rId654" tooltip="https://www.indmoney.com/stocks/3b-films-ltd-share-price"/>
-    <hyperlink ref="B329" r:id="rId655" tooltip="https://www.indmoney.com/stocks/compucom-software-ltd-share-price"/>
-    <hyperlink ref="M329" r:id="rId656" tooltip="https://www.indmoney.com/stocks/compucom-software-ltd-share-price"/>
-    <hyperlink ref="B330" r:id="rId657" tooltip="https://www.indmoney.com/stocks/s-m-gold-ltd-share-price"/>
-    <hyperlink ref="M330" r:id="rId658" tooltip="https://www.indmoney.com/stocks/s-m-gold-ltd-share-price"/>
-    <hyperlink ref="B331" r:id="rId659" tooltip="https://www.indmoney.com/stocks/rana-sugars-ltd-share-price"/>
-    <hyperlink ref="M331" r:id="rId660" tooltip="https://www.indmoney.com/stocks/rana-sugars-ltd-share-price"/>
-    <hyperlink ref="B332" r:id="rId661" tooltip="https://www.indmoney.com/stocks/sspdl-ltd-share-price"/>
-    <hyperlink ref="M332" r:id="rId662" tooltip="https://www.indmoney.com/stocks/sspdl-ltd-share-price"/>
-    <hyperlink ref="B333" r:id="rId663" tooltip="https://www.indmoney.com/stocks/patel-integrated-logistics-ltd-share-price"/>
-    <hyperlink ref="M333" r:id="rId664" tooltip="https://www.indmoney.com/stocks/patel-integrated-logistics-ltd-share-price"/>
-    <hyperlink ref="B334" r:id="rId665" tooltip="https://www.indmoney.com/stocks/virinchi-ltd-share-price"/>
-    <hyperlink ref="M334" r:id="rId666" tooltip="https://www.indmoney.com/stocks/virinchi-ltd-share-price"/>
-    <hyperlink ref="B335" r:id="rId667" tooltip="https://www.indmoney.com/stocks/shiva-cement-ltd-share-price"/>
-    <hyperlink ref="M335" r:id="rId668" tooltip="https://www.indmoney.com/stocks/shiva-cement-ltd-share-price"/>
-    <hyperlink ref="B336" r:id="rId669" tooltip="https://www.indmoney.com/stocks/super-crop-safe-ltd-share-price"/>
-    <hyperlink ref="M336" r:id="rId670" tooltip="https://www.indmoney.com/stocks/super-crop-safe-ltd-share-price"/>
-    <hyperlink ref="B337" r:id="rId671" tooltip="https://www.indmoney.com/stocks/utkarsh-small-finance-bank-ltd-share-price"/>
-    <hyperlink ref="M337" r:id="rId672" tooltip="https://www.indmoney.com/stocks/utkarsh-small-finance-bank-ltd-share-price"/>
-    <hyperlink ref="B338" r:id="rId673" tooltip="https://www.indmoney.com/stocks/aritas-vinyl-ltd-share-price"/>
-    <hyperlink ref="M338" r:id="rId674" tooltip="https://www.indmoney.com/stocks/aritas-vinyl-ltd-share-price"/>
-    <hyperlink ref="B339" r:id="rId675" tooltip="https://www.indmoney.com/stocks/consolidated-construction-consortium-ltd-share-price"/>
-    <hyperlink ref="M339" r:id="rId676" tooltip="https://www.indmoney.com/stocks/consolidated-construction-consortium-ltd-share-price"/>
-    <hyperlink ref="B340" r:id="rId677" tooltip="https://www.indmoney.com/stocks/prudential-sugar-corporation-ltd-share-price"/>
-    <hyperlink ref="M340" r:id="rId678" tooltip="https://www.indmoney.com/stocks/prudential-sugar-corporation-ltd-share-price"/>
-    <hyperlink ref="B341" r:id="rId679" tooltip="https://www.indmoney.com/stocks/victory-electric-vehicles-international-ltd-share-price"/>
-    <hyperlink ref="M341" r:id="rId680" tooltip="https://www.indmoney.com/stocks/victory-electric-vehicles-international-ltd-share-price"/>
-    <hyperlink ref="B342" r:id="rId681" tooltip="https://www.indmoney.com/stocks/mediaone-global-entertainment-ltd-share-price"/>
-    <hyperlink ref="M342" r:id="rId682" tooltip="https://www.indmoney.com/stocks/mediaone-global-entertainment-ltd-share-price"/>
-    <hyperlink ref="B343" r:id="rId683" tooltip="https://www.indmoney.com/stocks/cinevista-ltd-share-price"/>
-    <hyperlink ref="M343" r:id="rId684" tooltip="https://www.indmoney.com/stocks/cinevista-ltd-share-price"/>
-    <hyperlink ref="B344" r:id="rId685" tooltip="https://www.indmoney.com/stocks/kenrik-industries-ltd-share-price"/>
-    <hyperlink ref="M344" r:id="rId686" tooltip="https://www.indmoney.com/stocks/kenrik-industries-ltd-share-price"/>
-    <hyperlink ref="B345" r:id="rId687" tooltip="https://www.indmoney.com/stocks/nettlinx-ltd-share-price"/>
-    <hyperlink ref="M345" r:id="rId688" tooltip="https://www.indmoney.com/stocks/nettlinx-ltd-share-price"/>
-    <hyperlink ref="B346" r:id="rId689" tooltip="https://www.indmoney.com/stocks/rtcl-ltd-share-price"/>
-    <hyperlink ref="M346" r:id="rId690" tooltip="https://www.indmoney.com/stocks/rtcl-ltd-share-price"/>
-    <hyperlink ref="B347" r:id="rId691" tooltip="https://www.indmoney.com/stocks/gravity-india-ltd-share-price"/>
-    <hyperlink ref="M347" r:id="rId692" tooltip="https://www.indmoney.com/stocks/gravity-india-ltd-share-price"/>
-    <hyperlink ref="B348" r:id="rId693" tooltip="https://www.indmoney.com/stocks/mukat-pipes-ltd-share-price"/>
-    <hyperlink ref="M348" r:id="rId694" tooltip="https://www.indmoney.com/stocks/mukat-pipes-ltd-share-price"/>
-    <hyperlink ref="B349" r:id="rId695" tooltip="https://www.indmoney.com/stocks/ind-renewable-energy-ltd-share-price"/>
-    <hyperlink ref="M349" r:id="rId696" tooltip="https://www.indmoney.com/stocks/ind-renewable-energy-ltd-share-price"/>
-    <hyperlink ref="B350" r:id="rId697" tooltip="https://www.indmoney.com/stocks/modern-steels-ltd-share-price"/>
-    <hyperlink ref="M350" r:id="rId698" tooltip="https://www.indmoney.com/stocks/modern-steels-ltd-share-price"/>
-    <hyperlink ref="B351" r:id="rId699" tooltip="https://www.indmoney.com/stocks/innovative-tech-pack-ltd-share-price"/>
-    <hyperlink ref="M351" r:id="rId700" tooltip="https://www.indmoney.com/stocks/innovative-tech-pack-ltd-share-price"/>
-    <hyperlink ref="B352" r:id="rId701" tooltip="https://www.indmoney.com/stocks/cityman-ltd-share-price"/>
-    <hyperlink ref="M352" r:id="rId702" tooltip="https://www.indmoney.com/stocks/cityman-ltd-share-price"/>
-    <hyperlink ref="B353" r:id="rId703" tooltip="https://www.indmoney.com/stocks/maks-energy-solutions-india-ltd-share-price"/>
-    <hyperlink ref="M353" r:id="rId704" tooltip="https://www.indmoney.com/stocks/maks-energy-solutions-india-ltd-share-price"/>
-    <hyperlink ref="B354" r:id="rId705" tooltip="https://www.indmoney.com/stocks/a2z-infra-engineering-ltd-share-price"/>
-    <hyperlink ref="M354" r:id="rId706" tooltip="https://www.indmoney.com/stocks/a2z-infra-engineering-ltd-share-price"/>
-    <hyperlink ref="B355" r:id="rId707" tooltip="https://www.indmoney.com/stocks/arcee-industries-ltd-share-price"/>
-    <hyperlink ref="M355" r:id="rId708" tooltip="https://www.indmoney.com/stocks/arcee-industries-ltd-share-price"/>
-    <hyperlink ref="B356" r:id="rId709" tooltip="https://www.indmoney.com/stocks/best-eastern-hotels-ltd-share-price"/>
-    <hyperlink ref="M356" r:id="rId710" tooltip="https://www.indmoney.com/stocks/best-eastern-hotels-ltd-share-price"/>
-    <hyperlink ref="B357" r:id="rId711" tooltip="https://www.indmoney.com/stocks/lords-ishwar-hotels-ltd-share-price"/>
-    <hyperlink ref="M357" r:id="rId712" tooltip="https://www.indmoney.com/stocks/lords-ishwar-hotels-ltd-share-price"/>
-    <hyperlink ref="B358" r:id="rId713" tooltip="https://www.indmoney.com/stocks/marinetrans-india-ltd-share-price"/>
-    <hyperlink ref="M358" r:id="rId714" tooltip="https://www.indmoney.com/stocks/marinetrans-india-ltd-share-price"/>
-    <hyperlink ref="B359" r:id="rId715" tooltip="https://www.indmoney.com/stocks/energy-development-company-ltd-share-price"/>
-    <hyperlink ref="M359" r:id="rId716" tooltip="https://www.indmoney.com/stocks/energy-development-company-ltd-share-price"/>
-    <hyperlink ref="B360" r:id="rId717" tooltip="https://www.indmoney.com/stocks/agni-green-power-ltd-share-price"/>
-    <hyperlink ref="M360" r:id="rId718" tooltip="https://www.indmoney.com/stocks/agni-green-power-ltd-share-price"/>
-    <hyperlink ref="B361" r:id="rId719" tooltip="https://www.indmoney.com/stocks/containe-technologies-ltd-share-price"/>
-    <hyperlink ref="M361" r:id="rId720" tooltip="https://www.indmoney.com/stocks/containe-technologies-ltd-share-price"/>
-    <hyperlink ref="B362" r:id="rId721" tooltip="https://www.indmoney.com/stocks/peninsula-land-ltd-share-price"/>
-    <hyperlink ref="M362" r:id="rId722" tooltip="https://www.indmoney.com/stocks/peninsula-land-ltd-share-price"/>
-    <hyperlink ref="B363" r:id="rId723" tooltip="https://www.indmoney.com/stocks/bohra-industries-ltd-share-price"/>
-    <hyperlink ref="M363" r:id="rId724" tooltip="https://www.indmoney.com/stocks/bohra-industries-ltd-share-price"/>
-    <hyperlink ref="B364" r:id="rId725" tooltip="https://www.indmoney.com/stocks/venmax-drugs-and-pharmaceuticals-ltd-share-price"/>
-    <hyperlink ref="M364" r:id="rId726" tooltip="https://www.indmoney.com/stocks/venmax-drugs-and-pharmaceuticals-ltd-share-price"/>
-    <hyperlink ref="B365" r:id="rId727" tooltip="https://www.indmoney.com/stocks/rdb-infrastructure-and-power-ltd-share-price"/>
-    <hyperlink ref="M365" r:id="rId728" tooltip="https://www.indmoney.com/stocks/rdb-infrastructure-and-power-ltd-share-price"/>
-    <hyperlink ref="B366" r:id="rId729" tooltip="https://www.indmoney.com/stocks/digispice-technologies-ltd-share-price"/>
-    <hyperlink ref="M366" r:id="rId730" tooltip="https://www.indmoney.com/stocks/digispice-technologies-ltd-share-price"/>
-    <hyperlink ref="B367" r:id="rId731" tooltip="https://www.indmoney.com/stocks/jaiprakash-power-ventures-ltd-share-price"/>
-    <hyperlink ref="M367" r:id="rId732" tooltip="https://www.indmoney.com/stocks/jaiprakash-power-ventures-ltd-share-price"/>
-    <hyperlink ref="B368" r:id="rId733" tooltip="https://www.indmoney.com/stocks/hindustan-motors-ltd-share-price"/>
-    <hyperlink ref="M368" r:id="rId734" tooltip="https://www.indmoney.com/stocks/hindustan-motors-ltd-share-price"/>
-    <hyperlink ref="B369" r:id="rId735" tooltip="https://www.indmoney.com/stocks/broach-lifecare-hospital-ltd-share-price"/>
-    <hyperlink ref="M369" r:id="rId736" tooltip="https://www.indmoney.com/stocks/broach-lifecare-hospital-ltd-share-price"/>
-    <hyperlink ref="B370" r:id="rId737" tooltip="https://www.indmoney.com/stocks/popular-estate-management-ltd-share-price"/>
-    <hyperlink ref="M370" r:id="rId738" tooltip="https://www.indmoney.com/stocks/popular-estate-management-ltd-share-price"/>
-    <hyperlink ref="B371" r:id="rId739" tooltip="https://www.indmoney.com/stocks/gaekwar-mills-ltd-share-price"/>
-    <hyperlink ref="M371" r:id="rId740" tooltip="https://www.indmoney.com/stocks/gaekwar-mills-ltd-share-price"/>
-    <hyperlink ref="B372" r:id="rId741" tooltip="https://www.indmoney.com/stocks/aarcon-facilities-ltd-share-price"/>
-    <hyperlink ref="M372" r:id="rId742" tooltip="https://www.indmoney.com/stocks/aarcon-facilities-ltd-share-price"/>
-    <hyperlink ref="B373" r:id="rId743" tooltip="https://www.indmoney.com/stocks/rril-ltd-share-price"/>
-    <hyperlink ref="M373" r:id="rId744" tooltip="https://www.indmoney.com/stocks/rril-ltd-share-price"/>
-    <hyperlink ref="B374" r:id="rId745" tooltip="https://www.indmoney.com/stocks/balurghat-technologies-ltd-share-price"/>
-    <hyperlink ref="M374" r:id="rId746" tooltip="https://www.indmoney.com/stocks/balurghat-technologies-ltd-share-price"/>
-    <hyperlink ref="B375" r:id="rId747" tooltip="https://www.indmoney.com/stocks/enser-communications-ltd-share-price"/>
-    <hyperlink ref="M375" r:id="rId748" tooltip="https://www.indmoney.com/stocks/enser-communications-ltd-share-price"/>
-    <hyperlink ref="B376" r:id="rId749" tooltip="https://www.indmoney.com/stocks/avenuesai-ltd-share-price"/>
-    <hyperlink ref="M376" r:id="rId750" tooltip="https://www.indmoney.com/stocks/avenuesai-ltd-share-price"/>
-    <hyperlink ref="B377" r:id="rId751" tooltip="https://www.indmoney.com/stocks/artemis-electricals-and-projects-ltd-share-price"/>
-    <hyperlink ref="M377" r:id="rId752" tooltip="https://www.indmoney.com/stocks/artemis-electricals-and-projects-ltd-share-price"/>
-    <hyperlink ref="B378" r:id="rId753" tooltip="https://www.indmoney.com/stocks/pavna-industries-ltd-share-price"/>
-    <hyperlink ref="M378" r:id="rId754" tooltip="https://www.indmoney.com/stocks/pavna-industries-ltd-share-price"/>
-    <hyperlink ref="B379" r:id="rId755" tooltip="https://www.indmoney.com/stocks/baba-arts-ltd-share-price"/>
-    <hyperlink ref="M379" r:id="rId756" tooltip="https://www.indmoney.com/stocks/baba-arts-ltd-share-price"/>
-    <hyperlink ref="B380" r:id="rId757" tooltip="https://www.indmoney.com/stocks/aqylon-nexus-ltd-share-price"/>
-    <hyperlink ref="M380" r:id="rId758" tooltip="https://www.indmoney.com/stocks/aqylon-nexus-ltd-share-price"/>
-    <hyperlink ref="B381" r:id="rId759" tooltip="https://www.indmoney.com/stocks/thinking-hats-entertainment-solutions-ltd-share-price"/>
-    <hyperlink ref="M381" r:id="rId760" tooltip="https://www.indmoney.com/stocks/thinking-hats-entertainment-solutions-ltd-share-price"/>
-    <hyperlink ref="B382" r:id="rId761" tooltip="https://www.indmoney.com/stocks/media-matrix-worldwide-ltd-share-price"/>
-    <hyperlink ref="M382" r:id="rId762" tooltip="https://www.indmoney.com/stocks/media-matrix-worldwide-ltd-share-price"/>
-    <hyperlink ref="B383" r:id="rId763" tooltip="https://www.indmoney.com/stocks/modulex-construction-technologies-ltd-share-price"/>
-    <hyperlink ref="M383" r:id="rId764" tooltip="https://www.indmoney.com/stocks/modulex-construction-technologies-ltd-share-price"/>
-    <hyperlink ref="B384" r:id="rId765" tooltip="https://www.indmoney.com/stocks/airan-ltd-share-price"/>
-    <hyperlink ref="M384" r:id="rId766" tooltip="https://www.indmoney.com/stocks/airan-ltd-share-price"/>
-    <hyperlink ref="B385" r:id="rId767" tooltip="https://www.indmoney.com/stocks/eastcoast-steel-ltd-share-price"/>
-    <hyperlink ref="M385" r:id="rId768" tooltip="https://www.indmoney.com/stocks/eastcoast-steel-ltd-share-price"/>
-    <hyperlink ref="B386" r:id="rId769" tooltip="https://www.indmoney.com/stocks/rajeshwari-cans-ltd-share-price"/>
-    <hyperlink ref="M386" r:id="rId770" tooltip="https://www.indmoney.com/stocks/rajeshwari-cans-ltd-share-price"/>
-    <hyperlink ref="B387" r:id="rId771" tooltip="https://www.indmoney.com/stocks/rathi-bars-ltd-share-price"/>
-    <hyperlink ref="M387" r:id="rId772" tooltip="https://www.indmoney.com/stocks/rathi-bars-ltd-share-price"/>
-    <hyperlink ref="B388" r:id="rId773" tooltip="https://www.indmoney.com/stocks/standard-industries-ltd-share-price"/>
-    <hyperlink ref="M388" r:id="rId774" tooltip="https://www.indmoney.com/stocks/standard-industries-ltd-share-price"/>
-    <hyperlink ref="B389" r:id="rId775" tooltip="https://www.indmoney.com/stocks/rushil-decor-ltd-share-price"/>
-    <hyperlink ref="M389" r:id="rId776" tooltip="https://www.indmoney.com/stocks/rushil-decor-ltd-share-price"/>
-    <hyperlink ref="B390" r:id="rId777" tooltip="https://www.indmoney.com/stocks/surana-telecom-and-power-ltd-share-price"/>
-    <hyperlink ref="M390" r:id="rId778" tooltip="https://www.indmoney.com/stocks/surana-telecom-and-power-ltd-share-price"/>
-    <hyperlink ref="B391" r:id="rId779" tooltip="https://www.indmoney.com/stocks/bharat-road-network-ltd-share-price"/>
-    <hyperlink ref="M391" r:id="rId780" tooltip="https://www.indmoney.com/stocks/bharat-road-network-ltd-share-price"/>
-    <hyperlink ref="B392" r:id="rId781" tooltip="https://www.indmoney.com/stocks/swasth-foodtech-india-ltd-share-price"/>
-    <hyperlink ref="M392" r:id="rId782" tooltip="https://www.indmoney.com/stocks/swasth-foodtech-india-ltd-share-price"/>
-    <hyperlink ref="B393" r:id="rId783" tooltip="https://www.indmoney.com/stocks/pritika-auto-industries-ltd-share-price"/>
-    <hyperlink ref="M393" r:id="rId784" tooltip="https://www.indmoney.com/stocks/pritika-auto-industries-ltd-share-price"/>
-    <hyperlink ref="B394" r:id="rId785" tooltip="https://www.indmoney.com/stocks/prima-industries-ltd-share-price"/>
-    <hyperlink ref="M394" r:id="rId786" tooltip="https://www.indmoney.com/stocks/prima-industries-ltd-share-price"/>
-    <hyperlink ref="B395" r:id="rId787" tooltip="https://www.indmoney.com/stocks/poojawestern-metaliks-ltd-share-price"/>
-    <hyperlink ref="M395" r:id="rId788" tooltip="https://www.indmoney.com/stocks/poojawestern-metaliks-ltd-share-price"/>
-    <hyperlink ref="B396" r:id="rId789" tooltip="https://www.indmoney.com/stocks/globus-power-generation-ltd-share-price"/>
-    <hyperlink ref="M396" r:id="rId790" tooltip="https://www.indmoney.com/stocks/globus-power-generation-ltd-share-price"/>
-    <hyperlink ref="B397" r:id="rId791" tooltip="https://www.indmoney.com/stocks/jaysynth-orgochem-ltd-share-price"/>
-    <hyperlink ref="M397" r:id="rId792" tooltip="https://www.indmoney.com/stocks/jaysynth-orgochem-ltd-share-price"/>
-    <hyperlink ref="B398" r:id="rId793" tooltip="https://www.indmoney.com/stocks/orient-paper-and-industries-ltd-share-price"/>
-    <hyperlink ref="M398" r:id="rId794" tooltip="https://www.indmoney.com/stocks/orient-paper-and-industries-ltd-share-price"/>
-    <hyperlink ref="B399" r:id="rId795" tooltip="https://www.indmoney.com/stocks/advance-metering-technology-ltd-share-price"/>
-    <hyperlink ref="M399" r:id="rId796" tooltip="https://www.indmoney.com/stocks/advance-metering-technology-ltd-share-price"/>
-    <hyperlink ref="B400" r:id="rId797" tooltip="https://www.indmoney.com/stocks/rhetan-tmt-ltd-share-price"/>
-    <hyperlink ref="M400" r:id="rId798" tooltip="https://www.indmoney.com/stocks/rhetan-tmt-ltd-share-price"/>
-    <hyperlink ref="B401" r:id="rId799" tooltip="https://www.indmoney.com/stocks/containerway-international-ltd-share-price"/>
-    <hyperlink ref="M401" r:id="rId800" tooltip="https://www.indmoney.com/stocks/containerway-international-ltd-share-price"/>
-    <hyperlink ref="B402" r:id="rId801" tooltip="https://www.indmoney.com/stocks/zinema-media-and-entertainment-ltd-share-price"/>
-    <hyperlink ref="M402" r:id="rId802" tooltip="https://www.indmoney.com/stocks/zinema-media-and-entertainment-ltd-share-price"/>
-    <hyperlink ref="B403" r:id="rId803" tooltip="https://www.indmoney.com/stocks/galaxy-medicare-ltd-share-price"/>
-    <hyperlink ref="M403" r:id="rId804" tooltip="https://www.indmoney.com/stocks/galaxy-medicare-ltd-share-price"/>
-    <hyperlink ref="B404" r:id="rId805" tooltip="https://www.indmoney.com/stocks/irb-infrastructure-developers-ltd-share-price"/>
-    <hyperlink ref="M404" r:id="rId806" tooltip="https://www.indmoney.com/stocks/irb-infrastructure-developers-ltd-share-price"/>
-    <hyperlink ref="B405" r:id="rId807" tooltip="https://www.indmoney.com/stocks/phyto-chem-india-ltd-share-price"/>
-    <hyperlink ref="M405" r:id="rId808" tooltip="https://www.indmoney.com/stocks/phyto-chem-india-ltd-share-price"/>
-    <hyperlink ref="B406" r:id="rId809" tooltip="https://www.indmoney.com/stocks/rajgor-castor-derivatives-ltd-share-price"/>
-    <hyperlink ref="M406" r:id="rId810" tooltip="https://www.indmoney.com/stocks/rajgor-castor-derivatives-ltd-share-price"/>
-    <hyperlink ref="B407" r:id="rId811" tooltip="https://www.indmoney.com/stocks/shivam-autotech-ltd-share-price"/>
-    <hyperlink ref="M407" r:id="rId812" tooltip="https://www.indmoney.com/stocks/shivam-autotech-ltd-share-price"/>
-    <hyperlink ref="B408" r:id="rId813" tooltip="https://www.indmoney.com/stocks/pearl-polymers-ltd-share-price"/>
-    <hyperlink ref="M408" r:id="rId814" tooltip="https://www.indmoney.com/stocks/pearl-polymers-ltd-share-price"/>
-    <hyperlink ref="B409" r:id="rId815" tooltip="https://www.indmoney.com/stocks/vivo-bio-tech-ltd-share-price"/>
-    <hyperlink ref="M409" r:id="rId816" tooltip="https://www.indmoney.com/stocks/vivo-bio-tech-ltd-share-price"/>
-    <hyperlink ref="B410" r:id="rId817" tooltip="https://www.indmoney.com/stocks/kamanwala-housing-construction-ltd-share-price"/>
-    <hyperlink ref="M410" r:id="rId818" tooltip="https://www.indmoney.com/stocks/kamanwala-housing-construction-ltd-share-price"/>
-    <hyperlink ref="B411" r:id="rId819" tooltip="https://www.indmoney.com/stocks/essar-shipping-ltd-share-price"/>
-    <hyperlink ref="M411" r:id="rId820" tooltip="https://www.indmoney.com/stocks/essar-shipping-ltd-share-price"/>
-    <hyperlink ref="B412" r:id="rId821" tooltip="https://www.indmoney.com/stocks/ravikumar-distilleries-ltd-share-price"/>
-    <hyperlink ref="M412" r:id="rId822" tooltip="https://www.indmoney.com/stocks/ravikumar-distilleries-ltd-share-price"/>
-    <hyperlink ref="B413" r:id="rId823" tooltip="https://www.indmoney.com/stocks/adeshwar-meditex-ltd-share-price"/>
-    <hyperlink ref="M413" r:id="rId824" tooltip="https://www.indmoney.com/stocks/adeshwar-meditex-ltd-share-price"/>
-    <hyperlink ref="B414" r:id="rId825" tooltip="https://www.indmoney.com/stocks/shubhlaxmi-jewel-art-ltd-share-price"/>
-    <hyperlink ref="M414" r:id="rId826" tooltip="https://www.indmoney.com/stocks/shubhlaxmi-jewel-art-ltd-share-price"/>
-    <hyperlink ref="B415" r:id="rId827" tooltip="https://www.indmoney.com/stocks/anya-polytech-and-fertilizers-ltd-share-price"/>
-    <hyperlink ref="M415" r:id="rId828" tooltip="https://www.indmoney.com/stocks/anya-polytech-and-fertilizers-ltd-share-price"/>
-    <hyperlink ref="B416" r:id="rId829" tooltip="https://www.indmoney.com/stocks/kanoria-energy-and-infrastructure-ltd-share-price"/>
-    <hyperlink ref="M416" r:id="rId830" tooltip="https://www.indmoney.com/stocks/kanoria-energy-and-infrastructure-ltd-share-price"/>
-    <hyperlink ref="B417" r:id="rId831" tooltip="https://www.indmoney.com/stocks/vishal-fabrics-ltd-share-price"/>
-    <hyperlink ref="M417" r:id="rId832" tooltip="https://www.indmoney.com/stocks/vishal-fabrics-ltd-share-price"/>
-    <hyperlink ref="B418" r:id="rId833" tooltip="https://www.indmoney.com/stocks/best-agrolife-ltd-share-price"/>
-    <hyperlink ref="M418" r:id="rId834" tooltip="https://www.indmoney.com/stocks/best-agrolife-ltd-share-price"/>
-    <hyperlink ref="B419" r:id="rId835" tooltip="https://www.indmoney.com/stocks/sakthi-sugars-ltd-share-price"/>
-    <hyperlink ref="M419" r:id="rId836" tooltip="https://www.indmoney.com/stocks/sakthi-sugars-ltd-share-price"/>
-    <hyperlink ref="B420" r:id="rId837" tooltip="https://www.indmoney.com/stocks/noble-polymers-ltd-share-price"/>
-    <hyperlink ref="M420" r:id="rId838" tooltip="https://www.indmoney.com/stocks/noble-polymers-ltd-share-price"/>
-    <hyperlink ref="B421" r:id="rId839" tooltip="https://www.indmoney.com/stocks/kandr-rail-engineering-ltd-share-price"/>
-    <hyperlink ref="M421" r:id="rId840" tooltip="https://www.indmoney.com/stocks/kandr-rail-engineering-ltd-share-price"/>
-    <hyperlink ref="B422" r:id="rId841" tooltip="https://www.indmoney.com/stocks/rama-paper-mills-ltd-share-price"/>
-    <hyperlink ref="M422" r:id="rId842" tooltip="https://www.indmoney.com/stocks/rama-paper-mills-ltd-share-price"/>
-    <hyperlink ref="B423" r:id="rId843" tooltip="https://www.indmoney.com/stocks/omega-interactive-technologies-ltd-share-price"/>
-    <hyperlink ref="M423" r:id="rId844" tooltip="https://www.indmoney.com/stocks/omega-interactive-technologies-ltd-share-price"/>
-    <hyperlink ref="B424" r:id="rId845" tooltip="https://www.indmoney.com/stocks/sterling-green-woods-ltd-share-price"/>
-    <hyperlink ref="M424" r:id="rId846" tooltip="https://www.indmoney.com/stocks/sterling-green-woods-ltd-share-price"/>
-    <hyperlink ref="B425" r:id="rId847" tooltip="https://www.indmoney.com/stocks/uma-converter-ltd-share-price"/>
-    <hyperlink ref="M425" r:id="rId848" tooltip="https://www.indmoney.com/stocks/uma-converter-ltd-share-price"/>
-    <hyperlink ref="B426" r:id="rId849" tooltip="https://www.indmoney.com/stocks/motisons-jewellers-ltd-share-price"/>
-    <hyperlink ref="M426" r:id="rId850" tooltip="https://www.indmoney.com/stocks/motisons-jewellers-ltd-share-price"/>
-    <hyperlink ref="B427" r:id="rId851" tooltip="https://www.indmoney.com/stocks/g-s-auto-international-ltd-share-price"/>
-    <hyperlink ref="M427" r:id="rId852" tooltip="https://www.indmoney.com/stocks/g-s-auto-international-ltd-share-price"/>
-    <hyperlink ref="B428" r:id="rId853" tooltip="https://www.indmoney.com/stocks/howard-hotels-ltd-share-price"/>
-    <hyperlink ref="M428" r:id="rId854" tooltip="https://www.indmoney.com/stocks/howard-hotels-ltd-share-price"/>
-    <hyperlink ref="B429" r:id="rId855" tooltip="https://www.indmoney.com/stocks/hazoor-multi-projects-ltd-share-price"/>
-    <hyperlink ref="M429" r:id="rId856" tooltip="https://www.indmoney.com/stocks/hazoor-multi-projects-ltd-share-price"/>
-    <hyperlink ref="B430" r:id="rId857" tooltip="https://www.indmoney.com/stocks/cyber-media-india-ltd-share-price"/>
-    <hyperlink ref="M430" r:id="rId858" tooltip="https://www.indmoney.com/stocks/cyber-media-india-ltd-share-price"/>
-    <hyperlink ref="B431" r:id="rId859" tooltip="https://www.indmoney.com/stocks/sdc-techmedia-ltd-share-price"/>
-    <hyperlink ref="M431" r:id="rId860" tooltip="https://www.indmoney.com/stocks/sdc-techmedia-ltd-share-price"/>
-    <hyperlink ref="B432" r:id="rId861" tooltip="https://www.indmoney.com/stocks/pnc-media-and-entertainment-ltd-share-price"/>
-    <hyperlink ref="M432" r:id="rId862" tooltip="https://www.indmoney.com/stocks/pnc-media-and-entertainment-ltd-share-price"/>
-    <hyperlink ref="B433" r:id="rId863" tooltip="https://www.indmoney.com/stocks/setco-automotive-ltd-share-price"/>
-    <hyperlink ref="M433" r:id="rId864" tooltip="https://www.indmoney.com/stocks/setco-automotive-ltd-share-price"/>
-    <hyperlink ref="B434" r:id="rId865" tooltip="https://www.indmoney.com/stocks/century-extrusions-ltd-share-price"/>
-    <hyperlink ref="M434" r:id="rId866" tooltip="https://www.indmoney.com/stocks/century-extrusions-ltd-share-price"/>
-    <hyperlink ref="B435" r:id="rId867" tooltip="https://www.indmoney.com/stocks/solvex-edibles-ltd-share-price"/>
-    <hyperlink ref="M435" r:id="rId868" tooltip="https://www.indmoney.com/stocks/solvex-edibles-ltd-share-price"/>
-    <hyperlink ref="B436" r:id="rId869" tooltip="https://www.indmoney.com/stocks/rudra-global-infra-products-ltd-share-price"/>
-    <hyperlink ref="M436" r:id="rId870" tooltip="https://www.indmoney.com/stocks/rudra-global-infra-products-ltd-share-price"/>
-    <hyperlink ref="B437" r:id="rId871" tooltip="https://www.indmoney.com/stocks/surya-india-ltd-share-price"/>
-    <hyperlink ref="M437" r:id="rId872" tooltip="https://www.indmoney.com/stocks/surya-india-ltd-share-price"/>
-    <hyperlink ref="B438" r:id="rId873" tooltip="https://www.indmoney.com/stocks/mahip-industries-ltd-share-price"/>
-    <hyperlink ref="M438" r:id="rId874" tooltip="https://www.indmoney.com/stocks/mahip-industries-ltd-share-price"/>
-    <hyperlink ref="B439" r:id="rId875" tooltip="https://www.indmoney.com/stocks/vms-industries-ltd-share-price"/>
-    <hyperlink ref="M439" r:id="rId876" tooltip="https://www.indmoney.com/stocks/vms-industries-ltd-share-price"/>
-    <hyperlink ref="B440" r:id="rId877" tooltip="https://www.indmoney.com/stocks/tpi-india-ltd-share-price"/>
-    <hyperlink ref="M440" r:id="rId878" tooltip="https://www.indmoney.com/stocks/tpi-india-ltd-share-price"/>
-    <hyperlink ref="B441" r:id="rId879" tooltip="https://www.indmoney.com/stocks/udayshivakumar-infra-ltd-share-price"/>
-    <hyperlink ref="M441" r:id="rId880" tooltip="https://www.indmoney.com/stocks/udayshivakumar-infra-ltd-share-price"/>
-    <hyperlink ref="B442" r:id="rId881" tooltip="https://www.indmoney.com/stocks/electro-force-india-ltd-share-price"/>
-    <hyperlink ref="M442" r:id="rId882" tooltip="https://www.indmoney.com/stocks/electro-force-india-ltd-share-price"/>
-    <hyperlink ref="B443" r:id="rId883" tooltip="https://www.indmoney.com/stocks/mandeep-auto-industries-ltd-share-price"/>
-    <hyperlink ref="M443" r:id="rId884" tooltip="https://www.indmoney.com/stocks/mandeep-auto-industries-ltd-share-price"/>
-    <hyperlink ref="B444" r:id="rId885" tooltip="https://www.indmoney.com/stocks/north-eastern-carrying-corporation-ltd-share-price"/>
-    <hyperlink ref="M444" r:id="rId886" tooltip="https://www.indmoney.com/stocks/north-eastern-carrying-corporation-ltd-share-price"/>
-    <hyperlink ref="B445" r:id="rId887" tooltip="https://www.indmoney.com/stocks/identical-brains-studios-ltd-share-price"/>
-    <hyperlink ref="M445" r:id="rId888" tooltip="https://www.indmoney.com/stocks/identical-brains-studios-ltd-share-price"/>
-    <hyperlink ref="B446" r:id="rId889" tooltip="https://www.indmoney.com/stocks/kalana-ispat-ltd-share-price"/>
-    <hyperlink ref="M446" r:id="rId890" tooltip="https://www.indmoney.com/stocks/kalana-ispat-ltd-share-price"/>
-    <hyperlink ref="B447" r:id="rId891" tooltip="https://www.indmoney.com/stocks/magnum-ventures-ltd-share-price"/>
-    <hyperlink ref="M447" r:id="rId892" tooltip="https://www.indmoney.com/stocks/magnum-ventures-ltd-share-price"/>
-    <hyperlink ref="B448" r:id="rId893" tooltip="https://www.indmoney.com/stocks/jain-irrigation-systems-ltd-dvr-share-price"/>
-    <hyperlink ref="M448" r:id="rId894" tooltip="https://www.indmoney.com/stocks/jain-irrigation-systems-ltd-dvr-share-price"/>
-    <hyperlink ref="B449" r:id="rId895" tooltip="https://www.indmoney.com/stocks/kabra-drugs-ltd-share-price"/>
-    <hyperlink ref="M449" r:id="rId896" tooltip="https://www.indmoney.com/stocks/kabra-drugs-ltd-share-price"/>
-    <hyperlink ref="B450" r:id="rId897" tooltip="https://www.indmoney.com/stocks/dev-labtech-venture-ltd-share-price"/>
-    <hyperlink ref="M450" r:id="rId898" tooltip="https://www.indmoney.com/stocks/dev-labtech-venture-ltd-share-price"/>
-    <hyperlink ref="B451" r:id="rId899" tooltip="https://www.indmoney.com/stocks/garware-marine-industries-ltd-share-price"/>
-    <hyperlink ref="M451" r:id="rId900" tooltip="https://www.indmoney.com/stocks/garware-marine-industries-ltd-share-price"/>
-    <hyperlink ref="B452" r:id="rId901" tooltip="https://www.indmoney.com/stocks/swastik-pipe-ltd-share-price"/>
-    <hyperlink ref="M452" r:id="rId902" tooltip="https://www.indmoney.com/stocks/swastik-pipe-ltd-share-price"/>
-    <hyperlink ref="B453" r:id="rId903" tooltip="https://www.indmoney.com/stocks/bajaj-hindusthan-sugar-ltd-share-price"/>
-    <hyperlink ref="M453" r:id="rId904" tooltip="https://www.indmoney.com/stocks/bajaj-hindusthan-sugar-ltd-share-price"/>
-    <hyperlink ref="B454" r:id="rId905" tooltip="https://www.indmoney.com/stocks/le-merite-exports-ltd-share-price"/>
-    <hyperlink ref="M454" r:id="rId906" tooltip="https://www.indmoney.com/stocks/le-merite-exports-ltd-share-price"/>
-    <hyperlink ref="B455" r:id="rId907" tooltip="https://www.indmoney.com/stocks/subex-ltd-share-price"/>
-    <hyperlink ref="M455" r:id="rId908" tooltip="https://www.indmoney.com/stocks/subex-ltd-share-price"/>
-    <hyperlink ref="B456" r:id="rId909" tooltip="https://www.indmoney.com/stocks/reliance-power-ltd-share-price"/>
-    <hyperlink ref="M456" r:id="rId910" tooltip="https://www.indmoney.com/stocks/reliance-power-ltd-share-price"/>
-    <hyperlink ref="B457" r:id="rId911" tooltip="https://www.indmoney.com/stocks/jet-freight-logistics-ltd-share-price"/>
-    <hyperlink ref="M457" r:id="rId912" tooltip="https://www.indmoney.com/stocks/jet-freight-logistics-ltd-share-price"/>
-    <hyperlink ref="B458" r:id="rId913" tooltip="https://www.indmoney.com/stocks/rajshree-polypack-ltd-share-price"/>
-    <hyperlink ref="M458" r:id="rId914" tooltip="https://www.indmoney.com/stocks/rajshree-polypack-ltd-share-price"/>
-    <hyperlink ref="B459" r:id="rId915" tooltip="https://www.indmoney.com/stocks/swashthik-plascon-ltd-share-price"/>
-    <hyperlink ref="M459" r:id="rId916" tooltip="https://www.indmoney.com/stocks/swashthik-plascon-ltd-share-price"/>
-    <hyperlink ref="B460" r:id="rId917" tooltip="https://www.indmoney.com/stocks/blue-cloud-softech-solutions-ltd-share-price"/>
-    <hyperlink ref="M460" r:id="rId918" tooltip="https://www.indmoney.com/stocks/blue-cloud-softech-solutions-ltd-share-price"/>
-    <hyperlink ref="B461" r:id="rId919" tooltip="https://www.indmoney.com/stocks/centrum-capital-ltd-share-price"/>
-    <hyperlink ref="M461" r:id="rId920" tooltip="https://www.indmoney.com/stocks/centrum-capital-ltd-share-price"/>
+    <hyperlink ref="B2" r:id="rId1" tooltip="https://www.indmoney.com/stocks/bengal-steel-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="M2" r:id="rId2" tooltip="https://www.indmoney.com/stocks/bengal-steel-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B3" r:id="rId3" tooltip="https://www.indmoney.com/stocks/dharan-infra-epc-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="M3" r:id="rId4" tooltip="https://www.indmoney.com/stocks/dharan-infra-epc-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="B4" r:id="rId5" tooltip="https://www.indmoney.com/stocks/filatex-fashions-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="M4" r:id="rId6" tooltip="https://www.indmoney.com/stocks/filatex-fashions-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="B5" r:id="rId7" tooltip="https://www.indmoney.com/stocks/thinkink-picturez-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="M5" r:id="rId8" tooltip="https://www.indmoney.com/stocks/thinkink-picturez-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="B6" r:id="rId9" tooltip="https://www.indmoney.com/stocks/welcure-drugs-and-pharmaceuticals-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="M6" r:id="rId10" tooltip="https://www.indmoney.com/stocks/welcure-drugs-and-pharmaceuticals-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="B7" r:id="rId11" tooltip="https://www.indmoney.com/stocks/shalimar-productions-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="M7" r:id="rId12" tooltip="https://www.indmoney.com/stocks/shalimar-productions-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="B8" r:id="rId13" tooltip="https://www.indmoney.com/stocks/remedium-lifecare-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="M8" r:id="rId14" tooltip="https://www.indmoney.com/stocks/remedium-lifecare-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="B9" r:id="rId15" tooltip="https://www.indmoney.com/stocks/siti-networks-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="M9" r:id="rId16" tooltip="https://www.indmoney.com/stocks/siti-networks-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="B10" r:id="rId17" tooltip="https://www.indmoney.com/stocks/rajnish-wellness-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="M10" r:id="rId18" tooltip="https://www.indmoney.com/stocks/rajnish-wellness-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="B11" r:id="rId19" tooltip="https://www.indmoney.com/stocks/mfl-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="M11" r:id="rId20" tooltip="https://www.indmoney.com/stocks/mfl-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="B12" r:id="rId21" tooltip="https://www.indmoney.com/stocks/laddu-gopal-online-services-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="M12" r:id="rId22" tooltip="https://www.indmoney.com/stocks/laddu-gopal-online-services-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="B13" r:id="rId23" tooltip="https://www.indmoney.com/stocks/veerkrupa-jewellers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="M13" r:id="rId24" tooltip="https://www.indmoney.com/stocks/veerkrupa-jewellers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="B14" r:id="rId25" tooltip="https://www.indmoney.com/stocks/sgn-telecoms-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="M14" r:id="rId26" tooltip="https://www.indmoney.com/stocks/sgn-telecoms-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="B15" r:id="rId27" tooltip="https://www.indmoney.com/stocks/western-ministil-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="M15" r:id="rId28" tooltip="https://www.indmoney.com/stocks/western-ministil-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="B16" r:id="rId29" tooltip="https://www.indmoney.com/stocks/unison-metals-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="M16" r:id="rId30" tooltip="https://www.indmoney.com/stocks/unison-metals-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="B17" r:id="rId31" tooltip="https://www.indmoney.com/stocks/navkar-urbanstructure-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="M17" r:id="rId32" tooltip="https://www.indmoney.com/stocks/navkar-urbanstructure-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="B18" r:id="rId33" tooltip="https://www.indmoney.com/stocks/reliance-communications-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="M18" r:id="rId34" tooltip="https://www.indmoney.com/stocks/reliance-communications-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="B19" r:id="rId35" tooltip="https://www.indmoney.com/stocks/starbeam-ventures-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="M19" r:id="rId36" tooltip="https://www.indmoney.com/stocks/starbeam-ventures-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="B20" r:id="rId37" tooltip="https://www.indmoney.com/stocks/croissance-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="M20" r:id="rId38" tooltip="https://www.indmoney.com/stocks/croissance-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="B21" r:id="rId39" tooltip="https://www.indmoney.com/stocks/gtl-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="M21" r:id="rId40" tooltip="https://www.indmoney.com/stocks/gtl-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="B22" r:id="rId41" tooltip="https://www.indmoney.com/stocks/sundaram-multi-pap-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="M22" r:id="rId42" tooltip="https://www.indmoney.com/stocks/sundaram-multi-pap-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="B23" r:id="rId43" tooltip="https://www.indmoney.com/stocks/vision-cinemas-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="M23" r:id="rId44" tooltip="https://www.indmoney.com/stocks/vision-cinemas-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="B24" r:id="rId45" tooltip="https://www.indmoney.com/stocks/garment-mantra-lifestyle-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="M24" r:id="rId46" tooltip="https://www.indmoney.com/stocks/garment-mantra-lifestyle-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="B25" r:id="rId47" tooltip="https://www.indmoney.com/stocks/52-weeks-entertainment-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="M25" r:id="rId48" tooltip="https://www.indmoney.com/stocks/52-weeks-entertainment-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="B26" r:id="rId49" tooltip="https://www.indmoney.com/stocks/sprayking-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="M26" r:id="rId50" tooltip="https://www.indmoney.com/stocks/sprayking-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="B27" r:id="rId51" tooltip="https://www.indmoney.com/stocks/gala-global-products-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="M27" r:id="rId52" tooltip="https://www.indmoney.com/stocks/gala-global-products-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="B28" r:id="rId53" tooltip="https://www.indmoney.com/stocks/ducon-infratechnologies-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="M28" r:id="rId54" tooltip="https://www.indmoney.com/stocks/ducon-infratechnologies-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="B29" r:id="rId55" tooltip="https://www.indmoney.com/stocks/kanani-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="M29" r:id="rId56" tooltip="https://www.indmoney.com/stocks/kanani-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="B30" r:id="rId57" tooltip="https://www.indmoney.com/stocks/r-o-jewels-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="M30" r:id="rId58" tooltip="https://www.indmoney.com/stocks/r-o-jewels-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="B31" r:id="rId59" tooltip="https://www.indmoney.com/stocks/sri-havisha-hospitality-and-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="M31" r:id="rId60" tooltip="https://www.indmoney.com/stocks/sri-havisha-hospitality-and-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="B32" r:id="rId61" tooltip="https://www.indmoney.com/stocks/radhe-developers-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="M32" r:id="rId62" tooltip="https://www.indmoney.com/stocks/radhe-developers-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="B33" r:id="rId63" tooltip="https://www.indmoney.com/stocks/fcs-software-solutions-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="M33" r:id="rId64" tooltip="https://www.indmoney.com/stocks/fcs-software-solutions-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="B34" r:id="rId65" tooltip="https://www.indmoney.com/stocks/filmcity-media-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="M34" r:id="rId66" tooltip="https://www.indmoney.com/stocks/filmcity-media-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="B35" r:id="rId67" tooltip="https://www.indmoney.com/stocks/zodiac-ventures-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="M35" r:id="rId68" tooltip="https://www.indmoney.com/stocks/zodiac-ventures-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="B36" r:id="rId69" tooltip="https://www.indmoney.com/stocks/deep-health-ai-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="M36" r:id="rId70" tooltip="https://www.indmoney.com/stocks/deep-health-ai-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="B37" r:id="rId71" tooltip="https://www.indmoney.com/stocks/jalan-transolutions-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="M37" r:id="rId72" tooltip="https://www.indmoney.com/stocks/jalan-transolutions-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="B38" r:id="rId73" tooltip="https://www.indmoney.com/stocks/nagarjuna-fertilizers-and-chemicals-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="M38" r:id="rId74" tooltip="https://www.indmoney.com/stocks/nagarjuna-fertilizers-and-chemicals-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="B39" r:id="rId75" tooltip="https://www.indmoney.com/stocks/ortel-communications-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="M39" r:id="rId76" tooltip="https://www.indmoney.com/stocks/ortel-communications-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="B40" r:id="rId77" tooltip="https://www.indmoney.com/stocks/family-care-hospitals-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="M40" r:id="rId78" tooltip="https://www.indmoney.com/stocks/family-care-hospitals-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="B41" r:id="rId79" tooltip="https://www.indmoney.com/stocks/shivamshree-businesses-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="M41" r:id="rId80" tooltip="https://www.indmoney.com/stocks/shivamshree-businesses-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="B42" r:id="rId81" tooltip="https://www.indmoney.com/stocks/newtime-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="M42" r:id="rId82" tooltip="https://www.indmoney.com/stocks/newtime-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="B43" r:id="rId83" tooltip="https://www.indmoney.com/stocks/ilandfs-transportation-networks-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="M43" r:id="rId84" tooltip="https://www.indmoney.com/stocks/ilandfs-transportation-networks-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="B44" r:id="rId85" tooltip="https://www.indmoney.com/stocks/amin-tannery-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="M44" r:id="rId86" tooltip="https://www.indmoney.com/stocks/amin-tannery-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="B45" r:id="rId87" tooltip="https://www.indmoney.com/stocks/kenvi-jewels-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="M45" r:id="rId88" tooltip="https://www.indmoney.com/stocks/kenvi-jewels-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="B46" r:id="rId89" tooltip="https://www.indmoney.com/stocks/crystal-business-system-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="M46" r:id="rId90" tooltip="https://www.indmoney.com/stocks/crystal-business-system-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="B47" r:id="rId91" tooltip="https://www.indmoney.com/stocks/landmarc-leisure-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="M47" r:id="rId92" tooltip="https://www.indmoney.com/stocks/landmarc-leisure-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="B48" r:id="rId93" tooltip="https://www.indmoney.com/stocks/paras-petrofils-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="M48" r:id="rId94" tooltip="https://www.indmoney.com/stocks/paras-petrofils-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="B49" r:id="rId95" tooltip="https://www.indmoney.com/stocks/ankit-metal-and-power-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="M49" r:id="rId96" tooltip="https://www.indmoney.com/stocks/ankit-metal-and-power-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="B50" r:id="rId97" tooltip="https://www.indmoney.com/stocks/tatia-global-venture-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="M50" r:id="rId98" tooltip="https://www.indmoney.com/stocks/tatia-global-venture-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="B51" r:id="rId99" tooltip="https://www.indmoney.com/stocks/diligent-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="M51" r:id="rId100" tooltip="https://www.indmoney.com/stocks/diligent-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="B52" r:id="rId101" tooltip="https://www.indmoney.com/stocks/globe-enterprises-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="M52" r:id="rId102" tooltip="https://www.indmoney.com/stocks/globe-enterprises-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="B53" r:id="rId103" tooltip="https://www.indmoney.com/stocks/darshan-orna-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="M53" r:id="rId104" tooltip="https://www.indmoney.com/stocks/darshan-orna-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="B54" r:id="rId105" tooltip="https://www.indmoney.com/stocks/parsvnath-developers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="M54" r:id="rId106" tooltip="https://www.indmoney.com/stocks/parsvnath-developers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="B55" r:id="rId107" tooltip="https://www.indmoney.com/stocks/tuni-textile-mills-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="M55" r:id="rId108" tooltip="https://www.indmoney.com/stocks/tuni-textile-mills-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="B56" r:id="rId109" tooltip="https://www.indmoney.com/stocks/dish-tv-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="M56" r:id="rId110" tooltip="https://www.indmoney.com/stocks/dish-tv-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="B57" r:id="rId111" tooltip="https://www.indmoney.com/stocks/pvv-infra-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="M57" r:id="rId112" tooltip="https://www.indmoney.com/stocks/pvv-infra-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="B58" r:id="rId113" tooltip="https://www.indmoney.com/stocks/vision-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="M58" r:id="rId114" tooltip="https://www.indmoney.com/stocks/vision-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="B59" r:id="rId115" tooltip="https://www.indmoney.com/stocks/davangere-sugar-company-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="M59" r:id="rId116" tooltip="https://www.indmoney.com/stocks/davangere-sugar-company-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="B60" r:id="rId117" tooltip="https://www.indmoney.com/stocks/east-west-freight-carriers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="M60" r:id="rId118" tooltip="https://www.indmoney.com/stocks/east-west-freight-carriers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="B61" r:id="rId119" tooltip="https://www.indmoney.com/stocks/transgene-biotek-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="M61" r:id="rId120" tooltip="https://www.indmoney.com/stocks/transgene-biotek-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="B62" r:id="rId121" tooltip="https://www.indmoney.com/stocks/diligent-media-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="M62" r:id="rId122" tooltip="https://www.indmoney.com/stocks/diligent-media-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="B63" r:id="rId123" tooltip="https://www.indmoney.com/stocks/sadhana-nitro-chem-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="M63" r:id="rId124" tooltip="https://www.indmoney.com/stocks/sadhana-nitro-chem-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="B64" r:id="rId125" tooltip="https://www.indmoney.com/stocks/gvk-power-and-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="M64" r:id="rId126" tooltip="https://www.indmoney.com/stocks/gvk-power-and-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="B65" r:id="rId127" tooltip="https://www.indmoney.com/stocks/aci-infocom-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="M65" r:id="rId128" tooltip="https://www.indmoney.com/stocks/aci-infocom-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="B66" r:id="rId129" tooltip="https://www.indmoney.com/stocks/nandan-denim-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="M66" r:id="rId130" tooltip="https://www.indmoney.com/stocks/nandan-denim-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="B67" r:id="rId131" tooltip="https://www.indmoney.com/stocks/tv-vision-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="M67" r:id="rId132" tooltip="https://www.indmoney.com/stocks/tv-vision-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="B68" r:id="rId133" tooltip="https://www.indmoney.com/stocks/coromandel-agro-products-and-oils-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="M68" r:id="rId134" tooltip="https://www.indmoney.com/stocks/coromandel-agro-products-and-oils-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="B69" r:id="rId135" tooltip="https://www.indmoney.com/stocks/sadbhav-infrastructure-projects-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="M69" r:id="rId136" tooltip="https://www.indmoney.com/stocks/sadbhav-infrastructure-projects-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="B70" r:id="rId137" tooltip="https://www.indmoney.com/stocks/picturepost-studios-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="M70" r:id="rId138" tooltip="https://www.indmoney.com/stocks/picturepost-studios-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="B71" r:id="rId139" tooltip="https://www.indmoney.com/stocks/astron-paper-and-board-mill-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="M71" r:id="rId140" tooltip="https://www.indmoney.com/stocks/astron-paper-and-board-mill-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="B72" r:id="rId141" tooltip="https://www.indmoney.com/stocks/bhandari-hosiery-exports-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="M72" r:id="rId142" tooltip="https://www.indmoney.com/stocks/bhandari-hosiery-exports-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="B73" r:id="rId143" tooltip="https://www.indmoney.com/stocks/olympic-cards-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="M73" r:id="rId144" tooltip="https://www.indmoney.com/stocks/olympic-cards-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="B74" r:id="rId145" tooltip="https://www.indmoney.com/stocks/sea-tv-network-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="M74" r:id="rId146" tooltip="https://www.indmoney.com/stocks/sea-tv-network-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="B75" r:id="rId147" tooltip="https://www.indmoney.com/stocks/radaan-mediaworks-i-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="M75" r:id="rId148" tooltip="https://www.indmoney.com/stocks/radaan-mediaworks-i-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="B76" r:id="rId149" tooltip="https://www.indmoney.com/stocks/vaishno-cement-co-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="M76" r:id="rId150" tooltip="https://www.indmoney.com/stocks/vaishno-cement-co-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="B77" r:id="rId151" tooltip="https://www.indmoney.com/stocks/khyati-multimedia-entertainment-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="M77" r:id="rId152" tooltip="https://www.indmoney.com/stocks/khyati-multimedia-entertainment-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="B78" r:id="rId153" tooltip="https://www.indmoney.com/stocks/gautam-gems-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="M78" r:id="rId154" tooltip="https://www.indmoney.com/stocks/gautam-gems-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="B79" r:id="rId155" tooltip="https://www.indmoney.com/stocks/alliance-integrated-metaliks-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="M79" r:id="rId156" tooltip="https://www.indmoney.com/stocks/alliance-integrated-metaliks-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="B80" r:id="rId157" tooltip="https://www.indmoney.com/stocks/shah-metacorp-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="M80" r:id="rId158" tooltip="https://www.indmoney.com/stocks/shah-metacorp-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="B81" r:id="rId159" tooltip="https://www.indmoney.com/stocks/facor-alloys-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="M81" r:id="rId160" tooltip="https://www.indmoney.com/stocks/facor-alloys-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="B82" r:id="rId161" tooltip="https://www.indmoney.com/stocks/mishtann-foods-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="M82" r:id="rId162" tooltip="https://www.indmoney.com/stocks/mishtann-foods-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="B83" r:id="rId163" tooltip="https://www.indmoney.com/stocks/rajnandini-metal-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="M83" r:id="rId164" tooltip="https://www.indmoney.com/stocks/rajnandini-metal-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="B84" r:id="rId165" tooltip="https://www.indmoney.com/stocks/ok-play-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="M84" r:id="rId166" tooltip="https://www.indmoney.com/stocks/ok-play-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="B85" r:id="rId167" tooltip="https://www.indmoney.com/stocks/shipwaves-online-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="M85" r:id="rId168" tooltip="https://www.indmoney.com/stocks/shipwaves-online-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="B86" r:id="rId169" tooltip="https://www.indmoney.com/stocks/sarveshwar-foods-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="M86" r:id="rId170" tooltip="https://www.indmoney.com/stocks/sarveshwar-foods-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="B87" r:id="rId171" tooltip="https://www.indmoney.com/stocks/kcd-industries-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="M87" r:id="rId172" tooltip="https://www.indmoney.com/stocks/kcd-industries-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="B88" r:id="rId173" tooltip="https://www.indmoney.com/stocks/noida-toll-bridge-company-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="M88" r:id="rId174" tooltip="https://www.indmoney.com/stocks/noida-toll-bridge-company-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="B89" r:id="rId175" tooltip="https://www.indmoney.com/stocks/prakash-steelage-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="M89" r:id="rId176" tooltip="https://www.indmoney.com/stocks/prakash-steelage-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="B90" r:id="rId177" tooltip="https://www.indmoney.com/stocks/nb-footwear-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="M90" r:id="rId178" tooltip="https://www.indmoney.com/stocks/nb-footwear-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="B91" r:id="rId179" tooltip="https://www.indmoney.com/stocks/next-mediaworks-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="M91" r:id="rId180" tooltip="https://www.indmoney.com/stocks/next-mediaworks-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="B92" r:id="rId181" tooltip="https://www.indmoney.com/stocks/agio-paper-and-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="M92" r:id="rId182" tooltip="https://www.indmoney.com/stocks/agio-paper-and-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="B93" r:id="rId183" tooltip="https://www.indmoney.com/stocks/sacheta-metals-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="M93" r:id="rId184" tooltip="https://www.indmoney.com/stocks/sacheta-metals-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="B94" r:id="rId185" tooltip="https://www.indmoney.com/stocks/perfect-octave-media-projects-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="M94" r:id="rId186" tooltip="https://www.indmoney.com/stocks/perfect-octave-media-projects-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="B95" r:id="rId187" tooltip="https://www.indmoney.com/stocks/shree-hanuman-sugar-and-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="M95" r:id="rId188" tooltip="https://www.indmoney.com/stocks/shree-hanuman-sugar-and-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="B96" r:id="rId189" tooltip="https://www.indmoney.com/stocks/m-k-proteins-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="M96" r:id="rId190" tooltip="https://www.indmoney.com/stocks/m-k-proteins-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="B97" r:id="rId191" tooltip="https://www.indmoney.com/stocks/padmalaya-telefilms-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="M97" r:id="rId192" tooltip="https://www.indmoney.com/stocks/padmalaya-telefilms-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="B98" r:id="rId193" tooltip="https://www.indmoney.com/stocks/spectra-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="M98" r:id="rId194" tooltip="https://www.indmoney.com/stocks/spectra-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="B99" r:id="rId195" tooltip="https://www.indmoney.com/stocks/unitech-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="M99" r:id="rId196" tooltip="https://www.indmoney.com/stocks/unitech-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="B100" r:id="rId197" tooltip="https://www.indmoney.com/stocks/kshitij-polyline-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="M100" r:id="rId198" tooltip="https://www.indmoney.com/stocks/kshitij-polyline-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="B101" r:id="rId199" tooltip="https://www.indmoney.com/stocks/arunjyoti-bio-ventures-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="M101" r:id="rId200" tooltip="https://www.indmoney.com/stocks/arunjyoti-bio-ventures-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="B102" r:id="rId201" tooltip="https://www.indmoney.com/stocks/dhatre-udyog-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="M102" r:id="rId202" tooltip="https://www.indmoney.com/stocks/dhatre-udyog-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="B103" r:id="rId203" tooltip="https://www.indmoney.com/stocks/mini-diamonds-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="M103" r:id="rId204" tooltip="https://www.indmoney.com/stocks/mini-diamonds-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="B104" r:id="rId205" tooltip="https://www.indmoney.com/stocks/orient-tradelink-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="M104" r:id="rId206" tooltip="https://www.indmoney.com/stocks/orient-tradelink-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="B105" r:id="rId207" tooltip="https://www.indmoney.com/stocks/b-a-g-films-and-media-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="M105" r:id="rId208" tooltip="https://www.indmoney.com/stocks/b-a-g-films-and-media-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="B106" r:id="rId209" tooltip="https://www.indmoney.com/stocks/ansal-properties-and-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="M106" r:id="rId210" tooltip="https://www.indmoney.com/stocks/ansal-properties-and-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="B107" r:id="rId211" tooltip="https://www.indmoney.com/stocks/kamdhenu-ventures-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="M107" r:id="rId212" tooltip="https://www.indmoney.com/stocks/kamdhenu-ventures-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="B108" r:id="rId213" tooltip="https://www.indmoney.com/stocks/ridhi-synthetics-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="M108" r:id="rId214" tooltip="https://www.indmoney.com/stocks/ridhi-synthetics-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="B109" r:id="rId215" tooltip="https://www.indmoney.com/stocks/accuracy-shipping-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="M109" r:id="rId216" tooltip="https://www.indmoney.com/stocks/accuracy-shipping-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="B110" r:id="rId217" tooltip="https://www.indmoney.com/stocks/salasar-techno-engineering-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="M110" r:id="rId218" tooltip="https://www.indmoney.com/stocks/salasar-techno-engineering-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="B111" r:id="rId219" tooltip="https://www.indmoney.com/stocks/tahmar-enterprises-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
+    <hyperlink ref="M111" r:id="rId220" tooltip="https://www.indmoney.com/stocks/tahmar-enterprises-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="B112" r:id="rId221" tooltip="https://www.indmoney.com/stocks/supreme-engineering-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="M112" r:id="rId222" tooltip="https://www.indmoney.com/stocks/supreme-engineering-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="B113" r:id="rId223" tooltip="https://www.indmoney.com/stocks/minal-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="M113" r:id="rId224" tooltip="https://www.indmoney.com/stocks/minal-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="B114" r:id="rId225" tooltip="https://www.indmoney.com/stocks/ashapuri-gold-ornament-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="M114" r:id="rId226" tooltip="https://www.indmoney.com/stocks/ashapuri-gold-ornament-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="B115" r:id="rId227" tooltip="https://www.indmoney.com/stocks/sparc-electrex-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="M115" r:id="rId228" tooltip="https://www.indmoney.com/stocks/sparc-electrex-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="B116" r:id="rId229" tooltip="https://www.indmoney.com/stocks/aurus-gem-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="M116" r:id="rId230" tooltip="https://www.indmoney.com/stocks/aurus-gem-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="B117" r:id="rId231" tooltip="https://www.indmoney.com/stocks/rama-steel-tubes-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="M117" r:id="rId232" tooltip="https://www.indmoney.com/stocks/rama-steel-tubes-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="B118" r:id="rId233" tooltip="https://www.indmoney.com/stocks/silver-pearl-hospitality-and-luxury-spaces-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
+    <hyperlink ref="M118" r:id="rId234" tooltip="https://www.indmoney.com/stocks/silver-pearl-hospitality-and-luxury-spaces-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="B119" r:id="rId235" tooltip="https://www.indmoney.com/stocks/usha-martin-education-and-solutions-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="M119" r:id="rId236" tooltip="https://www.indmoney.com/stocks/usha-martin-education-and-solutions-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
+    <hyperlink ref="B120" r:id="rId237" tooltip="https://www.indmoney.com/stocks/gian-lifecare-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
+    <hyperlink ref="M120" r:id="rId238" tooltip="https://www.indmoney.com/stocks/gian-lifecare-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
+    <hyperlink ref="B121" r:id="rId239" tooltip="https://www.indmoney.com/stocks/rollatainers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
+    <hyperlink ref="M121" r:id="rId240" tooltip="https://www.indmoney.com/stocks/rollatainers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
+    <hyperlink ref="B122" r:id="rId241" tooltip="https://www.indmoney.com/stocks/kritika-wires-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
+    <hyperlink ref="M122" r:id="rId242" tooltip="https://www.indmoney.com/stocks/kritika-wires-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
+    <hyperlink ref="B123" r:id="rId243" tooltip="https://www.indmoney.com/stocks/ansal-housing-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
+    <hyperlink ref="M123" r:id="rId244" tooltip="https://www.indmoney.com/stocks/ansal-housing-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
+    <hyperlink ref="B124" r:id="rId245" tooltip="https://www.indmoney.com/stocks/cemantic-infra-tech-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
+    <hyperlink ref="M124" r:id="rId246" tooltip="https://www.indmoney.com/stocks/cemantic-infra-tech-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
+    <hyperlink ref="B125" r:id="rId247" tooltip="https://www.indmoney.com/stocks/shyam-century-ferrous-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="M125" r:id="rId248" tooltip="https://www.indmoney.com/stocks/shyam-century-ferrous-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
+    <hyperlink ref="B126" r:id="rId249" tooltip="https://www.indmoney.com/stocks/sepc-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="M126" r:id="rId250" tooltip="https://www.indmoney.com/stocks/sepc-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
+    <hyperlink ref="B127" r:id="rId251" tooltip="https://www.indmoney.com/stocks/zenith-steel-pipes-and-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="M127" r:id="rId252" tooltip="https://www.indmoney.com/stocks/zenith-steel-pipes-and-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
+    <hyperlink ref="B128" r:id="rId253" tooltip="https://www.indmoney.com/stocks/vakrangee-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="M128" r:id="rId254" tooltip="https://www.indmoney.com/stocks/vakrangee-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="B129" r:id="rId255" tooltip="https://www.indmoney.com/stocks/iel-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="M129" r:id="rId256" tooltip="https://www.indmoney.com/stocks/iel-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="B130" r:id="rId257" tooltip="https://www.indmoney.com/stocks/vishwaraj-sugar-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="M130" r:id="rId258" tooltip="https://www.indmoney.com/stocks/vishwaraj-sugar-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="B131" r:id="rId259" tooltip="https://www.indmoney.com/stocks/signature-green-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="M131" r:id="rId260" tooltip="https://www.indmoney.com/stocks/signature-green-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="B132" r:id="rId261" tooltip="https://www.indmoney.com/stocks/regent-enterprises-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="M132" r:id="rId262" tooltip="https://www.indmoney.com/stocks/regent-enterprises-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="B133" r:id="rId263" tooltip="https://www.indmoney.com/stocks/wardwizard-innovations-and-mobility-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="M133" r:id="rId264" tooltip="https://www.indmoney.com/stocks/wardwizard-innovations-and-mobility-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
+    <hyperlink ref="B134" r:id="rId265" tooltip="https://www.indmoney.com/stocks/infomedia-press-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
+    <hyperlink ref="M134" r:id="rId266" tooltip="https://www.indmoney.com/stocks/infomedia-press-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
+    <hyperlink ref="B135" r:id="rId267" tooltip="https://www.indmoney.com/stocks/last-mile-enterprises-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
+    <hyperlink ref="M135" r:id="rId268" tooltip="https://www.indmoney.com/stocks/last-mile-enterprises-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
+    <hyperlink ref="B136" r:id="rId269" tooltip="https://www.indmoney.com/stocks/patidar-buildcon-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
+    <hyperlink ref="M136" r:id="rId270" tooltip="https://www.indmoney.com/stocks/patidar-buildcon-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
+    <hyperlink ref="B137" r:id="rId271" tooltip="https://www.indmoney.com/stocks/universal-arts-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
+    <hyperlink ref="M137" r:id="rId272" tooltip="https://www.indmoney.com/stocks/universal-arts-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
+    <hyperlink ref="B138" r:id="rId273" tooltip="https://www.indmoney.com/stocks/sambhaav-media-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
+    <hyperlink ref="M138" r:id="rId274" tooltip="https://www.indmoney.com/stocks/sambhaav-media-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
+    <hyperlink ref="B139" r:id="rId275" tooltip="https://www.indmoney.com/stocks/lasa-supergenerics-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
+    <hyperlink ref="M139" r:id="rId276" tooltip="https://www.indmoney.com/stocks/lasa-supergenerics-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
+    <hyperlink ref="B140" r:id="rId277" tooltip="https://www.indmoney.com/stocks/parle-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
+    <hyperlink ref="M140" r:id="rId278" tooltip="https://www.indmoney.com/stocks/parle-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
+    <hyperlink ref="B141" r:id="rId279" tooltip="https://www.indmoney.com/stocks/indian-acrylics-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
+    <hyperlink ref="M141" r:id="rId280" tooltip="https://www.indmoney.com/stocks/indian-acrylics-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
+    <hyperlink ref="B142" r:id="rId281" tooltip="https://www.indmoney.com/stocks/vsd-confin-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
+    <hyperlink ref="M142" r:id="rId282" tooltip="https://www.indmoney.com/stocks/vsd-confin-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
+    <hyperlink ref="B143" r:id="rId283" tooltip="https://www.indmoney.com/stocks/kaiser-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
+    <hyperlink ref="M143" r:id="rId284" tooltip="https://www.indmoney.com/stocks/kaiser-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
+    <hyperlink ref="B144" r:id="rId285" tooltip="https://www.indmoney.com/stocks/dhenu-buildcon-infra-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
+    <hyperlink ref="M144" r:id="rId286" tooltip="https://www.indmoney.com/stocks/dhenu-buildcon-infra-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
+    <hyperlink ref="B145" r:id="rId287" tooltip="https://www.indmoney.com/stocks/vardhman-polytex-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
+    <hyperlink ref="M145" r:id="rId288" tooltip="https://www.indmoney.com/stocks/vardhman-polytex-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
+    <hyperlink ref="B146" r:id="rId289" tooltip="https://www.indmoney.com/stocks/vivimed-labs-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
+    <hyperlink ref="M146" r:id="rId290" tooltip="https://www.indmoney.com/stocks/vivimed-labs-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
+    <hyperlink ref="B147" r:id="rId291" tooltip="https://www.indmoney.com/stocks/easy-trip-planners-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
+    <hyperlink ref="M147" r:id="rId292" tooltip="https://www.indmoney.com/stocks/easy-trip-planners-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
+    <hyperlink ref="B148" r:id="rId293" tooltip="https://www.indmoney.com/stocks/achyut-healthcare-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
+    <hyperlink ref="M148" r:id="rId294" tooltip="https://www.indmoney.com/stocks/achyut-healthcare-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
+    <hyperlink ref="B149" r:id="rId295" tooltip="https://www.indmoney.com/stocks/music-broadcast-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
+    <hyperlink ref="M149" r:id="rId296" tooltip="https://www.indmoney.com/stocks/music-broadcast-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
+    <hyperlink ref="B150" r:id="rId297" tooltip="https://www.indmoney.com/stocks/avio-smart-market-stack-limited-share-price" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
+    <hyperlink ref="M150" r:id="rId298" tooltip="https://www.indmoney.com/stocks/avio-smart-market-stack-limited-share-price" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
+    <hyperlink ref="B151" r:id="rId299" tooltip="https://www.indmoney.com/stocks/u-h-zaveri-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
+    <hyperlink ref="M151" r:id="rId300" tooltip="https://www.indmoney.com/stocks/u-h-zaveri-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
+    <hyperlink ref="B152" r:id="rId301" tooltip="https://www.indmoney.com/stocks/indong-tea-company-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
+    <hyperlink ref="M152" r:id="rId302" tooltip="https://www.indmoney.com/stocks/indong-tea-company-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
+    <hyperlink ref="B153" r:id="rId303" tooltip="https://www.indmoney.com/stocks/exxaro-tiles-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
+    <hyperlink ref="M153" r:id="rId304" tooltip="https://www.indmoney.com/stocks/exxaro-tiles-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
+    <hyperlink ref="B154" r:id="rId305" tooltip="https://www.indmoney.com/stocks/purple-agrotech-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
+    <hyperlink ref="M154" r:id="rId306" tooltip="https://www.indmoney.com/stocks/purple-agrotech-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
+    <hyperlink ref="B155" r:id="rId307" tooltip="https://www.indmoney.com/stocks/aki-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
+    <hyperlink ref="M155" r:id="rId308" tooltip="https://www.indmoney.com/stocks/aki-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
+    <hyperlink ref="B156" r:id="rId309" tooltip="https://www.indmoney.com/stocks/creative-eye-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
+    <hyperlink ref="M156" r:id="rId310" tooltip="https://www.indmoney.com/stocks/creative-eye-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
+    <hyperlink ref="B157" r:id="rId311" tooltip="https://www.indmoney.com/stocks/vista-pharmaceuticals-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
+    <hyperlink ref="M157" r:id="rId312" tooltip="https://www.indmoney.com/stocks/vista-pharmaceuticals-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
+    <hyperlink ref="B158" r:id="rId313" tooltip="https://www.indmoney.com/stocks/landmark-property-development-company-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
+    <hyperlink ref="M158" r:id="rId314" tooltip="https://www.indmoney.com/stocks/landmark-property-development-company-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
+    <hyperlink ref="B159" r:id="rId315" tooltip="https://www.indmoney.com/stocks/sikko-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
+    <hyperlink ref="M159" r:id="rId316" tooltip="https://www.indmoney.com/stocks/sikko-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
+    <hyperlink ref="B160" r:id="rId317" tooltip="https://www.indmoney.com/stocks/heera-ispat-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
+    <hyperlink ref="M160" r:id="rId318" tooltip="https://www.indmoney.com/stocks/heera-ispat-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
+    <hyperlink ref="B161" r:id="rId319" tooltip="https://www.indmoney.com/stocks/zee-learn-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
+    <hyperlink ref="M161" r:id="rId320" tooltip="https://www.indmoney.com/stocks/zee-learn-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
+    <hyperlink ref="B162" r:id="rId321" tooltip="https://www.indmoney.com/stocks/hlv-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
+    <hyperlink ref="M162" r:id="rId322" tooltip="https://www.indmoney.com/stocks/hlv-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
+    <hyperlink ref="B163" r:id="rId323" tooltip="https://www.indmoney.com/stocks/country-condos-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="M163" r:id="rId324" tooltip="https://www.indmoney.com/stocks/country-condos-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="B164" r:id="rId325" tooltip="https://www.indmoney.com/stocks/ladam-affordable-housing-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="M164" r:id="rId326" tooltip="https://www.indmoney.com/stocks/ladam-affordable-housing-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="B165" r:id="rId327" tooltip="https://www.indmoney.com/stocks/tirupati-innovar-limited-share-price" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="M165" r:id="rId328" tooltip="https://www.indmoney.com/stocks/tirupati-innovar-limited-share-price" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="B166" r:id="rId329" tooltip="https://www.indmoney.com/stocks/tijaria-polypipes-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="M166" r:id="rId330" tooltip="https://www.indmoney.com/stocks/tijaria-polypipes-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="B167" r:id="rId331" tooltip="https://www.indmoney.com/stocks/bothra-metals-and-alloys-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="M167" r:id="rId332" tooltip="https://www.indmoney.com/stocks/bothra-metals-and-alloys-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="B168" r:id="rId333" tooltip="https://www.indmoney.com/stocks/deepak-builders-and-engineers-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="M168" r:id="rId334" tooltip="https://www.indmoney.com/stocks/deepak-builders-and-engineers-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="B169" r:id="rId335" tooltip="https://www.indmoney.com/stocks/impex-ferro-tech-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="M169" r:id="rId336" tooltip="https://www.indmoney.com/stocks/impex-ferro-tech-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="B170" r:id="rId337" tooltip="https://www.indmoney.com/stocks/terraform-realstate-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
+    <hyperlink ref="M170" r:id="rId338" tooltip="https://www.indmoney.com/stocks/terraform-realstate-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="B171" r:id="rId339" tooltip="https://www.indmoney.com/stocks/kkalpana-industries-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="M171" r:id="rId340" tooltip="https://www.indmoney.com/stocks/kkalpana-industries-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="B172" r:id="rId341" tooltip="https://www.indmoney.com/stocks/nila-infrastructures-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="M172" r:id="rId342" tooltip="https://www.indmoney.com/stocks/nila-infrastructures-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="B173" r:id="rId343" tooltip="https://www.indmoney.com/stocks/mos-utility-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="M173" r:id="rId344" tooltip="https://www.indmoney.com/stocks/mos-utility-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="B174" r:id="rId345" tooltip="https://www.indmoney.com/stocks/bits-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="M174" r:id="rId346" tooltip="https://www.indmoney.com/stocks/bits-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="B175" r:id="rId347" tooltip="https://www.indmoney.com/stocks/orosil-smiths-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="M175" r:id="rId348" tooltip="https://www.indmoney.com/stocks/orosil-smiths-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="B176" r:id="rId349" tooltip="https://www.indmoney.com/stocks/kmf-builders-and-developers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="M176" r:id="rId350" tooltip="https://www.indmoney.com/stocks/kmf-builders-and-developers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="B177" r:id="rId351" tooltip="https://www.indmoney.com/stocks/avro-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="M177" r:id="rId352" tooltip="https://www.indmoney.com/stocks/avro-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
+    <hyperlink ref="B178" r:id="rId353" tooltip="https://www.indmoney.com/stocks/simbhaoli-sugars-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
+    <hyperlink ref="M178" r:id="rId354" tooltip="https://www.indmoney.com/stocks/simbhaoli-sugars-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="B179" r:id="rId355" tooltip="https://www.indmoney.com/stocks/rattanindia-power-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="M179" r:id="rId356" tooltip="https://www.indmoney.com/stocks/rattanindia-power-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="B180" r:id="rId357" tooltip="https://www.indmoney.com/stocks/india-power-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="M180" r:id="rId358" tooltip="https://www.indmoney.com/stocks/india-power-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="B181" r:id="rId359" tooltip="https://www.indmoney.com/stocks/precision-metaliks-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="M181" r:id="rId360" tooltip="https://www.indmoney.com/stocks/precision-metaliks-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="B182" r:id="rId361" tooltip="https://www.indmoney.com/stocks/sadbhav-engineering-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="M182" r:id="rId362" tooltip="https://www.indmoney.com/stocks/sadbhav-engineering-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="B183" r:id="rId363" tooltip="https://www.indmoney.com/stocks/gtl-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="M183" r:id="rId364" tooltip="https://www.indmoney.com/stocks/gtl-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="B184" r:id="rId365" tooltip="https://www.indmoney.com/stocks/vas-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="M184" r:id="rId366" tooltip="https://www.indmoney.com/stocks/vas-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="B185" r:id="rId367" tooltip="https://www.indmoney.com/stocks/bgil-films-and-technologies-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="M185" r:id="rId368" tooltip="https://www.indmoney.com/stocks/bgil-films-and-technologies-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
+    <hyperlink ref="B186" r:id="rId369" tooltip="https://www.indmoney.com/stocks/dr-lalchandani-labs-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
+    <hyperlink ref="M186" r:id="rId370" tooltip="https://www.indmoney.com/stocks/dr-lalchandani-labs-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
+    <hyperlink ref="B187" r:id="rId371" tooltip="https://www.indmoney.com/stocks/parvati-sweetners-and-power-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
+    <hyperlink ref="M187" r:id="rId372" tooltip="https://www.indmoney.com/stocks/parvati-sweetners-and-power-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
+    <hyperlink ref="B188" r:id="rId373" tooltip="https://www.indmoney.com/stocks/velan-hotels-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="M188" r:id="rId374" tooltip="https://www.indmoney.com/stocks/velan-hotels-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="B189" r:id="rId375" tooltip="https://www.indmoney.com/stocks/trescon-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="M189" r:id="rId376" tooltip="https://www.indmoney.com/stocks/trescon-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="B190" r:id="rId377" tooltip="https://www.indmoney.com/stocks/alok-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
+    <hyperlink ref="M190" r:id="rId378" tooltip="https://www.indmoney.com/stocks/alok-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="B191" r:id="rId379" tooltip="https://www.indmoney.com/stocks/aksh-optifibre-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
+    <hyperlink ref="M191" r:id="rId380" tooltip="https://www.indmoney.com/stocks/aksh-optifibre-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="B192" r:id="rId381" tooltip="https://www.indmoney.com/stocks/bodhi-tree-multimedia-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
+    <hyperlink ref="M192" r:id="rId382" tooltip="https://www.indmoney.com/stocks/bodhi-tree-multimedia-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
+    <hyperlink ref="B193" r:id="rId383" tooltip="https://www.indmoney.com/stocks/manor-estates-and-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="M193" r:id="rId384" tooltip="https://www.indmoney.com/stocks/manor-estates-and-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
+    <hyperlink ref="B194" r:id="rId385" tooltip="https://www.indmoney.com/stocks/mauria-udyog-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
+    <hyperlink ref="M194" r:id="rId386" tooltip="https://www.indmoney.com/stocks/mauria-udyog-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
+    <hyperlink ref="B195" r:id="rId387" tooltip="https://www.indmoney.com/stocks/zee-media-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
+    <hyperlink ref="M195" r:id="rId388" tooltip="https://www.indmoney.com/stocks/zee-media-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
+    <hyperlink ref="B196" r:id="rId389" tooltip="https://www.indmoney.com/stocks/aruna-hotels-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
+    <hyperlink ref="M196" r:id="rId390" tooltip="https://www.indmoney.com/stocks/aruna-hotels-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
+    <hyperlink ref="B197" r:id="rId391" tooltip="https://www.indmoney.com/stocks/triveni-glass-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
+    <hyperlink ref="M197" r:id="rId392" tooltip="https://www.indmoney.com/stocks/triveni-glass-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
+    <hyperlink ref="B198" r:id="rId393" tooltip="https://www.indmoney.com/stocks/madhav-infra-projects-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
+    <hyperlink ref="M198" r:id="rId394" tooltip="https://www.indmoney.com/stocks/madhav-infra-projects-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
+    <hyperlink ref="B199" r:id="rId395" tooltip="https://www.indmoney.com/stocks/shreyas-intermediates-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
+    <hyperlink ref="M199" r:id="rId396" tooltip="https://www.indmoney.com/stocks/shreyas-intermediates-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
+    <hyperlink ref="B200" r:id="rId397" tooltip="https://www.indmoney.com/stocks/gayatri-sugars-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
+    <hyperlink ref="M200" r:id="rId398" tooltip="https://www.indmoney.com/stocks/gayatri-sugars-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
+    <hyperlink ref="B201" r:id="rId399" tooltip="https://www.indmoney.com/stocks/city-online-services-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
+    <hyperlink ref="M201" r:id="rId400" tooltip="https://www.indmoney.com/stocks/city-online-services-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
+    <hyperlink ref="B202" r:id="rId401" tooltip="https://www.indmoney.com/stocks/dolphin-kitchen-utensils-and-appliances-limited-share-price" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
+    <hyperlink ref="M202" r:id="rId402" tooltip="https://www.indmoney.com/stocks/dolphin-kitchen-utensils-and-appliances-limited-share-price" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
+    <hyperlink ref="B203" r:id="rId403" tooltip="https://www.indmoney.com/stocks/pil-italica-lifestyle-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
+    <hyperlink ref="M203" r:id="rId404" tooltip="https://www.indmoney.com/stocks/pil-italica-lifestyle-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
+    <hyperlink ref="B204" r:id="rId405" tooltip="https://www.indmoney.com/stocks/tirupati-sarjan-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
+    <hyperlink ref="M204" r:id="rId406" tooltip="https://www.indmoney.com/stocks/tirupati-sarjan-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
+    <hyperlink ref="B205" r:id="rId407" tooltip="https://www.indmoney.com/stocks/restile-ceramics-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
+    <hyperlink ref="M205" r:id="rId408" tooltip="https://www.indmoney.com/stocks/restile-ceramics-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
+    <hyperlink ref="B206" r:id="rId409" tooltip="https://www.indmoney.com/stocks/terraform-magnum-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
+    <hyperlink ref="M206" r:id="rId410" tooltip="https://www.indmoney.com/stocks/terraform-magnum-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
+    <hyperlink ref="B207" r:id="rId411" tooltip="https://www.indmoney.com/stocks/axita-cotton-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
+    <hyperlink ref="M207" r:id="rId412" tooltip="https://www.indmoney.com/stocks/axita-cotton-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
+    <hyperlink ref="B208" r:id="rId413" tooltip="https://www.indmoney.com/stocks/shree-karthik-papers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
+    <hyperlink ref="M208" r:id="rId414" tooltip="https://www.indmoney.com/stocks/shree-karthik-papers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
+    <hyperlink ref="B209" r:id="rId415" tooltip="https://www.indmoney.com/stocks/alankit-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
+    <hyperlink ref="M209" r:id="rId416" tooltip="https://www.indmoney.com/stocks/alankit-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
+    <hyperlink ref="B210" r:id="rId417" tooltip="https://www.indmoney.com/stocks/captain-pipes-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
+    <hyperlink ref="M210" r:id="rId418" tooltip="https://www.indmoney.com/stocks/captain-pipes-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
+    <hyperlink ref="B211" r:id="rId419" tooltip="https://www.indmoney.com/stocks/gvp-infotech-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
+    <hyperlink ref="M211" r:id="rId420" tooltip="https://www.indmoney.com/stocks/gvp-infotech-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
+    <hyperlink ref="B212" r:id="rId421" tooltip="https://www.indmoney.com/stocks/elitecon-international-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
+    <hyperlink ref="M212" r:id="rId422" tooltip="https://www.indmoney.com/stocks/elitecon-international-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
+    <hyperlink ref="B213" r:id="rId423" tooltip="https://www.indmoney.com/stocks/twamev-construction-and-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
+    <hyperlink ref="M213" r:id="rId424" tooltip="https://www.indmoney.com/stocks/twamev-construction-and-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
+    <hyperlink ref="B214" r:id="rId425" tooltip="https://www.indmoney.com/stocks/t-t-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
+    <hyperlink ref="M214" r:id="rId426" tooltip="https://www.indmoney.com/stocks/t-t-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
+    <hyperlink ref="B215" r:id="rId427" tooltip="https://www.indmoney.com/stocks/picturehouse-media-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
+    <hyperlink ref="M215" r:id="rId428" tooltip="https://www.indmoney.com/stocks/picturehouse-media-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
+    <hyperlink ref="B216" r:id="rId429" tooltip="https://www.indmoney.com/stocks/magenta-lifecare-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
+    <hyperlink ref="M216" r:id="rId430" tooltip="https://www.indmoney.com/stocks/magenta-lifecare-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
+    <hyperlink ref="B217" r:id="rId431" tooltip="https://www.indmoney.com/stocks/ultracab-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
+    <hyperlink ref="M217" r:id="rId432" tooltip="https://www.indmoney.com/stocks/ultracab-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
+    <hyperlink ref="B218" r:id="rId433" tooltip="https://www.indmoney.com/stocks/starlineps-enterprises-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
+    <hyperlink ref="M218" r:id="rId434" tooltip="https://www.indmoney.com/stocks/starlineps-enterprises-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
+    <hyperlink ref="B219" r:id="rId435" tooltip="https://www.indmoney.com/stocks/chartered-logistics-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
+    <hyperlink ref="M219" r:id="rId436" tooltip="https://www.indmoney.com/stocks/chartered-logistics-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
+    <hyperlink ref="B220" r:id="rId437" tooltip="https://www.indmoney.com/stocks/sibar-auto-parts-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
+    <hyperlink ref="M220" r:id="rId438" tooltip="https://www.indmoney.com/stocks/sibar-auto-parts-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
+    <hyperlink ref="B221" r:id="rId439" tooltip="https://www.indmoney.com/stocks/super-tannery-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
+    <hyperlink ref="M221" r:id="rId440" tooltip="https://www.indmoney.com/stocks/super-tannery-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
+    <hyperlink ref="B222" r:id="rId441" tooltip="https://www.indmoney.com/stocks/hampton-sky-realty-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
+    <hyperlink ref="M222" r:id="rId442" tooltip="https://www.indmoney.com/stocks/hampton-sky-realty-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
+    <hyperlink ref="B223" r:id="rId443" tooltip="https://www.indmoney.com/stocks/aditya-ispat-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
+    <hyperlink ref="M223" r:id="rId444" tooltip="https://www.indmoney.com/stocks/aditya-ispat-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
+    <hyperlink ref="B224" r:id="rId445" tooltip="https://www.indmoney.com/stocks/square-four-projects-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
+    <hyperlink ref="M224" r:id="rId446" tooltip="https://www.indmoney.com/stocks/square-four-projects-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
+    <hyperlink ref="B225" r:id="rId447" tooltip="https://www.indmoney.com/stocks/telogica-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
+    <hyperlink ref="M225" r:id="rId448" tooltip="https://www.indmoney.com/stocks/telogica-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
+    <hyperlink ref="B226" r:id="rId449" tooltip="https://www.indmoney.com/stocks/prime-urban-development-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
+    <hyperlink ref="M226" r:id="rId450" tooltip="https://www.indmoney.com/stocks/prime-urban-development-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
+    <hyperlink ref="B227" r:id="rId451" tooltip="https://www.indmoney.com/stocks/bharat-immunological-and-biological-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
+    <hyperlink ref="M227" r:id="rId452" tooltip="https://www.indmoney.com/stocks/bharat-immunological-and-biological-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
+    <hyperlink ref="B228" r:id="rId453" tooltip="https://www.indmoney.com/stocks/aakash-exploration-services-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
+    <hyperlink ref="M228" r:id="rId454" tooltip="https://www.indmoney.com/stocks/aakash-exploration-services-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
+    <hyperlink ref="B229" r:id="rId455" tooltip="https://www.indmoney.com/stocks/vaishali-pharma-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
+    <hyperlink ref="M229" r:id="rId456" tooltip="https://www.indmoney.com/stocks/vaishali-pharma-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
+    <hyperlink ref="B230" r:id="rId457" tooltip="https://www.indmoney.com/stocks/indowind-energy-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
+    <hyperlink ref="M230" r:id="rId458" tooltip="https://www.indmoney.com/stocks/indowind-energy-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
+    <hyperlink ref="B231" r:id="rId459" tooltip="https://www.indmoney.com/stocks/lorenzini-apparels-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
+    <hyperlink ref="M231" r:id="rId460" tooltip="https://www.indmoney.com/stocks/lorenzini-apparels-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
+    <hyperlink ref="B232" r:id="rId461" tooltip="https://www.indmoney.com/stocks/equilateral-enterprises-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
+    <hyperlink ref="M232" r:id="rId462" tooltip="https://www.indmoney.com/stocks/equilateral-enterprises-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
+    <hyperlink ref="B233" r:id="rId463" tooltip="https://www.indmoney.com/stocks/benara-bearings-and-pistons-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
+    <hyperlink ref="M233" r:id="rId464" tooltip="https://www.indmoney.com/stocks/benara-bearings-and-pistons-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
+    <hyperlink ref="B234" r:id="rId465" tooltip="https://www.indmoney.com/stocks/vallabh-steels-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
+    <hyperlink ref="M234" r:id="rId466" tooltip="https://www.indmoney.com/stocks/vallabh-steels-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
+    <hyperlink ref="B235" r:id="rId467" tooltip="https://www.indmoney.com/stocks/urja-global-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
+    <hyperlink ref="M235" r:id="rId468" tooltip="https://www.indmoney.com/stocks/urja-global-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
+    <hyperlink ref="B236" r:id="rId469" tooltip="https://www.indmoney.com/stocks/chadha-papers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
+    <hyperlink ref="M236" r:id="rId470" tooltip="https://www.indmoney.com/stocks/chadha-papers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
+    <hyperlink ref="B237" r:id="rId471" tooltip="https://www.indmoney.com/stocks/orient-green-power-company-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
+    <hyperlink ref="M237" r:id="rId472" tooltip="https://www.indmoney.com/stocks/orient-green-power-company-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
+    <hyperlink ref="B238" r:id="rId473" tooltip="https://www.indmoney.com/stocks/studio-lsd-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
+    <hyperlink ref="M238" r:id="rId474" tooltip="https://www.indmoney.com/stocks/studio-lsd-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
+    <hyperlink ref="B239" r:id="rId475" tooltip="https://www.indmoney.com/stocks/allcargo-terminals-ltd-partly-paidup-share-price" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
+    <hyperlink ref="M239" r:id="rId476" tooltip="https://www.indmoney.com/stocks/allcargo-terminals-ltd-partly-paidup-share-price" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
+    <hyperlink ref="B240" r:id="rId477" tooltip="https://www.indmoney.com/stocks/rajasthan-tube-manufacturing-co-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
+    <hyperlink ref="M240" r:id="rId478" tooltip="https://www.indmoney.com/stocks/rajasthan-tube-manufacturing-co-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
+    <hyperlink ref="B241" r:id="rId479" tooltip="https://www.indmoney.com/stocks/jyoti-structures-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
+    <hyperlink ref="M241" r:id="rId480" tooltip="https://www.indmoney.com/stocks/jyoti-structures-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
+    <hyperlink ref="B242" r:id="rId481" tooltip="https://www.indmoney.com/stocks/shreeji-translogistics-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
+    <hyperlink ref="M242" r:id="rId482" tooltip="https://www.indmoney.com/stocks/shreeji-translogistics-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
+    <hyperlink ref="B243" r:id="rId483" tooltip="https://www.indmoney.com/stocks/shukra-jewellery-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
+    <hyperlink ref="M243" r:id="rId484" tooltip="https://www.indmoney.com/stocks/shukra-jewellery-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
+    <hyperlink ref="B244" r:id="rId485" tooltip="https://www.indmoney.com/stocks/yuvraaj-hygiene-products-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
+    <hyperlink ref="M244" r:id="rId486" tooltip="https://www.indmoney.com/stocks/yuvraaj-hygiene-products-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
+    <hyperlink ref="B245" r:id="rId487" tooltip="https://www.indmoney.com/stocks/randb-denims-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
+    <hyperlink ref="M245" r:id="rId488" tooltip="https://www.indmoney.com/stocks/randb-denims-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
+    <hyperlink ref="B246" r:id="rId489" tooltip="https://www.indmoney.com/stocks/baroda-extrusion-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
+    <hyperlink ref="M246" r:id="rId490" tooltip="https://www.indmoney.com/stocks/baroda-extrusion-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
+    <hyperlink ref="B247" r:id="rId491" tooltip="https://www.indmoney.com/stocks/shakti-press-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
+    <hyperlink ref="M247" r:id="rId492" tooltip="https://www.indmoney.com/stocks/shakti-press-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
+    <hyperlink ref="B248" r:id="rId493" tooltip="https://www.indmoney.com/stocks/sharpline-broadcast-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
+    <hyperlink ref="M248" r:id="rId494" tooltip="https://www.indmoney.com/stocks/sharpline-broadcast-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
+    <hyperlink ref="B249" r:id="rId495" tooltip="https://www.indmoney.com/stocks/moksh-ornaments-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
+    <hyperlink ref="M249" r:id="rId496" tooltip="https://www.indmoney.com/stocks/moksh-ornaments-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
+    <hyperlink ref="B250" r:id="rId497" tooltip="https://www.indmoney.com/stocks/coral-newsprints-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
+    <hyperlink ref="M250" r:id="rId498" tooltip="https://www.indmoney.com/stocks/coral-newsprints-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
+    <hyperlink ref="B251" r:id="rId499" tooltip="https://www.indmoney.com/stocks/spicejet-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
+    <hyperlink ref="M251" r:id="rId500" tooltip="https://www.indmoney.com/stocks/spicejet-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
+    <hyperlink ref="B252" r:id="rId501" tooltip="https://www.indmoney.com/stocks/hathway-cable-and-datacom-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
+    <hyperlink ref="M252" r:id="rId502" tooltip="https://www.indmoney.com/stocks/hathway-cable-and-datacom-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
+    <hyperlink ref="B253" r:id="rId503" tooltip="https://www.indmoney.com/stocks/skyline-millars-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
+    <hyperlink ref="M253" r:id="rId504" tooltip="https://www.indmoney.com/stocks/skyline-millars-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
+    <hyperlink ref="B254" r:id="rId505" tooltip="https://www.indmoney.com/stocks/tgb-banquets-and-hotels-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
+    <hyperlink ref="M254" r:id="rId506" tooltip="https://www.indmoney.com/stocks/tgb-banquets-and-hotels-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
+    <hyperlink ref="B255" r:id="rId507" tooltip="https://www.indmoney.com/stocks/inspire-films-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000FA010000}"/>
+    <hyperlink ref="M255" r:id="rId508" tooltip="https://www.indmoney.com/stocks/inspire-films-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000FB010000}"/>
+    <hyperlink ref="B256" r:id="rId509" tooltip="https://www.indmoney.com/stocks/sabar-flex-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000FC010000}"/>
+    <hyperlink ref="M256" r:id="rId510" tooltip="https://www.indmoney.com/stocks/sabar-flex-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000FD010000}"/>
+    <hyperlink ref="B257" r:id="rId511" tooltip="https://www.indmoney.com/stocks/brightcom-group-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
+    <hyperlink ref="M257" r:id="rId512" tooltip="https://www.indmoney.com/stocks/brightcom-group-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000FF010000}"/>
+    <hyperlink ref="B258" r:id="rId513" tooltip="https://www.indmoney.com/stocks/ambo-agritec-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000000020000}"/>
+    <hyperlink ref="M258" r:id="rId514" tooltip="https://www.indmoney.com/stocks/ambo-agritec-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000001020000}"/>
+    <hyperlink ref="B259" r:id="rId515" tooltip="https://www.indmoney.com/stocks/viram-suvarn-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000002020000}"/>
+    <hyperlink ref="M259" r:id="rId516" tooltip="https://www.indmoney.com/stocks/viram-suvarn-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000003020000}"/>
+    <hyperlink ref="B260" r:id="rId517" tooltip="https://www.indmoney.com/stocks/looks-health-services-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000004020000}"/>
+    <hyperlink ref="M260" r:id="rId518" tooltip="https://www.indmoney.com/stocks/looks-health-services-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000005020000}"/>
+    <hyperlink ref="B261" r:id="rId519" tooltip="https://www.indmoney.com/stocks/kay-power-and-paper-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000006020000}"/>
+    <hyperlink ref="M261" r:id="rId520" tooltip="https://www.indmoney.com/stocks/kay-power-and-paper-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000007020000}"/>
+    <hyperlink ref="B262" r:id="rId521" tooltip="https://www.indmoney.com/stocks/gennex-laboratories-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000008020000}"/>
+    <hyperlink ref="M262" r:id="rId522" tooltip="https://www.indmoney.com/stocks/gennex-laboratories-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000009020000}"/>
+    <hyperlink ref="B263" r:id="rId523" tooltip="https://www.indmoney.com/stocks/raconteur-global-resources-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00000A020000}"/>
+    <hyperlink ref="M263" r:id="rId524" tooltip="https://www.indmoney.com/stocks/raconteur-global-resources-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00000B020000}"/>
+    <hyperlink ref="B264" r:id="rId525" tooltip="https://www.indmoney.com/stocks/mahalaxmi-seamless-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00000C020000}"/>
+    <hyperlink ref="M264" r:id="rId526" tooltip="https://www.indmoney.com/stocks/mahalaxmi-seamless-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00000D020000}"/>
+    <hyperlink ref="B265" r:id="rId527" tooltip="https://www.indmoney.com/stocks/jfl-life-sciences-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00000E020000}"/>
+    <hyperlink ref="M265" r:id="rId528" tooltip="https://www.indmoney.com/stocks/jfl-life-sciences-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00000F020000}"/>
+    <hyperlink ref="B266" r:id="rId529" tooltip="https://www.indmoney.com/stocks/la-tim-metal-and-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000010020000}"/>
+    <hyperlink ref="M266" r:id="rId530" tooltip="https://www.indmoney.com/stocks/la-tim-metal-and-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000011020000}"/>
+    <hyperlink ref="B267" r:id="rId531" tooltip="https://www.indmoney.com/stocks/allcargo-logistics-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000012020000}"/>
+    <hyperlink ref="M267" r:id="rId532" tooltip="https://www.indmoney.com/stocks/allcargo-logistics-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000013020000}"/>
+    <hyperlink ref="B268" r:id="rId533" tooltip="https://www.indmoney.com/stocks/boston-commerce-limited-share-price" xr:uid="{00000000-0004-0000-0000-000014020000}"/>
+    <hyperlink ref="M268" r:id="rId534" tooltip="https://www.indmoney.com/stocks/boston-commerce-limited-share-price" xr:uid="{00000000-0004-0000-0000-000015020000}"/>
+    <hyperlink ref="B269" r:id="rId535" tooltip="https://www.indmoney.com/stocks/nectar-lifescience-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000016020000}"/>
+    <hyperlink ref="M269" r:id="rId536" tooltip="https://www.indmoney.com/stocks/nectar-lifescience-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000017020000}"/>
+    <hyperlink ref="B270" r:id="rId537" tooltip="https://www.indmoney.com/stocks/colorchips-new-media-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000018020000}"/>
+    <hyperlink ref="M270" r:id="rId538" tooltip="https://www.indmoney.com/stocks/colorchips-new-media-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000019020000}"/>
+    <hyperlink ref="B271" r:id="rId539" tooltip="https://www.indmoney.com/stocks/sumeet-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00001A020000}"/>
+    <hyperlink ref="M271" r:id="rId540" tooltip="https://www.indmoney.com/stocks/sumeet-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00001B020000}"/>
+    <hyperlink ref="B272" r:id="rId541" tooltip="https://www.indmoney.com/stocks/gourmet-gateway-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00001C020000}"/>
+    <hyperlink ref="M272" r:id="rId542" tooltip="https://www.indmoney.com/stocks/gourmet-gateway-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00001D020000}"/>
+    <hyperlink ref="B273" r:id="rId543" tooltip="https://www.indmoney.com/stocks/gujarat-winding-systems-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00001E020000}"/>
+    <hyperlink ref="M273" r:id="rId544" tooltip="https://www.indmoney.com/stocks/gujarat-winding-systems-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00001F020000}"/>
+    <hyperlink ref="B274" r:id="rId545" tooltip="https://www.indmoney.com/stocks/max-heights-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000020020000}"/>
+    <hyperlink ref="M274" r:id="rId546" tooltip="https://www.indmoney.com/stocks/max-heights-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000021020000}"/>
+    <hyperlink ref="B275" r:id="rId547" tooltip="https://www.indmoney.com/stocks/shiva-granito-export-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000022020000}"/>
+    <hyperlink ref="M275" r:id="rId548" tooltip="https://www.indmoney.com/stocks/shiva-granito-export-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000023020000}"/>
+    <hyperlink ref="B276" r:id="rId549" tooltip="https://www.indmoney.com/stocks/genus-paper-and-boards-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000024020000}"/>
+    <hyperlink ref="M276" r:id="rId550" tooltip="https://www.indmoney.com/stocks/genus-paper-and-boards-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000025020000}"/>
+    <hyperlink ref="B277" r:id="rId551" tooltip="https://www.indmoney.com/stocks/lexus-granito-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000026020000}"/>
+    <hyperlink ref="M277" r:id="rId552" tooltip="https://www.indmoney.com/stocks/lexus-granito-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000027020000}"/>
+    <hyperlink ref="B278" r:id="rId553" tooltip="https://www.indmoney.com/stocks/vipul-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000028020000}"/>
+    <hyperlink ref="M278" r:id="rId554" tooltip="https://www.indmoney.com/stocks/vipul-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000029020000}"/>
+    <hyperlink ref="B279" r:id="rId555" tooltip="https://www.indmoney.com/stocks/goel-food-products-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00002A020000}"/>
+    <hyperlink ref="M279" r:id="rId556" tooltip="https://www.indmoney.com/stocks/goel-food-products-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00002B020000}"/>
+    <hyperlink ref="B280" r:id="rId557" tooltip="https://www.indmoney.com/stocks/raj-television-network-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00002C020000}"/>
+    <hyperlink ref="M280" r:id="rId558" tooltip="https://www.indmoney.com/stocks/raj-television-network-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00002D020000}"/>
+    <hyperlink ref="B281" r:id="rId559" tooltip="https://www.indmoney.com/stocks/uniinfo-telecom-services-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00002E020000}"/>
+    <hyperlink ref="M281" r:id="rId560" tooltip="https://www.indmoney.com/stocks/uniinfo-telecom-services-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00002F020000}"/>
+    <hyperlink ref="B282" r:id="rId561" tooltip="https://www.indmoney.com/stocks/raghunath-international-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000030020000}"/>
+    <hyperlink ref="M282" r:id="rId562" tooltip="https://www.indmoney.com/stocks/raghunath-international-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000031020000}"/>
+    <hyperlink ref="B283" r:id="rId563" tooltip="https://www.indmoney.com/stocks/eco-hotels-and-resorts-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000032020000}"/>
+    <hyperlink ref="M283" r:id="rId564" tooltip="https://www.indmoney.com/stocks/eco-hotels-and-resorts-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000033020000}"/>
+    <hyperlink ref="B284" r:id="rId565" tooltip="https://www.indmoney.com/stocks/basant-agro-tech-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000034020000}"/>
+    <hyperlink ref="M284" r:id="rId566" tooltip="https://www.indmoney.com/stocks/basant-agro-tech-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000035020000}"/>
+    <hyperlink ref="B285" r:id="rId567" tooltip="https://www.indmoney.com/stocks/chiraharit-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000036020000}"/>
+    <hyperlink ref="M285" r:id="rId568" tooltip="https://www.indmoney.com/stocks/chiraharit-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000037020000}"/>
+    <hyperlink ref="B286" r:id="rId569" tooltip="https://www.indmoney.com/stocks/gconnect-logitech-and-supply-chain-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000038020000}"/>
+    <hyperlink ref="M286" r:id="rId570" tooltip="https://www.indmoney.com/stocks/gconnect-logitech-and-supply-chain-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000039020000}"/>
+    <hyperlink ref="B287" r:id="rId571" tooltip="https://www.indmoney.com/stocks/lancer-containers-lines-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00003A020000}"/>
+    <hyperlink ref="M287" r:id="rId572" tooltip="https://www.indmoney.com/stocks/lancer-containers-lines-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00003B020000}"/>
+    <hyperlink ref="B288" r:id="rId573" tooltip="https://www.indmoney.com/stocks/h-s-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00003C020000}"/>
+    <hyperlink ref="M288" r:id="rId574" tooltip="https://www.indmoney.com/stocks/h-s-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00003D020000}"/>
+    <hyperlink ref="B289" r:id="rId575" tooltip="https://www.indmoney.com/stocks/maruti-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00003E020000}"/>
+    <hyperlink ref="M289" r:id="rId576" tooltip="https://www.indmoney.com/stocks/maruti-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00003F020000}"/>
+    <hyperlink ref="B290" r:id="rId577" tooltip="https://www.indmoney.com/stocks/nila-spaces-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000040020000}"/>
+    <hyperlink ref="M290" r:id="rId578" tooltip="https://www.indmoney.com/stocks/nila-spaces-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000041020000}"/>
+    <hyperlink ref="B291" r:id="rId579" tooltip="https://www.indmoney.com/stocks/steel-exchange-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000042020000}"/>
+    <hyperlink ref="M291" r:id="rId580" tooltip="https://www.indmoney.com/stocks/steel-exchange-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000043020000}"/>
+    <hyperlink ref="B292" r:id="rId581" tooltip="https://www.indmoney.com/stocks/suvidha-infraestate-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000044020000}"/>
+    <hyperlink ref="M292" r:id="rId582" tooltip="https://www.indmoney.com/stocks/suvidha-infraestate-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000045020000}"/>
+    <hyperlink ref="B293" r:id="rId583" tooltip="https://www.indmoney.com/stocks/crane-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000046020000}"/>
+    <hyperlink ref="M293" r:id="rId584" tooltip="https://www.indmoney.com/stocks/crane-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000047020000}"/>
+    <hyperlink ref="B294" r:id="rId585" tooltip="https://www.indmoney.com/stocks/hathway-bhawani-cabletel-and-datacom-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000048020000}"/>
+    <hyperlink ref="M294" r:id="rId586" tooltip="https://www.indmoney.com/stocks/hathway-bhawani-cabletel-and-datacom-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000049020000}"/>
+    <hyperlink ref="B295" r:id="rId587" tooltip="https://www.indmoney.com/stocks/v-r-films-and-studios-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00004A020000}"/>
+    <hyperlink ref="M295" r:id="rId588" tooltip="https://www.indmoney.com/stocks/v-r-films-and-studios-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00004B020000}"/>
+    <hyperlink ref="B296" r:id="rId589" tooltip="https://www.indmoney.com/stocks/shree-precoated-steels-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00004C020000}"/>
+    <hyperlink ref="M296" r:id="rId590" tooltip="https://www.indmoney.com/stocks/shree-precoated-steels-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00004D020000}"/>
+    <hyperlink ref="B297" r:id="rId591" tooltip="https://www.indmoney.com/stocks/chandrima-mercantiles-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00004E020000}"/>
+    <hyperlink ref="M297" r:id="rId592" tooltip="https://www.indmoney.com/stocks/chandrima-mercantiles-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00004F020000}"/>
+    <hyperlink ref="B298" r:id="rId593" tooltip="https://www.indmoney.com/stocks/tamil-nadu-telecommunications-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000050020000}"/>
+    <hyperlink ref="M298" r:id="rId594" tooltip="https://www.indmoney.com/stocks/tamil-nadu-telecommunications-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000051020000}"/>
+    <hyperlink ref="B299" r:id="rId595" tooltip="https://www.indmoney.com/stocks/shahi-shipping-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000052020000}"/>
+    <hyperlink ref="M299" r:id="rId596" tooltip="https://www.indmoney.com/stocks/shahi-shipping-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000053020000}"/>
+    <hyperlink ref="B300" r:id="rId597" tooltip="https://www.indmoney.com/stocks/inani-marbles-and-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000054020000}"/>
+    <hyperlink ref="M300" r:id="rId598" tooltip="https://www.indmoney.com/stocks/inani-marbles-and-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000055020000}"/>
+    <hyperlink ref="B301" r:id="rId599" tooltip="https://www.indmoney.com/stocks/deccan-health-care-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000056020000}"/>
+    <hyperlink ref="M301" r:id="rId600" tooltip="https://www.indmoney.com/stocks/deccan-health-care-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000057020000}"/>
+    <hyperlink ref="B302" r:id="rId601" tooltip="https://www.indmoney.com/stocks/earthstahl-and-alloys-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000058020000}"/>
+    <hyperlink ref="M302" r:id="rId602" tooltip="https://www.indmoney.com/stocks/earthstahl-and-alloys-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000059020000}"/>
+    <hyperlink ref="B303" r:id="rId603" tooltip="https://www.indmoney.com/stocks/kesar-petroproducts-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00005A020000}"/>
+    <hyperlink ref="M303" r:id="rId604" tooltip="https://www.indmoney.com/stocks/kesar-petroproducts-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00005B020000}"/>
+    <hyperlink ref="B304" r:id="rId605" tooltip="https://www.indmoney.com/stocks/spp-polymer-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00005C020000}"/>
+    <hyperlink ref="M304" r:id="rId606" tooltip="https://www.indmoney.com/stocks/spp-polymer-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00005D020000}"/>
+    <hyperlink ref="B305" r:id="rId607" tooltip="https://www.indmoney.com/stocks/tivoli-construction-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00005E020000}"/>
+    <hyperlink ref="M305" r:id="rId608" tooltip="https://www.indmoney.com/stocks/tivoli-construction-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00005F020000}"/>
+    <hyperlink ref="B306" r:id="rId609" tooltip="https://www.indmoney.com/stocks/global-longlife-hospital-and-research-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000060020000}"/>
+    <hyperlink ref="M306" r:id="rId610" tooltip="https://www.indmoney.com/stocks/global-longlife-hospital-and-research-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000061020000}"/>
+    <hyperlink ref="B307" r:id="rId611" tooltip="https://www.indmoney.com/stocks/global-defence-industries-limited-share-price" xr:uid="{00000000-0004-0000-0000-000062020000}"/>
+    <hyperlink ref="M307" r:id="rId612" tooltip="https://www.indmoney.com/stocks/global-defence-industries-limited-share-price" xr:uid="{00000000-0004-0000-0000-000063020000}"/>
+    <hyperlink ref="B308" r:id="rId613" tooltip="https://www.indmoney.com/stocks/tarapur-transformers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000064020000}"/>
+    <hyperlink ref="M308" r:id="rId614" tooltip="https://www.indmoney.com/stocks/tarapur-transformers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000065020000}"/>
+    <hyperlink ref="B309" r:id="rId615" tooltip="https://www.indmoney.com/stocks/bihar-sponge-iron-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000066020000}"/>
+    <hyperlink ref="M309" r:id="rId616" tooltip="https://www.indmoney.com/stocks/bihar-sponge-iron-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000067020000}"/>
+    <hyperlink ref="B310" r:id="rId617" tooltip="https://www.indmoney.com/stocks/kellton-tech-solutions-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000068020000}"/>
+    <hyperlink ref="M310" r:id="rId618" tooltip="https://www.indmoney.com/stocks/kellton-tech-solutions-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000069020000}"/>
+    <hyperlink ref="B311" r:id="rId619" tooltip="https://www.indmoney.com/stocks/sunraj-diamond-exports-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00006A020000}"/>
+    <hyperlink ref="M311" r:id="rId620" tooltip="https://www.indmoney.com/stocks/sunraj-diamond-exports-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00006B020000}"/>
+    <hyperlink ref="B312" r:id="rId621" tooltip="https://www.indmoney.com/stocks/diggi-multitrade-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00006C020000}"/>
+    <hyperlink ref="M312" r:id="rId622" tooltip="https://www.indmoney.com/stocks/diggi-multitrade-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00006D020000}"/>
+    <hyperlink ref="B313" r:id="rId623" tooltip="https://www.indmoney.com/stocks/kati-patang-lifestyle-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00006E020000}"/>
+    <hyperlink ref="M313" r:id="rId624" tooltip="https://www.indmoney.com/stocks/kati-patang-lifestyle-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00006F020000}"/>
+    <hyperlink ref="B314" r:id="rId625" tooltip="https://www.indmoney.com/stocks/a-b-infrabuild-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000070020000}"/>
+    <hyperlink ref="M314" r:id="rId626" tooltip="https://www.indmoney.com/stocks/a-b-infrabuild-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000071020000}"/>
+    <hyperlink ref="B315" r:id="rId627" tooltip="https://www.indmoney.com/stocks/vodafone-idea-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000072020000}"/>
+    <hyperlink ref="M315" r:id="rId628" tooltip="https://www.indmoney.com/stocks/vodafone-idea-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000073020000}"/>
+    <hyperlink ref="B316" r:id="rId629" tooltip="https://www.indmoney.com/stocks/take-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000074020000}"/>
+    <hyperlink ref="M316" r:id="rId630" tooltip="https://www.indmoney.com/stocks/take-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000075020000}"/>
+    <hyperlink ref="B317" r:id="rId631" tooltip="https://www.indmoney.com/stocks/kesar-enterprises-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000076020000}"/>
+    <hyperlink ref="M317" r:id="rId632" tooltip="https://www.indmoney.com/stocks/kesar-enterprises-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000077020000}"/>
+    <hyperlink ref="B318" r:id="rId633" tooltip="https://www.indmoney.com/stocks/tejnaksh-healthcare-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000078020000}"/>
+    <hyperlink ref="M318" r:id="rId634" tooltip="https://www.indmoney.com/stocks/tejnaksh-healthcare-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000079020000}"/>
+    <hyperlink ref="B319" r:id="rId635" tooltip="https://www.indmoney.com/stocks/nova-iron-and-steel-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00007A020000}"/>
+    <hyperlink ref="M319" r:id="rId636" tooltip="https://www.indmoney.com/stocks/nova-iron-and-steel-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00007B020000}"/>
+    <hyperlink ref="B320" r:id="rId637" tooltip="https://www.indmoney.com/stocks/atal-realtech-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00007C020000}"/>
+    <hyperlink ref="M320" r:id="rId638" tooltip="https://www.indmoney.com/stocks/atal-realtech-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00007D020000}"/>
+    <hyperlink ref="B321" r:id="rId639" tooltip="https://www.indmoney.com/stocks/pc-jeweller-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00007E020000}"/>
+    <hyperlink ref="M321" r:id="rId640" tooltip="https://www.indmoney.com/stocks/pc-jeweller-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00007F020000}"/>
+    <hyperlink ref="B322" r:id="rId641" tooltip="https://www.indmoney.com/stocks/goldstar-power-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000080020000}"/>
+    <hyperlink ref="M322" r:id="rId642" tooltip="https://www.indmoney.com/stocks/goldstar-power-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000081020000}"/>
+    <hyperlink ref="B323" r:id="rId643" tooltip="https://www.indmoney.com/stocks/nidan-laboratories-and-healthcare-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000082020000}"/>
+    <hyperlink ref="M323" r:id="rId644" tooltip="https://www.indmoney.com/stocks/nidan-laboratories-and-healthcare-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000083020000}"/>
+    <hyperlink ref="B324" r:id="rId645" tooltip="https://www.indmoney.com/stocks/royal-cushion-vinyl-products-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000084020000}"/>
+    <hyperlink ref="M324" r:id="rId646" tooltip="https://www.indmoney.com/stocks/royal-cushion-vinyl-products-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000085020000}"/>
+    <hyperlink ref="B325" r:id="rId647" tooltip="https://www.indmoney.com/stocks/shish-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000086020000}"/>
+    <hyperlink ref="M325" r:id="rId648" tooltip="https://www.indmoney.com/stocks/shish-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000087020000}"/>
+    <hyperlink ref="B326" r:id="rId649" tooltip="https://www.indmoney.com/stocks/country-club-hospitality-and-holidays-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000088020000}"/>
+    <hyperlink ref="M326" r:id="rId650" tooltip="https://www.indmoney.com/stocks/country-club-hospitality-and-holidays-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000089020000}"/>
+    <hyperlink ref="B327" r:id="rId651" tooltip="https://www.indmoney.com/stocks/drc-systems-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00008A020000}"/>
+    <hyperlink ref="M327" r:id="rId652" tooltip="https://www.indmoney.com/stocks/drc-systems-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00008B020000}"/>
+    <hyperlink ref="B328" r:id="rId653" tooltip="https://www.indmoney.com/stocks/3b-films-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00008C020000}"/>
+    <hyperlink ref="M328" r:id="rId654" tooltip="https://www.indmoney.com/stocks/3b-films-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00008D020000}"/>
+    <hyperlink ref="B329" r:id="rId655" tooltip="https://www.indmoney.com/stocks/compucom-software-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00008E020000}"/>
+    <hyperlink ref="M329" r:id="rId656" tooltip="https://www.indmoney.com/stocks/compucom-software-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00008F020000}"/>
+    <hyperlink ref="B330" r:id="rId657" tooltip="https://www.indmoney.com/stocks/s-m-gold-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000090020000}"/>
+    <hyperlink ref="M330" r:id="rId658" tooltip="https://www.indmoney.com/stocks/s-m-gold-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000091020000}"/>
+    <hyperlink ref="B331" r:id="rId659" tooltip="https://www.indmoney.com/stocks/rana-sugars-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000092020000}"/>
+    <hyperlink ref="M331" r:id="rId660" tooltip="https://www.indmoney.com/stocks/rana-sugars-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000093020000}"/>
+    <hyperlink ref="B332" r:id="rId661" tooltip="https://www.indmoney.com/stocks/sspdl-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000094020000}"/>
+    <hyperlink ref="M332" r:id="rId662" tooltip="https://www.indmoney.com/stocks/sspdl-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000095020000}"/>
+    <hyperlink ref="B333" r:id="rId663" tooltip="https://www.indmoney.com/stocks/patel-integrated-logistics-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000096020000}"/>
+    <hyperlink ref="M333" r:id="rId664" tooltip="https://www.indmoney.com/stocks/patel-integrated-logistics-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000097020000}"/>
+    <hyperlink ref="B334" r:id="rId665" tooltip="https://www.indmoney.com/stocks/virinchi-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000098020000}"/>
+    <hyperlink ref="M334" r:id="rId666" tooltip="https://www.indmoney.com/stocks/virinchi-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000099020000}"/>
+    <hyperlink ref="B335" r:id="rId667" tooltip="https://www.indmoney.com/stocks/shiva-cement-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00009A020000}"/>
+    <hyperlink ref="M335" r:id="rId668" tooltip="https://www.indmoney.com/stocks/shiva-cement-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00009B020000}"/>
+    <hyperlink ref="B336" r:id="rId669" tooltip="https://www.indmoney.com/stocks/super-crop-safe-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00009C020000}"/>
+    <hyperlink ref="M336" r:id="rId670" tooltip="https://www.indmoney.com/stocks/super-crop-safe-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00009D020000}"/>
+    <hyperlink ref="B337" r:id="rId671" tooltip="https://www.indmoney.com/stocks/utkarsh-small-finance-bank-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00009E020000}"/>
+    <hyperlink ref="M337" r:id="rId672" tooltip="https://www.indmoney.com/stocks/utkarsh-small-finance-bank-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00009F020000}"/>
+    <hyperlink ref="B338" r:id="rId673" tooltip="https://www.indmoney.com/stocks/aritas-vinyl-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A0020000}"/>
+    <hyperlink ref="M338" r:id="rId674" tooltip="https://www.indmoney.com/stocks/aritas-vinyl-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A1020000}"/>
+    <hyperlink ref="B339" r:id="rId675" tooltip="https://www.indmoney.com/stocks/consolidated-construction-consortium-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A2020000}"/>
+    <hyperlink ref="M339" r:id="rId676" tooltip="https://www.indmoney.com/stocks/consolidated-construction-consortium-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A3020000}"/>
+    <hyperlink ref="B340" r:id="rId677" tooltip="https://www.indmoney.com/stocks/prudential-sugar-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A4020000}"/>
+    <hyperlink ref="M340" r:id="rId678" tooltip="https://www.indmoney.com/stocks/prudential-sugar-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A5020000}"/>
+    <hyperlink ref="B341" r:id="rId679" tooltip="https://www.indmoney.com/stocks/victory-electric-vehicles-international-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A6020000}"/>
+    <hyperlink ref="M341" r:id="rId680" tooltip="https://www.indmoney.com/stocks/victory-electric-vehicles-international-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A7020000}"/>
+    <hyperlink ref="B342" r:id="rId681" tooltip="https://www.indmoney.com/stocks/mediaone-global-entertainment-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A8020000}"/>
+    <hyperlink ref="M342" r:id="rId682" tooltip="https://www.indmoney.com/stocks/mediaone-global-entertainment-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000A9020000}"/>
+    <hyperlink ref="B343" r:id="rId683" tooltip="https://www.indmoney.com/stocks/cinevista-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000AA020000}"/>
+    <hyperlink ref="M343" r:id="rId684" tooltip="https://www.indmoney.com/stocks/cinevista-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000AB020000}"/>
+    <hyperlink ref="B344" r:id="rId685" tooltip="https://www.indmoney.com/stocks/kenrik-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000AC020000}"/>
+    <hyperlink ref="M344" r:id="rId686" tooltip="https://www.indmoney.com/stocks/kenrik-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000AD020000}"/>
+    <hyperlink ref="B345" r:id="rId687" tooltip="https://www.indmoney.com/stocks/nettlinx-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000AE020000}"/>
+    <hyperlink ref="M345" r:id="rId688" tooltip="https://www.indmoney.com/stocks/nettlinx-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000AF020000}"/>
+    <hyperlink ref="B346" r:id="rId689" tooltip="https://www.indmoney.com/stocks/rtcl-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B0020000}"/>
+    <hyperlink ref="M346" r:id="rId690" tooltip="https://www.indmoney.com/stocks/rtcl-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B1020000}"/>
+    <hyperlink ref="B347" r:id="rId691" tooltip="https://www.indmoney.com/stocks/gravity-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B2020000}"/>
+    <hyperlink ref="M347" r:id="rId692" tooltip="https://www.indmoney.com/stocks/gravity-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B3020000}"/>
+    <hyperlink ref="B348" r:id="rId693" tooltip="https://www.indmoney.com/stocks/mukat-pipes-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B4020000}"/>
+    <hyperlink ref="M348" r:id="rId694" tooltip="https://www.indmoney.com/stocks/mukat-pipes-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B5020000}"/>
+    <hyperlink ref="B349" r:id="rId695" tooltip="https://www.indmoney.com/stocks/ind-renewable-energy-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B6020000}"/>
+    <hyperlink ref="M349" r:id="rId696" tooltip="https://www.indmoney.com/stocks/ind-renewable-energy-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B7020000}"/>
+    <hyperlink ref="B350" r:id="rId697" tooltip="https://www.indmoney.com/stocks/modern-steels-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B8020000}"/>
+    <hyperlink ref="M350" r:id="rId698" tooltip="https://www.indmoney.com/stocks/modern-steels-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000B9020000}"/>
+    <hyperlink ref="B351" r:id="rId699" tooltip="https://www.indmoney.com/stocks/innovative-tech-pack-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000BA020000}"/>
+    <hyperlink ref="M351" r:id="rId700" tooltip="https://www.indmoney.com/stocks/innovative-tech-pack-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000BB020000}"/>
+    <hyperlink ref="B352" r:id="rId701" tooltip="https://www.indmoney.com/stocks/cityman-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000BC020000}"/>
+    <hyperlink ref="M352" r:id="rId702" tooltip="https://www.indmoney.com/stocks/cityman-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000BD020000}"/>
+    <hyperlink ref="B353" r:id="rId703" tooltip="https://www.indmoney.com/stocks/maks-energy-solutions-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000BE020000}"/>
+    <hyperlink ref="M353" r:id="rId704" tooltip="https://www.indmoney.com/stocks/maks-energy-solutions-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000BF020000}"/>
+    <hyperlink ref="B354" r:id="rId705" tooltip="https://www.indmoney.com/stocks/a2z-infra-engineering-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C0020000}"/>
+    <hyperlink ref="M354" r:id="rId706" tooltip="https://www.indmoney.com/stocks/a2z-infra-engineering-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C1020000}"/>
+    <hyperlink ref="B355" r:id="rId707" tooltip="https://www.indmoney.com/stocks/arcee-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C2020000}"/>
+    <hyperlink ref="M355" r:id="rId708" tooltip="https://www.indmoney.com/stocks/arcee-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C3020000}"/>
+    <hyperlink ref="B356" r:id="rId709" tooltip="https://www.indmoney.com/stocks/best-eastern-hotels-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C4020000}"/>
+    <hyperlink ref="M356" r:id="rId710" tooltip="https://www.indmoney.com/stocks/best-eastern-hotels-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C5020000}"/>
+    <hyperlink ref="B357" r:id="rId711" tooltip="https://www.indmoney.com/stocks/lords-ishwar-hotels-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C6020000}"/>
+    <hyperlink ref="M357" r:id="rId712" tooltip="https://www.indmoney.com/stocks/lords-ishwar-hotels-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C7020000}"/>
+    <hyperlink ref="B358" r:id="rId713" tooltip="https://www.indmoney.com/stocks/marinetrans-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C8020000}"/>
+    <hyperlink ref="M358" r:id="rId714" tooltip="https://www.indmoney.com/stocks/marinetrans-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000C9020000}"/>
+    <hyperlink ref="B359" r:id="rId715" tooltip="https://www.indmoney.com/stocks/energy-development-company-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000CA020000}"/>
+    <hyperlink ref="M359" r:id="rId716" tooltip="https://www.indmoney.com/stocks/energy-development-company-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000CB020000}"/>
+    <hyperlink ref="B360" r:id="rId717" tooltip="https://www.indmoney.com/stocks/agni-green-power-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000CC020000}"/>
+    <hyperlink ref="M360" r:id="rId718" tooltip="https://www.indmoney.com/stocks/agni-green-power-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000CD020000}"/>
+    <hyperlink ref="B361" r:id="rId719" tooltip="https://www.indmoney.com/stocks/containe-technologies-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000CE020000}"/>
+    <hyperlink ref="M361" r:id="rId720" tooltip="https://www.indmoney.com/stocks/containe-technologies-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000CF020000}"/>
+    <hyperlink ref="B362" r:id="rId721" tooltip="https://www.indmoney.com/stocks/peninsula-land-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D0020000}"/>
+    <hyperlink ref="M362" r:id="rId722" tooltip="https://www.indmoney.com/stocks/peninsula-land-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D1020000}"/>
+    <hyperlink ref="B363" r:id="rId723" tooltip="https://www.indmoney.com/stocks/bohra-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D2020000}"/>
+    <hyperlink ref="M363" r:id="rId724" tooltip="https://www.indmoney.com/stocks/bohra-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D3020000}"/>
+    <hyperlink ref="B364" r:id="rId725" tooltip="https://www.indmoney.com/stocks/venmax-drugs-and-pharmaceuticals-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D4020000}"/>
+    <hyperlink ref="M364" r:id="rId726" tooltip="https://www.indmoney.com/stocks/venmax-drugs-and-pharmaceuticals-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D5020000}"/>
+    <hyperlink ref="B365" r:id="rId727" tooltip="https://www.indmoney.com/stocks/rdb-infrastructure-and-power-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D6020000}"/>
+    <hyperlink ref="M365" r:id="rId728" tooltip="https://www.indmoney.com/stocks/rdb-infrastructure-and-power-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D7020000}"/>
+    <hyperlink ref="B366" r:id="rId729" tooltip="https://www.indmoney.com/stocks/digispice-technologies-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D8020000}"/>
+    <hyperlink ref="M366" r:id="rId730" tooltip="https://www.indmoney.com/stocks/digispice-technologies-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000D9020000}"/>
+    <hyperlink ref="B367" r:id="rId731" tooltip="https://www.indmoney.com/stocks/jaiprakash-power-ventures-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000DA020000}"/>
+    <hyperlink ref="M367" r:id="rId732" tooltip="https://www.indmoney.com/stocks/jaiprakash-power-ventures-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000DB020000}"/>
+    <hyperlink ref="B368" r:id="rId733" tooltip="https://www.indmoney.com/stocks/hindustan-motors-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000DC020000}"/>
+    <hyperlink ref="M368" r:id="rId734" tooltip="https://www.indmoney.com/stocks/hindustan-motors-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000DD020000}"/>
+    <hyperlink ref="B369" r:id="rId735" tooltip="https://www.indmoney.com/stocks/broach-lifecare-hospital-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000DE020000}"/>
+    <hyperlink ref="M369" r:id="rId736" tooltip="https://www.indmoney.com/stocks/broach-lifecare-hospital-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000DF020000}"/>
+    <hyperlink ref="B370" r:id="rId737" tooltip="https://www.indmoney.com/stocks/popular-estate-management-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E0020000}"/>
+    <hyperlink ref="M370" r:id="rId738" tooltip="https://www.indmoney.com/stocks/popular-estate-management-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E1020000}"/>
+    <hyperlink ref="B371" r:id="rId739" tooltip="https://www.indmoney.com/stocks/gaekwar-mills-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E2020000}"/>
+    <hyperlink ref="M371" r:id="rId740" tooltip="https://www.indmoney.com/stocks/gaekwar-mills-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E3020000}"/>
+    <hyperlink ref="B372" r:id="rId741" tooltip="https://www.indmoney.com/stocks/aarcon-facilities-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E4020000}"/>
+    <hyperlink ref="M372" r:id="rId742" tooltip="https://www.indmoney.com/stocks/aarcon-facilities-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E5020000}"/>
+    <hyperlink ref="B373" r:id="rId743" tooltip="https://www.indmoney.com/stocks/rril-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E6020000}"/>
+    <hyperlink ref="M373" r:id="rId744" tooltip="https://www.indmoney.com/stocks/rril-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E7020000}"/>
+    <hyperlink ref="B374" r:id="rId745" tooltip="https://www.indmoney.com/stocks/balurghat-technologies-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E8020000}"/>
+    <hyperlink ref="M374" r:id="rId746" tooltip="https://www.indmoney.com/stocks/balurghat-technologies-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000E9020000}"/>
+    <hyperlink ref="B375" r:id="rId747" tooltip="https://www.indmoney.com/stocks/enser-communications-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000EA020000}"/>
+    <hyperlink ref="M375" r:id="rId748" tooltip="https://www.indmoney.com/stocks/enser-communications-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000EB020000}"/>
+    <hyperlink ref="B376" r:id="rId749" tooltip="https://www.indmoney.com/stocks/avenuesai-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000EC020000}"/>
+    <hyperlink ref="M376" r:id="rId750" tooltip="https://www.indmoney.com/stocks/avenuesai-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000ED020000}"/>
+    <hyperlink ref="B377" r:id="rId751" tooltip="https://www.indmoney.com/stocks/artemis-electricals-and-projects-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000EE020000}"/>
+    <hyperlink ref="M377" r:id="rId752" tooltip="https://www.indmoney.com/stocks/artemis-electricals-and-projects-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000EF020000}"/>
+    <hyperlink ref="B378" r:id="rId753" tooltip="https://www.indmoney.com/stocks/pavna-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F0020000}"/>
+    <hyperlink ref="M378" r:id="rId754" tooltip="https://www.indmoney.com/stocks/pavna-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F1020000}"/>
+    <hyperlink ref="B379" r:id="rId755" tooltip="https://www.indmoney.com/stocks/baba-arts-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F2020000}"/>
+    <hyperlink ref="M379" r:id="rId756" tooltip="https://www.indmoney.com/stocks/baba-arts-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F3020000}"/>
+    <hyperlink ref="B380" r:id="rId757" tooltip="https://www.indmoney.com/stocks/aqylon-nexus-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F4020000}"/>
+    <hyperlink ref="M380" r:id="rId758" tooltip="https://www.indmoney.com/stocks/aqylon-nexus-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F5020000}"/>
+    <hyperlink ref="B381" r:id="rId759" tooltip="https://www.indmoney.com/stocks/thinking-hats-entertainment-solutions-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F6020000}"/>
+    <hyperlink ref="M381" r:id="rId760" tooltip="https://www.indmoney.com/stocks/thinking-hats-entertainment-solutions-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F7020000}"/>
+    <hyperlink ref="B382" r:id="rId761" tooltip="https://www.indmoney.com/stocks/media-matrix-worldwide-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F8020000}"/>
+    <hyperlink ref="M382" r:id="rId762" tooltip="https://www.indmoney.com/stocks/media-matrix-worldwide-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000F9020000}"/>
+    <hyperlink ref="B383" r:id="rId763" tooltip="https://www.indmoney.com/stocks/modulex-construction-technologies-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000FA020000}"/>
+    <hyperlink ref="M383" r:id="rId764" tooltip="https://www.indmoney.com/stocks/modulex-construction-technologies-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000FB020000}"/>
+    <hyperlink ref="B384" r:id="rId765" tooltip="https://www.indmoney.com/stocks/airan-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000FC020000}"/>
+    <hyperlink ref="M384" r:id="rId766" tooltip="https://www.indmoney.com/stocks/airan-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000FD020000}"/>
+    <hyperlink ref="B385" r:id="rId767" tooltip="https://www.indmoney.com/stocks/eastcoast-steel-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000FE020000}"/>
+    <hyperlink ref="M385" r:id="rId768" tooltip="https://www.indmoney.com/stocks/eastcoast-steel-ltd-share-price" xr:uid="{00000000-0004-0000-0000-0000FF020000}"/>
+    <hyperlink ref="B386" r:id="rId769" tooltip="https://www.indmoney.com/stocks/rajeshwari-cans-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000000030000}"/>
+    <hyperlink ref="M386" r:id="rId770" tooltip="https://www.indmoney.com/stocks/rajeshwari-cans-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000001030000}"/>
+    <hyperlink ref="B387" r:id="rId771" tooltip="https://www.indmoney.com/stocks/rathi-bars-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000002030000}"/>
+    <hyperlink ref="M387" r:id="rId772" tooltip="https://www.indmoney.com/stocks/rathi-bars-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000003030000}"/>
+    <hyperlink ref="B388" r:id="rId773" tooltip="https://www.indmoney.com/stocks/standard-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000004030000}"/>
+    <hyperlink ref="M388" r:id="rId774" tooltip="https://www.indmoney.com/stocks/standard-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000005030000}"/>
+    <hyperlink ref="B389" r:id="rId775" tooltip="https://www.indmoney.com/stocks/rushil-decor-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000006030000}"/>
+    <hyperlink ref="M389" r:id="rId776" tooltip="https://www.indmoney.com/stocks/rushil-decor-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000007030000}"/>
+    <hyperlink ref="B390" r:id="rId777" tooltip="https://www.indmoney.com/stocks/surana-telecom-and-power-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000008030000}"/>
+    <hyperlink ref="M390" r:id="rId778" tooltip="https://www.indmoney.com/stocks/surana-telecom-and-power-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000009030000}"/>
+    <hyperlink ref="B391" r:id="rId779" tooltip="https://www.indmoney.com/stocks/bharat-road-network-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00000A030000}"/>
+    <hyperlink ref="M391" r:id="rId780" tooltip="https://www.indmoney.com/stocks/bharat-road-network-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00000B030000}"/>
+    <hyperlink ref="B392" r:id="rId781" tooltip="https://www.indmoney.com/stocks/swasth-foodtech-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00000C030000}"/>
+    <hyperlink ref="M392" r:id="rId782" tooltip="https://www.indmoney.com/stocks/swasth-foodtech-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00000D030000}"/>
+    <hyperlink ref="B393" r:id="rId783" tooltip="https://www.indmoney.com/stocks/pritika-auto-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00000E030000}"/>
+    <hyperlink ref="M393" r:id="rId784" tooltip="https://www.indmoney.com/stocks/pritika-auto-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00000F030000}"/>
+    <hyperlink ref="B394" r:id="rId785" tooltip="https://www.indmoney.com/stocks/prima-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000010030000}"/>
+    <hyperlink ref="M394" r:id="rId786" tooltip="https://www.indmoney.com/stocks/prima-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000011030000}"/>
+    <hyperlink ref="B395" r:id="rId787" tooltip="https://www.indmoney.com/stocks/poojawestern-metaliks-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000012030000}"/>
+    <hyperlink ref="M395" r:id="rId788" tooltip="https://www.indmoney.com/stocks/poojawestern-metaliks-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000013030000}"/>
+    <hyperlink ref="B396" r:id="rId789" tooltip="https://www.indmoney.com/stocks/globus-power-generation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000014030000}"/>
+    <hyperlink ref="M396" r:id="rId790" tooltip="https://www.indmoney.com/stocks/globus-power-generation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000015030000}"/>
+    <hyperlink ref="B397" r:id="rId791" tooltip="https://www.indmoney.com/stocks/jaysynth-orgochem-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000016030000}"/>
+    <hyperlink ref="M397" r:id="rId792" tooltip="https://www.indmoney.com/stocks/jaysynth-orgochem-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000017030000}"/>
+    <hyperlink ref="B398" r:id="rId793" tooltip="https://www.indmoney.com/stocks/orient-paper-and-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000018030000}"/>
+    <hyperlink ref="M398" r:id="rId794" tooltip="https://www.indmoney.com/stocks/orient-paper-and-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000019030000}"/>
+    <hyperlink ref="B399" r:id="rId795" tooltip="https://www.indmoney.com/stocks/advance-metering-technology-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00001A030000}"/>
+    <hyperlink ref="M399" r:id="rId796" tooltip="https://www.indmoney.com/stocks/advance-metering-technology-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00001B030000}"/>
+    <hyperlink ref="B400" r:id="rId797" tooltip="https://www.indmoney.com/stocks/rhetan-tmt-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00001C030000}"/>
+    <hyperlink ref="M400" r:id="rId798" tooltip="https://www.indmoney.com/stocks/rhetan-tmt-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00001D030000}"/>
+    <hyperlink ref="B401" r:id="rId799" tooltip="https://www.indmoney.com/stocks/containerway-international-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00001E030000}"/>
+    <hyperlink ref="M401" r:id="rId800" tooltip="https://www.indmoney.com/stocks/containerway-international-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00001F030000}"/>
+    <hyperlink ref="B402" r:id="rId801" tooltip="https://www.indmoney.com/stocks/zinema-media-and-entertainment-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000020030000}"/>
+    <hyperlink ref="M402" r:id="rId802" tooltip="https://www.indmoney.com/stocks/zinema-media-and-entertainment-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000021030000}"/>
+    <hyperlink ref="B403" r:id="rId803" tooltip="https://www.indmoney.com/stocks/galaxy-medicare-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000022030000}"/>
+    <hyperlink ref="M403" r:id="rId804" tooltip="https://www.indmoney.com/stocks/galaxy-medicare-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000023030000}"/>
+    <hyperlink ref="B404" r:id="rId805" tooltip="https://www.indmoney.com/stocks/irb-infrastructure-developers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000024030000}"/>
+    <hyperlink ref="M404" r:id="rId806" tooltip="https://www.indmoney.com/stocks/irb-infrastructure-developers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000025030000}"/>
+    <hyperlink ref="B405" r:id="rId807" tooltip="https://www.indmoney.com/stocks/phyto-chem-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000026030000}"/>
+    <hyperlink ref="M405" r:id="rId808" tooltip="https://www.indmoney.com/stocks/phyto-chem-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000027030000}"/>
+    <hyperlink ref="B406" r:id="rId809" tooltip="https://www.indmoney.com/stocks/rajgor-castor-derivatives-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000028030000}"/>
+    <hyperlink ref="M406" r:id="rId810" tooltip="https://www.indmoney.com/stocks/rajgor-castor-derivatives-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000029030000}"/>
+    <hyperlink ref="B407" r:id="rId811" tooltip="https://www.indmoney.com/stocks/shivam-autotech-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00002A030000}"/>
+    <hyperlink ref="M407" r:id="rId812" tooltip="https://www.indmoney.com/stocks/shivam-autotech-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00002B030000}"/>
+    <hyperlink ref="B408" r:id="rId813" tooltip="https://www.indmoney.com/stocks/pearl-polymers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00002C030000}"/>
+    <hyperlink ref="M408" r:id="rId814" tooltip="https://www.indmoney.com/stocks/pearl-polymers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00002D030000}"/>
+    <hyperlink ref="B409" r:id="rId815" tooltip="https://www.indmoney.com/stocks/vivo-bio-tech-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00002E030000}"/>
+    <hyperlink ref="M409" r:id="rId816" tooltip="https://www.indmoney.com/stocks/vivo-bio-tech-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00002F030000}"/>
+    <hyperlink ref="B410" r:id="rId817" tooltip="https://www.indmoney.com/stocks/kamanwala-housing-construction-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000030030000}"/>
+    <hyperlink ref="M410" r:id="rId818" tooltip="https://www.indmoney.com/stocks/kamanwala-housing-construction-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000031030000}"/>
+    <hyperlink ref="B411" r:id="rId819" tooltip="https://www.indmoney.com/stocks/essar-shipping-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000032030000}"/>
+    <hyperlink ref="M411" r:id="rId820" tooltip="https://www.indmoney.com/stocks/essar-shipping-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000033030000}"/>
+    <hyperlink ref="B412" r:id="rId821" tooltip="https://www.indmoney.com/stocks/ravikumar-distilleries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000034030000}"/>
+    <hyperlink ref="M412" r:id="rId822" tooltip="https://www.indmoney.com/stocks/ravikumar-distilleries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000035030000}"/>
+    <hyperlink ref="B413" r:id="rId823" tooltip="https://www.indmoney.com/stocks/adeshwar-meditex-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000036030000}"/>
+    <hyperlink ref="M413" r:id="rId824" tooltip="https://www.indmoney.com/stocks/adeshwar-meditex-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000037030000}"/>
+    <hyperlink ref="B414" r:id="rId825" tooltip="https://www.indmoney.com/stocks/shubhlaxmi-jewel-art-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000038030000}"/>
+    <hyperlink ref="M414" r:id="rId826" tooltip="https://www.indmoney.com/stocks/shubhlaxmi-jewel-art-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000039030000}"/>
+    <hyperlink ref="B415" r:id="rId827" tooltip="https://www.indmoney.com/stocks/anya-polytech-and-fertilizers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00003A030000}"/>
+    <hyperlink ref="M415" r:id="rId828" tooltip="https://www.indmoney.com/stocks/anya-polytech-and-fertilizers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00003B030000}"/>
+    <hyperlink ref="B416" r:id="rId829" tooltip="https://www.indmoney.com/stocks/kanoria-energy-and-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00003C030000}"/>
+    <hyperlink ref="M416" r:id="rId830" tooltip="https://www.indmoney.com/stocks/kanoria-energy-and-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00003D030000}"/>
+    <hyperlink ref="B417" r:id="rId831" tooltip="https://www.indmoney.com/stocks/vishal-fabrics-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00003E030000}"/>
+    <hyperlink ref="M417" r:id="rId832" tooltip="https://www.indmoney.com/stocks/vishal-fabrics-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00003F030000}"/>
+    <hyperlink ref="B418" r:id="rId833" tooltip="https://www.indmoney.com/stocks/best-agrolife-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000040030000}"/>
+    <hyperlink ref="M418" r:id="rId834" tooltip="https://www.indmoney.com/stocks/best-agrolife-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000041030000}"/>
+    <hyperlink ref="B419" r:id="rId835" tooltip="https://www.indmoney.com/stocks/sakthi-sugars-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000042030000}"/>
+    <hyperlink ref="M419" r:id="rId836" tooltip="https://www.indmoney.com/stocks/sakthi-sugars-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000043030000}"/>
+    <hyperlink ref="B420" r:id="rId837" tooltip="https://www.indmoney.com/stocks/noble-polymers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000044030000}"/>
+    <hyperlink ref="M420" r:id="rId838" tooltip="https://www.indmoney.com/stocks/noble-polymers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000045030000}"/>
+    <hyperlink ref="B421" r:id="rId839" tooltip="https://www.indmoney.com/stocks/kandr-rail-engineering-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000046030000}"/>
+    <hyperlink ref="M421" r:id="rId840" tooltip="https://www.indmoney.com/stocks/kandr-rail-engineering-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000047030000}"/>
+    <hyperlink ref="B422" r:id="rId841" tooltip="https://www.indmoney.com/stocks/rama-paper-mills-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000048030000}"/>
+    <hyperlink ref="M422" r:id="rId842" tooltip="https://www.indmoney.com/stocks/rama-paper-mills-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000049030000}"/>
+    <hyperlink ref="B423" r:id="rId843" tooltip="https://www.indmoney.com/stocks/omega-interactive-technologies-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00004A030000}"/>
+    <hyperlink ref="M423" r:id="rId844" tooltip="https://www.indmoney.com/stocks/omega-interactive-technologies-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00004B030000}"/>
+    <hyperlink ref="B424" r:id="rId845" tooltip="https://www.indmoney.com/stocks/sterling-green-woods-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00004C030000}"/>
+    <hyperlink ref="M424" r:id="rId846" tooltip="https://www.indmoney.com/stocks/sterling-green-woods-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00004D030000}"/>
+    <hyperlink ref="B425" r:id="rId847" tooltip="https://www.indmoney.com/stocks/uma-converter-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00004E030000}"/>
+    <hyperlink ref="M425" r:id="rId848" tooltip="https://www.indmoney.com/stocks/uma-converter-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00004F030000}"/>
+    <hyperlink ref="B426" r:id="rId849" tooltip="https://www.indmoney.com/stocks/motisons-jewellers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000050030000}"/>
+    <hyperlink ref="M426" r:id="rId850" tooltip="https://www.indmoney.com/stocks/motisons-jewellers-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000051030000}"/>
+    <hyperlink ref="B427" r:id="rId851" tooltip="https://www.indmoney.com/stocks/g-s-auto-international-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000052030000}"/>
+    <hyperlink ref="M427" r:id="rId852" tooltip="https://www.indmoney.com/stocks/g-s-auto-international-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000053030000}"/>
+    <hyperlink ref="B428" r:id="rId853" tooltip="https://www.indmoney.com/stocks/howard-hotels-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000054030000}"/>
+    <hyperlink ref="M428" r:id="rId854" tooltip="https://www.indmoney.com/stocks/howard-hotels-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000055030000}"/>
+    <hyperlink ref="B429" r:id="rId855" tooltip="https://www.indmoney.com/stocks/hazoor-multi-projects-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000056030000}"/>
+    <hyperlink ref="M429" r:id="rId856" tooltip="https://www.indmoney.com/stocks/hazoor-multi-projects-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000057030000}"/>
+    <hyperlink ref="B430" r:id="rId857" tooltip="https://www.indmoney.com/stocks/cyber-media-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000058030000}"/>
+    <hyperlink ref="M430" r:id="rId858" tooltip="https://www.indmoney.com/stocks/cyber-media-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000059030000}"/>
+    <hyperlink ref="B431" r:id="rId859" tooltip="https://www.indmoney.com/stocks/sdc-techmedia-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00005A030000}"/>
+    <hyperlink ref="M431" r:id="rId860" tooltip="https://www.indmoney.com/stocks/sdc-techmedia-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00005B030000}"/>
+    <hyperlink ref="B432" r:id="rId861" tooltip="https://www.indmoney.com/stocks/pnc-media-and-entertainment-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00005C030000}"/>
+    <hyperlink ref="M432" r:id="rId862" tooltip="https://www.indmoney.com/stocks/pnc-media-and-entertainment-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00005D030000}"/>
+    <hyperlink ref="B433" r:id="rId863" tooltip="https://www.indmoney.com/stocks/setco-automotive-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00005E030000}"/>
+    <hyperlink ref="M433" r:id="rId864" tooltip="https://www.indmoney.com/stocks/setco-automotive-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00005F030000}"/>
+    <hyperlink ref="B434" r:id="rId865" tooltip="https://www.indmoney.com/stocks/century-extrusions-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000060030000}"/>
+    <hyperlink ref="M434" r:id="rId866" tooltip="https://www.indmoney.com/stocks/century-extrusions-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000061030000}"/>
+    <hyperlink ref="B435" r:id="rId867" tooltip="https://www.indmoney.com/stocks/solvex-edibles-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000062030000}"/>
+    <hyperlink ref="M435" r:id="rId868" tooltip="https://www.indmoney.com/stocks/solvex-edibles-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000063030000}"/>
+    <hyperlink ref="B436" r:id="rId869" tooltip="https://www.indmoney.com/stocks/rudra-global-infra-products-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000064030000}"/>
+    <hyperlink ref="M436" r:id="rId870" tooltip="https://www.indmoney.com/stocks/rudra-global-infra-products-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000065030000}"/>
+    <hyperlink ref="B437" r:id="rId871" tooltip="https://www.indmoney.com/stocks/surya-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000066030000}"/>
+    <hyperlink ref="M437" r:id="rId872" tooltip="https://www.indmoney.com/stocks/surya-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000067030000}"/>
+    <hyperlink ref="B438" r:id="rId873" tooltip="https://www.indmoney.com/stocks/mahip-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000068030000}"/>
+    <hyperlink ref="M438" r:id="rId874" tooltip="https://www.indmoney.com/stocks/mahip-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000069030000}"/>
+    <hyperlink ref="B439" r:id="rId875" tooltip="https://www.indmoney.com/stocks/vms-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00006A030000}"/>
+    <hyperlink ref="M439" r:id="rId876" tooltip="https://www.indmoney.com/stocks/vms-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00006B030000}"/>
+    <hyperlink ref="B440" r:id="rId877" tooltip="https://www.indmoney.com/stocks/tpi-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00006C030000}"/>
+    <hyperlink ref="M440" r:id="rId878" tooltip="https://www.indmoney.com/stocks/tpi-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00006D030000}"/>
+    <hyperlink ref="B441" r:id="rId879" tooltip="https://www.indmoney.com/stocks/udayshivakumar-infra-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00006E030000}"/>
+    <hyperlink ref="M441" r:id="rId880" tooltip="https://www.indmoney.com/stocks/udayshivakumar-infra-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00006F030000}"/>
+    <hyperlink ref="B442" r:id="rId881" tooltip="https://www.indmoney.com/stocks/electro-force-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000070030000}"/>
+    <hyperlink ref="M442" r:id="rId882" tooltip="https://www.indmoney.com/stocks/electro-force-india-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000071030000}"/>
+    <hyperlink ref="B443" r:id="rId883" tooltip="https://www.indmoney.com/stocks/mandeep-auto-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000072030000}"/>
+    <hyperlink ref="M443" r:id="rId884" tooltip="https://www.indmoney.com/stocks/mandeep-auto-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000073030000}"/>
+    <hyperlink ref="B444" r:id="rId885" tooltip="https://www.indmoney.com/stocks/north-eastern-carrying-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000074030000}"/>
+    <hyperlink ref="M444" r:id="rId886" tooltip="https://www.indmoney.com/stocks/north-eastern-carrying-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000075030000}"/>
+    <hyperlink ref="B445" r:id="rId887" tooltip="https://www.indmoney.com/stocks/identical-brains-studios-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000076030000}"/>
+    <hyperlink ref="M445" r:id="rId888" tooltip="https://www.indmoney.com/stocks/identical-brains-studios-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000077030000}"/>
+    <hyperlink ref="B446" r:id="rId889" tooltip="https://www.indmoney.com/stocks/kalana-ispat-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000078030000}"/>
+    <hyperlink ref="M446" r:id="rId890" tooltip="https://www.indmoney.com/stocks/kalana-ispat-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000079030000}"/>
+    <hyperlink ref="B447" r:id="rId891" tooltip="https://www.indmoney.com/stocks/magnum-ventures-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00007A030000}"/>
+    <hyperlink ref="M447" r:id="rId892" tooltip="https://www.indmoney.com/stocks/magnum-ventures-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00007B030000}"/>
+    <hyperlink ref="B448" r:id="rId893" tooltip="https://www.indmoney.com/stocks/jain-irrigation-systems-ltd-dvr-share-price" xr:uid="{00000000-0004-0000-0000-00007C030000}"/>
+    <hyperlink ref="M448" r:id="rId894" tooltip="https://www.indmoney.com/stocks/jain-irrigation-systems-ltd-dvr-share-price" xr:uid="{00000000-0004-0000-0000-00007D030000}"/>
+    <hyperlink ref="B449" r:id="rId895" tooltip="https://www.indmoney.com/stocks/kabra-drugs-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00007E030000}"/>
+    <hyperlink ref="M449" r:id="rId896" tooltip="https://www.indmoney.com/stocks/kabra-drugs-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00007F030000}"/>
+    <hyperlink ref="B450" r:id="rId897" tooltip="https://www.indmoney.com/stocks/dev-labtech-venture-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000080030000}"/>
+    <hyperlink ref="M450" r:id="rId898" tooltip="https://www.indmoney.com/stocks/dev-labtech-venture-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000081030000}"/>
+    <hyperlink ref="B451" r:id="rId899" tooltip="https://www.indmoney.com/stocks/garware-marine-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000082030000}"/>
+    <hyperlink ref="M451" r:id="rId900" tooltip="https://www.indmoney.com/stocks/garware-marine-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000083030000}"/>
+    <hyperlink ref="B452" r:id="rId901" tooltip="https://www.indmoney.com/stocks/swastik-pipe-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000084030000}"/>
+    <hyperlink ref="M452" r:id="rId902" tooltip="https://www.indmoney.com/stocks/swastik-pipe-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000085030000}"/>
+    <hyperlink ref="B453" r:id="rId903" tooltip="https://www.indmoney.com/stocks/bajaj-hindusthan-sugar-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000086030000}"/>
+    <hyperlink ref="M453" r:id="rId904" tooltip="https://www.indmoney.com/stocks/bajaj-hindusthan-sugar-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000087030000}"/>
+    <hyperlink ref="B454" r:id="rId905" tooltip="https://www.indmoney.com/stocks/le-merite-exports-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000088030000}"/>
+    <hyperlink ref="M454" r:id="rId906" tooltip="https://www.indmoney.com/stocks/le-merite-exports-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000089030000}"/>
+    <hyperlink ref="B455" r:id="rId907" tooltip="https://www.indmoney.com/stocks/subex-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00008A030000}"/>
+    <hyperlink ref="M455" r:id="rId908" tooltip="https://www.indmoney.com/stocks/subex-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00008B030000}"/>
+    <hyperlink ref="B456" r:id="rId909" tooltip="https://www.indmoney.com/stocks/reliance-power-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00008C030000}"/>
+    <hyperlink ref="M456" r:id="rId910" tooltip="https://www.indmoney.com/stocks/reliance-power-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00008D030000}"/>
+    <hyperlink ref="B457" r:id="rId911" tooltip="https://www.indmoney.com/stocks/jet-freight-logistics-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00008E030000}"/>
+    <hyperlink ref="M457" r:id="rId912" tooltip="https://www.indmoney.com/stocks/jet-freight-logistics-ltd-share-price" xr:uid="{00000000-0004-0000-0000-00008F030000}"/>
+    <hyperlink ref="B458" r:id="rId913" tooltip="https://www.indmoney.com/stocks/rajshree-polypack-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000090030000}"/>
+    <hyperlink ref="M458" r:id="rId914" tooltip="https://www.indmoney.com/stocks/rajshree-polypack-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000091030000}"/>
+    <hyperlink ref="B459" r:id="rId915" tooltip="https://www.indmoney.com/stocks/swashthik-plascon-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000092030000}"/>
+    <hyperlink ref="M459" r:id="rId916" tooltip="https://www.indmoney.com/stocks/swashthik-plascon-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000093030000}"/>
+    <hyperlink ref="B460" r:id="rId917" tooltip="https://www.indmoney.com/stocks/blue-cloud-softech-solutions-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000094030000}"/>
+    <hyperlink ref="M460" r:id="rId918" tooltip="https://www.indmoney.com/stocks/blue-cloud-softech-solutions-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000095030000}"/>
+    <hyperlink ref="B461" r:id="rId919" tooltip="https://www.indmoney.com/stocks/centrum-capital-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000096030000}"/>
+    <hyperlink ref="M461" r:id="rId920" tooltip="https://www.indmoney.com/stocks/centrum-capital-ltd-share-price" xr:uid="{00000000-0004-0000-0000-000097030000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O115"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -17753,7 +17766,7 @@
     <col min="15" max="15" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>987</v>
       </c>
@@ -17800,7 +17813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -17835,7 +17848,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -17870,7 +17883,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -17887,7 +17900,7 @@
         <v>0.37</v>
       </c>
       <c r="F4" s="4">
-        <v>36.55</v>
+        <v>36.549999999999997</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -17905,7 +17918,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>990</v>
       </c>
@@ -17940,7 +17953,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>990</v>
       </c>
@@ -17965,7 +17978,7 @@
         <v>6.08</v>
       </c>
       <c r="J6" s="3">
-        <v>4.64</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
@@ -17975,7 +17988,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>992</v>
       </c>
@@ -18010,7 +18023,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>990</v>
       </c>
@@ -18045,7 +18058,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>992</v>
       </c>
@@ -18080,7 +18093,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>104</v>
       </c>
@@ -18115,7 +18128,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>992</v>
       </c>
@@ -18150,7 +18163,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>990</v>
       </c>
@@ -18185,7 +18198,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>992</v>
       </c>
@@ -18220,7 +18233,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>994</v>
       </c>
@@ -18234,7 +18247,7 @@
         <v>147</v>
       </c>
       <c r="E14" s="3">
-        <v>2.26</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="F14" s="4">
         <v>383.27</v>
@@ -18255,7 +18268,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>104</v>
       </c>
@@ -18290,7 +18303,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>992</v>
       </c>
@@ -18304,7 +18317,7 @@
         <v>159</v>
       </c>
       <c r="E16" s="3">
-        <v>2.51</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="F16" s="4">
         <v>396.38</v>
@@ -18325,7 +18338,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>992</v>
       </c>
@@ -18350,7 +18363,7 @@
         <v>-1.52</v>
       </c>
       <c r="J17" s="3">
-        <v>-9.2</v>
+        <v>-9.1999999999999993</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
@@ -18360,7 +18373,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>990</v>
       </c>
@@ -18395,7 +18408,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>990</v>
       </c>
@@ -18417,7 +18430,7 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3">
-        <v>4.23</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="J19" s="3">
         <v>3.43</v>
@@ -18430,7 +18443,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>990</v>
       </c>
@@ -18465,7 +18478,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>994</v>
       </c>
@@ -18500,7 +18513,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>990</v>
       </c>
@@ -18522,7 +18535,7 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3">
-        <v>4.85</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="J22" s="3">
         <v>-0.21</v>
@@ -18535,7 +18548,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>994</v>
       </c>
@@ -18557,7 +18570,7 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3">
-        <v>8.46</v>
+        <v>8.4600000000000009</v>
       </c>
       <c r="J23" s="3">
         <v>4.07</v>
@@ -18570,7 +18583,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>992</v>
       </c>
@@ -18587,7 +18600,7 @@
         <v>3.56</v>
       </c>
       <c r="F24" s="4">
-        <v>66.29</v>
+        <v>66.290000000000006</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -18605,7 +18618,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>990</v>
       </c>
@@ -18640,7 +18653,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>990</v>
       </c>
@@ -18662,7 +18675,7 @@
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3">
-        <v>10.2</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="J26" s="3">
         <v>8.89</v>
@@ -18675,7 +18688,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>990</v>
       </c>
@@ -18689,7 +18702,7 @@
         <v>242</v>
       </c>
       <c r="E27" s="3">
-        <v>4.02</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="F27" s="4">
         <v>43.8</v>
@@ -18710,7 +18723,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>990</v>
       </c>
@@ -18724,10 +18737,10 @@
         <v>252</v>
       </c>
       <c r="E28" s="3">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F28" s="4">
-        <v>134.89</v>
+        <v>134.88999999999999</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
@@ -18745,7 +18758,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>990</v>
       </c>
@@ -18767,7 +18780,7 @@
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3">
-        <v>10.05</v>
+        <v>10.050000000000001</v>
       </c>
       <c r="J29" s="3">
         <v>5.83</v>
@@ -18780,7 +18793,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>990</v>
       </c>
@@ -18815,7 +18828,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>990</v>
       </c>
@@ -18850,7 +18863,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>104</v>
       </c>
@@ -18867,7 +18880,7 @@
         <v>4.67</v>
       </c>
       <c r="F32" s="4">
-        <v>4.77</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
@@ -18885,7 +18898,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>990</v>
       </c>
@@ -18920,7 +18933,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>990</v>
       </c>
@@ -18955,7 +18968,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>992</v>
       </c>
@@ -18980,7 +18993,7 @@
         <v>1.97</v>
       </c>
       <c r="J35" s="3">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
@@ -18990,7 +19003,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>990</v>
       </c>
@@ -19004,7 +19017,7 @@
         <v>294</v>
       </c>
       <c r="E36" s="3">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="F36" s="4">
         <v>72.56</v>
@@ -19015,7 +19028,7 @@
         <v>0.74</v>
       </c>
       <c r="J36" s="3">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
@@ -19025,7 +19038,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>24</v>
       </c>
@@ -19060,7 +19073,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>24</v>
       </c>
@@ -19095,7 +19108,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>24</v>
       </c>
@@ -19112,7 +19125,7 @@
         <v>5.8</v>
       </c>
       <c r="F39" s="4">
-        <v>142.64</v>
+        <v>142.63999999999999</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
@@ -19130,7 +19143,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>24</v>
       </c>
@@ -19165,7 +19178,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>990</v>
       </c>
@@ -19200,7 +19213,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>990</v>
       </c>
@@ -19225,7 +19238,7 @@
         <v>2.52</v>
       </c>
       <c r="J42" s="3">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
@@ -19235,7 +19248,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>992</v>
       </c>
@@ -19252,15 +19265,15 @@
         <v>6.5</v>
       </c>
       <c r="F43" s="4">
-        <v>302.78</v>
+        <v>302.77999999999997</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3">
-        <v>20.35</v>
+        <v>20.350000000000001</v>
       </c>
       <c r="J43" s="3">
-        <v>20.26</v>
+        <v>20.260000000000002</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
@@ -19270,7 +19283,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>990</v>
       </c>
@@ -19305,7 +19318,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>992</v>
       </c>
@@ -19322,12 +19335,12 @@
         <v>6.57</v>
       </c>
       <c r="F45" s="4">
-        <v>258.79</v>
+        <v>258.79000000000002</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3">
-        <v>18.26</v>
+        <v>18.260000000000002</v>
       </c>
       <c r="J45" s="3">
         <v>13.88</v>
@@ -19340,7 +19353,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>404</v>
       </c>
@@ -19375,7 +19388,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>404</v>
       </c>
@@ -19397,7 +19410,7 @@
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3">
-        <v>2.49</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="J47" s="3">
         <v>0.44</v>
@@ -19410,7 +19423,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>992</v>
       </c>
@@ -19432,7 +19445,7 @@
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3">
-        <v>2.45</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="J48" s="3">
         <v>-23.09</v>
@@ -19445,7 +19458,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>104</v>
       </c>
@@ -19480,7 +19493,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>992</v>
       </c>
@@ -19515,7 +19528,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>994</v>
       </c>
@@ -19550,7 +19563,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>992</v>
       </c>
@@ -19585,7 +19598,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>990</v>
       </c>
@@ -19620,7 +19633,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>24</v>
       </c>
@@ -19655,7 +19668,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>24</v>
       </c>
@@ -19669,7 +19682,7 @@
         <v>510</v>
       </c>
       <c r="E55" s="3">
-        <v>8.38</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="F55" s="4">
         <v>109.33</v>
@@ -19690,7 +19703,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>404</v>
       </c>
@@ -19707,7 +19720,7 @@
         <v>8.44</v>
       </c>
       <c r="F56" s="4">
-        <v>135.89</v>
+        <v>135.88999999999999</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
@@ -19725,7 +19738,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>990</v>
       </c>
@@ -19760,7 +19773,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>404</v>
       </c>
@@ -19795,7 +19808,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>990</v>
       </c>
@@ -19809,7 +19822,7 @@
         <v>533</v>
       </c>
       <c r="E59" s="3">
-        <v>8.87</v>
+        <v>8.8699999999999992</v>
       </c>
       <c r="F59" s="4">
         <v>38.81</v>
@@ -19830,7 +19843,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>990</v>
       </c>
@@ -19844,7 +19857,7 @@
         <v>545</v>
       </c>
       <c r="E60" s="3">
-        <v>9.04</v>
+        <v>9.0399999999999991</v>
       </c>
       <c r="F60" s="4">
         <v>178.44</v>
@@ -19852,7 +19865,7 @@
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3">
-        <v>20.19</v>
+        <v>20.190000000000001</v>
       </c>
       <c r="J60" s="3">
         <v>20.78</v>
@@ -19865,7 +19878,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>104</v>
       </c>
@@ -19900,7 +19913,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>24</v>
       </c>
@@ -19914,7 +19927,7 @@
         <v>578</v>
       </c>
       <c r="E62" s="3">
-        <v>9.8</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="F62" s="4">
         <v>238.09</v>
@@ -19935,7 +19948,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>990</v>
       </c>
@@ -19949,7 +19962,7 @@
         <v>582</v>
       </c>
       <c r="E63" s="3">
-        <v>9.95</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="F63" s="4">
         <v>5.25</v>
@@ -19960,7 +19973,7 @@
         <v>8.6</v>
       </c>
       <c r="J63" s="3">
-        <v>9.78</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="K63" s="3"/>
       <c r="L63" s="3"/>
@@ -19970,7 +19983,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>24</v>
       </c>
@@ -20005,7 +20018,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>990</v>
       </c>
@@ -20022,7 +20035,7 @@
         <v>10</v>
       </c>
       <c r="F65" s="4">
-        <v>131.14</v>
+        <v>131.13999999999999</v>
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
@@ -20040,7 +20053,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>104</v>
       </c>
@@ -20054,7 +20067,7 @@
         <v>590</v>
       </c>
       <c r="E66" s="3">
-        <v>10.12</v>
+        <v>10.119999999999999</v>
       </c>
       <c r="F66" s="4">
         <v>7.08</v>
@@ -20075,7 +20088,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>24</v>
       </c>
@@ -20110,7 +20123,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>992</v>
       </c>
@@ -20145,7 +20158,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>990</v>
       </c>
@@ -20167,7 +20180,7 @@
       <c r="G69" s="3"/>
       <c r="H69" s="3"/>
       <c r="I69" s="3">
-        <v>8.8</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="J69" s="3">
         <v>2.65</v>
@@ -20180,7 +20193,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>104</v>
       </c>
@@ -20215,7 +20228,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>990</v>
       </c>
@@ -20237,7 +20250,7 @@
       <c r="G71" s="3"/>
       <c r="H71" s="3"/>
       <c r="I71" s="3">
-        <v>-9.63</v>
+        <v>-9.6300000000000008</v>
       </c>
       <c r="J71" s="3">
         <v>-14</v>
@@ -20250,7 +20263,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>104</v>
       </c>
@@ -20285,7 +20298,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>998</v>
       </c>
@@ -20320,7 +20333,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>990</v>
       </c>
@@ -20355,7 +20368,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>992</v>
       </c>
@@ -20390,7 +20403,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>104</v>
       </c>
@@ -20425,7 +20438,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>104</v>
       </c>
@@ -20460,7 +20473,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>990</v>
       </c>
@@ -20495,7 +20508,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>992</v>
       </c>
@@ -20530,7 +20543,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>104</v>
       </c>
@@ -20565,7 +20578,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>992</v>
       </c>
@@ -20590,7 +20603,7 @@
         <v>4.03</v>
       </c>
       <c r="J81" s="3">
-        <v>-2.55</v>
+        <v>-2.5499999999999998</v>
       </c>
       <c r="K81" s="3"/>
       <c r="L81" s="3"/>
@@ -20600,7 +20613,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>990</v>
       </c>
@@ -20617,7 +20630,7 @@
         <v>13.86</v>
       </c>
       <c r="F82" s="4">
-        <v>16.56</v>
+        <v>16.559999999999999</v>
       </c>
       <c r="G82" s="3"/>
       <c r="H82" s="3"/>
@@ -20635,7 +20648,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>404</v>
       </c>
@@ -20657,7 +20670,7 @@
       <c r="G83" s="3"/>
       <c r="H83" s="3"/>
       <c r="I83" s="3">
-        <v>0.07</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="J83" s="3">
         <v>0.34</v>
@@ -20670,7 +20683,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>990</v>
       </c>
@@ -20692,7 +20705,7 @@
       <c r="G84" s="3"/>
       <c r="H84" s="3"/>
       <c r="I84" s="3">
-        <v>8.38</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="J84" s="3">
         <v>8.41</v>
@@ -20705,7 +20718,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>992</v>
       </c>
@@ -20740,7 +20753,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>990</v>
       </c>
@@ -20775,7 +20788,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>404</v>
       </c>
@@ -20810,7 +20823,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>24</v>
       </c>
@@ -20832,10 +20845,10 @@
       <c r="G88" s="3"/>
       <c r="H88" s="3"/>
       <c r="I88" s="3">
-        <v>2.28</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="J88" s="3">
-        <v>2.07</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="K88" s="3"/>
       <c r="L88" s="3"/>
@@ -20845,7 +20858,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>404</v>
       </c>
@@ -20862,7 +20875,7 @@
         <v>14.8</v>
       </c>
       <c r="F89" s="4">
-        <v>10143.12</v>
+        <v>10143.120000000001</v>
       </c>
       <c r="G89" s="3"/>
       <c r="H89" s="3"/>
@@ -20880,7 +20893,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>104</v>
       </c>
@@ -20915,7 +20928,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>992</v>
       </c>
@@ -20932,7 +20945,7 @@
         <v>15.56</v>
       </c>
       <c r="F91" s="4">
-        <v>163.33</v>
+        <v>163.33000000000001</v>
       </c>
       <c r="G91" s="3"/>
       <c r="H91" s="3"/>
@@ -20950,7 +20963,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>990</v>
       </c>
@@ -20975,7 +20988,7 @@
         <v>-0.6</v>
       </c>
       <c r="J92" s="3">
-        <v>-2.51</v>
+        <v>-2.5099999999999998</v>
       </c>
       <c r="K92" s="3"/>
       <c r="L92" s="3"/>
@@ -20985,7 +20998,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>990</v>
       </c>
@@ -21020,7 +21033,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>404</v>
       </c>
@@ -21055,7 +21068,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>992</v>
       </c>
@@ -21090,7 +21103,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>990</v>
       </c>
@@ -21115,7 +21128,7 @@
         <v>6.92</v>
       </c>
       <c r="J96" s="3">
-        <v>4.35</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="K96" s="3"/>
       <c r="L96" s="3"/>
@@ -21125,7 +21138,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>404</v>
       </c>
@@ -21139,10 +21152,10 @@
         <v>852</v>
       </c>
       <c r="E97" s="3">
-        <v>16.19</v>
+        <v>16.190000000000001</v>
       </c>
       <c r="F97" s="4">
-        <v>160.2</v>
+        <v>160.19999999999999</v>
       </c>
       <c r="G97" s="3"/>
       <c r="H97" s="3"/>
@@ -21160,7 +21173,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>990</v>
       </c>
@@ -21195,7 +21208,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>104</v>
       </c>
@@ -21230,7 +21243,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>992</v>
       </c>
@@ -21247,7 +21260,7 @@
         <v>17</v>
       </c>
       <c r="F100" s="4">
-        <v>20532.6</v>
+        <v>20532.599999999999</v>
       </c>
       <c r="G100" s="3"/>
       <c r="H100" s="3"/>
@@ -21265,7 +21278,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>24</v>
       </c>
@@ -21287,7 +21300,7 @@
       <c r="G101" s="3"/>
       <c r="H101" s="3"/>
       <c r="I101" s="3">
-        <v>9.37</v>
+        <v>9.3699999999999992</v>
       </c>
       <c r="J101" s="3">
         <v>6.05</v>
@@ -21300,7 +21313,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>104</v>
       </c>
@@ -21335,7 +21348,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>992</v>
       </c>
@@ -21357,7 +21370,7 @@
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
       <c r="I103" s="3">
-        <v>8.2</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="J103" s="3">
         <v>6.75</v>
@@ -21370,7 +21383,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>992</v>
       </c>
@@ -21384,7 +21397,7 @@
         <v>919</v>
       </c>
       <c r="E104" s="3">
-        <v>17.94</v>
+        <v>17.940000000000001</v>
       </c>
       <c r="F104" s="4">
         <v>485.51</v>
@@ -21395,7 +21408,7 @@
         <v>6.06</v>
       </c>
       <c r="J104" s="3">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="K104" s="3"/>
       <c r="L104" s="3"/>
@@ -21405,7 +21418,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>990</v>
       </c>
@@ -21427,7 +21440,7 @@
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
       <c r="I105" s="3">
-        <v>18.06</v>
+        <v>18.059999999999999</v>
       </c>
       <c r="J105" s="3">
         <v>13.23</v>
@@ -21440,7 +21453,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>990</v>
       </c>
@@ -21475,7 +21488,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>998</v>
       </c>
@@ -21510,7 +21523,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>992</v>
       </c>
@@ -21545,7 +21558,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>990</v>
       </c>
@@ -21580,7 +21593,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>24</v>
       </c>
@@ -21602,7 +21615,7 @@
       <c r="G110" s="3"/>
       <c r="H110" s="3"/>
       <c r="I110" s="3">
-        <v>20.08</v>
+        <v>20.079999999999998</v>
       </c>
       <c r="J110" s="3">
         <v>17.63</v>
@@ -21615,7 +21628,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>998</v>
       </c>
@@ -21650,7 +21663,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>990</v>
       </c>
@@ -21685,7 +21698,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>994</v>
       </c>
@@ -21699,10 +21712,10 @@
         <v>969</v>
       </c>
       <c r="E113" s="3">
-        <v>19.19</v>
+        <v>19.190000000000001</v>
       </c>
       <c r="F113" s="4">
-        <v>4587.69</v>
+        <v>4587.6899999999996</v>
       </c>
       <c r="G113" s="3"/>
       <c r="H113" s="3"/>
@@ -21710,7 +21723,7 @@
         <v>2.15</v>
       </c>
       <c r="J113" s="3">
-        <v>4.64</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="K113" s="3"/>
       <c r="L113" s="3"/>
@@ -21720,7 +21733,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>404</v>
       </c>
@@ -21755,7 +21768,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="115" ht="32" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
         <v>999</v>
       </c>
@@ -21775,239 +21788,239 @@
       <c r="O115" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1"/>
+  <autoFilter ref="A1:O115" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A115:O115"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" tooltip="https://www.indmoney.com/stocks/welcure-drugs-and-pharmaceuticals-ltd-share-price"/>
-    <hyperlink ref="O2" r:id="rId2" tooltip="https://www.indmoney.com/stocks/welcure-drugs-and-pharmaceuticals-ltd-share-price"/>
-    <hyperlink ref="D3" r:id="rId3" tooltip="https://www.indmoney.com/stocks/remedium-lifecare-ltd-share-price"/>
-    <hyperlink ref="O3" r:id="rId4" tooltip="https://www.indmoney.com/stocks/remedium-lifecare-ltd-share-price"/>
-    <hyperlink ref="D4" r:id="rId5" tooltip="https://www.indmoney.com/stocks/rajnish-wellness-ltd-share-price"/>
-    <hyperlink ref="O4" r:id="rId6" tooltip="https://www.indmoney.com/stocks/rajnish-wellness-ltd-share-price"/>
-    <hyperlink ref="D5" r:id="rId7" tooltip="https://www.indmoney.com/stocks/western-ministil-ltd-share-price"/>
-    <hyperlink ref="O5" r:id="rId8" tooltip="https://www.indmoney.com/stocks/western-ministil-ltd-share-price"/>
-    <hyperlink ref="D6" r:id="rId9" tooltip="https://www.indmoney.com/stocks/unison-metals-ltd-share-price"/>
-    <hyperlink ref="O6" r:id="rId10" tooltip="https://www.indmoney.com/stocks/unison-metals-ltd-share-price"/>
-    <hyperlink ref="D7" r:id="rId11" tooltip="https://www.indmoney.com/stocks/navkar-urbanstructure-ltd-share-price"/>
-    <hyperlink ref="O7" r:id="rId12" tooltip="https://www.indmoney.com/stocks/navkar-urbanstructure-ltd-share-price"/>
-    <hyperlink ref="D8" r:id="rId13" tooltip="https://www.indmoney.com/stocks/sprayking-ltd-share-price"/>
-    <hyperlink ref="O8" r:id="rId14" tooltip="https://www.indmoney.com/stocks/sprayking-ltd-share-price"/>
-    <hyperlink ref="D9" r:id="rId15" tooltip="https://www.indmoney.com/stocks/ducon-infratechnologies-ltd-share-price"/>
-    <hyperlink ref="O9" r:id="rId16" tooltip="https://www.indmoney.com/stocks/ducon-infratechnologies-ltd-share-price"/>
-    <hyperlink ref="D10" r:id="rId17" tooltip="https://www.indmoney.com/stocks/family-care-hospitals-ltd-share-price"/>
-    <hyperlink ref="O10" r:id="rId18" tooltip="https://www.indmoney.com/stocks/family-care-hospitals-ltd-share-price"/>
-    <hyperlink ref="D11" r:id="rId19" tooltip="https://www.indmoney.com/stocks/ilandfs-transportation-networks-ltd-share-price"/>
-    <hyperlink ref="O11" r:id="rId20" tooltip="https://www.indmoney.com/stocks/ilandfs-transportation-networks-ltd-share-price"/>
-    <hyperlink ref="D12" r:id="rId21" tooltip="https://www.indmoney.com/stocks/ankit-metal-and-power-ltd-share-price"/>
-    <hyperlink ref="O12" r:id="rId22" tooltip="https://www.indmoney.com/stocks/ankit-metal-and-power-ltd-share-price"/>
-    <hyperlink ref="D13" r:id="rId23" tooltip="https://www.indmoney.com/stocks/parsvnath-developers-ltd-share-price"/>
-    <hyperlink ref="O13" r:id="rId24" tooltip="https://www.indmoney.com/stocks/parsvnath-developers-ltd-share-price"/>
-    <hyperlink ref="D14" r:id="rId25" tooltip="https://www.indmoney.com/stocks/davangere-sugar-company-ltd-share-price"/>
-    <hyperlink ref="O14" r:id="rId26" tooltip="https://www.indmoney.com/stocks/davangere-sugar-company-ltd-share-price"/>
-    <hyperlink ref="D15" r:id="rId27" tooltip="https://www.indmoney.com/stocks/transgene-biotek-ltd-share-price"/>
-    <hyperlink ref="O15" r:id="rId28" tooltip="https://www.indmoney.com/stocks/transgene-biotek-ltd-share-price"/>
-    <hyperlink ref="D16" r:id="rId29" tooltip="https://www.indmoney.com/stocks/gvk-power-and-infrastructure-ltd-share-price"/>
-    <hyperlink ref="O16" r:id="rId30" tooltip="https://www.indmoney.com/stocks/gvk-power-and-infrastructure-ltd-share-price"/>
-    <hyperlink ref="D17" r:id="rId31" tooltip="https://www.indmoney.com/stocks/sadbhav-infrastructure-projects-ltd-share-price"/>
-    <hyperlink ref="O17" r:id="rId32" tooltip="https://www.indmoney.com/stocks/sadbhav-infrastructure-projects-ltd-share-price"/>
-    <hyperlink ref="D18" r:id="rId33" tooltip="https://www.indmoney.com/stocks/alliance-integrated-metaliks-ltd-share-price"/>
-    <hyperlink ref="O18" r:id="rId34" tooltip="https://www.indmoney.com/stocks/alliance-integrated-metaliks-ltd-share-price"/>
-    <hyperlink ref="D19" r:id="rId35" tooltip="https://www.indmoney.com/stocks/shah-metacorp-ltd-share-price"/>
-    <hyperlink ref="O19" r:id="rId36" tooltip="https://www.indmoney.com/stocks/shah-metacorp-ltd-share-price"/>
-    <hyperlink ref="D20" r:id="rId37" tooltip="https://www.indmoney.com/stocks/facor-alloys-ltd-share-price"/>
-    <hyperlink ref="O20" r:id="rId38" tooltip="https://www.indmoney.com/stocks/facor-alloys-ltd-share-price"/>
-    <hyperlink ref="D21" r:id="rId39" tooltip="https://www.indmoney.com/stocks/mishtann-foods-ltd-share-price"/>
-    <hyperlink ref="O21" r:id="rId40" tooltip="https://www.indmoney.com/stocks/mishtann-foods-ltd-share-price"/>
-    <hyperlink ref="D22" r:id="rId41" tooltip="https://www.indmoney.com/stocks/rajnandini-metal-ltd-share-price"/>
-    <hyperlink ref="O22" r:id="rId42" tooltip="https://www.indmoney.com/stocks/rajnandini-metal-ltd-share-price"/>
-    <hyperlink ref="D23" r:id="rId43" tooltip="https://www.indmoney.com/stocks/sarveshwar-foods-ltd-share-price"/>
-    <hyperlink ref="O23" r:id="rId44" tooltip="https://www.indmoney.com/stocks/sarveshwar-foods-ltd-share-price"/>
-    <hyperlink ref="D24" r:id="rId45" tooltip="https://www.indmoney.com/stocks/noida-toll-bridge-company-ltd-share-price"/>
-    <hyperlink ref="O24" r:id="rId46" tooltip="https://www.indmoney.com/stocks/noida-toll-bridge-company-ltd-share-price"/>
-    <hyperlink ref="D25" r:id="rId47" tooltip="https://www.indmoney.com/stocks/prakash-steelage-ltd-share-price"/>
-    <hyperlink ref="O25" r:id="rId48" tooltip="https://www.indmoney.com/stocks/prakash-steelage-ltd-share-price"/>
-    <hyperlink ref="D26" r:id="rId49" tooltip="https://www.indmoney.com/stocks/sacheta-metals-ltd-share-price"/>
-    <hyperlink ref="O26" r:id="rId50" tooltip="https://www.indmoney.com/stocks/sacheta-metals-ltd-share-price"/>
-    <hyperlink ref="D27" r:id="rId51" tooltip="https://www.indmoney.com/stocks/dhatre-udyog-ltd-share-price"/>
-    <hyperlink ref="O27" r:id="rId52" tooltip="https://www.indmoney.com/stocks/dhatre-udyog-ltd-share-price"/>
-    <hyperlink ref="D28" r:id="rId53" tooltip="https://www.indmoney.com/stocks/kamdhenu-ventures-ltd-share-price"/>
-    <hyperlink ref="O28" r:id="rId54" tooltip="https://www.indmoney.com/stocks/kamdhenu-ventures-ltd-share-price"/>
-    <hyperlink ref="D29" r:id="rId55" tooltip="https://www.indmoney.com/stocks/salasar-techno-engineering-ltd-share-price"/>
-    <hyperlink ref="O29" r:id="rId56" tooltip="https://www.indmoney.com/stocks/salasar-techno-engineering-ltd-share-price"/>
-    <hyperlink ref="D30" r:id="rId57" tooltip="https://www.indmoney.com/stocks/supreme-engineering-ltd-share-price"/>
-    <hyperlink ref="O30" r:id="rId58" tooltip="https://www.indmoney.com/stocks/supreme-engineering-ltd-share-price"/>
-    <hyperlink ref="D31" r:id="rId59" tooltip="https://www.indmoney.com/stocks/rama-steel-tubes-ltd-share-price"/>
-    <hyperlink ref="O31" r:id="rId60" tooltip="https://www.indmoney.com/stocks/rama-steel-tubes-ltd-share-price"/>
-    <hyperlink ref="D32" r:id="rId61" tooltip="https://www.indmoney.com/stocks/gian-lifecare-ltd-share-price"/>
-    <hyperlink ref="O32" r:id="rId62" tooltip="https://www.indmoney.com/stocks/gian-lifecare-ltd-share-price"/>
-    <hyperlink ref="D33" r:id="rId63" tooltip="https://www.indmoney.com/stocks/kritika-wires-ltd-share-price"/>
-    <hyperlink ref="O33" r:id="rId64" tooltip="https://www.indmoney.com/stocks/kritika-wires-ltd-share-price"/>
-    <hyperlink ref="D34" r:id="rId65" tooltip="https://www.indmoney.com/stocks/shyam-century-ferrous-ltd-share-price"/>
-    <hyperlink ref="O34" r:id="rId66" tooltip="https://www.indmoney.com/stocks/shyam-century-ferrous-ltd-share-price"/>
-    <hyperlink ref="D35" r:id="rId67" tooltip="https://www.indmoney.com/stocks/sepc-ltd-share-price"/>
-    <hyperlink ref="O35" r:id="rId68" tooltip="https://www.indmoney.com/stocks/sepc-ltd-share-price"/>
-    <hyperlink ref="D36" r:id="rId69" tooltip="https://www.indmoney.com/stocks/zenith-steel-pipes-and-industries-ltd-share-price"/>
-    <hyperlink ref="O36" r:id="rId70" tooltip="https://www.indmoney.com/stocks/zenith-steel-pipes-and-industries-ltd-share-price"/>
-    <hyperlink ref="D37" r:id="rId71" tooltip="https://www.indmoney.com/stocks/lasa-supergenerics-ltd-share-price"/>
-    <hyperlink ref="O37" r:id="rId72" tooltip="https://www.indmoney.com/stocks/lasa-supergenerics-ltd-share-price"/>
-    <hyperlink ref="D38" r:id="rId73" tooltip="https://www.indmoney.com/stocks/vivimed-labs-ltd-share-price"/>
-    <hyperlink ref="O38" r:id="rId74" tooltip="https://www.indmoney.com/stocks/vivimed-labs-ltd-share-price"/>
-    <hyperlink ref="D39" r:id="rId75" tooltip="https://www.indmoney.com/stocks/achyut-healthcare-ltd-share-price"/>
-    <hyperlink ref="O39" r:id="rId76" tooltip="https://www.indmoney.com/stocks/achyut-healthcare-ltd-share-price"/>
-    <hyperlink ref="D40" r:id="rId77" tooltip="https://www.indmoney.com/stocks/vista-pharmaceuticals-ltd-share-price"/>
-    <hyperlink ref="O40" r:id="rId78" tooltip="https://www.indmoney.com/stocks/vista-pharmaceuticals-ltd-share-price"/>
-    <hyperlink ref="D41" r:id="rId79" tooltip="https://www.indmoney.com/stocks/heera-ispat-ltd-share-price"/>
-    <hyperlink ref="O41" r:id="rId80" tooltip="https://www.indmoney.com/stocks/heera-ispat-ltd-share-price"/>
-    <hyperlink ref="D42" r:id="rId81" tooltip="https://www.indmoney.com/stocks/bothra-metals-and-alloys-ltd-share-price"/>
-    <hyperlink ref="O42" r:id="rId82" tooltip="https://www.indmoney.com/stocks/bothra-metals-and-alloys-ltd-share-price"/>
-    <hyperlink ref="D43" r:id="rId83" tooltip="https://www.indmoney.com/stocks/deepak-builders-and-engineers-india-ltd-share-price"/>
-    <hyperlink ref="O43" r:id="rId84" tooltip="https://www.indmoney.com/stocks/deepak-builders-and-engineers-india-ltd-share-price"/>
-    <hyperlink ref="D44" r:id="rId85" tooltip="https://www.indmoney.com/stocks/impex-ferro-tech-ltd-share-price"/>
-    <hyperlink ref="O44" r:id="rId86" tooltip="https://www.indmoney.com/stocks/impex-ferro-tech-ltd-share-price"/>
-    <hyperlink ref="D45" r:id="rId87" tooltip="https://www.indmoney.com/stocks/nila-infrastructures-ltd-share-price"/>
-    <hyperlink ref="O45" r:id="rId88" tooltip="https://www.indmoney.com/stocks/nila-infrastructures-ltd-share-price"/>
-    <hyperlink ref="D46" r:id="rId89" tooltip="https://www.indmoney.com/stocks/rattanindia-power-ltd-share-price"/>
-    <hyperlink ref="O46" r:id="rId90" tooltip="https://www.indmoney.com/stocks/rattanindia-power-ltd-share-price"/>
-    <hyperlink ref="D47" r:id="rId91" tooltip="https://www.indmoney.com/stocks/india-power-corporation-ltd-share-price"/>
-    <hyperlink ref="O47" r:id="rId92" tooltip="https://www.indmoney.com/stocks/india-power-corporation-ltd-share-price"/>
-    <hyperlink ref="D48" r:id="rId93" tooltip="https://www.indmoney.com/stocks/sadbhav-engineering-ltd-share-price"/>
-    <hyperlink ref="O48" r:id="rId94" tooltip="https://www.indmoney.com/stocks/sadbhav-engineering-ltd-share-price"/>
-    <hyperlink ref="D49" r:id="rId95" tooltip="https://www.indmoney.com/stocks/dr-lalchandani-labs-ltd-share-price"/>
-    <hyperlink ref="O49" r:id="rId96" tooltip="https://www.indmoney.com/stocks/dr-lalchandani-labs-ltd-share-price"/>
-    <hyperlink ref="D50" r:id="rId97" tooltip="https://www.indmoney.com/stocks/madhav-infra-projects-ltd-share-price"/>
-    <hyperlink ref="O50" r:id="rId98" tooltip="https://www.indmoney.com/stocks/madhav-infra-projects-ltd-share-price"/>
-    <hyperlink ref="D51" r:id="rId99" tooltip="https://www.indmoney.com/stocks/elitecon-international-ltd-share-price"/>
-    <hyperlink ref="O51" r:id="rId100" tooltip="https://www.indmoney.com/stocks/elitecon-international-ltd-share-price"/>
-    <hyperlink ref="D52" r:id="rId101" tooltip="https://www.indmoney.com/stocks/twamev-construction-and-infrastructure-ltd-share-price"/>
-    <hyperlink ref="O52" r:id="rId102" tooltip="https://www.indmoney.com/stocks/twamev-construction-and-infrastructure-ltd-share-price"/>
-    <hyperlink ref="D53" r:id="rId103" tooltip="https://www.indmoney.com/stocks/aditya-ispat-ltd-share-price"/>
-    <hyperlink ref="O53" r:id="rId104" tooltip="https://www.indmoney.com/stocks/aditya-ispat-ltd-share-price"/>
-    <hyperlink ref="D54" r:id="rId105" tooltip="https://www.indmoney.com/stocks/bharat-immunological-and-biological-corporation-ltd-share-price"/>
-    <hyperlink ref="O54" r:id="rId106" tooltip="https://www.indmoney.com/stocks/bharat-immunological-and-biological-corporation-ltd-share-price"/>
-    <hyperlink ref="D55" r:id="rId107" tooltip="https://www.indmoney.com/stocks/vaishali-pharma-ltd-share-price"/>
-    <hyperlink ref="O55" r:id="rId108" tooltip="https://www.indmoney.com/stocks/vaishali-pharma-ltd-share-price"/>
-    <hyperlink ref="D56" r:id="rId109" tooltip="https://www.indmoney.com/stocks/indowind-energy-ltd-share-price"/>
-    <hyperlink ref="O56" r:id="rId110" tooltip="https://www.indmoney.com/stocks/indowind-energy-ltd-share-price"/>
-    <hyperlink ref="D57" r:id="rId111" tooltip="https://www.indmoney.com/stocks/vallabh-steels-ltd-share-price"/>
-    <hyperlink ref="O57" r:id="rId112" tooltip="https://www.indmoney.com/stocks/vallabh-steels-ltd-share-price"/>
-    <hyperlink ref="D58" r:id="rId113" tooltip="https://www.indmoney.com/stocks/orient-green-power-company-ltd-share-price"/>
-    <hyperlink ref="O58" r:id="rId114" tooltip="https://www.indmoney.com/stocks/orient-green-power-company-ltd-share-price"/>
-    <hyperlink ref="D59" r:id="rId115" tooltip="https://www.indmoney.com/stocks/rajasthan-tube-manufacturing-co-ltd-share-price"/>
-    <hyperlink ref="O59" r:id="rId116" tooltip="https://www.indmoney.com/stocks/rajasthan-tube-manufacturing-co-ltd-share-price"/>
-    <hyperlink ref="D60" r:id="rId117" tooltip="https://www.indmoney.com/stocks/baroda-extrusion-ltd-share-price"/>
-    <hyperlink ref="O60" r:id="rId118" tooltip="https://www.indmoney.com/stocks/baroda-extrusion-ltd-share-price"/>
-    <hyperlink ref="D61" r:id="rId119" tooltip="https://www.indmoney.com/stocks/looks-health-services-ltd-share-price"/>
-    <hyperlink ref="O61" r:id="rId120" tooltip="https://www.indmoney.com/stocks/looks-health-services-ltd-share-price"/>
-    <hyperlink ref="D62" r:id="rId121" tooltip="https://www.indmoney.com/stocks/gennex-laboratories-ltd-share-price"/>
-    <hyperlink ref="O62" r:id="rId122" tooltip="https://www.indmoney.com/stocks/gennex-laboratories-ltd-share-price"/>
-    <hyperlink ref="D63" r:id="rId123" tooltip="https://www.indmoney.com/stocks/mahalaxmi-seamless-ltd-share-price"/>
-    <hyperlink ref="O63" r:id="rId124" tooltip="https://www.indmoney.com/stocks/mahalaxmi-seamless-ltd-share-price"/>
-    <hyperlink ref="D64" r:id="rId125" tooltip="https://www.indmoney.com/stocks/jfl-life-sciences-ltd-share-price"/>
-    <hyperlink ref="O64" r:id="rId126" tooltip="https://www.indmoney.com/stocks/jfl-life-sciences-ltd-share-price"/>
-    <hyperlink ref="D65" r:id="rId127" tooltip="https://www.indmoney.com/stocks/la-tim-metal-and-industries-ltd-share-price"/>
-    <hyperlink ref="O65" r:id="rId128" tooltip="https://www.indmoney.com/stocks/la-tim-metal-and-industries-ltd-share-price"/>
-    <hyperlink ref="D66" r:id="rId129" tooltip="https://www.indmoney.com/stocks/boston-commerce-limited-share-price"/>
-    <hyperlink ref="O66" r:id="rId130" tooltip="https://www.indmoney.com/stocks/boston-commerce-limited-share-price"/>
-    <hyperlink ref="D67" r:id="rId131" tooltip="https://www.indmoney.com/stocks/nectar-lifescience-ltd-share-price"/>
-    <hyperlink ref="O67" r:id="rId132" tooltip="https://www.indmoney.com/stocks/nectar-lifescience-ltd-share-price"/>
-    <hyperlink ref="D68" r:id="rId133" tooltip="https://www.indmoney.com/stocks/maruti-infrastructure-ltd-share-price"/>
-    <hyperlink ref="O68" r:id="rId134" tooltip="https://www.indmoney.com/stocks/maruti-infrastructure-ltd-share-price"/>
-    <hyperlink ref="D69" r:id="rId135" tooltip="https://www.indmoney.com/stocks/steel-exchange-india-ltd-share-price"/>
-    <hyperlink ref="O69" r:id="rId136" tooltip="https://www.indmoney.com/stocks/steel-exchange-india-ltd-share-price"/>
-    <hyperlink ref="D70" r:id="rId137" tooltip="https://www.indmoney.com/stocks/deccan-health-care-ltd-share-price"/>
-    <hyperlink ref="O70" r:id="rId138" tooltip="https://www.indmoney.com/stocks/deccan-health-care-ltd-share-price"/>
-    <hyperlink ref="D71" r:id="rId139" tooltip="https://www.indmoney.com/stocks/earthstahl-and-alloys-ltd-share-price"/>
-    <hyperlink ref="O71" r:id="rId140" tooltip="https://www.indmoney.com/stocks/earthstahl-and-alloys-ltd-share-price"/>
-    <hyperlink ref="D72" r:id="rId141" tooltip="https://www.indmoney.com/stocks/global-longlife-hospital-and-research-ltd-share-price"/>
-    <hyperlink ref="O72" r:id="rId142" tooltip="https://www.indmoney.com/stocks/global-longlife-hospital-and-research-ltd-share-price"/>
-    <hyperlink ref="D73" r:id="rId143" tooltip="https://www.indmoney.com/stocks/global-defence-industries-limited-share-price"/>
-    <hyperlink ref="O73" r:id="rId144" tooltip="https://www.indmoney.com/stocks/global-defence-industries-limited-share-price"/>
-    <hyperlink ref="D74" r:id="rId145" tooltip="https://www.indmoney.com/stocks/bihar-sponge-iron-ltd-share-price"/>
-    <hyperlink ref="O74" r:id="rId146" tooltip="https://www.indmoney.com/stocks/bihar-sponge-iron-ltd-share-price"/>
-    <hyperlink ref="D75" r:id="rId147" tooltip="https://www.indmoney.com/stocks/a-b-infrabuild-ltd-share-price"/>
-    <hyperlink ref="O75" r:id="rId148" tooltip="https://www.indmoney.com/stocks/a-b-infrabuild-ltd-share-price"/>
-    <hyperlink ref="D76" r:id="rId149" tooltip="https://www.indmoney.com/stocks/take-ltd-share-price"/>
-    <hyperlink ref="O76" r:id="rId150" tooltip="https://www.indmoney.com/stocks/take-ltd-share-price"/>
-    <hyperlink ref="D77" r:id="rId151" tooltip="https://www.indmoney.com/stocks/tejnaksh-healthcare-ltd-share-price"/>
-    <hyperlink ref="O77" r:id="rId152" tooltip="https://www.indmoney.com/stocks/tejnaksh-healthcare-ltd-share-price"/>
-    <hyperlink ref="D78" r:id="rId153" tooltip="https://www.indmoney.com/stocks/nova-iron-and-steel-ltd-share-price"/>
-    <hyperlink ref="O78" r:id="rId154" tooltip="https://www.indmoney.com/stocks/nova-iron-and-steel-ltd-share-price"/>
-    <hyperlink ref="D79" r:id="rId155" tooltip="https://www.indmoney.com/stocks/atal-realtech-ltd-share-price"/>
-    <hyperlink ref="O79" r:id="rId156" tooltip="https://www.indmoney.com/stocks/atal-realtech-ltd-share-price"/>
-    <hyperlink ref="D80" r:id="rId157" tooltip="https://www.indmoney.com/stocks/nidan-laboratories-and-healthcare-ltd-share-price"/>
-    <hyperlink ref="O80" r:id="rId158" tooltip="https://www.indmoney.com/stocks/nidan-laboratories-and-healthcare-ltd-share-price"/>
-    <hyperlink ref="D81" r:id="rId159" tooltip="https://www.indmoney.com/stocks/consolidated-construction-consortium-ltd-share-price"/>
-    <hyperlink ref="O81" r:id="rId160" tooltip="https://www.indmoney.com/stocks/consolidated-construction-consortium-ltd-share-price"/>
-    <hyperlink ref="D82" r:id="rId161" tooltip="https://www.indmoney.com/stocks/mukat-pipes-ltd-share-price"/>
-    <hyperlink ref="O82" r:id="rId162" tooltip="https://www.indmoney.com/stocks/mukat-pipes-ltd-share-price"/>
-    <hyperlink ref="D83" r:id="rId163" tooltip="https://www.indmoney.com/stocks/ind-renewable-energy-ltd-share-price"/>
-    <hyperlink ref="O83" r:id="rId164" tooltip="https://www.indmoney.com/stocks/ind-renewable-energy-ltd-share-price"/>
-    <hyperlink ref="D84" r:id="rId165" tooltip="https://www.indmoney.com/stocks/modern-steels-ltd-share-price"/>
-    <hyperlink ref="O84" r:id="rId166" tooltip="https://www.indmoney.com/stocks/modern-steels-ltd-share-price"/>
-    <hyperlink ref="D85" r:id="rId167" tooltip="https://www.indmoney.com/stocks/a2z-infra-engineering-ltd-share-price"/>
-    <hyperlink ref="O85" r:id="rId168" tooltip="https://www.indmoney.com/stocks/a2z-infra-engineering-ltd-share-price"/>
-    <hyperlink ref="D86" r:id="rId169" tooltip="https://www.indmoney.com/stocks/arcee-industries-ltd-share-price"/>
-    <hyperlink ref="O86" r:id="rId170" tooltip="https://www.indmoney.com/stocks/arcee-industries-ltd-share-price"/>
-    <hyperlink ref="D87" r:id="rId171" tooltip="https://www.indmoney.com/stocks/energy-development-company-ltd-share-price"/>
-    <hyperlink ref="O87" r:id="rId172" tooltip="https://www.indmoney.com/stocks/energy-development-company-ltd-share-price"/>
-    <hyperlink ref="D88" r:id="rId173" tooltip="https://www.indmoney.com/stocks/venmax-drugs-and-pharmaceuticals-ltd-share-price"/>
-    <hyperlink ref="O88" r:id="rId174" tooltip="https://www.indmoney.com/stocks/venmax-drugs-and-pharmaceuticals-ltd-share-price"/>
-    <hyperlink ref="D89" r:id="rId175" tooltip="https://www.indmoney.com/stocks/jaiprakash-power-ventures-ltd-share-price"/>
-    <hyperlink ref="O89" r:id="rId176" tooltip="https://www.indmoney.com/stocks/jaiprakash-power-ventures-ltd-share-price"/>
-    <hyperlink ref="D90" r:id="rId177" tooltip="https://www.indmoney.com/stocks/broach-lifecare-hospital-ltd-share-price"/>
-    <hyperlink ref="O90" r:id="rId178" tooltip="https://www.indmoney.com/stocks/broach-lifecare-hospital-ltd-share-price"/>
-    <hyperlink ref="D91" r:id="rId179" tooltip="https://www.indmoney.com/stocks/modulex-construction-technologies-ltd-share-price"/>
-    <hyperlink ref="O91" r:id="rId180" tooltip="https://www.indmoney.com/stocks/modulex-construction-technologies-ltd-share-price"/>
-    <hyperlink ref="D92" r:id="rId181" tooltip="https://www.indmoney.com/stocks/eastcoast-steel-ltd-share-price"/>
-    <hyperlink ref="O92" r:id="rId182" tooltip="https://www.indmoney.com/stocks/eastcoast-steel-ltd-share-price"/>
-    <hyperlink ref="D93" r:id="rId183" tooltip="https://www.indmoney.com/stocks/rathi-bars-ltd-share-price"/>
-    <hyperlink ref="O93" r:id="rId184" tooltip="https://www.indmoney.com/stocks/rathi-bars-ltd-share-price"/>
-    <hyperlink ref="D94" r:id="rId185" tooltip="https://www.indmoney.com/stocks/surana-telecom-and-power-ltd-share-price"/>
-    <hyperlink ref="O94" r:id="rId186" tooltip="https://www.indmoney.com/stocks/surana-telecom-and-power-ltd-share-price"/>
-    <hyperlink ref="D95" r:id="rId187" tooltip="https://www.indmoney.com/stocks/bharat-road-network-ltd-share-price"/>
-    <hyperlink ref="O95" r:id="rId188" tooltip="https://www.indmoney.com/stocks/bharat-road-network-ltd-share-price"/>
-    <hyperlink ref="D96" r:id="rId189" tooltip="https://www.indmoney.com/stocks/poojawestern-metaliks-ltd-share-price"/>
-    <hyperlink ref="O96" r:id="rId190" tooltip="https://www.indmoney.com/stocks/poojawestern-metaliks-ltd-share-price"/>
-    <hyperlink ref="D97" r:id="rId191" tooltip="https://www.indmoney.com/stocks/globus-power-generation-ltd-share-price"/>
-    <hyperlink ref="O97" r:id="rId192" tooltip="https://www.indmoney.com/stocks/globus-power-generation-ltd-share-price"/>
-    <hyperlink ref="D98" r:id="rId193" tooltip="https://www.indmoney.com/stocks/rhetan-tmt-ltd-share-price"/>
-    <hyperlink ref="O98" r:id="rId194" tooltip="https://www.indmoney.com/stocks/rhetan-tmt-ltd-share-price"/>
-    <hyperlink ref="D99" r:id="rId195" tooltip="https://www.indmoney.com/stocks/galaxy-medicare-ltd-share-price"/>
-    <hyperlink ref="O99" r:id="rId196" tooltip="https://www.indmoney.com/stocks/galaxy-medicare-ltd-share-price"/>
-    <hyperlink ref="D100" r:id="rId197" tooltip="https://www.indmoney.com/stocks/irb-infrastructure-developers-ltd-share-price"/>
-    <hyperlink ref="O100" r:id="rId198" tooltip="https://www.indmoney.com/stocks/irb-infrastructure-developers-ltd-share-price"/>
-    <hyperlink ref="D101" r:id="rId199" tooltip="https://www.indmoney.com/stocks/vivo-bio-tech-ltd-share-price"/>
-    <hyperlink ref="O101" r:id="rId200" tooltip="https://www.indmoney.com/stocks/vivo-bio-tech-ltd-share-price"/>
-    <hyperlink ref="D102" r:id="rId201" tooltip="https://www.indmoney.com/stocks/adeshwar-meditex-ltd-share-price"/>
-    <hyperlink ref="O102" r:id="rId202" tooltip="https://www.indmoney.com/stocks/adeshwar-meditex-ltd-share-price"/>
-    <hyperlink ref="D103" r:id="rId203" tooltip="https://www.indmoney.com/stocks/kandr-rail-engineering-ltd-share-price"/>
-    <hyperlink ref="O103" r:id="rId204" tooltip="https://www.indmoney.com/stocks/kandr-rail-engineering-ltd-share-price"/>
-    <hyperlink ref="D104" r:id="rId205" tooltip="https://www.indmoney.com/stocks/hazoor-multi-projects-ltd-share-price"/>
-    <hyperlink ref="O104" r:id="rId206" tooltip="https://www.indmoney.com/stocks/hazoor-multi-projects-ltd-share-price"/>
-    <hyperlink ref="D105" r:id="rId207" tooltip="https://www.indmoney.com/stocks/century-extrusions-ltd-share-price"/>
-    <hyperlink ref="O105" r:id="rId208" tooltip="https://www.indmoney.com/stocks/century-extrusions-ltd-share-price"/>
-    <hyperlink ref="D106" r:id="rId209" tooltip="https://www.indmoney.com/stocks/rudra-global-infra-products-ltd-share-price"/>
-    <hyperlink ref="O106" r:id="rId210" tooltip="https://www.indmoney.com/stocks/rudra-global-infra-products-ltd-share-price"/>
-    <hyperlink ref="D107" r:id="rId211" tooltip="https://www.indmoney.com/stocks/vms-industries-ltd-share-price"/>
-    <hyperlink ref="O107" r:id="rId212" tooltip="https://www.indmoney.com/stocks/vms-industries-ltd-share-price"/>
-    <hyperlink ref="D108" r:id="rId213" tooltip="https://www.indmoney.com/stocks/udayshivakumar-infra-ltd-share-price"/>
-    <hyperlink ref="O108" r:id="rId214" tooltip="https://www.indmoney.com/stocks/udayshivakumar-infra-ltd-share-price"/>
-    <hyperlink ref="D109" r:id="rId215" tooltip="https://www.indmoney.com/stocks/kalana-ispat-ltd-share-price"/>
-    <hyperlink ref="O109" r:id="rId216" tooltip="https://www.indmoney.com/stocks/kalana-ispat-ltd-share-price"/>
-    <hyperlink ref="D110" r:id="rId217" tooltip="https://www.indmoney.com/stocks/kabra-drugs-ltd-share-price"/>
-    <hyperlink ref="O110" r:id="rId218" tooltip="https://www.indmoney.com/stocks/kabra-drugs-ltd-share-price"/>
-    <hyperlink ref="D111" r:id="rId219" tooltip="https://www.indmoney.com/stocks/garware-marine-industries-ltd-share-price"/>
-    <hyperlink ref="O111" r:id="rId220" tooltip="https://www.indmoney.com/stocks/garware-marine-industries-ltd-share-price"/>
-    <hyperlink ref="D112" r:id="rId221" tooltip="https://www.indmoney.com/stocks/swastik-pipe-ltd-share-price"/>
-    <hyperlink ref="O112" r:id="rId222" tooltip="https://www.indmoney.com/stocks/swastik-pipe-ltd-share-price"/>
-    <hyperlink ref="D113" r:id="rId223" tooltip="https://www.indmoney.com/stocks/bajaj-hindusthan-sugar-ltd-share-price"/>
-    <hyperlink ref="O113" r:id="rId224" tooltip="https://www.indmoney.com/stocks/bajaj-hindusthan-sugar-ltd-share-price"/>
-    <hyperlink ref="D114" r:id="rId225" tooltip="https://www.indmoney.com/stocks/reliance-power-ltd-share-price"/>
-    <hyperlink ref="O114" r:id="rId226" tooltip="https://www.indmoney.com/stocks/reliance-power-ltd-share-price"/>
+    <hyperlink ref="D2" r:id="rId1" tooltip="https://www.indmoney.com/stocks/welcure-drugs-and-pharmaceuticals-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="O2" r:id="rId2" tooltip="https://www.indmoney.com/stocks/welcure-drugs-and-pharmaceuticals-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="D3" r:id="rId3" tooltip="https://www.indmoney.com/stocks/remedium-lifecare-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="O3" r:id="rId4" tooltip="https://www.indmoney.com/stocks/remedium-lifecare-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="D4" r:id="rId5" tooltip="https://www.indmoney.com/stocks/rajnish-wellness-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="O4" r:id="rId6" tooltip="https://www.indmoney.com/stocks/rajnish-wellness-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="D5" r:id="rId7" tooltip="https://www.indmoney.com/stocks/western-ministil-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
+    <hyperlink ref="O5" r:id="rId8" tooltip="https://www.indmoney.com/stocks/western-ministil-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="D6" r:id="rId9" tooltip="https://www.indmoney.com/stocks/unison-metals-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
+    <hyperlink ref="O6" r:id="rId10" tooltip="https://www.indmoney.com/stocks/unison-metals-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
+    <hyperlink ref="D7" r:id="rId11" tooltip="https://www.indmoney.com/stocks/navkar-urbanstructure-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
+    <hyperlink ref="O7" r:id="rId12" tooltip="https://www.indmoney.com/stocks/navkar-urbanstructure-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
+    <hyperlink ref="D8" r:id="rId13" tooltip="https://www.indmoney.com/stocks/sprayking-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
+    <hyperlink ref="O8" r:id="rId14" tooltip="https://www.indmoney.com/stocks/sprayking-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
+    <hyperlink ref="D9" r:id="rId15" tooltip="https://www.indmoney.com/stocks/ducon-infratechnologies-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
+    <hyperlink ref="O9" r:id="rId16" tooltip="https://www.indmoney.com/stocks/ducon-infratechnologies-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
+    <hyperlink ref="D10" r:id="rId17" tooltip="https://www.indmoney.com/stocks/family-care-hospitals-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
+    <hyperlink ref="O10" r:id="rId18" tooltip="https://www.indmoney.com/stocks/family-care-hospitals-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
+    <hyperlink ref="D11" r:id="rId19" tooltip="https://www.indmoney.com/stocks/ilandfs-transportation-networks-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
+    <hyperlink ref="O11" r:id="rId20" tooltip="https://www.indmoney.com/stocks/ilandfs-transportation-networks-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
+    <hyperlink ref="D12" r:id="rId21" tooltip="https://www.indmoney.com/stocks/ankit-metal-and-power-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
+    <hyperlink ref="O12" r:id="rId22" tooltip="https://www.indmoney.com/stocks/ankit-metal-and-power-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
+    <hyperlink ref="D13" r:id="rId23" tooltip="https://www.indmoney.com/stocks/parsvnath-developers-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
+    <hyperlink ref="O13" r:id="rId24" tooltip="https://www.indmoney.com/stocks/parsvnath-developers-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
+    <hyperlink ref="D14" r:id="rId25" tooltip="https://www.indmoney.com/stocks/davangere-sugar-company-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
+    <hyperlink ref="O14" r:id="rId26" tooltip="https://www.indmoney.com/stocks/davangere-sugar-company-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
+    <hyperlink ref="D15" r:id="rId27" tooltip="https://www.indmoney.com/stocks/transgene-biotek-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
+    <hyperlink ref="O15" r:id="rId28" tooltip="https://www.indmoney.com/stocks/transgene-biotek-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
+    <hyperlink ref="D16" r:id="rId29" tooltip="https://www.indmoney.com/stocks/gvk-power-and-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
+    <hyperlink ref="O16" r:id="rId30" tooltip="https://www.indmoney.com/stocks/gvk-power-and-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
+    <hyperlink ref="D17" r:id="rId31" tooltip="https://www.indmoney.com/stocks/sadbhav-infrastructure-projects-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00001E000000}"/>
+    <hyperlink ref="O17" r:id="rId32" tooltip="https://www.indmoney.com/stocks/sadbhav-infrastructure-projects-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00001F000000}"/>
+    <hyperlink ref="D18" r:id="rId33" tooltip="https://www.indmoney.com/stocks/alliance-integrated-metaliks-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
+    <hyperlink ref="O18" r:id="rId34" tooltip="https://www.indmoney.com/stocks/alliance-integrated-metaliks-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
+    <hyperlink ref="D19" r:id="rId35" tooltip="https://www.indmoney.com/stocks/shah-metacorp-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
+    <hyperlink ref="O19" r:id="rId36" tooltip="https://www.indmoney.com/stocks/shah-metacorp-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
+    <hyperlink ref="D20" r:id="rId37" tooltip="https://www.indmoney.com/stocks/facor-alloys-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
+    <hyperlink ref="O20" r:id="rId38" tooltip="https://www.indmoney.com/stocks/facor-alloys-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
+    <hyperlink ref="D21" r:id="rId39" tooltip="https://www.indmoney.com/stocks/mishtann-foods-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
+    <hyperlink ref="O21" r:id="rId40" tooltip="https://www.indmoney.com/stocks/mishtann-foods-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000027000000}"/>
+    <hyperlink ref="D22" r:id="rId41" tooltip="https://www.indmoney.com/stocks/rajnandini-metal-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000028000000}"/>
+    <hyperlink ref="O22" r:id="rId42" tooltip="https://www.indmoney.com/stocks/rajnandini-metal-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000029000000}"/>
+    <hyperlink ref="D23" r:id="rId43" tooltip="https://www.indmoney.com/stocks/sarveshwar-foods-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
+    <hyperlink ref="O23" r:id="rId44" tooltip="https://www.indmoney.com/stocks/sarveshwar-foods-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
+    <hyperlink ref="D24" r:id="rId45" tooltip="https://www.indmoney.com/stocks/noida-toll-bridge-company-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
+    <hyperlink ref="O24" r:id="rId46" tooltip="https://www.indmoney.com/stocks/noida-toll-bridge-company-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
+    <hyperlink ref="D25" r:id="rId47" tooltip="https://www.indmoney.com/stocks/prakash-steelage-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
+    <hyperlink ref="O25" r:id="rId48" tooltip="https://www.indmoney.com/stocks/prakash-steelage-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00002F000000}"/>
+    <hyperlink ref="D26" r:id="rId49" tooltip="https://www.indmoney.com/stocks/sacheta-metals-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000030000000}"/>
+    <hyperlink ref="O26" r:id="rId50" tooltip="https://www.indmoney.com/stocks/sacheta-metals-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000031000000}"/>
+    <hyperlink ref="D27" r:id="rId51" tooltip="https://www.indmoney.com/stocks/dhatre-udyog-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000032000000}"/>
+    <hyperlink ref="O27" r:id="rId52" tooltip="https://www.indmoney.com/stocks/dhatre-udyog-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000033000000}"/>
+    <hyperlink ref="D28" r:id="rId53" tooltip="https://www.indmoney.com/stocks/kamdhenu-ventures-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000034000000}"/>
+    <hyperlink ref="O28" r:id="rId54" tooltip="https://www.indmoney.com/stocks/kamdhenu-ventures-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000035000000}"/>
+    <hyperlink ref="D29" r:id="rId55" tooltip="https://www.indmoney.com/stocks/salasar-techno-engineering-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000036000000}"/>
+    <hyperlink ref="O29" r:id="rId56" tooltip="https://www.indmoney.com/stocks/salasar-techno-engineering-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000037000000}"/>
+    <hyperlink ref="D30" r:id="rId57" tooltip="https://www.indmoney.com/stocks/supreme-engineering-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000038000000}"/>
+    <hyperlink ref="O30" r:id="rId58" tooltip="https://www.indmoney.com/stocks/supreme-engineering-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000039000000}"/>
+    <hyperlink ref="D31" r:id="rId59" tooltip="https://www.indmoney.com/stocks/rama-steel-tubes-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00003A000000}"/>
+    <hyperlink ref="O31" r:id="rId60" tooltip="https://www.indmoney.com/stocks/rama-steel-tubes-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00003B000000}"/>
+    <hyperlink ref="D32" r:id="rId61" tooltip="https://www.indmoney.com/stocks/gian-lifecare-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00003C000000}"/>
+    <hyperlink ref="O32" r:id="rId62" tooltip="https://www.indmoney.com/stocks/gian-lifecare-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00003D000000}"/>
+    <hyperlink ref="D33" r:id="rId63" tooltip="https://www.indmoney.com/stocks/kritika-wires-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00003E000000}"/>
+    <hyperlink ref="O33" r:id="rId64" tooltip="https://www.indmoney.com/stocks/kritika-wires-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00003F000000}"/>
+    <hyperlink ref="D34" r:id="rId65" tooltip="https://www.indmoney.com/stocks/shyam-century-ferrous-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000040000000}"/>
+    <hyperlink ref="O34" r:id="rId66" tooltip="https://www.indmoney.com/stocks/shyam-century-ferrous-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000041000000}"/>
+    <hyperlink ref="D35" r:id="rId67" tooltip="https://www.indmoney.com/stocks/sepc-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000042000000}"/>
+    <hyperlink ref="O35" r:id="rId68" tooltip="https://www.indmoney.com/stocks/sepc-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000043000000}"/>
+    <hyperlink ref="D36" r:id="rId69" tooltip="https://www.indmoney.com/stocks/zenith-steel-pipes-and-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000044000000}"/>
+    <hyperlink ref="O36" r:id="rId70" tooltip="https://www.indmoney.com/stocks/zenith-steel-pipes-and-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000045000000}"/>
+    <hyperlink ref="D37" r:id="rId71" tooltip="https://www.indmoney.com/stocks/lasa-supergenerics-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000046000000}"/>
+    <hyperlink ref="O37" r:id="rId72" tooltip="https://www.indmoney.com/stocks/lasa-supergenerics-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000047000000}"/>
+    <hyperlink ref="D38" r:id="rId73" tooltip="https://www.indmoney.com/stocks/vivimed-labs-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000048000000}"/>
+    <hyperlink ref="O38" r:id="rId74" tooltip="https://www.indmoney.com/stocks/vivimed-labs-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000049000000}"/>
+    <hyperlink ref="D39" r:id="rId75" tooltip="https://www.indmoney.com/stocks/achyut-healthcare-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00004A000000}"/>
+    <hyperlink ref="O39" r:id="rId76" tooltip="https://www.indmoney.com/stocks/achyut-healthcare-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00004B000000}"/>
+    <hyperlink ref="D40" r:id="rId77" tooltip="https://www.indmoney.com/stocks/vista-pharmaceuticals-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00004C000000}"/>
+    <hyperlink ref="O40" r:id="rId78" tooltip="https://www.indmoney.com/stocks/vista-pharmaceuticals-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00004D000000}"/>
+    <hyperlink ref="D41" r:id="rId79" tooltip="https://www.indmoney.com/stocks/heera-ispat-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00004E000000}"/>
+    <hyperlink ref="O41" r:id="rId80" tooltip="https://www.indmoney.com/stocks/heera-ispat-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00004F000000}"/>
+    <hyperlink ref="D42" r:id="rId81" tooltip="https://www.indmoney.com/stocks/bothra-metals-and-alloys-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000050000000}"/>
+    <hyperlink ref="O42" r:id="rId82" tooltip="https://www.indmoney.com/stocks/bothra-metals-and-alloys-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000051000000}"/>
+    <hyperlink ref="D43" r:id="rId83" tooltip="https://www.indmoney.com/stocks/deepak-builders-and-engineers-india-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000052000000}"/>
+    <hyperlink ref="O43" r:id="rId84" tooltip="https://www.indmoney.com/stocks/deepak-builders-and-engineers-india-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000053000000}"/>
+    <hyperlink ref="D44" r:id="rId85" tooltip="https://www.indmoney.com/stocks/impex-ferro-tech-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000054000000}"/>
+    <hyperlink ref="O44" r:id="rId86" tooltip="https://www.indmoney.com/stocks/impex-ferro-tech-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000055000000}"/>
+    <hyperlink ref="D45" r:id="rId87" tooltip="https://www.indmoney.com/stocks/nila-infrastructures-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000056000000}"/>
+    <hyperlink ref="O45" r:id="rId88" tooltip="https://www.indmoney.com/stocks/nila-infrastructures-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000057000000}"/>
+    <hyperlink ref="D46" r:id="rId89" tooltip="https://www.indmoney.com/stocks/rattanindia-power-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000058000000}"/>
+    <hyperlink ref="O46" r:id="rId90" tooltip="https://www.indmoney.com/stocks/rattanindia-power-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000059000000}"/>
+    <hyperlink ref="D47" r:id="rId91" tooltip="https://www.indmoney.com/stocks/india-power-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00005A000000}"/>
+    <hyperlink ref="O47" r:id="rId92" tooltip="https://www.indmoney.com/stocks/india-power-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00005B000000}"/>
+    <hyperlink ref="D48" r:id="rId93" tooltip="https://www.indmoney.com/stocks/sadbhav-engineering-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00005C000000}"/>
+    <hyperlink ref="O48" r:id="rId94" tooltip="https://www.indmoney.com/stocks/sadbhav-engineering-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00005D000000}"/>
+    <hyperlink ref="D49" r:id="rId95" tooltip="https://www.indmoney.com/stocks/dr-lalchandani-labs-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00005E000000}"/>
+    <hyperlink ref="O49" r:id="rId96" tooltip="https://www.indmoney.com/stocks/dr-lalchandani-labs-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00005F000000}"/>
+    <hyperlink ref="D50" r:id="rId97" tooltip="https://www.indmoney.com/stocks/madhav-infra-projects-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000060000000}"/>
+    <hyperlink ref="O50" r:id="rId98" tooltip="https://www.indmoney.com/stocks/madhav-infra-projects-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000061000000}"/>
+    <hyperlink ref="D51" r:id="rId99" tooltip="https://www.indmoney.com/stocks/elitecon-international-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000062000000}"/>
+    <hyperlink ref="O51" r:id="rId100" tooltip="https://www.indmoney.com/stocks/elitecon-international-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000063000000}"/>
+    <hyperlink ref="D52" r:id="rId101" tooltip="https://www.indmoney.com/stocks/twamev-construction-and-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000064000000}"/>
+    <hyperlink ref="O52" r:id="rId102" tooltip="https://www.indmoney.com/stocks/twamev-construction-and-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000065000000}"/>
+    <hyperlink ref="D53" r:id="rId103" tooltip="https://www.indmoney.com/stocks/aditya-ispat-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000066000000}"/>
+    <hyperlink ref="O53" r:id="rId104" tooltip="https://www.indmoney.com/stocks/aditya-ispat-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000067000000}"/>
+    <hyperlink ref="D54" r:id="rId105" tooltip="https://www.indmoney.com/stocks/bharat-immunological-and-biological-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000068000000}"/>
+    <hyperlink ref="O54" r:id="rId106" tooltip="https://www.indmoney.com/stocks/bharat-immunological-and-biological-corporation-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000069000000}"/>
+    <hyperlink ref="D55" r:id="rId107" tooltip="https://www.indmoney.com/stocks/vaishali-pharma-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00006A000000}"/>
+    <hyperlink ref="O55" r:id="rId108" tooltip="https://www.indmoney.com/stocks/vaishali-pharma-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00006B000000}"/>
+    <hyperlink ref="D56" r:id="rId109" tooltip="https://www.indmoney.com/stocks/indowind-energy-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00006C000000}"/>
+    <hyperlink ref="O56" r:id="rId110" tooltip="https://www.indmoney.com/stocks/indowind-energy-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00006D000000}"/>
+    <hyperlink ref="D57" r:id="rId111" tooltip="https://www.indmoney.com/stocks/vallabh-steels-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00006E000000}"/>
+    <hyperlink ref="O57" r:id="rId112" tooltip="https://www.indmoney.com/stocks/vallabh-steels-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00006F000000}"/>
+    <hyperlink ref="D58" r:id="rId113" tooltip="https://www.indmoney.com/stocks/orient-green-power-company-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000070000000}"/>
+    <hyperlink ref="O58" r:id="rId114" tooltip="https://www.indmoney.com/stocks/orient-green-power-company-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000071000000}"/>
+    <hyperlink ref="D59" r:id="rId115" tooltip="https://www.indmoney.com/stocks/rajasthan-tube-manufacturing-co-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000072000000}"/>
+    <hyperlink ref="O59" r:id="rId116" tooltip="https://www.indmoney.com/stocks/rajasthan-tube-manufacturing-co-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000073000000}"/>
+    <hyperlink ref="D60" r:id="rId117" tooltip="https://www.indmoney.com/stocks/baroda-extrusion-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000074000000}"/>
+    <hyperlink ref="O60" r:id="rId118" tooltip="https://www.indmoney.com/stocks/baroda-extrusion-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000075000000}"/>
+    <hyperlink ref="D61" r:id="rId119" tooltip="https://www.indmoney.com/stocks/looks-health-services-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000076000000}"/>
+    <hyperlink ref="O61" r:id="rId120" tooltip="https://www.indmoney.com/stocks/looks-health-services-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000077000000}"/>
+    <hyperlink ref="D62" r:id="rId121" tooltip="https://www.indmoney.com/stocks/gennex-laboratories-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000078000000}"/>
+    <hyperlink ref="O62" r:id="rId122" tooltip="https://www.indmoney.com/stocks/gennex-laboratories-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000079000000}"/>
+    <hyperlink ref="D63" r:id="rId123" tooltip="https://www.indmoney.com/stocks/mahalaxmi-seamless-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00007A000000}"/>
+    <hyperlink ref="O63" r:id="rId124" tooltip="https://www.indmoney.com/stocks/mahalaxmi-seamless-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00007B000000}"/>
+    <hyperlink ref="D64" r:id="rId125" tooltip="https://www.indmoney.com/stocks/jfl-life-sciences-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00007C000000}"/>
+    <hyperlink ref="O64" r:id="rId126" tooltip="https://www.indmoney.com/stocks/jfl-life-sciences-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00007D000000}"/>
+    <hyperlink ref="D65" r:id="rId127" tooltip="https://www.indmoney.com/stocks/la-tim-metal-and-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00007E000000}"/>
+    <hyperlink ref="O65" r:id="rId128" tooltip="https://www.indmoney.com/stocks/la-tim-metal-and-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00007F000000}"/>
+    <hyperlink ref="D66" r:id="rId129" tooltip="https://www.indmoney.com/stocks/boston-commerce-limited-share-price" xr:uid="{00000000-0004-0000-0100-000080000000}"/>
+    <hyperlink ref="O66" r:id="rId130" tooltip="https://www.indmoney.com/stocks/boston-commerce-limited-share-price" xr:uid="{00000000-0004-0000-0100-000081000000}"/>
+    <hyperlink ref="D67" r:id="rId131" tooltip="https://www.indmoney.com/stocks/nectar-lifescience-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000082000000}"/>
+    <hyperlink ref="O67" r:id="rId132" tooltip="https://www.indmoney.com/stocks/nectar-lifescience-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000083000000}"/>
+    <hyperlink ref="D68" r:id="rId133" tooltip="https://www.indmoney.com/stocks/maruti-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000084000000}"/>
+    <hyperlink ref="O68" r:id="rId134" tooltip="https://www.indmoney.com/stocks/maruti-infrastructure-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000085000000}"/>
+    <hyperlink ref="D69" r:id="rId135" tooltip="https://www.indmoney.com/stocks/steel-exchange-india-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000086000000}"/>
+    <hyperlink ref="O69" r:id="rId136" tooltip="https://www.indmoney.com/stocks/steel-exchange-india-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000087000000}"/>
+    <hyperlink ref="D70" r:id="rId137" tooltip="https://www.indmoney.com/stocks/deccan-health-care-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000088000000}"/>
+    <hyperlink ref="O70" r:id="rId138" tooltip="https://www.indmoney.com/stocks/deccan-health-care-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000089000000}"/>
+    <hyperlink ref="D71" r:id="rId139" tooltip="https://www.indmoney.com/stocks/earthstahl-and-alloys-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00008A000000}"/>
+    <hyperlink ref="O71" r:id="rId140" tooltip="https://www.indmoney.com/stocks/earthstahl-and-alloys-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00008B000000}"/>
+    <hyperlink ref="D72" r:id="rId141" tooltip="https://www.indmoney.com/stocks/global-longlife-hospital-and-research-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00008C000000}"/>
+    <hyperlink ref="O72" r:id="rId142" tooltip="https://www.indmoney.com/stocks/global-longlife-hospital-and-research-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00008D000000}"/>
+    <hyperlink ref="D73" r:id="rId143" tooltip="https://www.indmoney.com/stocks/global-defence-industries-limited-share-price" xr:uid="{00000000-0004-0000-0100-00008E000000}"/>
+    <hyperlink ref="O73" r:id="rId144" tooltip="https://www.indmoney.com/stocks/global-defence-industries-limited-share-price" xr:uid="{00000000-0004-0000-0100-00008F000000}"/>
+    <hyperlink ref="D74" r:id="rId145" tooltip="https://www.indmoney.com/stocks/bihar-sponge-iron-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000090000000}"/>
+    <hyperlink ref="O74" r:id="rId146" tooltip="https://www.indmoney.com/stocks/bihar-sponge-iron-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000091000000}"/>
+    <hyperlink ref="D75" r:id="rId147" tooltip="https://www.indmoney.com/stocks/a-b-infrabuild-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000092000000}"/>
+    <hyperlink ref="O75" r:id="rId148" tooltip="https://www.indmoney.com/stocks/a-b-infrabuild-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000093000000}"/>
+    <hyperlink ref="D76" r:id="rId149" tooltip="https://www.indmoney.com/stocks/take-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000094000000}"/>
+    <hyperlink ref="O76" r:id="rId150" tooltip="https://www.indmoney.com/stocks/take-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000095000000}"/>
+    <hyperlink ref="D77" r:id="rId151" tooltip="https://www.indmoney.com/stocks/tejnaksh-healthcare-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000096000000}"/>
+    <hyperlink ref="O77" r:id="rId152" tooltip="https://www.indmoney.com/stocks/tejnaksh-healthcare-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000097000000}"/>
+    <hyperlink ref="D78" r:id="rId153" tooltip="https://www.indmoney.com/stocks/nova-iron-and-steel-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000098000000}"/>
+    <hyperlink ref="O78" r:id="rId154" tooltip="https://www.indmoney.com/stocks/nova-iron-and-steel-ltd-share-price" xr:uid="{00000000-0004-0000-0100-000099000000}"/>
+    <hyperlink ref="D79" r:id="rId155" tooltip="https://www.indmoney.com/stocks/atal-realtech-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00009A000000}"/>
+    <hyperlink ref="O79" r:id="rId156" tooltip="https://www.indmoney.com/stocks/atal-realtech-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00009B000000}"/>
+    <hyperlink ref="D80" r:id="rId157" tooltip="https://www.indmoney.com/stocks/nidan-laboratories-and-healthcare-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00009C000000}"/>
+    <hyperlink ref="O80" r:id="rId158" tooltip="https://www.indmoney.com/stocks/nidan-laboratories-and-healthcare-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00009D000000}"/>
+    <hyperlink ref="D81" r:id="rId159" tooltip="https://www.indmoney.com/stocks/consolidated-construction-consortium-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00009E000000}"/>
+    <hyperlink ref="O81" r:id="rId160" tooltip="https://www.indmoney.com/stocks/consolidated-construction-consortium-ltd-share-price" xr:uid="{00000000-0004-0000-0100-00009F000000}"/>
+    <hyperlink ref="D82" r:id="rId161" tooltip="https://www.indmoney.com/stocks/mukat-pipes-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000A0000000}"/>
+    <hyperlink ref="O82" r:id="rId162" tooltip="https://www.indmoney.com/stocks/mukat-pipes-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000A1000000}"/>
+    <hyperlink ref="D83" r:id="rId163" tooltip="https://www.indmoney.com/stocks/ind-renewable-energy-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000A2000000}"/>
+    <hyperlink ref="O83" r:id="rId164" tooltip="https://www.indmoney.com/stocks/ind-renewable-energy-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000A3000000}"/>
+    <hyperlink ref="D84" r:id="rId165" tooltip="https://www.indmoney.com/stocks/modern-steels-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000A4000000}"/>
+    <hyperlink ref="O84" r:id="rId166" tooltip="https://www.indmoney.com/stocks/modern-steels-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000A5000000}"/>
+    <hyperlink ref="D85" r:id="rId167" tooltip="https://www.indmoney.com/stocks/a2z-infra-engineering-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000A6000000}"/>
+    <hyperlink ref="O85" r:id="rId168" tooltip="https://www.indmoney.com/stocks/a2z-infra-engineering-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000A7000000}"/>
+    <hyperlink ref="D86" r:id="rId169" tooltip="https://www.indmoney.com/stocks/arcee-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000A8000000}"/>
+    <hyperlink ref="O86" r:id="rId170" tooltip="https://www.indmoney.com/stocks/arcee-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000A9000000}"/>
+    <hyperlink ref="D87" r:id="rId171" tooltip="https://www.indmoney.com/stocks/energy-development-company-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000AA000000}"/>
+    <hyperlink ref="O87" r:id="rId172" tooltip="https://www.indmoney.com/stocks/energy-development-company-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000AB000000}"/>
+    <hyperlink ref="D88" r:id="rId173" tooltip="https://www.indmoney.com/stocks/venmax-drugs-and-pharmaceuticals-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000AC000000}"/>
+    <hyperlink ref="O88" r:id="rId174" tooltip="https://www.indmoney.com/stocks/venmax-drugs-and-pharmaceuticals-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000AD000000}"/>
+    <hyperlink ref="D89" r:id="rId175" tooltip="https://www.indmoney.com/stocks/jaiprakash-power-ventures-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000AE000000}"/>
+    <hyperlink ref="O89" r:id="rId176" tooltip="https://www.indmoney.com/stocks/jaiprakash-power-ventures-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000AF000000}"/>
+    <hyperlink ref="D90" r:id="rId177" tooltip="https://www.indmoney.com/stocks/broach-lifecare-hospital-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000B0000000}"/>
+    <hyperlink ref="O90" r:id="rId178" tooltip="https://www.indmoney.com/stocks/broach-lifecare-hospital-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000B1000000}"/>
+    <hyperlink ref="D91" r:id="rId179" tooltip="https://www.indmoney.com/stocks/modulex-construction-technologies-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000B2000000}"/>
+    <hyperlink ref="O91" r:id="rId180" tooltip="https://www.indmoney.com/stocks/modulex-construction-technologies-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000B3000000}"/>
+    <hyperlink ref="D92" r:id="rId181" tooltip="https://www.indmoney.com/stocks/eastcoast-steel-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000B4000000}"/>
+    <hyperlink ref="O92" r:id="rId182" tooltip="https://www.indmoney.com/stocks/eastcoast-steel-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000B5000000}"/>
+    <hyperlink ref="D93" r:id="rId183" tooltip="https://www.indmoney.com/stocks/rathi-bars-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000B6000000}"/>
+    <hyperlink ref="O93" r:id="rId184" tooltip="https://www.indmoney.com/stocks/rathi-bars-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000B7000000}"/>
+    <hyperlink ref="D94" r:id="rId185" tooltip="https://www.indmoney.com/stocks/surana-telecom-and-power-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000B8000000}"/>
+    <hyperlink ref="O94" r:id="rId186" tooltip="https://www.indmoney.com/stocks/surana-telecom-and-power-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000B9000000}"/>
+    <hyperlink ref="D95" r:id="rId187" tooltip="https://www.indmoney.com/stocks/bharat-road-network-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000BA000000}"/>
+    <hyperlink ref="O95" r:id="rId188" tooltip="https://www.indmoney.com/stocks/bharat-road-network-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000BB000000}"/>
+    <hyperlink ref="D96" r:id="rId189" tooltip="https://www.indmoney.com/stocks/poojawestern-metaliks-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000BC000000}"/>
+    <hyperlink ref="O96" r:id="rId190" tooltip="https://www.indmoney.com/stocks/poojawestern-metaliks-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000BD000000}"/>
+    <hyperlink ref="D97" r:id="rId191" tooltip="https://www.indmoney.com/stocks/globus-power-generation-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000BE000000}"/>
+    <hyperlink ref="O97" r:id="rId192" tooltip="https://www.indmoney.com/stocks/globus-power-generation-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000BF000000}"/>
+    <hyperlink ref="D98" r:id="rId193" tooltip="https://www.indmoney.com/stocks/rhetan-tmt-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000C0000000}"/>
+    <hyperlink ref="O98" r:id="rId194" tooltip="https://www.indmoney.com/stocks/rhetan-tmt-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000C1000000}"/>
+    <hyperlink ref="D99" r:id="rId195" tooltip="https://www.indmoney.com/stocks/galaxy-medicare-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000C2000000}"/>
+    <hyperlink ref="O99" r:id="rId196" tooltip="https://www.indmoney.com/stocks/galaxy-medicare-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000C3000000}"/>
+    <hyperlink ref="D100" r:id="rId197" tooltip="https://www.indmoney.com/stocks/irb-infrastructure-developers-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000C4000000}"/>
+    <hyperlink ref="O100" r:id="rId198" tooltip="https://www.indmoney.com/stocks/irb-infrastructure-developers-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000C5000000}"/>
+    <hyperlink ref="D101" r:id="rId199" tooltip="https://www.indmoney.com/stocks/vivo-bio-tech-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000C6000000}"/>
+    <hyperlink ref="O101" r:id="rId200" tooltip="https://www.indmoney.com/stocks/vivo-bio-tech-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000C7000000}"/>
+    <hyperlink ref="D102" r:id="rId201" tooltip="https://www.indmoney.com/stocks/adeshwar-meditex-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000C8000000}"/>
+    <hyperlink ref="O102" r:id="rId202" tooltip="https://www.indmoney.com/stocks/adeshwar-meditex-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000C9000000}"/>
+    <hyperlink ref="D103" r:id="rId203" tooltip="https://www.indmoney.com/stocks/kandr-rail-engineering-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000CA000000}"/>
+    <hyperlink ref="O103" r:id="rId204" tooltip="https://www.indmoney.com/stocks/kandr-rail-engineering-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000CB000000}"/>
+    <hyperlink ref="D104" r:id="rId205" tooltip="https://www.indmoney.com/stocks/hazoor-multi-projects-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000CC000000}"/>
+    <hyperlink ref="O104" r:id="rId206" tooltip="https://www.indmoney.com/stocks/hazoor-multi-projects-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000CD000000}"/>
+    <hyperlink ref="D105" r:id="rId207" tooltip="https://www.indmoney.com/stocks/century-extrusions-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000CE000000}"/>
+    <hyperlink ref="O105" r:id="rId208" tooltip="https://www.indmoney.com/stocks/century-extrusions-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000CF000000}"/>
+    <hyperlink ref="D106" r:id="rId209" tooltip="https://www.indmoney.com/stocks/rudra-global-infra-products-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000D0000000}"/>
+    <hyperlink ref="O106" r:id="rId210" tooltip="https://www.indmoney.com/stocks/rudra-global-infra-products-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000D1000000}"/>
+    <hyperlink ref="D107" r:id="rId211" tooltip="https://www.indmoney.com/stocks/vms-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000D2000000}"/>
+    <hyperlink ref="O107" r:id="rId212" tooltip="https://www.indmoney.com/stocks/vms-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000D3000000}"/>
+    <hyperlink ref="D108" r:id="rId213" tooltip="https://www.indmoney.com/stocks/udayshivakumar-infra-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000D4000000}"/>
+    <hyperlink ref="O108" r:id="rId214" tooltip="https://www.indmoney.com/stocks/udayshivakumar-infra-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000D5000000}"/>
+    <hyperlink ref="D109" r:id="rId215" tooltip="https://www.indmoney.com/stocks/kalana-ispat-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000D6000000}"/>
+    <hyperlink ref="O109" r:id="rId216" tooltip="https://www.indmoney.com/stocks/kalana-ispat-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000D7000000}"/>
+    <hyperlink ref="D110" r:id="rId217" tooltip="https://www.indmoney.com/stocks/kabra-drugs-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000D8000000}"/>
+    <hyperlink ref="O110" r:id="rId218" tooltip="https://www.indmoney.com/stocks/kabra-drugs-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000D9000000}"/>
+    <hyperlink ref="D111" r:id="rId219" tooltip="https://www.indmoney.com/stocks/garware-marine-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000DA000000}"/>
+    <hyperlink ref="O111" r:id="rId220" tooltip="https://www.indmoney.com/stocks/garware-marine-industries-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000DB000000}"/>
+    <hyperlink ref="D112" r:id="rId221" tooltip="https://www.indmoney.com/stocks/swastik-pipe-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000DC000000}"/>
+    <hyperlink ref="O112" r:id="rId222" tooltip="https://www.indmoney.com/stocks/swastik-pipe-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000DD000000}"/>
+    <hyperlink ref="D113" r:id="rId223" tooltip="https://www.indmoney.com/stocks/bajaj-hindusthan-sugar-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000DE000000}"/>
+    <hyperlink ref="O113" r:id="rId224" tooltip="https://www.indmoney.com/stocks/bajaj-hindusthan-sugar-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000DF000000}"/>
+    <hyperlink ref="D114" r:id="rId225" tooltip="https://www.indmoney.com/stocks/reliance-power-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000E0000000}"/>
+    <hyperlink ref="O114" r:id="rId226" tooltip="https://www.indmoney.com/stocks/reliance-power-ltd-share-price" xr:uid="{00000000-0004-0000-0100-0000E1000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>